--- a/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="654" yWindow="-96" windowWidth="22482" windowHeight="13152" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Golden Set" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Golden Set'!$A$1:$K$47</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,33 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-        <bgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8E8E8"/>
-        <bgColor rgb="FFE8E8E8"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,24 +45,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -441,23 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-  </cols>
+  <dimension ref="A1:Q46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="20.05" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -513,62 +484,142 @@
           <t>expected_semantic_intent</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>run:check_errors</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>run:verify_recursive</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>run:final_verify_recursive</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>run:final_verify_recursive_v2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>run:targeted_debug</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>run:verify_pipeline</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="86.40000000000001" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>What kind of topics does CSCE 611 cover in the beginning?</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>CSCE 611 begins with a review of computer architecture hardware/software evolution, which leads into contemporary operating systems. The course also covers basic operating system concepts, methods of operating system design and construction, and an overview of the general architecture and most important components of modern operating systems.</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>50668</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>50668</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="b">
+      <c r="K2" t="b">
         <v>0</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
     </row>
-    <row r="3" ht="172.8" customHeight="1">
-      <c r="A3" s="2" t="n">
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>What kind of skills will I pick up in CSCE 669?</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>In CSCE 669, you will develop several key skills related to computational optimization. Upon completing the course, you will be able to:
 *   Master basic theories and techniques in current computational optimization research.
@@ -577,47 +628,97 @@
 *   Gain a strong foundation for advanced research in computational optimization and related areas.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>CSCE 669</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>58438</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" t="n">
+        <v>58438</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>CSCE 669</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="b">
+      <c r="K3" t="b">
         <v>0</v>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="187.2" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>What kinds of modern computer and network security topics will CSCE 665 introduce?</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>CSCE 665 will introduce various modern topics in computer and network security. These topics may include:
 *   **Basic network &amp; system security:** such as software security, malware, botnets, and intrusion detection.
@@ -627,94 +728,317 @@
 *   **AI/LLM security:** focusing on LLM-based security, adversarial learning/backdoor, and advanced applications with AI.</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30874</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" t="n">
+        <v>30874</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="b">
+      <c r="K4" t="b">
         <v>0</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
     </row>
-    <row r="5" ht="288" customHeight="1">
-      <c r="A5" s="2" t="n">
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>What should I expect to be doing in CSCE 672?</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>In CSCE 672, you will explore the design, implementation, and use of technical systems that support people working cooperatively, drawing from the research area of Computer Supported Cooperative Work (CSCW). The course covers current theoretical, practical, technical, and social issues, as well as future directions in the field.
 You can expect to learn to describe the history of collaborative software, prioritize design issues, and design, implement, and evaluate software for collaboration.
 Your graded work will include an assignment (10%), a team project (35%), readings write-ups (35%), readings presentations (10%), and attendance (10%). Throughout the semester, you will engage with topics such as CSCW history, designing for awareness, forms of communication, collaborative decision-making, crowdsourcing, and online communities. Required materials are online papers from conferences and journals. You will also have weekly smaller project activities and readings write-ups due on average twice per week, with student presentations occurring throughout the semester.</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>CSCE 672</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58439</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" t="n">
+        <v>58439</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>CSCE 672</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="b">
+      <c r="K5" t="b">
         <v>0</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," focuses on the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics covered in the course include:
+*   CSCW history and central issues [Source 3]
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making and voting models [Source 3]
+*   Meeting capture and reuse [Source 3]
+*   Crowdsourcing and its issues [Source 3]
+*   Online communities and virtual teams [Source 3]
+*   Shared user history and its visualization [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Collaboration in online games [Source 3]
+*   Supporting software teams [Source 3]
+To enroll, students must have completed CSCE 671 or CSCE 610, or receive approval from the instructor [Source 1].
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," focuses on the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics covered in the course include:
+*   CSCW history and central issues [Source 3]
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making and voting models [Source 3]
+*   Meeting capture and reuse [Source 3]
+*   Crowdsourcing and its issues [Source 3]
+*   Online communities and virtual teams [Source 3]
+*   Shared user history and its visualization [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Collaboration in online games [Source 3]
+*   Supporting software teams [Source 3]
+To enroll, students must have completed CSCE 671 or CSCE 610, or receive approval from the instructor [Source 1].
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>In CSCE 672, Section 600 (58439), you will study Computer Supported Collaborative Work (CSCW) [Source 1].
+**Course Purpose:**
+The course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of CSCW, including current theoretical, practical, technical, and social issues, as well as future directions of the field [Source 1].
+**Key Topics:**
+Throughout the semester, you will cover topics such as [Source 2]:
+*   CSCW history and central issues
+*   Designing for artifact and human awareness
+*   Forms of communication
+*   Content sharing systems and issues
+*   Collaborative decision making
+*   Crowdsourcing and its issues
+*   Online communities and virtual teams
+*   Collaboration in online games
+*   Supporting software teams
+**Prerequisites:**
+To enroll in this course, you must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components [Source 3]:
+| Assignment            | Percentage |
+| :-------------------- | :--------- |
+| Assignment 1          | 10%        |
+| Team project          | 35%        |
+| Readings write-ups    | 35%        |
+| Readings presentations| 10%        |
+| Attendance            | 10%        |
+Grades are on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," focuses on the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics covered in the course include:
+*   CSCW history and central issues [Source 3]
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making and voting models [Source 3]
+*   Meeting capture and reuse [Source 3]
+*   Crowdsourcing and its issues [Source 3]
+*   Online communities and virtual teams [Source 3]
+*   Shared user history and its visualization [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Collaboration in online games [Source 3]
+*   Supporting software teams [Source 3]
+To enroll, students must have completed CSCE 671 or CSCE 610, or receive approval from the instructor [Source 1].
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," focuses on the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics covered in the course include:
+*   CSCW history and central issues [Source 3]
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making and voting models [Source 3]
+*   Meeting capture and reuse [Source 3]
+*   Crowdsourcing and its issues [Source 3]
+*   Online communities and virtual teams [Source 3]
+*   Shared user history and its visualization [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Collaboration in online games [Source 3]
+*   Supporting software teams [Source 3]
+To enroll, students must have completed CSCE 671 or CSCE 610, or receive approval from the instructor [Source 1].
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," focuses on the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics covered in the course include:
+*   CSCW history and central issues [Source 3]
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making and voting models [Source 3]
+*   Meeting capture and reuse [Source 3]
+*   Crowdsourcing and its issues [Source 3]
+*   Online communities and virtual teams [Source 3]
+*   Shared user history and its visualization [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Collaboration in online games [Source 3]
+*   Supporting software teams [Source 3]
+To enroll, students must have completed CSCE 671 or CSCE 610, or receive approval from the instructor [Source 1].
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="6" ht="158.4" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>What should I know before taking CSCE 624?</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>To take CSCE 624, you must have graduate classification.
 While not strictly required, it will be helpful to have familiarity with at least one of the following:
@@ -725,140 +1049,408 @@
 Students from related disciplines such as engineering, human-computer interaction (HCI), or data science are also welcome.</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>CSCE 624</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>PREREQUISITES</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>58435</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" t="n">
+        <v>58435</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>CSCE 624</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="b">
+      <c r="K6" t="b">
         <v>0</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>To take CSCE 624, you must have **Graduate classification** [Source 1, 2].
+While not strictly required, familiarity with at least one of the following will be helpful:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, Human-Computer Interaction (HCI), and data science are welcome and have historically performed well in the course [Source 2].</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>For CSCE 624, Section 600 (58435), titled "Sketch Recognition," you should know the following before taking the course:
+**Prerequisites:**
+*   Graduate classification [Source 1, 2].
+**Recommended Knowledge:**
+*   General graduate-level knowledge in computer science [Source 2].
+*   Familiarity with at least one of the following is helpful but not strictly required:
+    *   Programming (any language) [Source 2].
+    *   Basic machine learning or artificial intelligence concepts [Source 2].
+    *   Linear algebra or probability [Source 2].
+    *   Software engineering practices [Source 2].
+*   Students from related disciplines (e.g., engineering, HCI, data science) are welcome [Source 2].
+**Course Focus:**
+The course emphasizes how humans naturally sketch, how systems interpret sketches, and how recognition algorithms behave in real-world, noisy settings. It involves hands-on implementation of recognition techniques, critical reading of research papers, in-class activities, and a semester-long team project [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Before taking CSCE 624 (Sketch Recognition), you should be aware of the following:
+**Prerequisites:**
+*   You must have graduate classification [Source 1, 3].
+**Recommended Background/Knowledge:**
+*   Students are expected to have general graduate-level knowledge in computer science [Source 3].
+*   Familiarity with at least one of the following will be helpful, but is not strictly required:
+    *   Programming (any language) [Source 3]
+    *   Basic machine learning or artificial intelligence concepts [Source 3]
+    *   Linear algebra or probability [Source 3]
+    *   Software engineering practices [Source 3]
+*   Students from related disciplines (e.g., engineering, HCI, data science) are welcome and have historically performed well in the course [Source 3].</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>To take CSCE 624, you must have **Graduate classification** [Source 1, 2].
+While not strictly required, familiarity with at least one of the following areas will be helpful:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, Human-Computer Interaction (HCI), or data science are also welcome [Source 2].
+**Course ID and Section:** CSCE 624, Section 600 (58435) [Source 1]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>To take CSCE 624, you must have **Graduate classification** [Source 1, 2].
+While not strictly required, familiarity with at least one of the following areas will be helpful:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, Human-Computer Interaction (HCI), or data science are also welcome [Source 2].
+**Course ID and Section:** CSCE 624, Section 600 (58435) [Source 1]</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>For CSCE 624, Section 600 (58435), titled "Sketch Recognition," you should know the following before taking the course:
+**Prerequisites:**
+*   Graduate classification [Source 1, 2].
+**Recommended Knowledge:**
+*   General graduate-level knowledge in computer science [Source 2].
+*   Familiarity with at least one of the following is helpful but not strictly required:
+    *   Programming (any language) [Source 2].
+    *   Basic machine learning or artificial intelligence concepts [Source 2].
+    *   Linear algebra or probability [Source 2].
+    *   Software engineering practices [Source 2].
+*   Students from related disciplines (e.g., engineering, HCI, data science) are welcome [Source 2].
+**Course Focus:**
+The course emphasizes how humans naturally sketch, how systems interpret sketches, and how recognition algorithms behave in real-world, noisy settings. It involves hands-on implementation of recognition techniques, critical reading of research papers, in-class activities, and a semester-long team project [Source 1, 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="187.2" customHeight="1">
-      <c r="A7" s="2" t="n">
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Would CSCE 638 be beneficial for someone wanting to work with large language models?</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Yes, based on the syllabus, CSCE 638 would be beneficial for someone wanting to work with large language models.
 The course catalog description states it focuses on "Natural Language Processing (NLP) fundamentals including language models." The course schedule explicitly lists "Large Language Models" as a topic in Week 6. Additionally, other relevant topics covered include "Transformers" (Week 5), "Contextualized Representations, Pre-Training" (Week 6), "Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation" (Week 7), "Instruction Tuning, Alignment, Post-Training" (Week 8), "Large Reasoning Models" (Week 9), and "Retrieval-Augmented Generation" (Week 10).</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>CSCE 638</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54988</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" t="n">
+        <v>54988</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>CSCE 638</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="b">
+      <c r="K7" t="b">
         <v>0</v>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
     </row>
-    <row r="8" ht="230.4" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Would you recommend CSCE 656 if I'm mostly interested in the interactive media design parts and less about the digital rights and policy topics?</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Based on the syllabus for CSCE 656, a significant portion of the course focuses on interactive media design. Topics such as designing software for immersion, agency, and transformation, interactive media and computer characters, interactive text, social media, bridging physical and digital media, audio/video manipulation, games, and automatic narrative control are covered in approximately 10 out of 15 weeks.
 However, the course also dedicates about 4 weeks to digital rights and policy topics, including digital rights management, property rights, software licenses, intellectual property, and evaluating policy effects. These topics are also reflected in the learning outcomes.
 Therefore, while there is a strong emphasis on interactive media design, the course also includes a substantial component on digital rights and policy.</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>CSCE 656</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42432</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" t="n">
+        <v>42432</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>CSCE 656</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="b">
+      <c r="K8" t="b">
         <v>0</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600, 42432) covers a substantial amount of interactive media design, but also includes digital rights and policy topics [Source 2].
+The course schedule dedicates approximately 10 weeks to topics related to interactive media design, such as:
+*   Designing software for immersion, agency, and transformation [Source 1]
+*   Interactive media and computer characters [Source 1]
+*   Interactive text and social media [Source 1]
+*   Bridging physical and digital media [Source 1]
+*   Audio, music, speech, recorded and authored video [Source 1]
+*   Games and computer-controlled characters, and automatic narrative control [Source 1]
+The learning outcomes also emphasize designing software features for immersion, agency, and transformation, creating computer characters and narrative control, and developing software for audio/video manipulation [Source 3].
+However, the course also dedicates about 4 weeks to digital rights and policy, including:
+*   Digital rights management [Source 1]
+*   Property rights and issues [Source 1]
+*   Software licenses and intellectual property [Source 1]
+*   Evaluating policy effects [Source 1]
+Learning outcomes also include describing core differences between physical and intellectual property and assessing characteristics of software licenses, software patents, and digital rights management software [Source 3].
+Therefore, while a significant portion of CSCE 656 focuses on interactive media design, the digital rights and policy topics are also a notable component of the curriculum.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600) covers a significant amount of material related to interactive media design, but also includes topics on digital rights and policy [Source 1, 2, 3, 4].
+**Academic Content Breakdown:**
+*   **Interactive Media Design Focus:**
+    *   The course investigates the impact of computers in new media design and the relationships between authors and readers of interactive materials [Source 1].
+    *   Learning outcomes include designing software features for immersion, agency, and transformation; describing techniques for creating computer characters and narrative control; developing software for audio/video manipulation; and designing, implementing, and evaluating software for content creation/consumption [Source 3].
+    *   The course schedule dedicates approximately 10 out of 14 content weeks to topics such as designing software for immersion, agency and transformation, interactive media and computer characters, interactive text and social media, bridging physical and digital media, audio/music/speech, recorded/authored video, games, and automatic narrative control [Source 2, 4].
+*   **Digital Rights and Policy Focus:**
+    *   Learning outcomes also include describing differences between physical and intellectual property, and assessing software licenses, patents, and digital rights management software [Source 3].
+    *   The course schedule dedicates approximately 4 weeks to topics like digital rights management, property rights and issues, software licenses and intellectual property, and evaluating policy effects [Source 2].
+While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CSCE 656, "Computers and New Media" (Section 600), covers a substantial amount of interactive media design. The course catalog description states it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 2].
+Key topics and learning outcomes related to interactive media design include:
+*   Designing software for immersion, agency, and transformation [Source 1, Source 3]
+*   Interactive media and computer characters [Source 1]
+*   Interactive text and social media [Source 1]
+*   Bridging physical and digital media [Source 1]
+*   Audio, music, speech, recorded and authored video [Source 1, Source 3]
+*   Games and computer-controlled characters [Source 1]
+*   Automatic narrative control [Source 1]
+*   Developing software for the manipulation/use of audio and/or video [Source 3]
+*   Designing, implementing, and evaluating software supporting content creation/consumption [Source 3]
+While the course does dedicate weeks 11-14 to topics such as digital rights management, property rights, software licenses, intellectual property, and evaluating policy effects, a significant portion of the course (weeks 1-10) focuses on the design and technical aspects of new media [Source 1]. Therefore, it appears to align well with an interest in interactive media design, despite the inclusion of policy topics.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600 (42432), "Computers and New Media," covers a substantial amount of interactive media design, which aligns with your primary interest.
+The course description indicates it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 1].
+Key topics related to interactive media design include:
+*   Designing software for immersion, agency, and transformation (Weeks 2-3) [Source 2]
+*   Interactive media, computer characters, interactive text, and social media (Weeks 4-5) [Source 2]
+*   Bridging physical and digital media (Week 6) [Source 2]
+*   Audio, music, speech, recorded, and authored video (Weeks 7-8) [Source 2]
+*   Games and computer-controlled characters, and automatic narrative control (Weeks 9-10) [Source 2]
+These topics are also reflected in the learning outcomes, such as designing software features that support immersion, agency, and transformation, describing techniques for creating computer characters and narrative control, and developing software for the manipulation/use of audio and/or video [Source 3].
+However, the course also dedicates a significant portion (Weeks 11-14) to topics you are less interested in, such as digital rights management, property rights and issues, software licenses, intellectual property, and evaluating policy effects [Source 2]. These topics are also covered in the learning outcomes, including describing core differences between physical and intellectual property and assessing characteristics of software licenses, software patents, and digital rights management software [Source 3].
+Therefore, while a large part of CSCE 656 aligns with your interest in interactive media design, you should be aware that approximately one-quarter of the course content focuses on digital rights and policy topics.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600 (42432), "Computers and New Media," covers a substantial amount of interactive media design, which aligns with your primary interest.
+The course description indicates it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 1].
+Key topics related to interactive media design include:
+*   Designing software for immersion, agency, and transformation (Weeks 2-3) [Source 2]
+*   Interactive media, computer characters, interactive text, and social media (Weeks 4-5) [Source 2]
+*   Bridging physical and digital media (Week 6) [Source 2]
+*   Audio, music, speech, recorded, and authored video (Weeks 7-8) [Source 2]
+*   Games and computer-controlled characters, and automatic narrative control (Weeks 9-10) [Source 2]
+These topics are also reflected in the learning outcomes, such as designing software features that support immersion, agency, and transformation, describing techniques for creating computer characters and narrative control, and developing software for the manipulation/use of audio and/or video [Source 3].
+However, the course also dedicates a significant portion (Weeks 11-14) to topics you are less interested in, such as digital rights management, property rights and issues, software licenses, intellectual property, and evaluating policy effects [Source 2]. These topics are also covered in the learning outcomes, including describing core differences between physical and intellectual property and assessing characteristics of software licenses, software patents, and digital rights management software [Source 3].
+Therefore, while a large part of CSCE 656 aligns with your interest in interactive media design, you should be aware that approximately one-quarter of the course content focuses on digital rights and policy topics.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600) covers a significant amount of material related to interactive media design, but also includes topics on digital rights and policy [Source 1, 2, 3, 4].
+**Academic Content Breakdown:**
+*   **Interactive Media Design Focus:**
+    *   The course investigates the impact of computers in new media design and the relationships between authors and readers of interactive materials [Source 1].
+    *   Learning outcomes include designing software features for immersion, agency, and transformation; describing techniques for creating computer characters and narrative control; developing software for audio/video manipulation; and designing, implementing, and evaluating software for content creation/consumption [Source 3].
+    *   The course schedule dedicates approximately 10 out of 14 content weeks to topics such as designing software for immersion, agency and transformation, interactive media and computer characters, interactive text and social media, bridging physical and digital media, audio/music/speech, recorded/authored video, games, and automatic narrative control [Source 2, 4].
+*   **Digital Rights and Policy Focus:**
+    *   Learning outcomes also include describing differences between physical and intellectual property, and assessing software licenses, patents, and digital rights management software [Source 3].
+    *   The course schedule dedicates approximately 4 weeks to topics like digital rights management, property rights and issues, software licenses and intellectual property, and evaluating policy effects [Source 2].
+While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
+        </is>
+      </c>
     </row>
-    <row r="9" ht="172.8" customHeight="1">
-      <c r="A9" s="2" t="n">
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Would CSCE 665 be a strong foundation if I'm looking to specialize in real-world software or cloud security?</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Yes, based on the syllabus, CSCE 665 appears to offer a strong foundation for specializing in real-world software and cloud security.
 The course description states it is "suitable for those interested in... real-world security issues/techniques." Specific topics covered include:
@@ -867,47 +1459,135 @@
 Additionally, a learning outcome is to "demonstrate a practical working knowledge of offensive and/or defensive techniques," which would contribute to a strong foundation in these areas.</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>30874</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" t="n">
+        <v>30874</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="b">
+      <c r="K9" t="b">
         <v>0</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665: Advanced Networking and Security, Section 600 (30874), would be a strong foundation if you are looking to specialize in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security for students interested in real-world security issues and techniques [Source 1].
+Key topics covered include:
+*   **Basic network &amp; system security**: such as software security, malware, botnets, and intrusion detection [Source 1, 2].
+*   **Security in a software-defined world**: including SDN/NFV, Cloud, 5G/Edge, and Vehicle security [Source 2].
+*   **Web and Web3 security**: covering traditional web security and Web3 (DeFi, blockchain) security [Source 2].
+*   **AI/LLM security** [Source 2].
+Upon completion, you will be able to analyze trade-offs in securing modern distributed systems and networks, synthesize security principles for robust defenses, and demonstrate practical knowledge of offensive and defensive techniques [Source 2].
+**Prerequisites**: Graduate classification and approval of the instructor [Source 1, 2].
+**Grading Policy**: The course emphasizes practical application and research, with grading based on paper mini-reviews (25%), class participation and presentation (10%), and a mini-research project (65%) [Source 3]. There are no mid-term or final exams [Source 3].</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665: Advanced Networking and Security, Section 600 (30874), would be a strong foundation if you are looking to specialize in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security for students interested in real-world security issues and techniques [Source 1].
+Key topics covered include:
+*   **Basic network &amp; system security**: such as software security, malware, botnets, and intrusion detection [Source 1, 2].
+*   **Security in a software-defined world**: including SDN/NFV, Cloud, 5G/Edge, and Vehicle security [Source 2].
+*   **Web and Web3 security**: covering traditional web security and Web3 (DeFi, blockchain) security [Source 2].
+*   **AI/LLM security** [Source 2].
+Upon completion, you will be able to analyze trade-offs in securing modern distributed systems and networks, synthesize security principles for robust defenses, and demonstrate practical knowledge of offensive and defensive techniques [Source 2].
+**Prerequisites**: Graduate classification and approval of the instructor [Source 1, 2].
+**Grading Policy**: The course emphasizes practical application and research, with grading based on paper mini-reviews (25%), class participation and presentation (10%), and a mini-research project (65%) [Source 3]. There are no mid-term or final exams [Source 3].</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="10" ht="302.4" customHeight="1">
-      <c r="A10" s="2" t="n">
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Would CSCE 641 be a beneficial course for someone aiming for a career in game or graphics development?</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Yes, based on the syllabus content, CSCE 641 appears to be a beneficial course for someone aiming for a career in game or graphics development.
 The course focuses on:
@@ -918,47 +1598,139 @@
 These topics and practical skills are fundamental to both game and graphics development.</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>CSCE 641</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58437</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" t="n">
+        <v>58437</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>CSCE 641</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="b">
+      <c r="K10" t="b">
         <v>0</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
     </row>
-    <row r="11" ht="230.4" customHeight="1">
-      <c r="A11" s="2" t="n">
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Is CSCE 672 a worthwhile course if I'm interested in the practical aspects of building collaborative applications?</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Yes, based on the syllabus, CSCE 672 appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
 The course catalog description states it "Covers design, implementation and use of technical systems that support people working cooperatively."
@@ -968,93 +1740,302 @@
 Additionally, a significant portion of your grade (35%) is dedicated to a "Team project," which often involves practical application.</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>CSCE 672</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58439</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" t="n">
+        <v>58439</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>CSCE 672</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="b">
+      <c r="K11" t="b">
         <v>0</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672, Computer Supported Collaborative Work, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the "design, implementation and use of technical systems that support people working cooperatively" [Source 1]. It draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical, and social issues [Source 1].
+Key topics covered in the course include:
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Supporting software teams [Source 3]
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2]
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2]
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2]
+The course involves a team project (35% of the grade) and smaller project activities due weekly, which would provide practical experience [Source 2, 3].
+**Course ID and Section:** CSCE 672, Section 600 (58439) [Source 1]
+**Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672, Computer Supported Collaborative Work, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the "design, implementation and use of technical systems that support people working cooperatively" [Source 1]. It draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical, and social issues [Source 1].
+Key topics covered in the course include:
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Supporting software teams [Source 3]
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2]
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2]
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2]
+The course involves a team project (35% of the grade) and smaller project activities due weekly, which would provide practical experience [Source 2, 3].
+**Course ID and Section:** CSCE 672, Section 600 (58439) [Source 1]
+**Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672, Computer Supported Collaborative Work, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the "design, implementation and use of technical systems that support people working cooperatively" [Source 1]. It draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical, and social issues [Source 1].
+Key topics covered in the course include:
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Supporting software teams [Source 3]
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2]
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2]
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2]
+The course involves a team project (35% of the grade) and smaller project activities due weekly, which would provide practical experience [Source 2, 3].
+**Course ID and Section:** CSCE 672, Section 600 (58439) [Source 1]
+**Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672, Computer Supported Collaborative Work, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the "design, implementation and use of technical systems that support people working cooperatively" [Source 1]. It draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical, and social issues [Source 1].
+Key topics covered in the course include:
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Supporting software teams [Source 3]
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2]
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2]
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2]
+The course involves a team project (35% of the grade) and smaller project activities due weekly, which would provide practical experience [Source 2, 3].
+**Course ID and Section:** CSCE 672, Section 600 (58439) [Source 1]
+**Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672, Computer Supported Collaborative Work, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the "design, implementation and use of technical systems that support people working cooperatively" [Source 1]. It draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical, and social issues [Source 1].
+Key topics covered in the course include:
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Supporting software teams [Source 3]
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2]
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2]
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2]
+The course involves a team project (35% of the grade) and smaller project activities due weekly, which would provide practical experience [Source 2, 3].
+**Course ID and Section:** CSCE 672, Section 600 (58439) [Source 1]
+**Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
+        </is>
+      </c>
     </row>
-    <row r="12" ht="187.2" customHeight="1">
-      <c r="A12" s="2" t="n">
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Does CSCE 608 cover enough practical skills for someone looking to build or manage database systems in the real world?</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Based on the syllabus for CSCE 608 Database Systems, the course aims to equip learners with practical skills relevant to building and managing database systems.
 Specifically, the course learning outcomes state that students will be able to "develop database systems for applications," "master efficient query processing techniques," and "deal with system issues related to database systems." The catalog description further details topics such as database modeling techniques, query languages, physical data organization, relational database design theory, query processing, transaction management and recovery, and distributed data management, all of which are foundational for practical application in the field.</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>46648</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" t="n">
+        <v>46648</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="b">
+      <c r="K12" t="b">
         <v>0</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 (Section 600) covers practical skills relevant to building and managing database systems in the real world.
+The course focuses on:
+*   **Database modeling techniques** and **relational database design theory** [Source 1].
+*   **Expressiveness in query languages**, including **SQL**, and **manipulation languages data models** [Source 1, 3].
+*   **Physical data organization**, **query processing**, **transaction management and recovery**, and **distributed data management** [Source 1].
+*   **System issues related to database systems**, **concurrency control**, and **Bigdata** [Source 2, 3, 4].
+Upon completion, learners will be able to "develop database systems for applications" and "deal with system issues related to database systems" [Source 2]. The course includes two projects, which likely involve practical application of these concepts [Source 2, 3, 4].</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
     </row>
-    <row r="13" ht="403.2" customHeight="1">
-      <c r="A13" s="2" t="n">
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Are there many TAMU courses where your final grade isn't just based on your calculated average?</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Some Texas A&amp;M University courses employ flexible grading policies or alternative calculation methods that deviate from a straightforward weighted or simple average of all graded components. These methods often aim to mitigate the impact of poor performance on a few assignments or provide opportunities for improvement.
 Based on the provided syllabi, the following courses have grading policies where the final grade is not solely based on a simple calculated average of all individual scores:
@@ -1064,92 +2045,249 @@
 CSCE 605 (Fall 2025): While the course grade is based on a weighted average of components (quizzes, exams, project), the final letter grades are assigned using a system where "people are cutpoints; whole-numbered percentages are not." This means the cutpoint for a particular letter grade is the lowest-scoring person who received that grade, rather than fixed percentage ranges.</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>semantic_general</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>CSCE 632</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54784</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H13" t="n">
+        <v>54784</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>CSCE 632</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="b">
+      <c r="K13" t="b">
         <v>0</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Yes, there are several Texas A&amp;M University courses where the final grade is not solely based on the calculated average of graded components, or where additional conditions apply:
+*   **CSCE 681**
+    *   To pass this course, students must complete a syllabus quiz on Canvas with a 100% grade and receive an average score of 80% or higher. Any course requirements completed before passing the syllabus quiz will not be considered [Source 3].
+    *   Missed reports without a proper Excused Absence will receive an automatic score of zero [Source 3].
+    *   Seminar reports containing plagiarized content (including self-plagiarism or use of machine-generated text) may result in a recommendation for an F* for the course [Source 5].
+*   **CSCE 632**
+    *   The instructor can assign a failing grade regardless of a student's computed final score if warranted [Source 4].
+    *   For group projects, an instructor can modify a student's multiplier based on team peer evaluations, which can adjust their final score [Source 4].
+    *   Some assignments are peer-graded, and scores can be affected by how critically a student grades their peers compared to others [Source 9].
+*   **CSCE 629**
+    *   A slight curve might be applied if the course average is low [Source 7].
+    *   The lowest grade in quizzes/exercises and homework components will be dropped [Source 7, 2].</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided syllabi, there are several instances where a final grade at Texas A&amp;M University is not solely based on a straightforward calculated average of all components. This can be due to instructor discretion, specific conditions for passing, or policies that modify how individual component scores contribute to the final grade.
+Here are some examples:
+*   **Instructor Discretion for Final Grade Assignment:**
+    *   In CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 3].
+    *   For CSCE 632, the instructor can also establish and modify a multiplier based on team peer evaluations, which directly impacts a student's final project score [Source 3].
+*   **Conditional Passing Requirements:**
+    *   In CSCE 681, to pass the course, students must not only achieve an average score of 80% or higher but also complete a syllabus quiz on Canvas with a 100% grade. Any course requirements completed before passing the syllabus quiz will not be considered [Source 8].
+*   **Dropping Lowest Grades:**
+    *   CSCE 629 drops the lowest grade in the quizzes and exercises component, and also drops the lowest homework grade [Source 5].
+    *   CSCE 681 calculates the final grade as the statistical mean of the top 75% of individual quiz grades, meaning the lowest 25% of quiz grades do not count [Source 4].
+*   **Application of Curves:**
+    *   CSCE 629 states that "A slight curve might be applied if the course average is low" [Source 5].
+*   **Bonus Opportunities:**
+    *   CSCE 713 offers optional "Independent-Study Reports" that can add +10% to the total grade [Source 2].
+    *   CSCE 648 mentions that students who regularly contribute insightful comments during class discussions may receive bonus points [Source 7].
+*   **Penalties and Specific Grading Rules:**
+    *   In CSCE 648, if a project or quiz deadline is missed, the item will be graded at 50% of the actual score [Source 7].
+    *   CSCE 648 also deducts points from the class participation grade for each missed class [Source 7].
+    *   In CSCE 652, homework challenges submitted late can receive half credit, but quizzes and the final project cannot be submitted late at all [Source 6].
+These examples demonstrate that final grades can be influenced by factors beyond a simple arithmetic average of all scores.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Yes, there are several Texas A&amp;M University courses where the final grade is not solely based on a simple calculated average, due to various policies and instructor discretions.
+The principle at play is that while a numerical average often forms the foundation of a final grade, academic policies and instructor discretion can modify, adjust, or even override this calculated average. This can occur through:
+*   **Dropping lowest scores:** Some courses drop the lowest grades for specific components. For example, in CSCE 629, the lowest quiz/exercise grade and the lowest homework grade are dropped [Source 1, 7]. In CSCE 681, the final grade is the statistical mean of the top 75% of individual quiz grades, meaning the lowest 25% do not count [Source 2].
+*   **Conditional requirements for passing:** In CSCE 681, to pass, students must complete a syllabus quiz with a 100% grade in addition to receiving an average score of 80% or higher. Any course requirements completed before passing the syllabus quiz will not be considered [Source 4].
+*   **Instructor discretion and multipliers:** In CSCE 632, a student's score can be based on peer evaluations, and the instructor establishes a multiplier based on team peer evaluations, which can be modified at their discretion [Source 6].
+*   **Overriding calculated scores:** In CSCE 632, the instructor may assign a failing grade regardless of a student’s computed final score if warranted [Source 6]. Similarly, in CSCE 681, seminar reports containing plagiarized content can lead to a recommendation for an F* for the course, overriding any calculated average [Source 10].
+*   **Curving or threshold adjustments:** CSCE 629 mentions that a "slight curve might be applied if the course average is low" [Source 7]. In CSCE 752, the instructor reserves the right to adjust letter grade thresholds downward [Source 9].
+*   **Extra credit opportunities:** CSCE 713 offers "Independent-Study Reports" as an optional component worth +10%, allowing students to increase their final grade beyond the standard components [Source 3].
+*   **Re-weighting components:** In CSCE 611, the total scores for daily quizzes and homework assignments may be re-weighed at the end of the semester to sum up to 100 points each, which can affect the final average [Source 8].
+These examples demonstrate that a student's final grade is not always a straightforward average of all numerical scores.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided context, there are several Texas A&amp;M University courses where the final grade is not solely determined by a calculated average of all scores. Grading policies can include additional conditions, instructor discretion, or specific calculation methods that deviate from a simple average.
+Here are examples from the provided syllabi:
+*   **Instructor Discretion and Conditions for Passing:**
+    *   In **CSCE 632**, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 3]. Additionally, the instructor can modify a student's multiplier for peer evaluations at their discretion [Source 3].
+    *   In **CSCE 681**, to pass the course, students must "complete the syllabus quiz on canvas with a grade of 100%" and "receive an average score of 80% or higher." Any course requirements completed before passing the syllabus quiz will not be considered [Source 4]. Furthermore, seminar reports containing plagiarized content can result in a recommendation for an F* for the course, regardless of other scores [Source 6].
+*   **Adjustments to Calculated Averages:**
+    *   **CSCE 629** states that "a slight curve might be applied if the course average is low," indicating that the final grade might be adjusted from the raw calculated average [Source 8].
+    *   **CSCE 632** incorporates a completion rate for group class activities, where 15% (capped at 100%) is added to the score at the end of the semester, allowing for missed activities without negative impact [Source 9].
+*   **Specific Calculation Methods:**
+    *   In **CSCE 629**, the lowest grade in quizzes/exercises and homework components will be dropped [Source 1].
+    *   In **CSCE 681**, the final grade is calculated as "the statistical mean of the top 75% of the individual quiz grades," meaning the lowest 25% of quiz grades do not count [Source 5].
+    *   **CSCE 632** uses peer grading where students can lose points for grading significantly differently than their peers or giving all students the same scores, which influences the final score calculation [Source 3, 9].
+*   **Penalties for Non-Compliance:**
+    *   In **CSCE 681**, missed reports without a proper excused absence will receive an automatic score of zero [Source 4]. Reports submitted without verified attendance will also receive a score of zero [Source 10].</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes, there are several instances in the provided course syllabi where the final grade is not solely based on a simple calculated average, or where specific conditions and instructor discretion can influence the final grade.
+The principle at play is that while a numerical average often forms the foundation of a student's grade, instructors may implement policies that allow for adjustments, prerequisites, or overrides based on academic integrity, participation, or specific performance criteria.
+Here are examples from the context:
+*   **Instructor Discretion/Overrides:**
+    *   In CSCE 632, the instructor can modify a student's project score multiplier at their discretion, and "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 3].
+    *   In CSCE 629, "A slight curve might be applied if the course average is low" [Source 8].
+    *   In CSCE 681, "Seminar reports containing plagiarized content... will be submitted to the Aggie Honors Office, with the recommendation that the student receives an F* for the course," which would override any computed average [Source 6].
+*   **Specific Calculation Methods:**
+    *   In CSCE 681, the final grade is calculated as "the statistical mean of the top 75% of the individual quiz grades, i.e., the lowest 25% of your quiz grades do not count" [Source 5]. This is not a simple average of all grades.
+    *   In CSCE 632, a completion rate is calculated, and "15% capped at 100%" is added to the score, allowing for missed group activities without negative impact [Source 9].
+*   **Prerequisites/Conditions for Passing:**
+    *   For CSCE 681, to pass the course, students "must complete the syllabus quiz on canvas with a grade of 100%, and receive an average score of 80% or higher." Additionally, "Any course requirements completed before passing the syllabus quiz... will not be considered" [Source 4].
+    *   In CSCE 681, "Reports submitted without verified attendance will receive a score of zero" [Source 10].
+These examples demonstrate that while a calculated average is often a significant component, other factors, specific rules, and instructor judgment can play a role in determining the final grade.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided syllabi, there are several instances where a student's final grade at Texas A&amp;M University may not be solely determined by a straightforward calculated average of all submitted work. The principle underlying this is that grading policies can incorporate various mechanisms to assess student achievement beyond a simple numerical mean.
+Here are examples of how final grades can be determined or adjusted:
+*   **Instructor Discretion for Failing Grades:** In CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 3].
+*   **Specific Passing Requirements:** For CSCE 681, students must "complete the syllabus quiz on canvas with a grade of 100%" and "receive an average score of 80% or higher" to pass the course. Additionally, any course requirements completed before passing the syllabus quiz will not be considered [Source 8].
+*   **Dropping Lowest Grades:**
+    *   In CSCE 629, the lowest grade in the quizzes/exercises component and the lowest homework grade will be dropped [Source 1, 5].
+    *   In CSCE 681, the final grade is the statistical mean of the top 75% of individual quiz grades, meaning the lowest 25% of quiz grades do not count [Source 4].
+*   **Applying Curves:** CSCE 629 states that "a slight curve might be applied if the course average is low" [Source 5].
+*   **Peer Evaluation Multipliers:** In CSCE 632, the instructor establishes a multiplier based on team peer evaluations, which can modify a student's project score. The instructor can also modify this multiplier at their discretion [Source 3].
+*   **Penalties for Late Work or Absences:**
+    *   In CSCE 648, projects and quizzes submitted after the deadline will be graded at 50% of the actual score [Source 7]. Students also lose 1.0 point from their class participation grade for each missed class, up to a maximum deduction of 12 points [Source 7].
+    *   In CSCE 681, missed reports without an excused absence receive an automatic score of zero [Source 8].
+*   **Bonus Opportunities:**
+    *   In CSCE 648, students who regularly contribute insightful comments during class discussions may receive bonus points [Source 7].
+    *   In CSCE 713, optional "Independent-Study Reports" can add +10% to the total grade [Source 2].
+*   **Adjustments for Group Activity Completion:** In CSCE 632, a completion rate for group class activities can add 15% (capped at 100%) to a student's score, allowing for missed activities without negative impact [Source 10].
+These examples demonstrate that final grades can be influenced by various factors beyond a simple arithmetic average of all graded components.</t>
+        </is>
+      </c>
     </row>
-    <row r="14" ht="86.40000000000001" customHeight="1">
-      <c r="A14" s="2" t="n">
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Which other courses at TAMU cover topics like crowdsourcing, online communities, or collaboration in games?</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>The syllabus for CSCE 672, Computer Supported Collaborative Work, explicitly covers topics such as crowdsourcing (week 8), online communities and virtual teams (week 9), and collaboration in online games (week 13). However, the provided syllabus only details information for CSCE 672 and does not list other courses at TAMU that cover these specific topics.</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>semantic_general</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>CSCE 672</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58439</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" t="n">
+        <v>58439</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>CSCE 672</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="b">
+      <c r="K14" t="b">
         <v>0</v>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>The principle for answering this question involves identifying courses based on specific thematic keywords present in their descriptions, learning outcomes, or schedules.
+Based on the provided context, the course **CSCE 672: Computer Supported Collaborative Work** explicitly covers topics such as crowdsourcing, online communities, and collaboration in games [Source 1, Source 3].
+*   **Crowdsourcing:** Week 8 of CSCE 672 covers "crowdsourcing and its issues" [Source 1].
+*   **Online Communities:** Week 9 of CSCE 672 covers "online communities and virtual teams" [Source 1].
+*   **Collaboration in Games:** Week 13 of CSCE 672 covers "collaboration in online games" [Source 1].
+The catalog description for CSCE 672 also states it "Covers design, implementation and use of technical systems that support people working cooperatively; draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical and social issues in CSCW and future directions of the field" [Source 3]. Its learning outcomes include designing software capabilities that facilitate awareness, communication, and coordination, and designing, implementing, and evaluating software to support collaboration in specific settings [Source 2].
+I cannot find information about other courses in the provided context that specifically cover crowdsourcing, online communities, or collaboration in games. I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the course **CSCE 672: Computer Supported Collaborative Work** covers topics such as crowdsourcing, online communities, and collaboration in games [Source 1, Source 2].
+Specifically, the course schedule for CSCE 672 includes:
+*   **Week 8:** Crowdsourcing and its issues [Source 1]
+*   **Week 9:** Online communities and virtual teams [Source 1]
+*   **Week 13:** Collaboration in online games [Source 1]
+The course's learning outcomes also involve designing, implementing, and evaluating software to support collaboration in specific settings, and analyzing use contexts in terms of social processes [Source 3].
+I cannot find information about other courses at TAMU that cover these specific topics in the provided context.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>The principle for identifying relevant courses involves examining course schedules, catalog descriptions, and learning outcomes for keywords related to the requested topics.
+Based on the provided context, the course **CSCE 672: Computer Supported Collaborative Work** explicitly covers topics such as crowdsourcing, online communities, and collaboration in games [Source 1, Source 3].
+Specifically, the course schedule for CSCE 672 includes:
+*   **Crowdsourcing**: "week 8: crowdsourcing and its issues" [Source 1]
+*   **Online Communities**: "week 9: online communities and virtual teams" [Source 1]
+*   **Collaboration in Games**: "week 13: collaboration in online games" [Source 1]
+The catalog description for CSCE 672 also states that it "Covers design, implementation and use of technical systems that support people working cooperatively; draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical and social issues in CSCW and future directions of the field" [Source 3]. Its learning outcomes include designing software capabilities that facilitate awareness, communication, and coordination [Source 2].
+However, I cannot find information about *other* courses at TAMU that cover these specific topics in the provided context. I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>I cannot find information about other courses at TAMU that cover topics like crowdsourcing, online communities, or collaboration in games in the provided context. The context only details the CSCE 672 course, which includes these topics in its schedule [Source 1].</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>I cannot find information about other courses at TAMU that cover topics like crowdsourcing, online communities, or collaboration in games in the provided context. The context only details the CSCE 672 course, which includes these topics in its schedule [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the course **CSCE 672: Computer Supported Collaborative Work** covers topics such as crowdsourcing, online communities, and collaboration in games [Source 1, Source 2].
+Specifically, the course schedule for CSCE 672 includes:
+*   **Crowdsourcing:** "week 8: crowdsourcing and its issues" [Source 1]
+*   **Online Communities:** "week 9: online communities and virtual teams" [Source 1]
+*   **Collaboration in Games:** "week 13: collaboration in online games" [Source 1]
+I cannot find information about other courses at TAMU that cover these specific topics in the provided context.</t>
+        </is>
+      </c>
     </row>
-    <row r="15" ht="374.4" customHeight="1">
-      <c r="A15" s="2" t="n">
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>What other classes at A&amp;M cover advanced topics in AI like transformers and large language models?</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Several courses at Texas A&amp;M cover advanced topics in AI, including Transformers and Large Language Models (LLMs):
 CSCE 670: Information Retrieval and Web Search
@@ -1163,228 +2301,612 @@
 It is important to note that the specific content and depth of coverage may vary by instructor and term.</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>semantic_general</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>46627</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H15" t="n">
+        <v>46627</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="b">
+      <c r="K15" t="b">
         <v>0</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following courses cover advanced topics in AI such as Transformers and Large Language Models (LLMs):
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   Week 5: Transformers [Source 1]
+    *   Week 6: Contextualized Representations, Pre-Training, Large Language Models [Source 1]
+    *   Week 8: Instruction Tuning, Alignment, Post-Training [Source 1]
+    *   Week 9: Large Reasoning Models, Test-Time Scaling, Decoding [Source 1]
+    *   Week 11: Multilingual Language Models, Vision-Language Models [Source 1]
+    *   Week 14: Bias Mitigation, Hallucinations [Source 1]
+*   **CSCE 624: Sketch Recognition**
+    *   Weeks 8-9: Hidden Markov Models, LLMs, and related techniques [Source 5]
+*   **CSCE 670: Information Retrieval**
+    *   Week 10: Transformer; BERT-Based Ranking [Source 2]
+    *   Week 12: Large Language Models Basics [Source 2]
+    *   Week 13: Large Language Models with Search Engines [Source 2]
+    *   Week 14: Large Language Models for Ranking and Recommendation [Source 2]
+*   **CSCE 665: Advanced Computer Security**
+    *   Week 11: AI/LLM Security [Source 10]
+    *   Week 13: AI/LLM Security II [Source 10]
+    *   Week 14: AI/LLM Security III [Source 10]
+    *   Week 15: AI/LLM Security IV [Source 10]</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Several classes at Texas A&amp;M cover advanced topics in AI, including transformers and large language models (LLMs):
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   Week 5: Transformers [Source 1]
+    *   Week 6: Contextualized Representations, Pre-Training, Large Language Models [Source 1]
+*   **CSCE 670**
+    *   Week 10: Transformer; BERT-Based Ranking [Source 2]
+    *   Week 12: Large Language Models Basics [Source 2]
+    *   Week 13: Large Language Models with Search Engines [Source 2]
+    *   Week 14: Large Language Models for Ranking and Recommendation [Source 2]
+*   **CSCE 624**
+    *   Weeks 8-9: Hidden Markov Models, LLMs, and related techniques [Source 5]
+*   **CSCE 665**
+    *   Weeks 11, 13, 14: AI/LLM Security [Source 10]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Several courses at Texas A&amp;M cover advanced topics such as Transformers and Large Language Models (LLMs):
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   Week 5: Transformers [Source 1]
+    *   Week 6: Contextualized Representations, Pre-Training, Large Language Models [Source 1]
+    *   Week 8: Instruction Tuning, Alignment, Post-Training [Source 1]
+    *   Week 9: Large Reasoning Models, Test-Time Scaling, Decoding [Source 1]
+    *   Week 11: Multilingual Language Models, Vision-Language Models [Source 1]
+    *   Week 14: Bias Mitigation, Hallucinations [Source 1]
+*   **CSCE 624: Sketch Recognition**
+    *   Weeks 8-9: Hidden Markov Models, LLMs, and related techniques [Source 5]
+*   **CSCE 670: Information Retrieval**
+    *   Week 10: Transformer; BERT-Based Ranking [Source 2]
+    *   Week 12: Large Language Models Basics [Source 2]
+    *   Week 13: Large Language Models with Search Engines [Source 2]
+    *   Week 14: Large Language Models for Ranking and Recommendation [Source 2]
+*   **CSCE 665: Advanced Computer Security**
+    *   Weeks 11, 13, 14: AI/LLM Security [Source 10]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, here are the courses that cover advanced topics in AI like transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   This course covers "Transformers" in Week 5 and "Contextualized Representations, Pre-Training, Large Language Models" in Week 6 [Source 1].
+    *   It also includes "Language Modeling" in Week 3 and "Multilingual Language Models, Vision-Language Models" in Week 11 [Source 1].
+    *   The course aims for learners to "Be aware of recent trends in natural language processing research" [Source 3].
+*   **CSCE 624: Sketch Recognition**
+    *   This course mentions "Hidden Markov Models, LLMs, and related techniques" in Weeks 8-9 [Source 5].
+*   **CSCE 665: Security**
+    *   This course includes "AI/LLM Security" as a topic in Weeks 11, 13, and 14 [Source 10].
+Other courses like CSCE 726 (Large-Scale Optimization for Machine Learning) and CSCE 633 (Machine Learning) provide foundational knowledge in machine learning and deep learning, which are prerequisites or recommended background for advanced AI topics, but do not explicitly list "transformers" or "large language models" as core topics in their schedules or descriptions [Sources 6, 7, 8, 9].</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following courses cover advanced topics in AI like transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   This course covers "Transformers," "Contextualized Representations, Pre-Training, Large Language Models," "Instruction Tuning, Alignment, Post-Training," "Large Reasoning Models," and "Multilingual Language Models, Vision-Language Models" [Source 1].
+    *   The course aims for learners to "Be aware of recent trends in natural language processing research" [Source 3].
+*   **CSCE 624**
+    *   This course includes "LLMs" under its "Mathematical and Sequential Models" topics [Source 5].
+*   **CSCE 665**
+    *   This course dedicates several weeks to "AI/LLM Security" [Source 10].</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Several courses at Texas A&amp;M cover advanced topics in AI, including transformers and large language models (LLMs):
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   Covers "Transformers" in Week 5 and "Large Language Models" in Week 6 [Source 1].
+*   **CSCE 670**
+    *   Discusses "Transformer; BERT-Based Ranking" in Week 10, "Large Language Models Basics" in Week 12, "Large Language Models with Search Engines" in Week 13, and "Large Language Models for Ranking and Recommendation" in Week 14 [Source 2].
+*   **CSCE 624**
+    *   Mentions "LLMs" as part of "Hidden Markov Models, LLMs, and related techniques" in Weeks 8-9 [Source 5].
+*   **CSCE 665**
+    *   Focuses on "AI/LLM Security" across Weeks 11, 13, and 14 [Source 10].</t>
+        </is>
+      </c>
     </row>
-    <row r="16" ht="100.8" customHeight="1">
-      <c r="A16" s="2" t="n">
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>What other TAMU CS courses would you recommend for students who want to get better at preparing research reports and discussing technical articles?</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>CSCE 681 (Seminar) is a course designed to help students develop these skills. Its learning outcomes explicitly state that upon completion, students should be able to prepare reports and discuss research works and selected published technical articles. Students in CSCE 681 are required to write reports for each lecture, which involve analyzing the background, problem statement, proposed solution, results, and critique of the presented research.</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>semantic_general</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>CSCE 681</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12644</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H16" t="n">
+        <v>12644</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>CSCE 681</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="b">
+      <c r="K16" t="b">
         <v>0</v>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>To recommend courses for students seeking to improve their skills in preparing research reports and discussing technical articles, we can look for courses that emphasize **active engagement with academic literature and research communication**. This principle involves critically analyzing, synthesizing, and presenting research findings.
+Based on the provided context, the following Texas A&amp;M CS courses align with this principle and would be beneficial:
+*   **CSCE 681 (Seminar)**
+    *   **Academic Dimension:** The primary purpose of this course is to expose students to current and seminal research topics in computer science. Students are expected to "prepare reports and discuss research works and selected published technical articles" [Source 1, 2]. For Section 600, this involves writing reports for each lecture, with each report quiz requiring sections such as background, problem statement, proposed solution, results, and critique [Source 2]. Section 700 also requires writing reports based on lecture recordings [Source 6].
+*   **CSCE 635**
+    *   **Academic Dimension:** This course requires students to submit short reviews of research papers. These reviews involve articulating the papers' main contributions, providing critical analysis of their strengths and limitations, and discussing open research questions or potential extensions [Source 3]. Additionally, students lead class discussions on assigned papers, preparing prompts and facilitating conversations around methodology, results, and broader implications [Source 3].
+*   **CSCE 632**
+    *   **Academic Dimension:** Students in CSCE 632 are required to compile a literature review on an accessibility topic, drawing from at least 10 peer-reviewed conference or journal papers. This review must identify themes and gaps in the research, supported by evidence, and include an annotated bibliography [Source 10]. Students also present their current research based on their literature review [Source 10].</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>For students interested in improving their skills in preparing research reports and discussing technical articles, the following Texas A&amp;M CS courses are recommended based on their academic content and learning activities:
+*   **CSCE 681 (Seminar)**
+    *   **Academic Dimension:** The primary purpose of this course is to expose students to current and seminal research topics in computer science. Students are expected to prepare reports and discuss research works and selected published technical articles. A key requirement is to write a report for each lecture, which includes sections like background, problem statement, proposed solution, results, and critique [Source 1, 2].
+*   **CSCE 635**
+    *   **Academic Dimension:** This course requires students to submit short reviews (within 2 pages) based on two research papers each week. These reviews involve articulating the papers' main contributions, critically analyzing their strengths and limitations, and discussing open research questions or potential extensions. Students also lead class discussions on assigned papers, preparing slides or discussion prompts to facilitate conversation around methodology, results, and broader implications [Source 3].
+*   **CSCE 632**
+    *   **Academic Dimension:** Students in this course compile a literature review on an accessibility topic, requiring analysis of at least 10 related peer-reviewed conference or journal papers. The literature review must clearly outline themes and gaps in the research, supported by evidence from the papers, and include an annotated bibliography. Students also give a "Current Research Presentation" based on their literature review [Source 9].
+*   **CSCE 665**
+    *   **Academic Dimension:** This course includes "Paper mini-review" and "Class participation and presentation" as significant grading components. The course material primarily consists of various research papers from top security conferences and journals, indicating a focus on engaging with and presenting on published technical articles [Source 10].
+*   **CSCE 648**
+    *   **Academic Dimension:** While not explicitly detailing report writing, this course recommends "Conference Articles on Shape Modeling" and "Shape Modeling Articles from Computer Aided Design and Engineering &amp; Computer Graphics Journals" as resource materials [Source 6]. This suggests that engaging with and potentially discussing these technical articles is an integral part of the course's academic experience.
+These courses offer structured opportunities to read, analyze, critique, report on, and discuss academic research and technical articles, which are crucial skills for students pursuing advanced studies or research careers.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, the following Texas A&amp;M University CS courses would be beneficial:
+*   **CSCE 681 (Seminar)**: The purpose of this course is to expose students to current and seminal research topics. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1]. Students are expected to write reports for each lecture, which include sections like background, problem statement, proposed solution, results, and critique [Source 2].
+*   **CSCE 635**: In this course, students are expected to submit short reviews (within 2 pages) based on two papers from a weekly list. These reviews require articulating understanding of main contributions, providing critical analysis of strengths and limitations, and discussing open research questions or potential extensions. Students also lead class discussions on assigned papers, preparing slides or discussion prompts to engage classmates and facilitate conversation around methodology, results, and broader implications [Source 4].</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>To improve at preparing research reports and discussing technical articles, students should look for courses that emphasize critical analysis of published research, structured writing assignments, and active participation in academic discourse.
+Based on the provided context, the following courses would be beneficial:
+*   **CSCE 681 (Seminar)**: This course's explicit purpose is to "expose students to a broad range of current and seminal research topics in computer science and related fields." Upon completion, students are expected to "prepare reports and discuss research works and selected published technical articles" [Source 1]. Students are required to write reports for each lecture, which include sections like background, problem statement, proposed solution, results, and critique [Source 2].
+*   **CSCE 635**: In this course, students are expected to submit "short review[s]... based on two papers from that week’s list." These reviews require articulating understanding of main contributions, providing critical analysis of strengths and limitations, and discussing open research questions or potential extensions. Students also "lead class discussions on the assigned papers," preparing slides or discussion prompts to facilitate conversation around methodology, results, and broader implications [Source 4].</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, the following courses are relevant based on the provided context:
+*   **CSCE 681 (Seminar)**: This course's purpose is to expose students to current and seminal research topics. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1]. Students are expected to write a report for each lecture, which includes sections like background, problem statement, proposed solution, results, and critique [Source 2].
+*   **CSCE 635**: In this course, students are expected to submit short reviews (within 2 pages) based on two papers from a weekly list. These reviews require students to articulate their understanding of the papers' main contributions, provide a critical analysis of their strengths and limitations, and discuss open research questions or potential extensions. Students also lead class discussions on assigned papers, preparing slides or discussion prompts to engage classmates and facilitate conversation around methodology, results, and broader implications [Source 4].</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Based on the provided context, several other TAMU CS courses offer opportunities for students to develop skills in preparing research reports and discussing technical articles:
+*   **CSCE 635**
+    *   Students are expected to submit short reviews (within 2 pages) based on two research papers, articulating their understanding of main contributions, providing critical analysis of strengths and limitations, and discussing open research questions or potential extensions [Source 3].
+    *   Students will also lead class discussions on assigned papers, preparing slides or discussion prompts to engage classmates and facilitating meaningful conversation around methodology, results, and broader implications [Source 3].
+    *   A project proposal and short presentation are also required, outlining goals, motivation, and expected contributions, accompanied by an in-class presentation for feedback [Source 3].
+*   **CSCE 632**
+    *   Graduate students (CSCE 632) are required to compile a literature review on an accessibility topic, comprising at least 10 related peer-reviewed conference or journal papers. This review must clearly lay out themes and gaps in research, supported by evidence from the papers, and include an annotated bibliography [Source 9].
+    *   Students will also give a "Current Research Presentation" based on their literature review, which will be peer-graded [Source 9].
+*   **CSCE 665**
+    *   This course requires a "Paper mini-review" as part of its grading policy [Source 10].
+    *   Class participation and presentation are also components of the grade, suggesting discussion of technical content [Source 10].
+    *   The course material primarily consists of various research papers from top security conferences and journals [Source 10].
+These courses explicitly involve activities such as writing reviews of research papers, leading discussions on technical articles, conducting literature reviews, and giving presentations on research topics, which directly align with the skills mentioned in your question.</t>
+        </is>
+      </c>
     </row>
-    <row r="17" ht="172.8" customHeight="1">
-      <c r="A17" s="2" t="n">
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Given courses often have multiple final projects and papers due around the same time, what are some effective strategies for managing the end-of-semester workload at TAMU?</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>To effectively manage the end-of-semester workload, students should proactively identify and prioritize significant due dates across all courses. For example, in CSCE 656, the syllabus indicates that the Survey paper, Final project presentations, and Final project reports are all due within a concentrated period from April 20 to May 1.
 Understanding these clusters of major assignments early allows for strategic planning and allocation of time. Additionally, students should be mindful of strict late work policies, such as those in CSCE 656 which deduct 50% immediately for late write-ups and 10% per day for other assignments, reinforcing the importance of timely submission to avoid significant grade penalties.</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>semantic_general</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>CSCE 656</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42432</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H17" t="n">
+        <v>42432</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>CSCE 656</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="b">
+      <c r="K17" t="b">
         <v>0</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Effective end-of-semester workload management at Texas A&amp;M University relies on proactive planning, strict adherence to deadlines, understanding late work policies, and leveraging available resources. Given that multiple courses often have final projects, papers, and exams due around the same time, students must strategically approach their academic progression to avoid being overwhelmed.
+Based on the provided course syllabi, here are some effective strategies for managing your end-of-semester workload:
+1.  **Proactive Planning and Early Start:**
+    *   Begin working on assignments as soon as they are assigned, rather than waiting until closer to the deadline [Source 6, 7].
+    *   Plan your time carefully, especially around major deadlines like final projects and exams [Source 8]. For example, CSCE 633 has a Final Project due May 4, CSCE 608 has a project due April 27 and a Final Exam on May 4, and CSCE 672 has final project presentations April 27-28 and reports due May 1 [Source 3, 6, 9]. CSCE 611 has a "hard" deadline for MP7 on May 3 and a Final Exam on May 5 [Source 2].
+2.  **Understand and Adhere to Strict Deadlines and Late Policies:**
+    *   Many courses have very strict late work policies. For instance, CSCE 633 and CSCE 614 state that "No Late Assignments will be accepted" or "Late assignments are not going to be accepted in general" unless a university-sanctioned excuse is provided [Source 3, 7].
+    *   Other courses, like CSCE 752 and CSCE 672, implement significant grade deductions for late submissions, with credit potentially becoming impossible after a few days [Source 8, 9].
+    *   Be aware of specific due times, such as 11:59 pm CT, as listed in CSCE 633 [Source 3].
+3.  **Utilize Excused Absence Policies Appropriately:**
+    *   Familiarize yourself with Texas A&amp;M's Student Rule 7 regarding excused absences. If you anticipate a situation that might affect your ability to meet a deadline, follow the course-specific procedures for requesting an excused absence, including providing advance notice and necessary documentation [Source 5]. Note that this is for legitimate excused absences, not general workload relief.
+4.  **Maintain Continuous Engagement and Attendance:**
+    *   It is strongly recommended to "keep up with the course material and do not fall behind" [Source 6].
+    *   Regular class attendance is often emphasized as "essential" or "strongly recommended" to ensure you don't miss critical information or ongoing assignments [Source 4, 6, 8]. For CSCE 681, continuous reports are due at the end of each lecture [Source 1].
+5.  **Seek Assistance Early When Needed:**
+    *   If you encounter difficulties with assignments, contact your instructor or TA as early as possible. Waiting until closer to the deadline may make it harder to receive timely help [Source 7].
+By integrating these strategies into your academic routine, you can better manage the demanding end-of-semester period at TAMU.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>The end of the semester often presents a significant challenge due to the convergence of multiple high-stakes assignments. The underlying principle for managing this is **proactive workload planning and time management**. This involves understanding all upcoming deadlines and strategically allocating time and effort to avoid last-minute rushes and ensure quality work.
+Based on the provided course schedules for the 202611 term, it is evident that many courses indeed have final projects, reports, and exams clustered around late April and early May:
+*   **CSCE 611**: Machine Problem 7 (MP7) is due on May 3, with the Final Exam on May 5 [Source 1].
+*   **CSCE 632**: Final Presentations are scheduled for April 21 &amp; 23, and the Final Report and Video Demo are due on April 28 [Source 3].
+*   **CSCE 633**: The Final Project is due on May 4 [Source 4].
+*   **CSCE 672**: Final project presentations are due April 27-28, and Final project reports are due May 1 [Source 5].
+*   **CSCE 752**: The Final Exam is on May 1 [Source 6].
+*   **CSCE 656**: A Survey paper is due May 1, with Final project presentations from April 20-28 and Final project reports also due on May 1 [Source 7].
+*   **CSCE 635**: The Final Project Report is due April 27, and Final Project Presentations are from April 17, 20, 22 [Source 8].
+*   **CSCE 652**: The Final Project is due on April 28, following dedicated project time in weeks 14 and 15 [Source 2].
+To effectively manage this concentrated workload, consider the following strategies:
+1.  **Map All Deadlines Early**: As soon as syllabi are available, create a comprehensive calendar that includes all final project due dates, presentation dates, paper submissions, and exam schedules across all your courses. This visual overview helps identify potential conflicts and peak workload periods.
+2.  **Break Down Large Tasks**: For each final project or paper, break it down into smaller, manageable sub-tasks (e.g., research, outline, draft, revise, proofread, create presentation slides). Assign mini-deadlines for these sub-tasks throughout the semester, well in advance of the final due date.
+3.  **Start Early**: Begin working on components of your final projects and papers as early as possible. For example, if a course has weekly smaller assignments or readings, consider how these might contribute to your final project. Some courses, like CSCE 652, dedicate specific weeks for final project work, which should be utilized fully [Source 2].
+4.  **Prioritize and Allocate Time**: Based on the weight of each assignment, its complexity, and your personal strengths/weaknesses, prioritize your tasks. Allocate dedicated blocks of time for each project, especially during the weeks leading up to the end of the semester.
+5.  **Utilize Course Resources**: Attend office hours, engage with TAs, and seek feedback on drafts if available. Some courses, like CSCE 635, include project checkpoints (e.g., Midterm project check-in on March 2, 4) that can help you stay on track [Source 8].
+6.  **Plan for Contingencies**: Build in buffer time for unexpected delays, technical issues, or revisions. Remember that some deadlines, like MP7 in CSCE 611, are "hard" due to timely grading requirements [Source 1].
+By proactively planning and distributing your effort throughout the semester, you can navigate the demanding end-of-semester period more effectively.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Effectively managing the end-of-semester workload, especially when multiple final projects and papers are due, relies on robust time management and proactive planning. This approach helps students navigate converging deadlines and significant assignments to ensure academic success.
+Based on the provided course information, here are some effective strategies for managing your end-of-semester workload at TAMU:
+1.  **Start Early and Plan Ahead:** Many courses emphasize the importance of beginning assignments as soon as they are released. For example, CSCE 608 strongly recommends keeping up with course material and starting assignments immediately [Source 6]. Similarly, CSCE 614 advises starting assignments "as early as possible" [Source 7]. CSCE 752 also suggests students "plan their time... in accordance with this schedule" [Source 8].
+2.  **Monitor All Due Dates Closely:** Consistently check Canvas for official due dates, as these are the definitive deadlines [Source 3, 6]. Be aware that final projects and exams often cluster around the end of the semester, such as the "Final Project - Due Mon. May 4" for CSCE 633 [Source 3], "course project #2 due" on April 27 and "Final exam" on May 4 for CSCE 608 [Source 6], "Final project presentations due April 27-28" and "Final project reports due May 1" for CSCE 672 [Source 9], and "MP7 due on Sunday, May 3" with a "hard" deadline for CSCE 611 [Source 2].
+3.  **Understand and Adhere to Late Work Policies:** Be aware that many courses have strict late work policies, with some stating "No Late Assignments will be accepted" [Source 3, 7]. Others may deduct points for late submissions [Source 9, 8]. Missing deadlines can significantly impact your grade, as some courses will assign an automatic zero for unexcused late work [Source 1, 8].
+4.  **Utilize Instructor and TA Support Proactively:** If you encounter difficulties, contact your instructor or TA well in advance of the deadline. CSCE 614 notes that "the closer to the deadline you request our assistance, the harder it may be to obtain our help" [Source 7].
+5.  **Maintain Regular Attendance:** Attending lectures is crucial for staying informed about course material, project requirements, and any updates. CSCE 648 states that "regular class attendance is essential" [Source 4], and CSCE 608 "strongly recommended" it [Source 6].
+6.  **Understand Excused Absence Procedures:** Familiarize yourself with Student Rule 7 regarding excused absences, especially for missed exams or assignments. Note the strict timeline for submitting requests, typically before the absence or within two business days after [Source 5]. Missed work without an approved excused absence may result in a zero [Source 1, 5, 8].
+**Academic Progression Dimension:**
+Effective management of end-of-semester workload is critical for your academic progression. Successfully completing final projects and exams demonstrates your mastery of course material, which is essential for earning credits and advancing in your degree program. Proactive planning helps prevent academic setbacks, such as failing grades due to missed deadlines or inadequate preparation, ensuring you stay on track for timely graduation.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Effective academic planning and time management are crucial principles for navigating periods of high workload, such as the end of a semester when multiple final projects, papers, and exams are often due concurrently.
+Based on the provided course syllabi for the 202611 term, there is a significant concentration of major assignments and exams in late April and early May. For example:
+*   **Late April:**
+    *   CSCE 635 has Final Project Presentation and Feedback sessions on April 17, 20, and 22, with the Final Project Report due April 27 [Source 6].
+    *   CSCE 656 has Final project presentations between April 20-28 and Final project reports due May 1 [Source 2].
+    *   CSCE 652's CTF Scoreboard closes April 21, and the FINAL PROJECT is DUE April 28 [Source 5].
+    *   CSCE 672 has Final project presentations on April 27-28 [Source 3].
+*   **Early May:**
+    *   CSCE 672 Final project reports are due May 1 [Source 3].
+    *   CSCE 656's Survey paper and Final project reports are due May 1 [Source 2].
+    *   CSCE 752 has its Final Exam on May 1 [Source 10].
+    *   CSCE 611's MP7 is due May 3 [Source 1].
+    *   CSCE 633's Final Project is due May 4 [Source 4].
+    *   CSCE 611 has its Final Exam on May 5 [Source 1].
+This overlap indicates that students taking multiple courses with these deadlines will experience a high-intensity period. Understanding this academic progression and the clustering of major deliverables is essential for planning your semester effectively from the outset.
+The provided context highlights the timing of these critical deadlines but does not offer specific strategies for managing this workload. I cannot find that information in the provided context.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>To effectively manage the end-of-semester workload, which often includes multiple final projects and papers, a key principle is **proactive academic planning and time management**. This involves understanding the scope and deadlines of major assignments across all courses and strategically allocating your time to avoid last-minute rushes.
+Based on the provided course information, several courses have significant deliverables concentrated in late April and early May:
+*   **CSCE 672**: Final project presentations are scheduled for April 27-28, with final project reports due on May 1 [Source 3].
+*   **CSCE 635**: The Final Project Report is due on April 27, and Final Project Presentation and Feedback sessions occur on April 17, 20, and 22 [Source 6].
+*   **CSCE 652**: The final project is due on April 28 [Source 5].
+*   **CSCE 656**: A survey paper is due on May 1, final project presentations are from April 20-28, and final project reports are due on May 1 [Source 2].
+*   **CSCE 633**: The Final Project is due on May 4 [Source 4].
+*   **CSCE 611**: Machine Problem 7 (MP7) is due on May 3, and the Final Exam is on May 5 [Source 1].
+*   **CSCE 752**: The Final Exam is on May 1, and projects are due approximately every two weeks, implying potential project deadlines around this time [Source 10].
+Given this concentration of deadlines, here are some effective strategies for managing your end-of-semester workload:
+1.  **Start Early and Break Down Tasks**: Begin working on final projects and papers well in advance of their due dates. Break down large assignments into smaller, manageable tasks and set internal deadlines for each component. For courses like CSCE 611, where Machine Problems are posted weekly, staying on top of these can prevent a large backlog [Source 1].
+2.  **Understand Late Policies**: Be aware of each course's specific late work policy, as they vary significantly. For example, CSCE 633 accepts no late assignments [Source 4], while CSCE 672 and CSCE 656 deduct 10% per day late up to a maximum of one week [Source 3, Source 2]. CSCE 752 also has a tiered deduction for late projects [Source 10]. Knowing these policies can help you prioritize and decide if a minor deduction is acceptable for one assignment to ensure a higher quality submission for another.
+3.  **Utilize Weekly Assignments and Readings**: Some courses, like CSCE 672 and CSCE 656, have smaller project activities or reading write-ups due weekly [Source 3, Source 2]. Consistently completing these can help distribute your workload and prevent a build-up of tasks at the end of the semester.
+4.  **Prioritize and Allocate Time**: Create a master schedule that includes all final project deadlines, exam dates, and other significant due dates. Identify periods of high overlap and prioritize your work based on assignment weight, complexity, and your personal strengths.
+5.  **Leverage Group Work Effectively**: For courses with group projects, such as CSCE 713 [Source 9], establish clear roles, responsibilities, and internal deadlines with your team early in the semester to ensure equitable contribution and timely completion.
+6.  **Attend Classes and Stay Engaged**: Regular class attendance is emphasized in some courses (e.g., CSCE 648, CSCE 681, CSCE 752) [Source 7, Source 8, Source 10]. Staying engaged with course material throughout the semester can reduce the amount of catch-up work required during the busy end-of-semester period.
+I don't have enough data to provide specific advice on managing final exams that are not explicitly listed with dates in the provided syllabi.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>The end of the semester at Texas A&amp;M University often involves a concentration of significant assignments, including final projects, reports, and exams. This clustering of deadlines necessitates effective workload management.
+Based on the provided course syllabi for the 202611 term, several courses have major deliverables scheduled in late April and early May:
+| Course    | Assignment Type                 | Due Date(s)           | Source |
+| :-------- | :------------------------------ | :-------------------- | :----- |
+| CSCE 635  | Final Project Presentation      | Apr. 17, 20, 22       | [Source 8] |
+| CSCE 656  | Final project presentations     | Apr. 20-28            | [Source 7] |
+| CSCE 632  | Final Presentation              | Apr 21 &amp; 23           | [Source 3] |
+| CSCE 652  | CTF Scoreboard closes           | Apr 21                | [Source 2] |
+| CSCE 635  | Final Project Report            | Apr. 27               | [Source 8] |
+| CSCE 672  | Final project presentations     | Apr 27-28             | [Source 5] |
+| CSCE 632  | Final Report, Video Demo        | Apr 28                | [Source 3] |
+| CSCE 652  | FINAL PROJECT DUE               | Apr 28                | [Source 2] |
+| CSCE 656  | Survey paper due                | May 1                 | [Source 7] |
+| CSCE 656  | Final project reports           | May 1                 | [Source 7] |
+| CSCE 672  | Final project reports           | May 1                 | [Source 5] |
+| CSCE 752  | Final Exam                      | May 1                 | [Source 6] |
+| CSCE 611  | MP7 due                         | May 3                 | [Source 1] |
+| CSCE 633  | Final Project                   | May 4                 | [Source 4] |
+| CSCE 611  | Final Exam                      | May 5                 | [Source 1] |
+This overlap demonstrates the importance of proactive planning to manage academic progression effectively. Students should be aware of each course's specific late work policies, as these can vary significantly:
+*   Some courses, like CSCE 633, state "No Late Assignments will be accepted" [Source 4].
+*   Others, such as CSCE 672 and CSCE 656, deduct a percentage per day late, typically "10% is deducted per day late up to a maximum of one week after the original due date" [Source 5, Source 7].
+*   CSCE 752 has a tiered deduction system, where a project submitted three days late might only receive a maximum of 40% of the score, and after approximately five days, no credit can be earned [Source 6].
+*   CSCE 611 explicitly states that the due date for MP7 is "hard" to allow for timely grading [Source 1].
+While the provided context highlights the critical periods for assignments and the varying late work policies, it does not explicitly detail strategies for managing the end-of-semester workload. Therefore, I cannot provide specific strategies based solely on the available syllabi.</t>
+        </is>
+      </c>
     </row>
-    <row r="18" ht="86.40000000000001" customHeight="1">
-      <c r="A18" s="2" t="n">
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Is it common in other TAMU graduate CS courses to have a single, tool-specific project like D3.js count for half of your final grade?</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>In CSCE 679, the course project accounts for 50% of the final grade. For graduate students enrolled in CSCE 679, this project specifically requires implementation using the D3.js visualization library. The provided syllabus details the grading structure for CSCE 679 but does not offer information about the grading policies or project requirements in other TAMU graduate CS courses.</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>semantic_general</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>CSCE 679</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>55144</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H18" t="n">
+        <v>55144</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>CSCE 679</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="b">
+      <c r="K18" t="b">
         <v>0</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>The principle underlying your question relates to the grading policies and the weighting of different academic components, specifically projects and tool-specific requirements, within Texas A&amp;M University graduate CS courses.
+Based on the provided syllabi:
+*   **CSCE 679** requires a course project worth 50% of the final grade. Graduate students are specifically required to implement their project using the D3.js visualization library [Source 1].
+*   **CSCE 648** includes six projects that collectively contribute 36% to the final grade, with each project equally weighted at 6 points out of 100 [Source 3, 5]. There is no mention of a specific tool requirement for these projects.
+*   **CSCE 713** has a "Vulnerabilities PoC" (Proof of Concept) component worth 50% of the grade, which is individual and requires delivering source code and a video demonstrating exploitation [Source 8]. Additionally, it has a "First project" and a "Final project," each worth 25% and completed in groups [Source 8]. While the PoC involves tool use for exploitation, it's not specified as a single, named library like D3.js.
+*   **CSCE 624** includes a team-based project worth 30% of the final grade [Source 10].
+*   **CSCE 629** does not list projects as a grading component, focusing instead on exams (60%), homework (30%), and quizzes/exercises (10%) [Source 7].
+Comparing these, it appears that a single component, whether a "course project" (CSCE 679) or an individual "Vulnerabilities PoC" (CSCE 713), can indeed account for 50% of the final grade in some graduate CS courses. However, the specific requirement for graduate students to use a particular tool like D3.js for a 50% project, as seen in CSCE 679, is not explicitly mirrored in the other provided syllabi. Other courses either have projects with lower weightings, multiple projects, or do not specify a single tool for a major project component.
+I don't have enough data to definitively state how common it is across *all* TAMU graduate CS courses to have a single, tool-specific project count for half of the final grade, as the provided context is limited to a few course syllabi.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the grading policies for graduate CS courses at Texas A&amp;M University show some variation in the weighting and nature of major projects.
+While not universally common across all courses in the provided context, at least two courses feature a single, substantial project or individual component that accounts for 50% of the final grade:
+*   In **CSCE 679**, the course project constitutes 50% of the final grade for graduate students, and they are specifically required to implement it using the D3.js visualization library [Source 1]. This directly aligns with your description of a "single, tool-specific project" counting for half the grade. The project involves exploring key frameworks, advanced visualization topics, and hands-on tutorials in D3 and Vega-Lite, culminating in presentations [Source 5].
+*   In **CSCE 713**, the "Vulnerabilities PoC" (Proof of Concept) is an individual component worth 50% of the grade. Students are required to deliver PoCs for vulnerabilities explained in class, including source code and a video demonstrating exploitation, and are expected to run security tools on their own machines [Source 3]. This can be considered a single, tool-specific project component.
+Other courses show different structures:
+*   **CSCE 648** has projects contributing 36% of the grade, but this is distributed across six equally weighted projects [Source 4, 6].
+*   **CSCE 652** includes a final project worth 30% [Source 7].
+*   **CSCE 748** has "Programming assignments" as a category worth 50%, but this consists of five programming assignments, not a single one [Source 9].
+Therefore, while not every course follows this model, the structure of a single, tool-specific project or substantial individual component accounting for 50% of the final grade is present in at least two of the graduate CS courses provided in the context [Source 1, 3]. I don't have enough data to definitively state if it is "common" across all TAMU graduate CS courses.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Based on the provided syllabi, the weighting and tool-specificity of projects vary among Texas A&amp;M University graduate CS courses.
+In **CSCE 679**, the course project accounts for 50% of the final grade, and graduate students are specifically required to implement their project using the D3.js visualization library [Source 1]. This project involves exploring key frameworks like the Nested Model of Visual Analytics, principles of marks and channels, and advanced topics in visualization, with hands-on tutorials in D3 and Vega-Lite [Source 6].
+In contrast, other courses show different approaches:
+*   **CSCE 648** has projects contributing 36% to the final grade, but this is split across six equally weighted projects, with no specific tool requirement mentioned [Source 4, 5].
+*   **CSCE 624** includes a team-based project that accounts for 30% of the final grade, without specifying a particular tool [Source 9].
+*   **CSCE 629** primarily bases grades on exams (60%), quizzes/exercises (10%), and homework (30%), with no mention of a single large project component [Source 8].
+*   **CSCE 752** and **CSCE 633** mention projects or assignments but do not specify a single project counting for half the grade or a tool-specific requirement for such a project in the provided context [Source 3, 10].
+Therefore, while CSCE 679 features a single, tool-specific project (D3.js for graduate students) counting for 50% of the final grade, this does not appear to be a common practice across all the graduate CS courses for which information is provided. Other courses either have lower project weights, multiple projects, or do not specify tool requirements for a major project component.
+I don't have enough data to answer this accurately based on the available syllabi for all TAMU graduate CS courses.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Grading policies in graduate CS courses at Texas A&amp;M University vary, often incorporating projects, assignments, exams, and participation with different weightings.
+While CSCE 679 explicitly features a single, tool-specific course project (D3.js) accounting for 50% of the final grade for graduate students [Source 1], this specific structure is not universally common across all provided graduate CS courses.
+Here's a breakdown of project weightings in other courses:
+*   **CSCE 713**: "Vulnerabilities PoC" (Proof of Concept) accounts for 50% of the grade. This is an individual component requiring students to deliver source code and video demonstrations of exploits for vulnerabilities explained in class, implying the use of specific security tools [Source 3].
+*   **CSCE 648**: Projects contribute 36 points out of 100 (36%), distributed across six equally weighted projects, meaning no single project accounts for 50% [Source 4, 6].
+*   **CSCE 652**: A final project accounts for 30% of the grade, with an expectation for graduate students to undertake a more substantive project involving reusable tools or complex malware samples [Source 7].
+*   **CSCE 748**: Programming assignments collectively make up 50% of the grade, but this is divided among five programming assignments, not a single project. A separate final project accounts for 20% [Source 9].
+*   **CSCE 629**: This course's grading is based on exams (60%), quizzes/exercises (10%), and homework (30%), with no explicit project component listed [Source 8].
+Therefore, while a 50% weighting for a project-like component is present in some courses (CSCE 679 and CSCE 713), the specific scenario of a *single, tool-specific project* counting for exactly half of the final grade, as seen in CSCE 679, is not a universal standard across all the provided graduate CS courses [Source 1, 3, 4, 6, 7, 8, 9].</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grading policies for graduate courses at Texas A&amp;M University can vary significantly, with different components weighted differently to assess student learning outcomes [Source 1, 3, 4, 7, 8, 9].
+In CSCE 679, the course project, which requires graduate students to implement using the D3.js visualization library, accounts for 50% of the final grade [Source 1].
+Looking at other graduate CS courses in the provided context:
+*   **CSCE 713** also has a single component, "Vulnerabilities PoC" (Proof of Concept), which is an individual assignment requiring students to deliver end-to-end exploits of sample applications, counting for 50% of the grade [Source 3].
+*   **CSCE 648** has projects contributing 36% to the final grade, split across six projects [Source 4].
+*   **CSCE 652** has a final project contributing 30% to the final grade [Source 7].
+*   **CSCE 748** has programming assignments totaling 50% of the grade, but these are split across five assignments, not a single one, and a final project for 20% [Source 9].
+*   **CSCE 629** does not list projects as a grading component, focusing on exams, quizzes, and homework [Source 8].
+Based on the available syllabi, a single, practical, and somewhat tool/technique-specific component accounting for 50% of the final grade is observed in CSCE 679 (D3.js project) and CSCE 713 (Vulnerabilities PoC) [Source 1, 3]. While it is present in more than one course, the provided context is insufficient to determine if this specific grading structure is broadly "common" across all TAMU graduate CS courses.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Based on the provided context, it is not universally common for a single, tool-specific project to count for half of the final grade in TAMU graduate CS courses, though there are instances where a single component holds significant weight.
+For example:
+*   In **CSCE 679**, the course project, which for graduate students must be implemented using the D3.js visualization library, accounts for 50% of the final grade [Source 1].
+*   In **CSCE 713**, the "Vulnerabilities PoC" (Proof of Concept), an individual component requiring students to deliver exploits for vulnerabilities, also accounts for 50% of the grade [Source 3]. This is a single, practical component, though not explicitly tied to a single named tool in the same way D3.js is for CSCE 679.
+*   Other courses show different grading structures:
+    *   **CSCE 648** has quizzes (52 points), projects (36 points, split among six projects), and class participation (12 points) [Source 4].
+    *   **CSCE 652** allocates 60% to homework, 30% to a final project, and 10% to quizzes [Source 7].
+    *   **CSCE 629** bases grades on exams (60%), quizzes and exercises (10%), and homework (30%) [Source 8].
+    *   **CSCE 748** assigns 50% to programming assignments (five assignments), 30% to a midterm exam, and 20% to a final project [Source 9].
+While CSCE 679 explicitly requires a single, tool-specific project for 50% of the grade for graduate students, and CSCE 713 also has a single component worth 50%, this structure is not observed in all other graduate CS courses listed in the context.</t>
+        </is>
+      </c>
     </row>
-    <row r="19" ht="28.8" customHeight="1">
-      <c r="A19" s="2" t="n">
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>When is the midterm for CSCE 629?</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>The midterm exam for CSCE 629 is scheduled for Thursday, February 26th, and will be held in class.</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>CSCE 629</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>54978</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="H19" t="n">
+        <v>54978</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>CSCE 629</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="b">
+      <c r="K19" t="b">
         <v>0</v>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
     </row>
-    <row r="20" ht="115.2" customHeight="1">
-      <c r="A20" s="2" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>What is the required textbook for CSCE 608?</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>The required textbook for CSCE 608 is:
 *   **Title:** Database Systems: The Complete Book
@@ -1395,92 +2917,144 @@
 *   **ISBN:** 978-0-13-187325-4</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>MATERIALS</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>46648</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H20" t="n">
+        <v>46648</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="b">
+      <c r="K20" t="b">
         <v>0</v>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="21" ht="43.2" customHeight="1">
-      <c r="A21" s="2" t="n">
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>What programming language is permitted for CSCE 633?</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>For CSCE 633, the permitted programming language is Python. Your Python code must be executable on CS Unix hosts or other public systems in the department lab.</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="H21" t="n">
+        <v>58706</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="b">
+      <c r="K21" t="b">
         <v>0</v>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="22" ht="158.4" customHeight="1">
-      <c r="A22" s="2" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>What skills are we expected to have after completing CSCE 633?</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Upon completing CSCE 633, students are expected to be able to:
 *   Formalize the fundamental techniques and methods of machine learning, including data processing and model selection.
@@ -1489,47 +3063,97 @@
 *   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H22" t="n">
+        <v>58706</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="b">
+      <c r="K22" t="b">
         <v>0</v>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, Source 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, Source 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
     </row>
-    <row r="23" ht="144" customHeight="1">
-      <c r="A23" s="2" t="n">
+    <row r="23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>What will I be able to do after completing CSCE 669?</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Upon completing CSCE 669, you will be able to:
 *   Master basic theories and techniques in current computational optimization research.
@@ -1538,47 +3162,107 @@
 *   Gain a solid background and preparation for advanced research in computational optimization and related areas.</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>CSCE 669</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>58438</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H23" t="n">
+        <v>58438</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>CSCE 669</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="b">
+      <c r="K23" t="b">
         <v>0</v>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply these theories and techniques to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and related areas [Source 2].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids [Source 1]. The geometric interpretation of these results highlights the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1].
+**Career Relevance:** The course directly prepares students for advanced research in computational optimization, indicating its relevance for academic and R&amp;D careers. The ability to apply theories and techniques to "real-world problems" suggests its utility in industry roles that involve complex problem-solving, algorithm design, and optimization in fields like logistics, data science, machine learning, and operations research [Source 1, 2]. The course project, which involves reading recent published papers and conducting research on current problems, further enhances skills valuable for innovation and problem-solving in professional settings [Source 2].
+The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply these theories and techniques to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and related areas [Source 2].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids [Source 1]. The geometric interpretation of these results highlights the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1].
+**Career Relevance:** The course directly prepares students for advanced research in computational optimization, indicating its relevance for academic and R&amp;D careers. The ability to apply theories and techniques to "real-world problems" suggests its utility in industry roles that involve complex problem-solving, algorithm design, and optimization in fields like logistics, data science, machine learning, and operations research [Source 1, 2]. The course project, which involves reading recent published papers and conducting research on current problems, further enhances skills valuable for innovation and problem-solving in professional settings [Source 2].
+The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, section 600, you will be able to:
+*   Master basic theories and techniques in the current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].
+This course focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, with applications to max flow, matching, and matroids. It also covers the geometric interpretation of these results, highlighting the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1]. The course content, including topics like approximation algorithms, parameterized algorithms, and exact algorithms for NP-hard problems, directly relates to industry applications and career paths in areas requiring advanced problem-solving, algorithm design, and optimization techniques for complex computational challenges [Source 1, 4].</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply these theories and techniques to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and related areas [Source 2].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids [Source 1]. The geometric interpretation of these results highlights the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1].
+**Career Relevance:** The course directly prepares students for advanced research in computational optimization, indicating its relevance for academic and R&amp;D careers. The ability to apply theories and techniques to "real-world problems" suggests its utility in industry roles that involve complex problem-solving, algorithm design, and optimization in fields like logistics, data science, machine learning, and operations research [Source 1, 2]. The course project, which involves reading recent published papers and conducting research on current problems, further enhances skills valuable for innovation and problem-solving in professional settings [Source 2].
+The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="24" ht="144" customHeight="1">
-      <c r="A24" s="2" t="n">
+    <row r="24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>What will students be able to do upon completing CSCE 665</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Upon completing CSCE 665, students will be able to:
 *   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks.
@@ -1587,138 +3271,260 @@
 *   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts.</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>30874</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H24" t="n">
+        <v>30874</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="b">
+      <c r="K24" t="b">
         <v>0</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="25" ht="43.2" customHeight="1">
-      <c r="A25" s="2" t="n">
+    <row r="25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Where can I find all the course information for CSCE 608?</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>All course information for CSCE 608 will be posted in Canvas. You should check your course announcements, course material, and due dates daily within the Canvas Learning Management System.</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>46648</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" t="n">
+        <v>46648</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="b">
+      <c r="K25" t="b">
         <v>0</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas [Source 3]. You should check your course announcements, course material, and due dates daily [Source 3]. The course uses the Canvas Learning Management System, and students submit their homework and projects via Canvas [Source 3].</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="26" ht="144" customHeight="1">
-      <c r="A26" s="2" t="n">
+    <row r="26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Do the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research?</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Yes, according to the CSCE 681 syllabus, preparing reports and discussing research are explicitly stated as learning outcomes for the course.
 The syllabus states: "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles." The course structure, which includes attending lectures and writing reports for each (Section 600) or watching recordings and completing report quizzes (Section 700), is designed to help students achieve these objectives.</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>CSCE 681</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>12644</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="H26" t="n">
+        <v>12644</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>CSCE 681</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="b">
+      <c r="K26" t="b">
         <v>0</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681, which include preparing reports and discussing research works and selected published technical articles, appear attainable based on the course structure and requirements [Source 1].
+Here's why:
+*   **Course Purpose:** The course's explicit purpose is to "expose students to a broad range of current and seminal research topics in computer science and related fields" [Source 1]. This direct exposure is foundational for discussing research.
+*   **Prerequisites:** The course requires graduate classification, indicating students are expected to have a foundational academic background suitable for engaging with research topics [Source 1].
+*   **Required Activities:**
+    *   Students are expected to "attend all the lectures scheduled during the semester" (Section 600) or "watch the recordings of all the lectures" (Section 700) [Source 2, 4].
+    *   For each lecture, students are required to "write a report" [Source 2, 4].
+    *   For Section 600, these reports are structured with specific sections: background, problem statement, proposed solution, results, and critique, which directly guides students in analyzing and reporting on research [Source 2].
+    *   For Section 700, report quizzes consist of multiple-choice/multiple-answer questions related to lecture content, testing comprehension of research [Source 4].
+*   **Grading Policy:** To pass, students must achieve an average score of 80% or higher, ensuring a certain level of mastery in these tasks [Source 2].
+The seminar format, combined with structured report writing and exposure to diverse research topics, directly supports the development of skills needed to prepare reports and discuss research effectively.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
     </row>
-    <row r="27" ht="244.8" customHeight="1">
-      <c r="A27" s="2" t="n">
+    <row r="27">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>What should I know about CSCE 611, especially regarding the topics we'll be covering in the early weeks like OS structures and memory management?</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>CSCE 611, Operating Systems, provides an overview of the general architecture and most important components of modern operating systems. It covers basic operating system concepts and methods of design and construction.
 Regarding the topics you mentioned:
@@ -1727,47 +3533,221 @@
 The syllabus does not specify which topics are covered in the early weeks of the course.</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>50668</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="H27" t="n">
+        <v>50668</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="b">
+      <c r="K27" t="b">
         <v>0</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), "Operating Systems," is a graduate-level course offered in Spring 2026 [Source 2].
+**Course Purpose and Overview:**
+This course provides an overview of the general architecture and most important components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. The course also covers fundamental approaches to virtualization and building distributed systems. A key component is implementing a simple operating system that can boot and run on a bare PC [Source 3].
+**Prerequisites:**
+The prerequisites for CSCE 611 are CSCE 313 and graduate classification [Source 3].
+**Early Week Topics:**
+The course schedule outlines the following topics for the early weeks:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 1].
+*   **Week 2:** System Calls, Interrupts, and Exceptions on the x86 [Source 1].
+*   **Week 3:** Memory management, including Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 1].
+*   **Week 4:** Further memory management topics such as The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 1].
+**Grading Policy:**
+The grading for CSCE 611 is based on the following components:
+*   **Midterm Exam:** 200 points [Source 6]
+*   **Final Exam:** 200 points [Source 6]
+*   **Design and Programming Assignments (Machine Problems):** 400 points [Source 6]
+*   **Daily Quizzes:** 100 points [Source 6]
+*   **Homework Assignments:** 100 points [Source 6]
+The course uses a standard letter grading scale: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 6].</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
     </row>
-    <row r="28" ht="409.5" customHeight="1">
-      <c r="A28" s="2" t="n">
+    <row r="28">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>How should I plan my time for CSCE 670, including the numerous homeworks, quizzes, and the big group project?</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>To effectively plan your time for CSCE 670, consider the following components and their respective deadlines and weights:
 *   **Homeworks (30% total)**: There are five programming assignments in Python (2%, 7%, 7%, 7%, 7%).
@@ -1790,47 +3770,152 @@
 Prioritize these deadlines and allocate study and work time accordingly, especially noting the individual nature of homeworks and the team-based effort required for the group project.</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>46627</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="H28" t="n">
+        <v>46627</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="b">
+      <c r="K28" t="b">
         <v>0</v>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600 (46627), here's a breakdown to help you plan your time effectively:
+**Course Overview:**
+The course runs from January 12, 2026, to May 5, 2026 [Source 5]. It covers topics such as Boolean Retrieval, TF-IDF, Link Analysis, Learning to Rank, Recommender Systems, Neural Ranking, Transformers, BERT-Based Ranking, and Large Language Models [Source 3].
+**Grading Components and Time Planning:**
+1.  **Homeworks (30% of final grade):**
+    *   There are five programming assignments, all in Python [Source 2].
+    *   **Weight Distribution:** Homework 0 (2%), Homework 1 (7%), Homework 2 (7%), Homework 3 (7%), Homework 4 (7%) [Source 2].
+    *   **Due Dates:**
+        *   Homework 0: January 26 [Source 1]
+        *   Homework 1: February 9 [Source 1]
+        *   Homework 2: March 2 [Source 1]
+        *   Homework 3: March 30 [Source 1]
+        *   Homework 4: April 20 [Source 1]
+    *   **Policy:** Homeworks are individual assignments, but discussing approaches is encouraged (no code sharing). You must acknowledge all help [Source 2, 4]. AI-generated code is permitted if properly documented with prompt and significant parts of the response [Source 1].
+    *   **Late Work:** You have five total late days, each an indivisible 24-hour unit. Once used, late assignments receive a grade of 0 [Source 3, 4].
+    *   **Planning Tip:** Given the significant weight and individual nature, start early on each homework. The first assignment is introductory to Jupyter Notebook and Python operations [Source 2].
+2.  **Quizzes (20% of final grade):**
+    *   There will be four brief in-class quizzes [Source 2].
+    *   **Weight Distribution:** Each quiz is 5% of your final grade [Source 2].
+    *   **Dates:**
+        *   Quiz 1: February 6 [Source 1]
+        *   Quiz 2: February 27 [Source 1]
+        *   Quiz 3: March 25 [Source 1]
+        *   Quiz 4: April 15 [Source 1]
+    *   **Planning Tip:** These are in-class, so consistent engagement with lecture material and weekly topics is crucial to perform well.
+3.  **Group Project (20% of final grade):**
+    *   Students will work in teams of 3 or 4 on a mini-research project [Source 2].
+    *   **Key Deadlines:**
+        *   Proposal: Due March 7 [Source 1]
+        *   Presentation: In classes on April 20, April 22, April 24, and April 27 [Source 1]
+        *   Report: Due May 2 [Source 1]
+    *   **Planning Tip:** This project spans a significant portion of the semester. Begin forming groups and brainstorming ideas early. The proposal is due in early March, and presentations/reports are at the very end of the semester, requiring sustained effort.
+4.  **Final Exam (30% of final grade):**
+    *   A comprehensive final exam will be held on May 4, from 3:30 PM to 5:30 PM in HRBB 113 [Source 2].
+    *   **Planning Tip:** This is the single largest component of your grade. Allocate sufficient time for review, especially considering the breadth of topics covered throughout the semester.
+**Overall Planning Advice:**
+*   **Stay on top of weekly material:** Quizzes are in-class, and homeworks build on concepts.
+*   **Utilize late days wisely:** You have a limited number for homeworks [Source 3].
+*   **Collaborate responsibly:** Discuss concepts for homeworks, but ensure your submitted code is your own [Source 2, 4].
+*   **Start the group project early:** The proposal is due mid-semester, and the final deliverables are at the very end, requiring consistent team effort [Source 1].</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
     </row>
-    <row r="29" ht="273.6" customHeight="1">
-      <c r="A29" s="2" t="n">
+    <row r="29">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>What should I know about CSCE 632, especially regarding how final grades are determined?</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>For CSCE 632, your final grade is determined by the following weighted components:
 *   **Pre-Class Engagement:** 5% (Calculated based on your completion rate, with 15% capped at 100% allowing for some missed engagements without penalty.)
@@ -1841,47 +3926,199 @@
 You have one week from when a grade is published to challenge it. The instructors also reserve the right to audit grades, which could result in scores being increased or decreased.</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>CSCE 632</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>54784</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="H29" t="n">
+        <v>54784</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>CSCE 632</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="b">
+      <c r="K29" t="b">
         <v>0</v>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>For CSCE 632, Section 600 (54784), Accessible Computing, here's an overview of the course and how final grades are determined:
+**Course Overview**
+*   **Course ID &amp; Section**: CSCE 632, Section 600 (54784) [Source 5]
+*   **Term**: Spring 2026 [Source 5]
+*   **Meeting Times**: Tuesdays and Thursdays, 12:45 PM - 2:00 PM, in ZACH 350 [Source 5]
+*   **Credit Hours**: 3 [Source 5]
+*   **Catalog Description**: This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, universal design, and its role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. It also covers the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+*   **Prerequisites**: Graduate classification [Source 5].
+**Grading Breakdown**
+The final grade for CSCE 632 is determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 1]
+    *   Includes course readings, quizzes, polls, and surveys. Credit is given for submissions prior to class. A completion rate is calculated, capped at 100% with a 15% allowance for missed engagements [Source 1].
+*   **Group Class Activities**: 10% [Source 1]
+    *   Students work in groups of at least 3. Credit is given for attending class and providing what is required for the activity. A completion rate is calculated, capped at 100% with a 15% allowance for missed activities [Source 1, 2].
+*   **Assignments**: 25% [Source 2]
+    *   Completed individually or with others. Some assignments are peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 2].
+*   **Quick Applications**: 20% [Source 2]
+    *   Timed assignments designed for quick application of class materials, typically taking 15-20 minutes but with at least 45 minutes provided [Source 2].
+*   **Literature Review**: 10% [Source 3]
+    *   Students compile a literature review on an accessibility topic, comprising at least 10 related peer-reviewed conference or journal papers. It must clearly lay out themes and gaps, supported by evidence, and include an annotated bibliography [Source 3].
+*   **Current Research Presentation**: 5% [Source 3]
+    *   A summary of HCI research based on the student's Literature Review. This is peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 3].
+*   **Team Project**: 25% [Source 3]
+    *   Students work in groups to address a barrier for people with disabilities that lacks an acceptable solution. The team's barrier must be instructor-approved. Teams design and implement a technology-based solution for equitable interactions. Parts of this are peer-graded, with scores based on peer evaluations and self-evaluation. The instructor may apply a multiplier based on team peer evaluations, which can be modified at their discretion [Source 3, 4].
+**Grading Scale**
+Grades are rounded to the nearest whole number and assigned as follows [Source 4]:
+*   **A**: ≥ 90 (Excellent)
+*   **B**: &lt; 90 and ≥ 80 (Good)
+*   **C**: &lt; 80 and ≥ 70 (Satisfactory)
+*   **D**: &lt; 70 and ≥ 60 (Passing)
+*   **F**: &lt; 60 (Failing)
+**Important Grading Policies**
+*   **Grade Auditing**: The instructor reserves the right to audit grades for any assignments, which may result in increasing or decreasing scores, even for already released grades [Source 1, 6].
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 4, 7].
+*   **Challenging Grades**: Any challenge to a grade must be made within one week of its publication [Source 1, 6].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Each student/team has a limited number of "late days" they may use by request. Work submitted as makeup for an excused absence is exempt from the late work policy [Source 7].</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>For CSCE 632, Section 600 (54784), Accessible Computing, here's an overview of the course and how final grades are determined:
+**Course Overview**
+*   **Course ID &amp; Section**: CSCE 632, Section 600 (54784) [Source 5]
+*   **Term**: Spring 2026 [Source 5]
+*   **Meeting Times**: Tuesdays and Thursdays, 12:45 PM - 2:00 PM, in ZACH 350 [Source 5]
+*   **Credit Hours**: 3 [Source 5]
+*   **Catalog Description**: This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, universal design, and its role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. It also covers the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+*   **Prerequisites**: Graduate classification [Source 5].
+**Grading Breakdown**
+The final grade for CSCE 632 is determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 1]
+    *   Includes course readings, quizzes, polls, and surveys. Credit is given for submissions prior to class. A completion rate is calculated, capped at 100% with a 15% allowance for missed engagements [Source 1].
+*   **Group Class Activities**: 10% [Source 1]
+    *   Students work in groups of at least 3. Credit is given for attending class and providing what is required for the activity. A completion rate is calculated, capped at 100% with a 15% allowance for missed activities [Source 1, 2].
+*   **Assignments**: 25% [Source 2]
+    *   Completed individually or with others. Some assignments are peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 2].
+*   **Quick Applications**: 20% [Source 2]
+    *   Timed assignments designed for quick application of class materials, typically taking 15-20 minutes but with at least 45 minutes provided [Source 2].
+*   **Literature Review**: 10% [Source 3]
+    *   Students compile a literature review on an accessibility topic, comprising at least 10 related peer-reviewed conference or journal papers. It must clearly lay out themes and gaps, supported by evidence, and include an annotated bibliography [Source 3].
+*   **Current Research Presentation**: 5% [Source 3]
+    *   A summary of HCI research based on the student's Literature Review. This is peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 3].
+*   **Team Project**: 25% [Source 3]
+    *   Students work in groups to address a barrier for people with disabilities that lacks an acceptable solution. The team's barrier must be instructor-approved. Teams design and implement a technology-based solution for equitable interactions. Parts of this are peer-graded, with scores based on peer evaluations and self-evaluation. The instructor may apply a multiplier based on team peer evaluations, which can be modified at their discretion [Source 3, 4].
+**Grading Scale**
+Grades are rounded to the nearest whole number and assigned as follows [Source 4]:
+*   **A**: ≥ 90 (Excellent)
+*   **B**: &lt; 90 and ≥ 80 (Good)
+*   **C**: &lt; 80 and ≥ 70 (Satisfactory)
+*   **D**: &lt; 70 and ≥ 60 (Passing)
+*   **F**: &lt; 60 (Failing)
+**Important Grading Policies**
+*   **Grade Auditing**: The instructor reserves the right to audit grades for any assignments, which may result in increasing or decreasing scores, even for already released grades [Source 1, 6].
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 4, 7].
+*   **Challenging Grades**: Any challenge to a grade must be made within one week of its publication [Source 1, 6].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Each student/team has a limited number of "late days" they may use by request. Work submitted as makeup for an excused absence is exempt from the late work policy [Source 7].</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSCE 632, Section 600 (54784), is titled "Accessible Computing" and is offered in Spring 2026 in College Station [Source 5].
+**Course Purpose:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and covers universal design's role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 5].
+**Prerequisites:**
+Graduate classification is required [Source 5].
+**Final Grade Determination:**
+Final grades for CSCE 632 are determined by the following components and weights:
+| Component                       | Weight (CSCE 632) | Details                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSCE 632, Section 600 (54784), is titled "Accessible Computing" and is offered in Spring 2026 in College Station [Source 5].
+**Course Purpose:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and covers universal design's role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 5].
+**Prerequisites:**
+Graduate classification is required [Source 5].
+**Final Grade Determination:**
+Final grades for CSCE 632 are determined by the following components and weights:
+| Component                       | Weight (CSCE 632) | Details                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSCE 632, Section 600 (54784), is titled "Accessible Computing" and is offered in Spring 2026 in College Station [Source 5].
+**Course Purpose:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and covers universal design's role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 5].
+**Prerequisites:**
+Graduate classification is required [Source 5].
+**Final Grade Determination:**
+Final grades for CSCE 632 are determined by the following components and weights:
+| Component                       | Weight (CSCE 632) | Details                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>For CSCE 632, Section 600 (54784), Accessible Computing, here's an overview of the course and how final grades are determined:
+**Course Overview**
+*   **Course ID &amp; Section**: CSCE 632, Section 600 (54784) [Source 5]
+*   **Term**: Spring 2026 [Source 5]
+*   **Meeting Times**: Tuesdays and Thursdays, 12:45 PM - 2:00 PM, in ZACH 350 [Source 5]
+*   **Credit Hours**: 3 [Source 5]
+*   **Catalog Description**: This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, universal design, and its role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. It also covers the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+*   **Prerequisites**: Graduate classification [Source 5].
+**Grading Breakdown**
+The final grade for CSCE 632 is determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 1]
+    *   Includes course readings, quizzes, polls, and surveys. Credit is given for submissions prior to class. A completion rate is calculated, capped at 100% with a 15% allowance for missed engagements [Source 1].
+*   **Group Class Activities**: 10% [Source 1]
+    *   Students work in groups of at least 3. Credit is given for attending class and providing what is required for the activity. A completion rate is calculated, capped at 100% with a 15% allowance for missed activities [Source 1, 2].
+*   **Assignments**: 25% [Source 2]
+    *   Completed individually or with others. Some assignments are peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 2].
+*   **Quick Applications**: 20% [Source 2]
+    *   Timed assignments designed for quick application of class materials, typically taking 15-20 minutes but with at least 45 minutes provided [Source 2].
+*   **Literature Review**: 10% [Source 3]
+    *   Students compile a literature review on an accessibility topic, comprising at least 10 related peer-reviewed conference or journal papers. It must clearly lay out themes and gaps, supported by evidence, and include an annotated bibliography [Source 3].
+*   **Current Research Presentation**: 5% [Source 3]
+    *   A summary of HCI research based on the student's Literature Review. This is peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 3].
+*   **Team Project**: 25% [Source 3]
+    *   Students work in groups to address a barrier for people with disabilities that lacks an acceptable solution. The team's barrier must be instructor-approved. Teams design and implement a technology-based solution for equitable interactions. Parts of this are peer-graded, with scores based on peer evaluations and self-evaluation. The instructor may apply a multiplier based on team peer evaluations, which can be modified at their discretion [Source 3, 4].
+**Grading Scale**
+Grades are rounded to the nearest whole number and assigned as follows [Source 4]:
+*   **A**: ≥ 90 (Excellent)
+*   **B**: &lt; 90 and ≥ 80 (Good)
+*   **C**: &lt; 80 and ≥ 70 (Satisfactory)
+*   **D**: &lt; 70 and ≥ 60 (Passing)
+*   **F**: &lt; 60 (Failing)
+**Important Grading Policies**
+*   **Grade Auditing**: The instructor reserves the right to audit grades for any assignments, which may result in increasing or decreasing scores, even for already released grades [Source 1, 6].
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 4, 7].
+*   **Challenging Grades**: Any challenge to a grade must be made within one week of its publication [Source 1, 6].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Each student/team has a limited number of "late days" they may use by request. Work submitted as makeup for an excused absence is exempt from the late work policy [Source 7].</t>
+        </is>
+      </c>
     </row>
-    <row r="30" ht="201.6" customHeight="1">
-      <c r="A30" s="2" t="n">
+    <row r="30">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>What should I know about CSCE 669, particularly about how performance on homework, projects, and the exam impacts our overall grade?</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>In CSCE 669, your overall grade is determined by three main components:
 *   **Homework:** There are 3 homework assignments, which collectively account for 30% of your final grade (10% each). These are designed to test your understanding of course lectures.
@@ -1890,47 +4127,131 @@
 To achieve a specific letter grade, the following scale is used: A = 90-100%, B = 70-89%, C = 60-70%, F = 0-59%.</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>CSCE 669</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>58438</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="H30" t="n">
+        <v>58438</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>CSCE 669</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="b">
+      <c r="K30" t="b">
         <v>0</v>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>For CSCE 669, Section 600 (58438), the grading policy is as follows [Source 1, 2, 4]:
+*   **Homework:** 3 assignments, contributing 30% to the final grade (10% each).
+*   **Course Project:** 35% of the final grade.
+*   **Final Exam:** Comprehensive, contributing 35% to the final grade.
+The grading scale is [Source 1, 2]:
+*   A = 90-100%
+*   B = 70-89%
+*   C = 60-70%
+*   F = 0-59%</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="31" ht="259.2" customHeight="1">
-      <c r="A31" s="2" t="n">
+    <row r="31">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>What should I know about CSCE 670, including what types of data structures and algorithms are covered?</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>CSCE 670 is titled "Information Storage and Retrieval." This course focuses on the representation, storage, and access to very large multimedia document collections, as well as techniques for designing and evaluating complete retrieval systems.
 Regarding data structures and algorithms, the course covers:
@@ -1940,182 +4261,506 @@
 *   The course schedule also lists algorithms and models such as Boolean Retrieval, TF-IDF, Vector Space Model, BM25, word2vec, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, and Large Language Models.</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>46627</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="H31" t="n">
+        <v>46627</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="b">
+      <c r="K31" t="b">
         <v>0</v>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, titled "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course focuses on the representation, storage, and access of very large multimedia document collections. It covers fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems [Source 1].
+Key topics include:
+*   **Web Search**: Text indexing, retrieval models (e.g., Boolean Retrieval, TF-IDF, Vector Space Model, BM25), evaluation, Web crawling, link-based algorithms (e.g., PageRank), and learning to rank [Source 2, 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, evaluation, and implicit recommendation [Source 2, 3].
+*   **Advanced Topics**: Word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, for ranking and recommendation) [Source 2].
+*   **Algorithms**: The course covers algorithms for indexing, compressing, and querying very large collections [Source 1].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have approval from the instructor, and be of graduate classification [Source 1, 3].
+**Grading:**
+The course includes homework assignments and quizzes. Students are allotted five late days for assignments; after these are used, late submissions will receive a grade of 0 [Source 2]. The specific grading breakdown (e.g., percentage weight of assignments, quizzes, projects) is not provided in the context.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
     </row>
-    <row r="32" ht="86.40000000000001" customHeight="1">
-      <c r="A32" s="2" t="n">
+    <row r="32">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>What should I take after CSCE 612?</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>CSCE 612, "Applied Networks and Distributed Processing," focuses on network design, protocol analysis, network architecture, and engineering principles, including programming network applications and decentralized frameworks. While the syllabus does not specify courses to take after CSCE 612, I can help you search for other courses that might complement these topics.</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>CSCE 612</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>42640</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="H32" t="n">
+        <v>42640</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>CSCE 612</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="b">
+      <c r="K32" t="b">
         <v>0</v>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CSCE 612, "Applied Networks and Distributed Processing," focuses on fundamentals of network design, protocol analysis, and engineering issues, including applying layered architecture to real networks [Source 1].
+Based on the provided syllabi, a potential course to consider after CSCE 612, especially if you are interested in specializing in network security, is **CSCE 665: Advanced Networking and Security** [Source 6].
+CSCE 665 builds upon networking concepts by introducing "security aspects of various network protocols" and involves "investigation and tool development using 'live' machines and networks" [Source 6]. Its topics include:
+*   Basic network &amp; system security (e.g., malware, botnet, intrusion detection) [Source 7]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge) [Source 7]
+*   Mobile &amp; IoT security [Source 7]
+*   Web and Web3 security [Source 7]
+*   AI/LLM security [Source 7]
+Another related course in the security domain is **CSCE 713: Introduction to Security**, which covers topics such as Web Security, Network Security, Mobile Apps Security, and Application Security [Source 8].
+I don't have enough data to definitively state a direct "next course" as the context does not explicitly outline course progression paths beyond prerequisites. However, CSCE 665 appears to be a logical advanced step for students interested in networking with a security focus.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing provides a foundation in network design, protocol analysis, network architecture, and principles of network engineering, including the analysis of network security and the development of network applications using operating-system sockets APIs [Source 1, 2].
+For academic progression, a logical next step would be a course that builds upon these networking fundamentals, especially in specialized areas like network security, which is introduced in CSCE 612.
+Based on the provided context, **CSCE 665: Advanced Networking and Security** is a suitable course to take after CSCE 612.
+*   **Principle of Progression:** CSCE 665 directly expands on the networking knowledge gained in CSCE 612 by focusing on "security aspects of various network protocols" and "investigation and tool development using 'live' machines and networks" [Source 6]. It aims to provide a deep understanding of computer and network security, which aligns with and builds upon the "analyze performance and security of networks" learning outcome of CSCE 612 [Source 2, 7].
+*   **Content Alignment:** CSCE 665 covers advanced topics such as basic network &amp; system security (e.g., malware, intrusion detection), security in software-defined environments, mobile &amp; IoT security, Web and Web3 security, and AI/LLM security [Source 7]. These topics require a solid understanding of network protocols and architecture, which is provided by CSCE 612.
+*   **Prerequisites:** CSCE 665 requires graduate classification and approval of the instructor [Source 6, 7].
+While **CSCE 713: Advanced Topics in Security** also covers various security topics, including network security [Source 8, 11], the provided context does not offer a full catalog description or learning outcomes for CSCE 713, making it less clear how directly it builds on CSCE 612 compared to the detailed description of CSCE 665.
+Therefore, to continue your academic progression in networking with a focus on security, CSCE 665 is a well-aligned choice after completing CSCE 612.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational knowledge to explore more advanced or specialized topics. CSCE 612, "Applied Networks and Distributed Processing," provides fundamentals in network design, protocol analysis, and principles of layered architecture, covering topics such as Internet structure, application, transport, network, and data-link layers [Source 1, 3].
+A logical next step in your academic progression could be a course that delves deeper into advanced aspects of networking or applies networking knowledge to specialized fields like security.
+Based on the provided context, **CSCE 665: Advanced Networking and Security** appears to be a relevant follow-up course. Its catalog description indicates it focuses on "Security aspects of various network protocols" and "modern topics in computer and network security" [Source 6]. This course would allow you to apply and expand your understanding of network protocols from CSCE 612 by exploring their security implications and advanced techniques, including basic network &amp; system security, security in a software-defined world, mobile &amp; IoT security, and Web and Web3 security [Source 6, 7].
+Another course that includes network security topics is **CSCE 713: Advanced Topics in Security**, which lists "Network Security" among its subtopics [Source 8].
+While these courses align thematically with the content of CSCE 612, the provided context does not explicitly list CSCE 612 as a prerequisite for either CSCE 665 or CSCE 713. For CSCE 665, the prerequisites are "Graduate classification and approval of instructor" [Source 6, 7]. The prerequisites for CSCE 713 are not available in the provided context. Therefore, you would need to confirm specific prerequisites or seek instructor approval for enrollment in these courses.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>While the provided context does not explicitly state which courses *require* CSCE 612 as a prerequisite, we can identify courses that logically build upon the foundational knowledge gained in CSCE 612, "Applied Networks and Distributed Processing" [Source 1].
+CSCE 612 covers fundamentals of network design, protocol analysis, network architecture, and principles of network engineering, including the analysis of network performance and security [Source 1, 2]. Therefore, courses that delve deeper into network security or advanced networking concepts would be a logical next step.
+Based on the available syllabi, **CSCE 665: Advanced Networking and Security** appears to be a suitable follow-up course.
+*   **CSCE 665** focuses on "Security aspects of various network protocols" and "modern topics in computer and network security" [Source 6]. Its topics include "Basic network &amp; system security," "Security in a software-defined world," and "Web and Web3 security" [Source 7]. This directly expands on the "security of networks" aspect introduced in CSCE 612 [Source 2]. The prerequisite for CSCE 665 is graduate classification and instructor approval [Source 6, 7].
+Another relevant course could be **CSCE 713: Advanced Topics in Security**, which covers a broader range of security topics, including "Network Security" [Source 9]. Its learning outcomes include performing penetration testing and analyzing software for defects [Source 11].
+**Academic Progression:**
+Taking a course like CSCE 665 or CSCE 713 after CSCE 612 would allow you to specialize further in network security, building upon the foundational understanding of network protocols and architecture provided by CSCE 612. This progression would be beneficial for students interested in careers or research in cybersecurity, network defense, or secure system design.
+I cannot find information on other courses that might directly follow CSCE 612 in the provided context.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>After completing CSCE 612, which focuses on applied networks and distributed processing, including network design, protocol analysis, and the security of networks [Source 1, 2], a logical next step for further specialization in networking and security would be **CSCE 665: Advanced Networking and Security**.
+**Why CSCE 665 is a suitable progression:**
+*   **Direct Relevance:** CSCE 612's learning outcomes include analyzing the performance and security of networks [Source 2]. CSCE 665 directly builds on this by focusing on "security aspects of various network protocols" and "investigation and tool development using 'live' machines and networks" [Source 6].
+*   **Advanced Topics:** CSCE 665 covers advanced topics such as basic network &amp; system security, security in a software-defined world, mobile &amp; IoT security, Web and Web3 security, and AI/LLM security [Source 7]. This provides a deeper dive into the security dimension of networking.
+*   **Skill Development:** In CSCE 665, you would learn to analyze complex trade-offs in securing distributed systems and networks, synthesize security principles for robust defenses, critique state-of-the-art security literature, and demonstrate practical offensive and/or defensive techniques [Source 7]. These skills complement the foundational network application development and protocol analysis from CSCE 612.
+This progression would allow you to build upon your understanding of network fundamentals and application development from CSCE 612 to specialize in the advanced security challenges and solutions within modern network environments.</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational knowledge acquired in prerequisite or introductory courses by taking more advanced or specialized courses in related fields.
+Based on the provided context, CSCE 612, "Applied Networks and Distributed Processing," provides foundational knowledge in network design, protocol analysis, and the analysis of network security [Source 1, 2]. A logical next step would be a course that delves deeper into advanced aspects of networking or specializes in a related field like network security.
+CSCE 665, "Advanced Networking and Security," appears to be a suitable follow-up course. Its catalog description indicates it covers "security aspects of various network protocols" and "modern topics in computer and network security" [Source 6, 7]. This directly builds upon the networking fundamentals and the "analysis of performance and security of networks" learned in CSCE 612 [Source 2].
+While the prerequisites for CSCE 665 are "Graduate classification and approval of instructor" [Source 6, 7] rather than CSCE 612 specifically, its content aligns well as a subsequent course for students interested in specializing in networking and security.
+The context does not explicitly list CSCE 612 as a prerequisite for any other course, nor does it provide a recommended course sequence for academic planning beyond the individual course descriptions.</t>
+        </is>
+      </c>
     </row>
-    <row r="33" ht="100.8" customHeight="1">
-      <c r="A33" s="2" t="n">
+    <row r="33">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>What other courses at TAMU would go well with CSCE 670, especially for someone interested in web search or recommender systems?</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>CSCE 670, Information Storage and Retrieval, focuses on the fundamental data structures and algorithms for web search and recommender systems, covering topics such as text indexing, PageRank, collaborative filtering, and large language models. The provided syllabus does not list specific complementary courses. However, I can help you search the university course catalog for other courses that might align with your interests in these areas.</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>LEARNING_OUTCOMES</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>46627</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="H33" t="n">
+        <v>46627</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="b">
+      <c r="K33" t="b">
         <v>0</v>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>To understand how courses complement each other, it's helpful to consider the **academic progression principle**. This principle suggests that courses can build upon foundational knowledge, offer deeper dives into specialized topics, or provide complementary skills that enhance a student's overall understanding and capability in a particular domain.
+For someone interested in web search or recommender systems, CSCE 670: Information Storage and Retrieval provides a strong foundation. This course covers core concepts like text indexing, retrieval models, evaluation, web crawling, link-based algorithms (e.g., PageRank), learning to rank, collaborative filtering, matrix factorization, and neural models for retrieval and recommendation [Source 2]. It also touches on Large Language Models (LLMs) in the context of search engines, ranking, and recommendation [Source 3].
+Based on the provided context, here are other courses that would complement CSCE 670 for your interests:
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** This course offers a broad overview of data mining, integrating concepts from machine learning and statistics. It covers exploratory data analysis, pattern mining, clustering, and classification [Source 11]. These techniques are highly relevant for extracting insights from large datasets, which is crucial for improving search relevance, understanding user behavior for recommender systems, and developing more sophisticated retrieval algorithms. It also mentions "graph mining" and "large-scale ML" [Source 6], which can be applied to web graphs and user interaction networks.
+    *   **Planning Dimension:** CSCE 676 would deepen your understanding of how to process and analyze the massive datasets that web search and recommender systems operate on, providing practical skills in data-driven decision-making.
+*   **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 explicitly mentions "learning to rank" and "neural models of retrieval and recommendation" [Source 2], and its schedule includes topics like "Learning to Rank," "Neural Ranking," "Transformer; BERT-Based Ranking," and "Neural Collaborative Filtering" [Source 3]. CSCE 633 focuses on the fundamental techniques and methods of machine learning [Source 10], which are the underlying principles for many advanced search and recommendation algorithms.
+    *   **Planning Dimension:** A strong background in machine learning from CSCE 633 would enable you to design, implement, and evaluate more advanced and intelligent search and recommender systems, moving beyond basic algorithms to state-of-the-art approaches.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it complements CSCE 670:** CSCE 670 deals with "Information Storage and Retrieval" of "very large multimedia document collections" [Source 1] and covers topics like "Boolean Retrieval," "TF-IDF," and "Vector Space Model" [Source 3], which are foundational to text processing. CSCE 638 focuses on NLP fundamentals, including language models, automatic syntactic processing, semantic understanding, and applications like information extraction and text summarization [Source 9].
+    *   **Planning Dimension:** For web search, understanding natural language is paramount for query understanding, document indexing, and relevance ranking. For recommender systems, NLP can be used to analyze item descriptions, user reviews, and content-based recommendations. CSCE 638 would provide the specialized knowledge to handle the textual data inherent in these systems effectively.
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** While CSCE 670 covers the application of neural models and ranking [Source 3], CSCE 726 focuses on the "classic deterministic optimization and modern large-scale stochastic optimization algorithms for solving ML/AI problems" [Source 8]. Many advanced search and recommender systems, especially those using machine learning and deep learning, rely heavily on optimization techniques to train their models.
+    *   **Planning Dimension:** This course would provide a deeper theoretical and practical understanding of how to efficiently train and tune the complex models used in modern web search and recommender systems, allowing you to improve their performance and scalability.
+These courses offer different but complementary perspectives and skill sets that would significantly enhance your expertise in web search and recommender systems beyond the scope of CSCE 670.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>For students interested in web search or recommender systems, selecting complementary courses involves identifying those that either provide foundational knowledge in related areas or delve deeper into specific techniques and models used in these fields. This approach ensures a well-rounded academic progression and a deeper understanding of the underlying principles.
+Based on the provided context, the following courses would go well with CSCE 670 (Information Storage and Retrieval) for someone interested in web search or recommender systems:
+1.  **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it complements CSCE 670**: CSCE 670 covers topics like `word2vec`, `Neural Ranking`, `Transformer`, `BERT-Based Ranking`, `Neural Collaborative Filtering`, `Sequential Recommendation`, and `Large Language Models` (basics, with search engines, for ranking and recommendation) [Source 3]. CSCE 638 focuses on `NLP fundamentals`, `language models`, `automatic syntactic processing`, `semantic understanding`, and specifically includes `Word Representations`, `Language Modeling`, `Transformers`, `Contextualized Representations`, `Pre-Training`, and `Large Language Models` in its schedule [Source 6, 11]. This direct overlap in advanced neural and language model techniques makes CSCE 638 an excellent companion for understanding the linguistic and semantic aspects crucial for modern search and recommendation.
+    *   **Planning Dimension**: Taking CSCE 638 would provide a deeper theoretical and practical understanding of the Large Language Models and neural techniques introduced in CSCE 670, enhancing your ability to design and implement advanced systems.
+2.  **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670**: CSCE 670 deals with `information storage and retrieval` for `very large multimedia document collections` and `techniques to design and evaluate complete retrieval systems` [Source 1]. CSCE 676 provides a `broad overview of data mining`, integrating `machine learning and statistics`, covering `exploratory data analysis`, `pattern mining`, `clustering`, and `classification`, with applications to `scientific and online data` [Source 12]. The course schedule for CSCE 676 includes `Frequent Itemset Mining`, `Graph Mining`, `Large-Scale ML`, `Clustering`, `Text Mining`, and `Data Mining and Distributed Computing` [Source 8]. Both courses also list "Mining of Massive Datasets" as a resource [Source 2, 4, 9]. These data mining techniques are fundamental for processing, analyzing, and extracting insights from the massive datasets that underpin web search and recommender systems.
+    *   **Planning Dimension**: CSCE 676 would provide a strong foundation in the data-centric methodologies necessary for building robust and scalable information retrieval and recommendation platforms, complementing the system-specific focus of CSCE 670.
+3.  **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670**: While not explicitly detailed in the context as a direct complement, CSCE 633 covers the `study of self-modifying computer systems that can acquire new knowledge and improve their own performance`, surveying `machine learning techniques` [Source 10]. CSCE 670 explicitly mentions `Learning to Rank` and `Neural Ranking` [Source 3], and CSCE 676 integrates `related concepts from machine learning` [Source 12]. A strong foundation in machine learning is crucial for understanding and developing the advanced algorithms used in modern web search (e.g., ranking algorithms) and recommender systems (e.g., collaborative filtering, matrix factorization, neural models).
+    *   **Planning Dimension**: Taking CSCE 633 would provide the essential theoretical and practical background in machine learning, which is a core principle underlying many of the advanced techniques discussed and applied in CSCE 670. This would enable a deeper understanding and more effective application of these methods.
+These courses offer a comprehensive academic progression, building on the concepts of information retrieval and recommender systems by providing deeper insights into natural language processing, data mining, and foundational machine learning principles.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>For someone interested in web search or recommender systems, complementary courses would typically build upon the foundational concepts of information retrieval and introduce advanced techniques in data analysis, machine learning, and optimization, which are crucial for developing sophisticated systems.
+Based on the provided context, the following courses would go well with CSCE 670:
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Academic Dimension:** This course provides a "broad overview of data mining, integrating related concepts from machine learning and statistics" [Source 7]. It covers topics like "data preparation, normalization, dimensionality reduction, text mining" [Source 8], "Frequent Itemset Mining, Graph Mining, Large-Scale ML, Clustering, Text Mining, Data Mining and Distributed Computing" [Source 6]. These topics are highly relevant for processing and analyzing the massive datasets involved in web search and recommender systems. Notably, both CSCE 670 and CSCE 676 list "Mining of Massive Datasets" as a resource, indicating a shared domain of interest [Source 2, 4, 8].
+*   **CSCE 633: Machine Learning**
+    *   **Academic Dimension:** CSCE 670 delves into advanced topics such as "Learning to Rank," "Neural Ranking," "Transformer; BERT-Based Ranking," "Neural Collaborative Filtering," and "Large Language Models for Ranking and Recommendation" [Source 3]. A strong foundation in machine learning, as provided by CSCE 633, which surveys "machine learning techniques, which include induction from examples, conceptual clustering, explanation-based learning, exemplar learning and analogy, discovery and genetic algorithms" [Source 10], would be highly beneficial for understanding the underlying principles of these advanced techniques.
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   **Academic Dimension:** Given CSCE 670's coverage of "Neural Ranking," "Transformer; BERT-Based Ranking," "Neural Collaborative Filtering," and "Large Language Models" [Source 3], which rely heavily on complex machine learning models, CSCE 726 offers a deeper dive into the "fundamental optimization algorithms and their analysis for solving machine learning problems" [Source 11]. This includes "deterministic and stochastic gradient-based algorithms; adaptive gradient-based methods; momentum-based methods; convergence analysis of selected algorithms" [Source 11]. Understanding these optimization techniques is critical for effectively designing and training the large-scale models used in modern search and recommendation systems. CSCE 633 is a prerequisite for CSCE 726, highlighting the progression of knowledge [Source 11].</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>For someone interested in web search or recommender systems, selecting complementary courses can significantly deepen your understanding and practical skills by providing foundational knowledge or advanced techniques that are directly applicable.
+CSCE 670: Information Storage and Retrieval focuses on the fundamental data structures and algorithms for information storage and retrieval, including techniques for designing and evaluating retrieval systems, indexing, compressing, and querying large collections. It specifically covers web search, recommender systems (collaborative filtering, matrix factorization), neural models, and the application of Large Language Models (LLMs) to search and recommendation [Source 1, Source 2, Source 3].
+To complement CSCE 670, especially with an interest in web search or recommender systems, the following courses would be beneficial:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Relevance:** CSCE 670's schedule includes topics like "Large Language Models with Search Engines" and "Large Language Models for Ranking and Recommendation" [Source 3]. CSCE 638 provides a deep dive into NLP fundamentals, including language models, transformers, contextualized representations, pre-training, and Large Language Models (LLMs) [Source 9, Source 11]. This foundational knowledge is crucial for understanding and developing modern search and recommendation systems that heavily rely on text understanding and generation.
+    *   **Planning Dimension:** Taking CSCE 638 would provide the theoretical and practical background in NLP necessary to effectively work with the advanced LLM applications discussed in CSCE 670.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Relevance:** This course covers a broad overview of data mining, integrating concepts from machine learning and statistics, including exploratory data analysis, pattern mining, clustering, classification, and applications to scientific and online data [Source 8]. Specific topics like Text Mining, Graph Mining, and Large-Scale ML [Source 7] are highly relevant to processing and analyzing the vast datasets inherent in web search and recommender systems.
+    *   **Planning Dimension:** CSCE 676 would equip you with a broader toolkit for handling and extracting insights from large datasets, which is essential for both building and evaluating search and recommendation systems.
+*   **CSCE 633: Machine Learning**
+    *   **Relevance:** Machine learning is the study of self-modifying computer systems that can acquire new knowledge and improve their own performance [Source 6]. Many of the advanced techniques used in web search and recommender systems, such as learning to rank, collaborative filtering, and neural models, are rooted in machine learning principles. CSCE 633 provides a survey of these fundamental techniques [Source 6].
+    *   **Planning Dimension:** As a foundational course, CSCE 633 would provide the core machine learning knowledge necessary to understand the algorithms and models used in CSCE 670 and to develop more sophisticated search and recommendation solutions.
+These courses would provide a comprehensive academic progression, moving from foundational machine learning and data analysis (CSCE 633, CSCE 676) to specialized areas like natural language processing (CSCE 638), which directly inform and enhance the application-focused content of CSCE 670 in web search and recommender systems.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>To effectively plan your academic progression and deepen your understanding in areas like web search and recommender systems, it's beneficial to consider courses that offer foundational knowledge or advanced applications related to these topics. Complementary courses can provide the theoretical underpinnings, practical skills, or specialized insights that enhance your expertise.
+Based on your interest in web search and recommender systems, and the content of CSCE 670 (Information Storage and Retrieval), the following courses would go well with it:
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** CSCE 670 covers specific applications like web search and recommender systems, which often rely on data mining techniques [Source 1, 2]. CSCE 676 provides a broad overview of data mining, including concepts from machine learning and statistics, exploratory data analysis, pattern mining, clustering, and classification [Source 7]. It also covers "Text Mining" and "Large-Scale ML," which are highly relevant to processing and analyzing data for search and recommendation [Source 6, 8]. Notably, both CSCE 670 and CSCE 676 list "Mining of Massive Datasets" as a resource, indicating conceptual overlap [Source 2, 4, 8].
+    *   **Academic Progression:** This course would provide a broader toolkit of data analysis techniques applicable to the large datasets encountered in search and recommendation.
+*   **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 delves into advanced topics like "Learning to Rank," "Neural Ranking," "Neural Collaborative Filtering," and the application of "Large Language Models" for ranking and recommendation [Source 3]. These techniques are deeply rooted in machine learning principles. CSCE 633 provides the foundational knowledge of machine learning techniques, including induction from examples, clustering, and genetic algorithms, which are crucial for understanding and developing such systems [Source 10].
+    *   **Academic Progression:** This course is foundational. A strong understanding of machine learning from CSCE 633 would enable a deeper comprehension and more effective application of the advanced search and recommendation algorithms discussed in CSCE 670.
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** Given CSCE 670's coverage of "Large Language Models" and "BERT-Based Ranking" [Source 3], optimizing these complex models is critical. CSCE 726 focuses on fundamental optimization algorithms for solving machine learning problems, including deterministic and stochastic gradient-based methods, and their application to real-world ML/AI problems [Source 11].
+    *   **Academic Progression:** This is an advanced course that would be particularly beneficial for students interested in the performance and scalability aspects of machine learning models used in large-scale search and recommender systems, building upon the foundational ML knowledge from courses like CSCE 633 [Source 9, 11].
+I don't have enough data to answer this accurately based on the available syllabi for all possible courses at TAMU, but these courses show strong thematic connections to CSCE 670's content regarding web search and recommender systems.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>To effectively plan your academic progression and deepen your understanding in specific areas, it's beneficial to select courses that build upon or complement your existing knowledge. For someone interested in web search or recommender systems, courses that cover foundational machine learning, data mining, and advanced optimization techniques would be highly relevant to CSCE 670.
+Here are some courses that would go well with CSCE 670, especially for your interests:
+1.  **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** CSCE 676 provides a broad overview of data mining, including concepts from machine learning and statistics, with applications to scientific and online data [Source 7]. It covers topics like text mining, graph mining, and large-scale machine learning [Source 6, 9]. This directly aligns with the large-scale data processing and algorithmic aspects of web search and recommender systems, which often deal with massive datasets. Notably, "Mining of Massive Datasets" is an optional textbook for CSCE 670 and a required textbook for CSCE 676, indicating significant topical overlap [Source 2, 4, 9].
+    *   **Planning Dimension:** This course would provide a broader context and additional techniques for handling and extracting insights from the types of data encountered in information retrieval and recommendation.
+2.  **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 delves into advanced topics like "Learning to Rank," "Neural Ranking," "Transformer; BERT-Based Ranking," "Neural Collaborative Filtering," and "Large Language Models" [Source 3]. These are all rooted in machine learning principles. CSCE 633 offers a foundational understanding of machine learning techniques, including induction from examples, conceptual clustering, and various algorithms [Source 8]. It aims to help students formalize, analyze, and apply machine learning algorithms in real-world applications [Source 12].
+    *   **Planning Dimension:** A strong foundation in machine learning from CSCE 633 would provide the theoretical and practical background necessary to deeply understand and innovate within the ML-driven aspects of modern search and recommender systems covered in CSCE 670.
+3.  **CSCE 726: Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** Building on a machine learning foundation, CSCE 726 focuses on "deterministic optimization and modern large-scale stochastic optimization algorithms for solving ML/AI problems" [Source 10]. Given that CSCE 670 covers advanced neural models and large language models for ranking and recommendation [Source 3], understanding the optimization techniques behind these models is crucial for advanced work.
+    *   **Planning Dimension:** This course is suitable for students who have already taken CSCE 633 (or CSCE 636) and wish to gain a deeper, more mathematical understanding of how machine learning models, particularly those used in search and recommendation, are trained and improved [Source 10, 11].
+These courses offer a progression from foundational data handling and machine learning to advanced optimization, providing a comprehensive academic path for someone specializing in web search and recommender systems.</t>
+        </is>
+      </c>
     </row>
-    <row r="34" ht="86.40000000000001" customHeight="1">
-      <c r="A34" s="2" t="n">
+    <row r="34">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>What courses are similar to CSCE 608?</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems covers fundamental and advanced topics in database systems, including modeling techniques, query languages, relational database design theory, query processing, transaction management, and distributed data management. If you are looking for courses that complement or build upon these areas, I can help you search for relevant options.</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>46648</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="H34" t="n">
+        <v>46648</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>CSCE 608 Database Systems</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="b">
+      <c r="K34" t="b">
         <v>0</v>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>To determine similarity between courses, we can look for overlapping topics in their catalog descriptions and shared prerequisites.
+**CSCE 608: Database Systems**
+*   **Catalog Description:** Covers "Database modeling techniques; expressiveness in query languages including knowledge representation; manipulation languages data models; physical data organization; relational database design theory; query processing; transaction management and recovery; distributed data management" [Source 1].
+*   **Prerequisite:** CSCE 310 or approval of Instructor [Source 1].
+**CSCE 670: Information Storage and Retrieval**
+*   **Catalog Description:** Focuses on "Representation, storage, and access to very large multimedia document collections; fundamental data structures and algorithms of information storage and retrieval systems; techniques to design and evaluate complete retrieval systems, including cover of algorithms for indexing, compressing, and querying very large collections" [Source 5].
+*   **Prerequisite:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5].
+Based on the provided context, **CSCE 670 (Information Storage and Retrieval)** appears to be similar to CSCE 608. Both courses deal with the storage, retrieval, and querying of data, and both list CSCE 310 as a prerequisite [Source 1, 5].</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>When considering course similarity, we can look for overlapping topics, shared prerequisites, or related fields of study.
+Based on the provided context:
+**CSCE 608: Database Systems**
+*   **Catalog Description:** Covers "Database modeling techniques; expressiveness in query languages... manipulation languages data models; physical data organization; relational database design theory; query processing; transaction management and recovery; distributed data management." [Source 1]
+*   **Prerequisite:** CSCE 310 or approval of Instructor. [Source 1]
+**CSCE 670: Information Storage and Retrieval**
+*   **Catalog Description:** Focuses on "Representation, storage, and access to very large multimedia document collections; fundamental data structures and algorithms of information storage and retrieval systems; techniques to design and evaluate complete retrieval systems, including cover of algorithms for indexing, compressing, and querying very large collections." [Source 5]
+*   **Prerequisites:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification. [Source 5]
+**Similarity:**
+CSCE 670 shares significant conceptual overlap with CSCE 608. Both courses deal with:
+*   **Storage and Access:** CSCE 608 covers physical data organization and distributed data management [Source 1], while CSCE 670 focuses on representation, storage, and access to large document collections [Source 5].
+*   **Querying:** CSCE 608 addresses expressiveness in query languages and query processing [Source 1], and CSCE 670 includes techniques for querying large collections [Source 5].
+*   **Data Structures and Algorithms:** CSCE 670 explicitly mentions "fundamental data structures and algorithms of information storage and retrieval systems" [Source 5], which are foundational to efficient database systems as well.
+*   **Shared Prerequisite:** Both courses list CSCE 310 as a prerequisite [Source 1, 5].
+Therefore, **CSCE 670 (Information Storage and Retrieval)** appears to be similar to CSCE 608 due to its focus on data storage, retrieval, querying, and underlying data structures and algorithms, as well as a shared prerequisite [Source 1, 5].</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CSCE 608, "Database Systems," focuses on database modeling, query languages, physical data organization, relational database design, query processing, transaction management, recovery, and distributed data management [Source 1]. Similar courses can be identified by shared foundational concepts, prerequisites, or overlapping topics.
+Based on the provided context, the following courses exhibit similarities to CSCE 608:
+*   **CSCE 670: Information Storage and Retrieval**
+    *   **Similarity:** This course deals with the "representation, storage, and access to very large multimedia document collections," including "fundamental data structures and algorithms of information storage and retrieval systems," and "techniques to design and evaluate complete retrieval systems" [Source 5]. Both CSCE 608 and CSCE 670 address aspects of data storage, organization, and querying for large datasets.
+    *   **Shared Prerequisite:** Both courses list CSCE 310 as a prerequisite or corequisite [Source 1, 5].
+*   **CSCE 611: Operating Systems**
+    *   **Similarity:** While a different domain, CSCE 611 covers system-level topics such as "Concurrency," "Scheduling," "Synchronization," "Atomic Transactions," "I/O," and "File Systems" [Source 9]. These concepts are foundational to the "transaction management and recovery" and "physical data organization" aspects of database systems discussed in CSCE 608 [Source 1].
+I don't have enough data to identify other similar courses accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Based on the provided context, CSCE 670 (Information Storage and Retrieval) shares some similarities with CSCE 608 (Database Systems) [Source 1, 5].
+Both courses require CSCE 310 or instructor approval as a prerequisite [Source 1, 5].
+However, their primary focus differs:
+*   **CSCE 608 (Database Systems)** covers database modeling techniques, query languages, data models, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management [Source 1].
+*   **CSCE 670 (Information Storage and Retrieval)** focuses on the representation, storage, and access to very large multimedia document collections, including fundamental data structures and algorithms of information storage and retrieval systems, and techniques for designing and evaluating complete retrieval systems (indexing, compressing, and querying large collections) [Source 5].
+While both deal with managing and querying information, CSCE 608 is centered on traditional database systems, and CSCE 670 is geared towards information retrieval from large document collections. I don't have enough data to determine if other courses are similar to CSCE 608 based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Based on the provided context, another course that shares some foundational prerequisites with CSCE 608 is CSCE 670.
+Here's a comparison:
+*   **CSCE 608: Database Systems**
+    *   **Description:** Covers database modeling techniques, query languages, data models, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management [Source 1].
+    *   **Prerequisite:** CSCE 310 or approval of Instructor [Source 1].
+*   **CSCE 670: Information Storage and Retrieval**
+    *   **Description:** Focuses on representation, storage, and access to very large multimedia document collections; fundamental data structures and algorithms of information storage and retrieval systems; techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying very large collections [Source 5].
+    *   **Prerequisite:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5].
+While CSCE 608 focuses on the core principles of database management systems, CSCE 670 delves into the specifics of information storage and retrieval for large document collections, including indexing and querying. Both courses list CSCE 310 as a prerequisite, suggesting a common underlying knowledge base [Source 1, Source 5].</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>To determine similarity between courses, we compare their catalog descriptions, learning outcomes, and key topics to identify shared concepts, methodologies, or application domains.
+Based on the provided context, CSCE 608 (Database Systems) focuses on database modeling, query languages, relational database design, query processing, transaction management, and distributed data management [Source 1, 2].
+Courses with some similarities or related concepts include:
+*   **CSCE 670 (Information Storage and Retrieval)**: This course covers "storage, and access to very large multimedia document collections" and "querying very large collections" [Source 5]. Both CSCE 608 and CSCE 670 address fundamental aspects of storing, accessing, and querying information, though CSCE 608 focuses on structured databases while CSCE 670 deals with broader information retrieval systems.
+*   **CSCE 611 (Operating Systems)**: CSCE 608 includes "transaction management and recovery" and "system issues related to database systems" [Source 1, 2]. CSCE 611 covers topics such as "Concurrency" and "Atomic Transactions" [Source 9], which are foundational concepts for the reliable operation and implementation of database systems.
+*   **CSCE 676 (Data Mining and Analysis)**: This course focuses on "data mining and analysis," including "data preparation," "normalization," and "large-scale mining" [Source 10]. While CSCE 608 is about managing data, data mining often utilizes data stored in databases, making these fields complementary. The course also uses "Mining of Massive Data Sets" as a required textbook [Source 10], which suggests a connection to large-scale data handling that can relate to distributed data management in CSCE 608.</t>
+        </is>
+      </c>
     </row>
-    <row r="35" ht="409.5" customHeight="1">
-      <c r="A35" s="2" t="n">
+    <row r="35">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Given that AI is strictly prohibited in CSCE 629, what other courses could I take that focus on using AI tools?</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Based on your interest in courses that permit the use of AI tools, here are some recommendations that align with the policies outlined in CSCE 624:
 CSCE 670: Information Storage and Retrieval This course explicitly allows the submission of AI-generated code or code derived from AI, provided its use is thoroughly documented with the prompt and significant parts of the response. This policy is similar to CSCE 624, which permits AI tools for coding and ideation when explicitly allowed and documented. Taking CSCE 670 would allow you to further develop your skills in applying AI tools responsibly in practical system development, building on the algorithmic design and implementation aspects of CSCE 624's team-based project.
@@ -2123,47 +4768,115 @@
 CSCE 632: Advanced Topics in Computer Science In CSCE 632, you are permitted to use generative AI tools for assistance with assignments, such as brainstorming ideas or receiving feedback. Similar to CSCE 624, this course stresses the importance of citing any AI-generated content and limits AI-generated text to no more than 30% of any assignment to ensure originality and critical thinking [Source 4, 5]. This course would allow you to explore advanced computer science topics while reinforcing the responsible and documented use of AI for ideation and support, a skill emphasized in CSCE 624.</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>CSCE 629</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>AI_POLICY</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>54978</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="H35" t="n">
+        <v>54978</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>CSCE 629</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="b">
+      <c r="K35" t="b">
         <v>0</v>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I cannot confirm whether AI is strictly prohibited in CSCE 629, as information about that specific course is not available in the provided context. [Source 1, 2, 3, 4, 5, 6, 7, 8, 9, 10]
+However, I can provide information on other courses that permit or restrict the use of AI tools, which is governed by the principle of **Academic Integrity and Responsible Use of AI Tools**. Texas A&amp;M University courses are establishing policies that balance academic integrity with the integration of new technologies. These policies often involve explicit permission, documentation requirements, and limitations on the extent of AI-generated content.
+When planning your academic progression, it is crucial to review the AI statements in each course syllabus. This will help you select courses that align with your preferred learning methods and ensure you maintain academic integrity by adhering to specific guidelines for AI tool usage.
+Based on the available syllabi, here are courses that permit the use of AI tools, along with their specific conditions:
+| Course    | AI Tool Usage Policy                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>The provided syllabi outline policies for the responsible integration of AI tools into academic work, emphasizing academic integrity, documentation, and proper attribution. While several courses permit the use of AI tools for assistance, ideation, or feedback, the context does not explicitly state that any particular course *focuses* on the use of AI tools as a primary subject of study or a central methodology. Instead, the policies guide students on how to responsibly incorporate these tools into their learning and assignment completion.
+Based on the available information, the following courses permit the use of AI tools under specific conditions:
+*   **CSCE 624**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the output was validated or modified. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 1, 5, 8].
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments for ideation or to provide feedback. Students must cite any AI-generated material that informed their work, and generally, no more than 30% of an assignment should come directly from AI-generated text [Source 3].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts and evaluation. It is critical to cite the use of Generative AI tools and document student contributions, as submitting work with a significant percentage of undocumented AI-generated content can be considered academic misconduct [Source 7].
+*   **CSCE 713**: The use of AI support is allowed if any assignment delivered is accompanied by the delivery of all AI interactions (prompts, responses, chatbot session links) to enable the instructor to evaluate the student's rationale [Source 10].
+*   **CSCE 632**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments for brainstorming ideas or providing feedback. Students must cite any AI-generated content, and no more than 30% of any assignment should consist of AI-generated text [Source 2].
+It is important to note that while these courses allow AI tool usage, the syllabi primarily focus on the *rules and expectations* for their responsible application rather than teaching the *use of the tools themselves* as a core course objective.
+I don't have enough data to accurately identify courses that *focus* on using AI tools as a primary subject based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>CSCE 629 strictly prohibits the use of AI tools [Source 2]. However, several other courses permit or encourage the use of AI tools under specific conditions:
+*   **CSCE 624 (Sketch Recognition)**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, Source 9, Source 11].
+*   **CSCE 632**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments for brainstorming ideas or feedback, but should not complete the work. Students must cite any AI-generated content that informs their work, and no more than 30% of any assignment should consist of AI-generated text. Failure to properly attribute AI-generated material is considered academic dishonesty [Source 6].
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to get started with ideas or provide feedback. Students must cite any AI-generated material that informed their work, and no more than 30% of an assignment should come directly from text generated from an AI tool. Using an AI tool to generate content without proper attribution qualifies as academic dishonesty [Source 8].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct. Students must cite the use of Generative AI tools and document their contribution to an assignment [Source 12].
+*   **CSCE 713**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible to allow the instructor to evaluate the student rationale to solve the problem [Source 13].
+It is important to note that CSCE 665 (Security) explicitly states that "No AI tools such as ChatGPT are allowed to use in the review writing" [Source 10]. CSCE 726 (Advanced Machine Learning) prohibits the use of AI tools for completing homework assignments, exams, or the course project, but allows them for tasks such as editing writing or debugging code [Source 7]. CSCE 612 prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 14].</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>CSCE 629 strictly prohibits the use of AI tools [Source 2]. However, several other courses permit or discuss the use of AI tools:
+*   **CSCE 624 (Sketch Recognition)**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 9, Source 11].
+*   **CSCE 632 (Advanced Computer Graphics)**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts provided and how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct, so students must cite the use of Generative AI tools and document their contributions [Source 12].
+*   **CSCE 633 (Advanced Computer Graphics)**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments for brainstorming ideas or providing feedback, but should not complete the work. Students must cite any AI-generated content that informs their work, and no more than 30% of any assignment should consist of AI-generated text. Failure to properly attribute AI-generated material is considered academic dishonesty [Source 6].
+*   **CSCE 614 (Advanced Computer Graphics)**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to get started with ideas or provide feedback. Students must cite any AI-generated material that informed their work, and no more than 30% of an assignment should come directly from text generated from an AI tool. Using an AI tool to generate content without proper attribution qualifies as academic dishonesty [Source 8].
+*   **CSCE 713 (Advanced Computer Security)**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible to allow the instructor to evaluate the student rationale to solve the problem [Source 13].
+Conversely, CSCE 665 (Advanced Computer Security) explicitly states that "No AI tools such as ChatGPT are allowed to use in the review writing" [Source 10]. CSCE 726 (Advanced Machine Learning) prohibits the use of AI tools for completing homework assignments, exams, or the course project, but allows them for tasks such as editing writing or debugging code [Source 7]. CSCE 612 (Advanced Computer Architecture) strictly prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 14].</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Based on the provided context, several courses permit or encourage the use of AI tools, with varying guidelines:
+*   **CSCE 624 (Sketch Recognition)**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, 9, 11].
+*   **CSCE 632**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments for brainstorming ideas or providing feedback, but should not complete the work. Students must cite any AI-generated content that informs their work, and no more than 30% of any assignment should consist of AI-generated text. Failure to properly attribute AI-generated material is considered academic dishonesty [Source 6].
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to get started with ideas or to provide feedback. Students must cite any AI-generated material that informed their work, and no more than 30% of an assignment should come directly from text generated from an AI tool. Using an AI tool to generate content without proper attribution qualifies as academic dishonesty [Source 8].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct, so students must cite the use of Generative AI tools and document their contribution [Source 12].
+*   **CSCE 713**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible to allow the instructor to evaluate the student rationale to solve the problem [Source 13].
+It is important to note that **CSCE 726 (Advanced Machine Learning)** strictly prohibits the use of AI tools such as large language models for completing homework assignments, exams, or the course project, though it is acceptable for tasks like editing writing or debugging code [Source 7]. **CSCE 665** explicitly states that no AI tools such as ChatGPT are allowed for paper mini-review writing, but also includes "AI/LLM Security" as a topic in its course schedule [Source 10]. **CSCE 612** strictly prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 14].</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>The relevant principle underlying your question is **Academic Integrity and Responsible Use of Technology**, specifically concerning the integration and application of Artificial Intelligence (AI) tools in academic work. Universities establish policies to guide students on when and how AI tools can be used to ensure fairness, originality, and proper attribution in coursework.
+Based on the provided syllabi, I cannot find information about courses that *focus* on using AI tools as a primary subject of study. The context primarily outlines the policies regarding the *permission or prohibition* of AI tool usage for assignments and projects within various courses.
+However, if you are looking for courses where the use of AI tools is generally permitted for assistance, you might consider the following:
+*   **CSCE 614**: Generative AI tools are permitted on assignments to help with ideas or feedback, but not to do all the work. Any AI-generated material must be cited, and no more than 30% of an assignment should come directly from AI-generated text [Source 3].
+*   **CSCE 624**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the output was validated or modified. Students remain fully responsible for the correctness and originality of their work [Source 1, 5, 8].
+*   **CSCE 632**: Generative AI tools are permitted to assist with assignments for brainstorming or feedback. Students must cite any AI-generated content, and no more than 30% of an assignment should consist of AI-generated text [Source 2].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts and evaluation methods. Submitting work with a significant percentage of undocumented AI-generated content can be considered academic misconduct [Source 7].
+*   **CSCE 713**: The use of AI support is allowed if all AI interactions (prompts, responses, chatbot session links) are delivered alongside the assignment to allow the instructor to evaluate the student's rationale [Source 10].
+*   **CSCE 726**: The use of AI tools for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 4].
+Courses where AI tools are explicitly prohibited for certain tasks or entirely include:
+*   **CSCE 612**: Any usage of AI, copilot, or LLMs is prohibited and will be treated as cheating [Source 9].
+*   **CSCE 665**: No AI tools such as ChatGPT are allowed for paper mini-review writing [Source 6].
+I don't have enough data to answer this accurately based on the available syllabi regarding courses that *focus* on using AI tools. The provided context only details the policies for their use as an aid or their prohibition.</t>
+        </is>
+      </c>
     </row>
-    <row r="36" ht="360" customHeight="1">
-      <c r="A36" s="2" t="n">
+    <row r="36">
+      <c r="A36" t="n">
         <v>36</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>What specific information retrieval algorithms and models does CSCE 670 cover in the second half of the course?</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Based on the syllabus, the specific information retrieval algorithms and models covered in the second half of CSCE 670 include:
 *   **Week 8:** word2vec, Neural Ranking
@@ -2174,94 +4887,176 @@
 *   **Week 14:** Large Language Models for Ranking and Recommendation</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>46627</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="H36" t="n">
+        <v>46627</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="b">
+      <c r="K36" t="b">
         <v>0</v>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
     </row>
-    <row r="37" ht="158.4" customHeight="1">
-      <c r="A37" s="2" t="n">
+    <row r="37">
+      <c r="A37" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Does CSCE 633 cover regularization techniques and ensemble methods, or does it focus only on foundational ML algorithms?</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule.
 The syllabus also indicates a focus on foundational and advanced machine learning algorithms through its catalog description, learning outcomes, and other modules listed in the course schedule (e.g., Linear Models, Decision Tree-Based Models, Support Vector Machines, Neural Networks).
 However, the provided syllabus content does not explicitly mention whether ensemble methods are covered.</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="H37" t="n">
+        <v>58706</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="b">
+      <c r="K37" t="b">
         <v>0</v>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
     </row>
-    <row r="38" ht="172.8" customHeight="1">
-      <c r="A38" s="2" t="n">
+    <row r="38">
+      <c r="A38" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Which deep learning architectures are taught in CSCE 638, and do they include transformers or attention mechanisms?</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Yes, CSCE 638 covers several deep learning architectures. The course schedule explicitly lists:
 *   Convolutional Neural Networks (CNN)
@@ -2271,92 +5066,170 @@
 *   Large Language Models (LLMs)</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>CSCE 638</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>54988</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="H38" t="n">
+        <v>54988</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>CSCE 638</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="b">
+      <c r="K38" t="b">
         <v>0</v>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers several deep learning architectures, including:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Sequence-to-Sequence models [Source 1]
+The course specifically includes **Attention** mechanisms (Week 4) and **Transformers** (Week 5) [Source 1].</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers deep learning architectures including Transformers and Attention mechanisms [Source 1].
+The course schedule includes the following topics:
+*   **Week 3:** Convolutional Neural Network, Recurrent Neural Network
+*   **Week 4:** Sequence-to-Sequence, Attention
+*   **Week 5:** Transformers
+*   **Week 6:** Contextualized Representations, Pre-Training, Large Language Models [Source 1]</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers several deep learning architectures, including:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Sequence-to-Sequence models [Source 1]
+The course specifically includes **Attention** mechanisms (Week 4) and **Transformers** (Week 5) [Source 1].</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers several deep learning architectures, including:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Sequence-to-Sequence models [Source 1]
+The course specifically includes **Attention** mechanisms (Week 4) and **Transformers** (Week 5) [Source 1].</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers several deep learning architectures, including:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Sequence-to-Sequence models [Source 1]
+The course specifically includes **Attention** mechanisms (Week 4) and **Transformers** (Week 5) [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers deep learning architectures including Transformers and Attention mechanisms [Source 1].
+The course schedule includes the following topics:
+*   **Week 3:** Convolutional Neural Network, Recurrent Neural Network
+*   **Week 4:** Sequence-to-Sequence, Attention
+*   **Week 5:** Transformers
+*   **Week 6:** Contextualized Representations, Pre-Training, Large Language Models [Source 1]</t>
+        </is>
+      </c>
     </row>
-    <row r="39" ht="115.2" customHeight="1">
-      <c r="A39" s="2" t="n">
+    <row r="39">
+      <c r="A39" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>What cryptographic concepts and protocols are covered in CSCE 665?</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Based on the provided syllabus for CSCE 665, specific cryptographic concepts and protocols are not explicitly listed as topics to be covered. The syllabus outlines various modern topics in computer and network security, including areas like malware, intrusion detection, software-defined security, Web/Web3 security (including DeFi and blockchain), and AI/LLM security.</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>30874</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="H39" t="n">
+        <v>30874</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>CSCE 665</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="b">
+      <c r="K39" t="b">
         <v>0</v>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2]. The course description and topics for CSCE 665 focus on advanced networking and security, including areas like software security, malware, botnets, intrusion detection, and web/AI security, but do not specifically mention cryptographic concepts or protocols.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
     </row>
-    <row r="40" ht="86.40000000000001" customHeight="1">
-      <c r="A40" s="2" t="n">
+    <row r="40">
+      <c r="A40" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>What systems-level topics does CSCE 612 focus on — for example, does it go deep into network protocol implementation or distributed system design?</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>CSCE 612, "Applied Networks and Distributed Processing," focuses on several systems-level topics.
 The course delves deeply into network protocol implementation and analysis. This includes:
@@ -2369,47 +5242,129 @@
 *   **Programming Constructs**: Topics like sockets, threads, and synchronization are covered, which are foundational for distributed systems.</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>CSCE 612</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>42640</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="H40" t="n">
+        <v>42640</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>CSCE 612</t>
         </is>
       </c>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="b">
+      <c r="K40" t="b">
         <v>0</v>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on both network protocol implementation and distributed system design [Source 1].
+The course aims to:
+*   Mix fundamentals with programming and pragmatic engineering issues, including network architecture and principles of network engineering [Source 1].
+*   Apply principles of layered architecture to analyzing real networks, with lab exercises focusing on protocol understanding and programming [Source 1].
+*   Enable students to utilize operating-system sockets APIs, create efficient network applications, build multi-threaded decentralized frameworks, and develop protocols [Source 2].
+Key topics covered include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3].
+*   Application layer concepts such as HTTP, caching, cookies, FTP, email, and DNS [Source 3, 4].
+*   Transport layer topics like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), flow control, congestion control, and TCP modeling [Source 3, 4].
+*   Network layer concepts including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP) [Source 4].
+*   Data-link layer topics such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on both network protocol implementation and distributed system design [Source 1].
+The course aims to:
+*   Mix fundamentals with programming and pragmatic engineering issues, including network architecture and principles of network engineering [Source 1].
+*   Apply principles of layered architecture to analyzing real networks, with lab exercises focusing on protocol understanding and programming [Source 1].
+*   Enable students to utilize operating-system sockets APIs, create efficient network applications, build multi-threaded decentralized frameworks, and develop protocols [Source 2].
+Key topics covered include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3].
+*   Application layer concepts such as HTTP, caching, cookies, FTP, email, and DNS [Source 3, 4].
+*   Transport layer topics like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), flow control, congestion control, and TCP modeling [Source 3, 4].
+*   Network layer concepts including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP) [Source 4].
+*   Data-link layer topics such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on both network protocol implementation and distributed system design [Source 1].
+The course aims to:
+*   Mix fundamentals with programming and pragmatic engineering issues, including network architecture and principles of network engineering [Source 1].
+*   Apply principles of layered architecture to analyzing real networks, with lab exercises focusing on protocol understanding and programming [Source 1].
+*   Enable students to utilize operating-system sockets APIs, create efficient network applications, build multi-threaded decentralized frameworks, and develop protocols [Source 2].
+Key topics covered include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3].
+*   Application layer concepts such as HTTP, caching, cookies, FTP, email, and DNS [Source 3, 4].
+*   Transport layer topics like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), flow control, congestion control, and TCP modeling [Source 3, 4].
+*   Network layer concepts including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP) [Source 4].
+*   Data-link layer topics such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>CSCE 612, Applied Networks and Distributed Processing, focuses on both network protocol implementation and distributed system design [Source 1, 2].
+Key systems-level topics include:
+*   **Network Protocol Implementation**: The course involves programming and pragmatic views of engineering issues, with lab exercises focusing on protocol understanding and programming. Students will learn to utilize operating-system sockets APIs and create efficient network applications [Source 1, 2]. The schedule includes topics like "Sockets, threads, synchronization" [Source 3].
+*   **Distributed System Design**: The course covers "Applied Networks and Distributed Processing" and aims for students to "build multi-threaded decentralized frameworks" [Source 1, 2].
+The course also emphasizes applying principles of layered architecture to analyzing real networks, network design, protocol analysis, and principles of network engineering [Source 1]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>CSCE 612, Applied Networks and Distributed Processing, focuses on both network protocol implementation and distributed system design [Source 1, 2].
+Key systems-level topics include:
+*   **Network Protocol Implementation**: The course involves programming and pragmatic views of engineering issues, with lab exercises focusing on protocol understanding and programming. Students will learn to utilize operating-system sockets APIs and create efficient network applications [Source 1, 2]. The schedule includes topics like "Sockets, threads, synchronization" [Source 3].
+*   **Distributed System Design**: The course covers "Applied Networks and Distributed Processing" and aims for students to "build multi-threaded decentralized frameworks" [Source 1, 2].
+The course also emphasizes applying principles of layered architecture to analyzing real networks, network design, protocol analysis, and principles of network engineering [Source 1]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on both network protocol implementation and distributed system design [Source 1].
+The course aims to:
+*   Mix fundamentals with programming and pragmatic engineering issues, including network architecture and principles of network engineering [Source 1].
+*   Apply principles of layered architecture to analyzing real networks, with lab exercises focusing on protocol understanding and programming [Source 1].
+*   Enable students to utilize operating-system sockets APIs, create efficient network applications, build multi-threaded decentralized frameworks, and develop protocols [Source 2].
+Key topics covered include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3].
+*   Application layer concepts such as HTTP, caching, cookies, FTP, email, and DNS [Source 3, 4].
+*   Transport layer topics like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), flow control, congestion control, and TCP modeling [Source 3, 4].
+*   Network layer concepts including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP) [Source 4].
+*   Data-link layer topics such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
     </row>
-    <row r="41" ht="345.6" customHeight="1">
-      <c r="A41" s="2" t="n">
+    <row r="41">
+      <c r="A41" t="n">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>How is the final grade weighted across homework, projects, and exams in CSCE 670?</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>In CSCE 670, your final grade is weighted as follows:
 *   **Homework:** 30%
@@ -2418,51 +5373,102 @@
 *   **Quizzes:** 20%</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>46627</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="H41" t="n">
+        <v>46627</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>CSCE 670</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="K41" s="2" t="b">
+      <c r="K41" t="b">
         <v>0</v>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
     </row>
-    <row r="42" ht="86.40000000000001" customHeight="1">
-      <c r="A42" s="2" t="n">
+    <row r="42">
+      <c r="A42" t="n">
         <v>42</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>How many programming projects are assigned in CSCE 611, and what do they cover? What are they about?</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>CSCE 611, section 600, includes a series of seven programming assignments, referred to as Machine Problems (MPs), which guide students through designing and developing a simple operating system .
 The topics covered by these assignments are:
@@ -2475,229 +5481,413 @@
 MP7: Journaled and Log-Based File Systems, Virtualization Introduction, Virtualization Mechanisms, and Memory Virtualization.</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>50668</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="H42" t="n">
+        <v>50668</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>GRADING</t>
         </is>
       </c>
-      <c r="K42" s="2" t="b">
+      <c r="K42" t="b">
         <v>0</v>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of seven programming assignments, referred to as Machine Problems (MPs) [4, 6]. These assignments are designed to guide students through the process of designing and developing a simple operating system [4].
+The Machine Problems cover the following topics:
+*   **MP1:** Project setup, introduction to operating systems, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [3].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [3].
+*   **MP3:** Page replacement policies, recursive page table lookup, concurrency introduction, and scheduling [3, 6].
+*   **MP4:** Thread dispatching on the x86, kernel vs. user-level threads, and event-based concurrency [6].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [6].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, file systems (intro, allocation, UNIX file systems) [6].
+*   **MP7:** Journaled and log-based file systems, and virtualization (introduction, mechanisms, memory virtualization) [6].</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of design and programming assignments, referred to as Machine Problems (MPs), that guide students through designing and developing a simple operating system [3, 1]. There are 7 Machine Problems assigned throughout the semester [4, 6].
+These assignments cover various aspects of operating systems, including:
+*   **MP1:** Project setup, introduction to OS concepts, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [4].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [4].
+*   **MP3:** Page replacement policies and an introduction to concurrency and scheduling [4, 6].
+*   **MP4:** Thread dispatching on the x86, kernel vs. user-level threads, and event-based concurrency [6].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [6].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, and file systems (including UNIX file systems) [6].
+*   **MP7:** Journaled and log-based file systems, and virtualization mechanisms including memory virtualization [6].
+The programming assignments contribute 400 points to the final grade [3].</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>In CSCE 611, there are 7 programming assignments, referred to as Machine Problems (MPs) [Source 3, 4]. These assignments are designed to guide students through the steps of designing and developing a simple operating system that can boot and run on a bare PC [Source 2, 6].
+The Machine Problems cover topics such as:
+*   Project setup, OS introduction, architectural support, OS structures, system calls, interrupts, and exceptions [Source 3].
+*   Memory management, including allocation, address spaces, paging, TLB, segmentation, and virtual memory mechanisms [Source 3].
+*   Page replacement policies [Source 3].
+*   Concurrency, scheduling, thread dispatching, and event-based concurrency [Source 3, 4].
+*   Synchronization mechanisms, critical section problems, concurrent data structures, and atomic transactions [Source 4].
+*   I/O management, device drivers, disks, RAID, flash memory, and file systems [Source 4].
+*   Journaled and log-based file systems, and virtualization mechanisms [Source 4].
+Through these projects, students will implement components of a virtual memory manager, a threading system, a simple device driver, and a simple file system [Source 5].</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of seven programming assignments, referred to as Machine Problems (MPs) [4, 6]. These assignments are designed to guide students through the process of designing and developing a simple operating system [4].
+The Machine Problems cover the following topics:
+*   **MP1:** Project setup, introduction to operating systems, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [3].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [3].
+*   **MP3:** Page replacement policies, recursive page table lookup, concurrency introduction, and scheduling [3, 6].
+*   **MP4:** Thread dispatching on the x86, kernel vs. user-level threads, and event-based concurrency [6].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [6].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, file systems (intro, allocation, UNIX file systems) [6].
+*   **MP7:** Journaled and log-based file systems, and virtualization (introduction, mechanisms, memory virtualization) [6].</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of seven programming assignments, referred to as Machine Problems (MPs) [4, 6]. These assignments are designed to guide students through the process of designing and developing a simple operating system [4].
+The Machine Problems cover the following topics:
+*   **MP1:** Project setup, introduction to operating systems, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [3].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [3].
+*   **MP3:** Page replacement policies, recursive page table lookup, concurrency introduction, and scheduling [3, 6].
+*   **MP4:** Thread dispatching on the x86, kernel vs. user-level threads, and event-based concurrency [6].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [6].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, file systems (intro, allocation, UNIX file systems) [6].
+*   **MP7:** Journaled and log-based file systems, and virtualization (introduction, mechanisms, memory virtualization) [6].</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of design and programming assignments, referred to as Machine Problems (MPs), that guide students through designing and developing a simple operating system [3, 1]. There are 7 Machine Problems assigned throughout the semester [4, 6].
+These assignments cover various aspects of operating systems, including:
+*   **MP1:** Project setup, introduction to OS concepts, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [4].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [4].
+*   **MP3:** Page replacement policies and an introduction to concurrency and scheduling [4, 6].
+*   **MP4:** Thread dispatching on the x86, kernel vs. user-level threads, and event-based concurrency [6].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [6].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, and file systems (including UNIX file systems) [6].
+*   **MP7:** Journaled and log-based file systems, and virtualization mechanisms including memory virtualization [6].
+The programming assignments contribute 400 points to the final grade [3].</t>
+        </is>
+      </c>
     </row>
-    <row r="43" ht="360" customHeight="1">
-      <c r="A43" s="2" t="n">
+    <row r="43">
+      <c r="A43" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>What is the late submission policy for assignments in CSCE 633?</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>For CSCE 633, the course has a strict late work policy: **No late assignments will be accepted.**
 The syllabus defines late assignments as any deliverables submitted after the established deadline. However, work submitted as makeup for an excused absence is not considered late and is exempt from this policy, as per Student Rule 7.</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="H43" t="n">
+        <v>58706</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="b">
+      <c r="K43" t="b">
         <v>0</v>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
     </row>
-    <row r="44" ht="100.8" customHeight="1">
-      <c r="A44" s="2" t="n">
+    <row r="44">
+      <c r="A44" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>What mathematical background does CSCE 633 expect students to have before the course begins?</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>The syllabus for CSCE 633 does not explicitly state specific mathematical background requirements for students before the course begins.
 The only stated prerequisites are CSCE 420 or CSCE 625. While the course learning outcomes indicate that students will "evaluate the underlying mathematical relationships within and across advanced machine learning algorithms," and the required textbooks are mathematically oriented, the syllabus does not list particular mathematical topics as prerequisites.</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>PREREQUISITES</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="H44" t="n">
+        <v>58706</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>CSCE 633</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="b">
+      <c r="K44" t="b">
         <v>0</v>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
     </row>
-    <row r="45" ht="144" customHeight="1">
-      <c r="A45" s="2" t="n">
+    <row r="45">
+      <c r="A45" t="n">
         <v>45</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Does CSCE 611 have an explicit policy on the use of AI tools or generative AI for assignments?</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Yes, CSCE 611 has an explicit policy on the use of AI tools.
 For programming assignments, homework, and exams, students are explicitly prohibited from submitting or making use of AI-generated solutions or AI tools. The course emphasizes that the solution handed in must be the student's own, and this includes not using any part (code, text, figures, etc.) that has been developed by others, including AI. The course will use code-similarity detection tools and automated plagiarism detection tools, and any submission flagged by these tools will be treated as a potential violation.</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>AI_POLICY</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>50668</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="H45" t="n">
+        <v>50668</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>CSCE 611</t>
         </is>
       </c>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="b">
+      <c r="K45" t="b">
         <v>0</v>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments and exams.
+For programming assignments and homework, students are not to use any part (code, text, figures, etc.) that has been developed by others, including AI. This means students should not submit or make use of AI-generated solutions [Source 1].
+For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments and exams. Students are prohibited from using any part (code, text, figures, etc.) developed by others, including AI, for programming assignments and homework. This means students should not submit or make use of AI-generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments.
+For programming assignments, students are not to submit or make use of AI generated solutions [Source 1]. Similarly, for homework, students are not to submit or make use of AI generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2]. The course states that it will use code-similarity detection tools and automated plagiarism detection tools, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments.
+For programming assignments, students are not to submit or make use of AI generated solutions [Source 1]. Similarly, for homework, students are not to submit or make use of AI generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2]. The course states that it will use code-similarity detection tools and automated plagiarism detection tools, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments.
+For programming assignments, students are not to submit or make use of AI generated solutions [Source 1]. Similarly, for homework, students are not to submit or make use of AI generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2]. The course states that it will use code-similarity detection tools and automated plagiarism detection tools, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments and exams. Students are prohibited from using any part (code, text, figures, etc.) developed by others, including AI, for programming assignments and homework. This means students should not submit or make use of AI-generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
+        </is>
+      </c>
     </row>
-    <row r="46" ht="144" customHeight="1">
-      <c r="A46" s="2" t="n">
+    <row r="46">
+      <c r="A46" t="n">
         <v>46</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>What programming languages or tools are required for CSCE 612 assignments?</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>For CSCE 612 assignments, all homework submissions must compile in **Visual Studio 2022** in both debug and release mode. Solutions should not depend on non-standard libraries.
 While knowledge of UNIX and C programming is mentioned as helpful, the syllabus does not explicitly state a required programming language for the assignments.</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>hybrid_course</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>CSCE 612</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>COURSE_OVERVIEW</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>42640</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H46" t="n">
+        <v>42640</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>CSCE 612</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="b">
+      <c r="K46" t="b">
         <v>0</v>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
     </row>
-    <row r="47" ht="100.8" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:K47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,11 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>run:verify_pipeline</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>run:new_golden_rows</t>
         </is>
       </c>
     </row>
@@ -609,6 +614,15 @@
 *   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, covers the following topics in the beginning of the Spring 2026 semester:
+*   **Week 1 (Jan 12):** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2 (Jan 19):** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3 (Jan 26):** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].
+*   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -700,6 +714,15 @@
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Upon completion of CSCE 669, students will be able to:
 *   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
@@ -810,6 +833,17 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
 *   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
@@ -1028,6 +1062,33 @@
 Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," focuses on the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics covered in the course include:
+*   CSCW history and central issues [Source 3]
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making and voting models [Source 3]
+*   Meeting capture and reuse [Source 3]
+*   Crowdsourcing and its issues [Source 3]
+*   Online communities and virtual teams [Source 3]
+*   Shared user history and its visualization [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Collaboration in online games [Source 3]
+*   Supporting software teams [Source 3]
+To enroll, students must have completed CSCE 671 or CSCE 610, or receive approval from the instructor [Source 1].
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 2]
+*   Team project: 35% [Source 2]
+*   Readings write-ups: 35% [Source 2]
+*   Readings presentations: 10% [Source 2]
+*   Attendance (via sign-in sheet): 10% [Source 2]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1220,23 @@
 The course emphasizes how humans naturally sketch, how systems interpret sketches, and how recognition algorithms behave in real-world, noisy settings. It involves hands-on implementation of recognition techniques, critical reading of research papers, in-class activities, and a semester-long team project [Source 1, 2].</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>For CSCE 624, Section 600 (58435), titled "Sketch Recognition," you should know the following before taking the course:
+**Prerequisites:**
+*   Graduate classification [Source 1, 2].
+**Recommended Knowledge:**
+*   General graduate-level knowledge in computer science [Source 2].
+*   Familiarity with at least one of the following is helpful but not strictly required:
+    *   Programming (any language) [Source 2].
+    *   Basic machine learning or artificial intelligence concepts [Source 2].
+    *   Linear algebra or probability [Source 2].
+    *   Software engineering practices [Source 2].
+*   Students from related disciplines (e.g., engineering, HCI, data science) are welcome [Source 2].
+**Course Focus:**
+The course emphasizes how humans naturally sketch, how systems interpret sketches, and how recognition algorithms behave in real-world, noisy settings. It involves hands-on implementation of recognition techniques, critical reading of research papers, in-class activities, and a semester-long team project [Source 1, 2].</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1365,23 @@
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
 The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
@@ -1440,6 +1535,20 @@
 While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600) covers a significant amount of material related to interactive media design, but also includes topics on digital rights and policy [Source 1, 2, 3, 4].
+**Academic Content Breakdown:**
+*   **Interactive Media Design Focus:**
+    *   The course investigates the impact of computers in new media design and the relationships between authors and readers of interactive materials [Source 1].
+    *   Learning outcomes include designing software features for immersion, agency, and transformation; describing techniques for creating computer characters and narrative control; developing software for audio/video manipulation; and designing, implementing, and evaluating software for content creation/consumption [Source 3].
+    *   The course schedule dedicates approximately 10 out of 14 content weeks to topics such as designing software for immersion, agency and transformation, interactive media and computer characters, interactive text and social media, bridging physical and digital media, audio/music/speech, recorded/authored video, games, and automatic narrative control [Source 2, 4].
+*   **Digital Rights and Policy Focus:**
+    *   Learning outcomes also include describing differences between physical and intellectual property, and assessing software licenses, patents, and digital rights management software [Source 3].
+    *   The course schedule dedicates approximately 4 weeks to topics like digital rights management, property rights and issues, software licenses and intellectual property, and evaluating policy effects [Source 2].
+While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1686,22 @@
 **Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1705,6 +1830,22 @@
         </is>
       </c>
       <c r="Q10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
 The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
@@ -1892,6 +2033,27 @@
 **Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672, Computer Supported Collaborative Work, appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the "design, implementation and use of technical systems that support people working cooperatively" [Source 1]. It draws from the research area of Computer Supported Cooperative Work (CSCW) and includes current theoretical, practical, technical, and social issues [Source 1].
+Key topics covered in the course include:
+*   Designing for artifact and human awareness [Source 3]
+*   Forms of communication [Source 3]
+*   Content sharing systems and issues [Source 3]
+*   Collaborative decision making [Source 3]
+*   Collaborative search and design [Source 3]
+*   Software supporting social skill development [Source 3]
+*   Supporting software teams [Source 3]
+Upon completion, you will be able to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2]
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2]
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2]
+The course involves a team project (35% of the grade) and smaller project activities due weekly, which would provide practical experience [Source 2, 3].
+**Course ID and Section:** CSCE 672, Section 600 (58439) [Source 1]
+**Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2010,6 +2172,22 @@
         </is>
       </c>
       <c r="Q12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
 Key topics covered include:
@@ -2182,6 +2360,31 @@
 These examples demonstrate that final grades can be influenced by various factors beyond a simple arithmetic average of all graded components.</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided course syllabi, there are several instances where a final grade is not solely determined by a straightforward calculated average of component scores. The principle at play is that grading policies can incorporate various mechanisms beyond a simple weighted average, including instructor discretion, specific passing conditions, dropping low scores, applying curves, peer evaluation multipliers, and bonus opportunities.
+Here are examples of such policies:
+*   **Instructor Discretion and Overriding Grades:**
+    *   In CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 3].
+    *   For CSCE 632, the instructor can also modify a peer evaluation multiplier at their discretion, which directly impacts a student's project score [Source 3].
+*   **Specific Passing Conditions:**
+    *   In CSCE 681, to pass the course, students must complete a syllabus quiz on Canvas with a 100% grade AND receive an average score of 80% or higher. Any course requirements completed before passing the syllabus quiz will not be considered [Source 8].
+*   **Dropping Lowest Grades:**
+    *   CSCE 629 drops the lowest grade in quizzes/exercises and the lowest homework grade [Source 1, 5].
+    *   CSCE 681 calculates the final quiz grade as the statistical mean of the top 75% of individual quiz grades, effectively dropping the lowest 25% [Source 4].
+*   **Curves:**
+    *   CSCE 629 states that "A slight curve might be applied if the course average is low" [Source 5].
+*   **Peer Evaluation Multipliers:**
+    *   In CSCE 632, a student's score on team projects is based on peer evaluations, and the instructor establishes a multiplier based on these evaluations, which can adjust the final project score [Source 3].
+*   **Bonus Opportunities:**
+    *   CSCE 648 mentions that students who regularly contribute insightful comments during class discussions may receive bonus points [Source 7].
+    *   CSCE 713 offers an optional "Independent-Study Reports" component that can add +10% to the total grade [Source 2].
+*   **Attendance-Based Deductions:**
+    *   CSCE 648 deducts 1.0 point from the class participation grade for each missed class, up to a maximum of 12 points [Source 7].
+*   **Completion Rate Adjustments:**
+    *   CSCE 632 calculates a completion rate for group class activities and adds 15% (capped at 100%) to the score, allowing students to miss some activities without negative impact [Source 10].</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2275,6 +2478,12 @@
 *   **Online Communities:** "week 9: online communities and virtual teams" [Source 1]
 *   **Collaboration in Games:** "week 13: collaboration in online games" [Source 1]
 I cannot find information about other courses at TAMU that cover these specific topics in the provided context.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the course CSCE 672: Computer Supported Collaborative Work explicitly covers topics such as crowdsourcing, online communities, and collaboration in online games [Source 1, Source 2].
+However, I cannot find information about *other* courses at TAMU that cover these specific topics in the provided context. I don't have enough data to answer this accurately based on the available syllabi.</t>
         </is>
       </c>
     </row>
@@ -2428,6 +2637,23 @@
     *   Focuses on "AI/LLM Security" across Weeks 11, 13, and 14 [Source 10].</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Several courses at Texas A&amp;M cover advanced topics in AI, including transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   Week 5: Transformers [Source 1]
+    *   Week 6: Contextualized Representations, Pre-Training, Large Language Models [Source 1]
+*   **CSCE 624: Foundations of Sketch Recognition**
+    *   Weeks 8-9: Hidden Markov Models, LLMs, and related techniques [Source 5]
+*   **CSCE 670: Information Retrieval and Web Search**
+    *   Week 10: Transformer; BERT-Based Ranking [Source 2]
+    *   Week 12: Large Language Models Basics [Source 2]
+    *   Week 13: Large Language Models with Search Engines [Source 2]
+    *   Week 14: Large Language Models for Ranking and Recommendation [Source 2]
+*   **CSCE 665: Advanced Topics in Security**
+    *   Weeks 11-15: AI/LLM Security [Source 10]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2534,6 +2760,15 @@
     *   Class participation and presentation are also components of the grade, suggesting discussion of technical content [Source 10].
     *   The course material primarily consists of various research papers from top security conferences and journals [Source 10].
 These courses explicitly involve activities such as writing reviews of research papers, leading discussions on technical articles, conducting literature reviews, and giving presentations on research topics, which directly align with the skills mentioned in your question.</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>For students interested in improving their skills in preparing research reports and discussing technical articles, the following Texas A&amp;M CS courses would be beneficial:
+*   **CSCE 681 (Seminar)**: This course's primary purpose is to expose students to current and seminal research topics. Upon completion, students are expected to be able to prepare reports and discuss research works and selected published technical articles. Students are required to write a report for each lecture, which includes sections like background, problem statement, proposed solution, results, and critique [Source 1, 2].
+*   **CSCE 635**: In this course, students are expected to submit short reviews of research papers, articulating their understanding of main contributions, providing critical analysis of strengths and limitations, and discussing open research questions or potential extensions. Students also lead class discussions on assigned papers, preparing slides or discussion prompts to facilitate conversation around methodology, results, and broader implications [Source 3].
+*   **CSCE 632**: This course requires students to compile a literature review on an accessibility topic, based on at least 10 peer-reviewed conference or journal papers. The literature review must clearly lay out themes and gaps in research, supported by evidence. Students also give a "Current Research Presentation" based on their literature review [Source 9].
+*   **CSCE 665**: This course includes a "Paper mini-review" component and emphasizes "Class participation and presentation" [Source 10].</t>
         </is>
       </c>
     </row>
@@ -2705,6 +2940,33 @@
 While the provided context highlights the critical periods for assignments and the varying late work policies, it does not explicitly detail strategies for managing the end-of-semester workload. Therefore, I cannot provide specific strategies based solely on the available syllabi.</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Managing the end-of-semester workload, especially when multiple final projects and papers are due around the same time, requires proactive planning and effective time management. The principle is to anticipate peak workload periods and distribute tasks over time to avoid last-minute crunch.
+Based on the provided course schedules for the 202611 term, it is evident that many significant deliverables, such as final projects, reports, and presentations, often converge in late April and early May:
+*   **Late April:**
+    *   CSCE 632 has a Final Presentation on April 21 &amp; 23, with the Final Report and Video Demo due on April 28 [Source 3].
+    *   CSCE 635 has Final Project Presentations and Feedback on April 17, 20, 22, and the Final Project Report due on April 27 [Source 8].
+    *   CSCE 652 dedicates Weeks 14 and 15 to "FINAL PROJECT TIME," with the Final Project due on April 28 and the CTF Scoreboard closing on April 21 [Source 2].
+    *   CSCE 672 schedules Final project presentations for April 27-28 [Source 5].
+    *   CSCE 656 also has Final project presentations between April 20-28 [Source 7].
+*   **Early May:**
+    *   CSCE 611 has Machine Problem 7 (MP7) due on May 3, just before the Final Exam on May 5 [Source 1].
+    *   CSCE 633's Final Project is due on May 4 [Source 4].
+    *   CSCE 672's Final project reports are due on May 1 [Source 5].
+    *   CSCE 752 has its Final Exam on May 1 [Source 6].
+    *   CSCE 656 has a Survey paper due on May 1 and Final project reports due on May 1 [Source 7].
+Given this clustering of deadlines, here are some effective strategies for managing your end-of-semester workload:
+1.  **Early Identification of Deadlines:** At the beginning of the semester, review all syllabi to identify major project, paper, and exam dates. Create a master calendar that includes all these significant deadlines [Source 1, 2, 3, 4, 5, 6, 7, 8].
+2.  **Break Down Large Tasks:** For each final project or paper, break it down into smaller, manageable sub-tasks (e.g., research, outline, first draft, revisions). Assign mini-deadlines for these sub-tasks throughout the semester, well in advance of the final due date.
+3.  **Prioritize and Allocate Time:** Assess the weight and complexity of each final deliverable. Allocate more time to projects that are worth a higher percentage of your grade or require more intensive effort.
+4.  **Start Early:** Begin working on final projects and papers as soon as possible. For example, CSCE 672 and CSCE 656 mention smaller project activities and reading write-ups due weekly, which can help you stay engaged and prepare for larger deliverables [Source 5, 7]. CSCE 752 notes that projects are due approximately every two weeks, encouraging consistent work [Source 6].
+5.  **Utilize "Buffer" Time:** Build in extra time for unexpected challenges, technical issues, or the need for additional revisions. Some courses, like CSCE 611, explicitly state "hard" due dates for final assignments like MP7 to allow for timely grading, emphasizing the need to meet deadlines [Source 1].
+6.  **Leverage Regular Assignments:** Some courses have regular assignments (e.g., weekly machine problems in CSCE 611 [Source 1], bi-weekly projects in CSCE 752 [Source 6]) that can help you practice skills and stay on track, reducing the burden at the very end.
+**Planning Dimension:**
+Understanding this end-of-semester convergence is crucial for your academic progression. By proactively mapping out your major assignments from all courses, you can strategically distribute your workload, identify potential conflicts, and avoid overwhelming periods. This allows you to produce higher quality work, reduce stress, and ensure you meet all academic requirements effectively.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2825,6 +3087,19 @@
 While CSCE 679 explicitly requires a single, tool-specific project for 50% of the grade for graduate students, and CSCE 713 also has a single component worth 50%, this structure is not observed in all other graduate CS courses listed in the context.</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Grading policies and the weighting of assessment components, such as projects, vary across different courses. In the provided context, there are instances where a significant portion of the final grade is allocated to projects, sometimes with specific tool requirements.
+Specifically:
+*   In **CSCE 679**, the course project accounts for 50% of the final grade. Graduate students are required to implement their project using the D3.js visualization library [Source 1]. This aligns directly with your example of a single, tool-specific project counting for half the grade.
+*   In **CSCE 713**, "Vulnerabilities PoC" (Proof of Concept) is an individual component worth 50% of the grade. Students are required to deliver PoCs for vulnerabilities explained in class, which involves running security tools [Source 3]. While this is a single grading category, the description suggests it might involve multiple proofs of concept rather than one monolithic project.
+Other courses show different project weightings and structures:
+*   **CSCE 648** includes "Projects" worth 36 points out of 100, which are comprised of six equally weighted projects [Source 4, 6].
+*   **CSCE 652** has a "Final Project" worth 30% of the overall grade [Source 7].
+*   **CSCE 748** includes "Programming assignments" worth 50%, but these consist of five separate assignments, not a single project. It also has a "Final project" worth 20% [Source 9].
+Based on the available syllabi, while not every course follows this model, at least one course (CSCE 679) explicitly features a single, tool-specific project (D3.js) for graduate students that accounts for 50% of the final grade [Source 1]. Another course (CSCE 713) also has a significant individual, tool-related component ("Vulnerabilities PoC") weighted at 50% [Source 3].</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2892,6 +3167,11 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
         </is>
@@ -2973,6 +3253,11 @@
           <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3040,6 +3325,11 @@
         </is>
       </c>
       <c r="Q21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
         </is>
@@ -3135,6 +3425,15 @@
         </is>
       </c>
       <c r="Q22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
 *   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
@@ -3252,6 +3551,18 @@
 The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply these theories and techniques to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and related areas [Source 2].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids [Source 1]. The geometric interpretation of these results highlights the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1].
+**Career Relevance:** The course directly prepares students for advanced research in computational optimization, indicating its relevance for academic and R&amp;D careers. The ability to apply theories and techniques to "real-world problems" suggests its utility in industry roles that involve complex problem-solving, algorithm design, and optimization in fields like logistics, data science, machine learning, and operations research [Source 1, 2]. The course project, which involves reading recent published papers and conducting research on current problems, further enhances skills valuable for innovation and problem-solving in professional settings [Source 2].
+The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,6 +3662,15 @@
 *   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3418,6 +3738,11 @@
         </is>
       </c>
       <c r="Q25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
         </is>
@@ -3508,6 +3833,13 @@
         </is>
       </c>
       <c r="Q26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
 The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
@@ -3707,6 +4039,37 @@
         </is>
       </c>
       <c r="Q27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
 **Course Purpose:**
@@ -3905,6 +4268,19 @@
 | Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4108,6 +4484,46 @@
 *   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Each student/team has a limited number of "late days" they may use by request. Work submitted as makeup for an excused absence is exempt from the late work policy [Source 7].</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>For CSCE 632, Section 600 (54784), Accessible Computing, here's an overview of the course and how final grades are determined:
+**Course Overview**
+*   **Course ID &amp; Section**: CSCE 632, Section 600 (54784) [Source 5]
+*   **Term**: Spring 2026 [Source 5]
+*   **Meeting Times**: Tuesdays and Thursdays, 12:45 PM - 2:00 PM, in ZACH 350 [Source 5]
+*   **Credit Hours**: 3 [Source 5]
+*   **Catalog Description**: This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, universal design, and its role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. It also covers the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+*   **Prerequisites**: Graduate classification [Source 5].
+**Grading Breakdown**
+The final grade for CSCE 632 is determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 1]
+    *   Includes course readings, quizzes, polls, and surveys. Credit is given for submissions prior to class. A completion rate is calculated, capped at 100% with a 15% allowance for missed engagements [Source 1].
+*   **Group Class Activities**: 10% [Source 1]
+    *   Students work in groups of at least 3. Credit is given for attending class and providing what is required for the activity. A completion rate is calculated, capped at 100% with a 15% allowance for missed activities [Source 1, 2].
+*   **Assignments**: 25% [Source 2]
+    *   Completed individually or with others. Some assignments are peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 2].
+*   **Quick Applications**: 20% [Source 2]
+    *   Timed assignments designed for quick application of class materials, typically taking 15-20 minutes but with at least 45 minutes provided [Source 2].
+*   **Literature Review**: 10% [Source 3]
+    *   Students compile a literature review on an accessibility topic, comprising at least 10 related peer-reviewed conference or journal papers. It must clearly lay out themes and gaps, supported by evidence, and include an annotated bibliography [Source 3].
+*   **Current Research Presentation**: 5% [Source 3]
+    *   A summary of HCI research based on the student's Literature Review. This is peer-graded, with scores based on peer evaluations and self-evaluation of other student assignments. Students can lose points for grading significantly differently than peers or giving all students the same scores [Source 3].
+*   **Team Project**: 25% [Source 3]
+    *   Students work in groups to address a barrier for people with disabilities that lacks an acceptable solution. The team's barrier must be instructor-approved. Teams design and implement a technology-based solution for equitable interactions. Parts of this are peer-graded, with scores based on peer evaluations and self-evaluation. The instructor may apply a multiplier based on team peer evaluations, which can be modified at their discretion [Source 3, 4].
+**Grading Scale**
+Grades are rounded to the nearest whole number and assigned as follows [Source 4]:
+*   **A**: ≥ 90 (Excellent)
+*   **B**: &lt; 90 and ≥ 80 (Good)
+*   **C**: &lt; 80 and ≥ 70 (Satisfactory)
+*   **D**: &lt; 70 and ≥ 60 (Passing)
+*   **F**: &lt; 60 (Failing)
+**Important Grading Policies**
+*   **Grade Auditing**: The instructor reserves the right to audit grades for any assignments, which may result in increasing or decreasing scores, even for already released grades [Source 1, 6].
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 4, 7].
+*   **Challenging Grades**: Any challenge to a grade must be made within one week of its publication [Source 1, 6].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Each student/team has a limited number of "late days" they may use by request. Work submitted as makeup for an excused absence is exempt from the late work policy [Source 7].</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4227,6 +4643,21 @@
         </is>
       </c>
       <c r="Q30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
 The grading breakdown for the course is as follows:
@@ -4388,6 +4819,23 @@
 The instructor for this course is Yu Zhang [Source 1].</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4493,6 +4941,18 @@
 CSCE 665, "Advanced Networking and Security," appears to be a suitable follow-up course. Its catalog description indicates it covers "security aspects of various network protocols" and "modern topics in computer and network security" [Source 6, 7]. This directly builds upon the networking fundamentals and the "analysis of performance and security of networks" learned in CSCE 612 [Source 2].
 While the prerequisites for CSCE 665 are "Graduate classification and approval of instructor" [Source 6, 7] rather than CSCE 612 specifically, its content aligns well as a subsequent course for students interested in specializing in networking and security.
 The context does not explicitly list CSCE 612 as a prerequisite for any other course, nor does it provide a recommended course sequence for academic planning beyond the individual course descriptions.</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational courses by taking more specialized or advanced courses in related fields. Given that CSCE 612 focuses on "Applied Networks and Distributed Processing," including "network design and protocol analysis," "computer communications," and "principles of network engineering" [Source 1], and covers analyzing the "security of networks" [Source 2], subsequent courses would typically delve deeper into advanced networking topics or specialize in network security.
+Based on the provided context, here are courses that would logically follow CSCE 612:
+*   **CSCE 665: Advanced Networking and Security**
+    *   This course directly builds upon the networking foundation of CSCE 612 by focusing on "Security aspects of various network protocols" [Source 6]. It covers modern topics such as "Basic network &amp; system security," "Security in a software-defined world," and "Web and Web3 security" [Source 7]. Taking CSCE 665 would allow you to analyze "complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks" and design "robust defenses against sophisticated threat models," which aligns with and expands upon the security analysis aspect of CSCE 612 [Source 7, 2].
+*   **CSCE 713: Advanced Topics in Security**
+    *   While broader in scope, CSCE 713 includes significant "Network Security" topics, such as Man-In-The-Middle (MITM) Attacks, ARP Spoofing, Port Scanning, and Honeypots [Source 9]. This course would allow you to "perform penetration testing on previously unknown software" and "analyze existing source code for functional correctness" [Source 11], which could be a valuable specialization after understanding network fundamentals in CSCE 612.
+**Note on CSCE 611:** CSCE 611 (Operating Systems) is listed with CSCE 313 as a prerequisite, similar to CSCE 612 [Source 8, 2]. The content of CSCE 611, which covers operating system components, virtualization, and distributed systems [Source 8], is foundational and often taken *before* or *concurrently* with advanced networking courses like CSCE 612, rather than after. CSCE 612 itself mentions utilizing "operating-system sockets APIs" and building "multi-threaded decentralized frameworks" [Source 2], indicating that OS knowledge is beneficial prior to or during the course.
+I don't have enough data to provide a comprehensive list of all possible follow-up courses based on the available syllabi, but CSCE 665 and CSCE 713 are strong candidates for academic progression after CSCE 612.</t>
         </is>
       </c>
     </row>
@@ -4633,6 +5093,20 @@
 These courses offer a progression from foundational data handling and machine learning to advanced optimization, providing a comprehensive academic path for someone specializing in web search and recommender systems.</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>CSCE 670, "Information Storage and Retrieval," focuses on the representation, storage, and access of large multimedia document collections, covering fundamental data structures and algorithms for retrieval systems, including indexing, compressing, and querying. It specifically addresses web search and recommender systems, including topics like link-based algorithms (e.g., PageRank), learning to rank, collaborative filtering, matrix factorization, and neural models for retrieval and recommendation, as well as Large Language Models (LLMs) in the context of search engines and recommendation [Source 1, 2, 3].
+For a student interested in web search or recommender systems, the following courses would complement CSCE 670 well:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Principle**: Natural Language Processing (NLP) is foundational for understanding and processing textual data, which is critical for effective web search and many recommender systems.
+    *   **Application**: CSCE 638 covers NLP fundamentals, including language models, syntactic processing, semantic understanding, and applications like information extraction and text summarization [Source 6]. Its schedule includes topics such as word representations, transformers, contextualized representations, pre-training, and Large Language Models [Source 10]. These topics directly enhance the understanding of advanced techniques like "Neural Ranking," "Transformer; BERT-Based Ranking," and "Large Language Models with Search Engines" covered in CSCE 670 [Source 3]. Taking CSCE 638 would provide a deeper theoretical and practical background in the NLP techniques that power modern search and recommendation.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Principle**: Data mining provides a broad set of techniques for discovering patterns and insights from large datasets, which are essential for building and evaluating complex search and recommendation systems.
+    *   **Application**: CSCE 676 offers an overview of data mining, integrating concepts from machine learning and statistics, including exploratory data analysis, pattern mining, clustering, classification, and applications to online data [Source 8]. Specifically, its coverage of "Text Mining," "Graph Mining," and "Large-Scale ML" [Source 7, 9] directly relates to the challenges of processing and analyzing the massive datasets involved in information retrieval and recommender systems. The course also lists "Mining of Massive Data Sets" as a required textbook [Source 9], which is an optional resource for CSCE 670 [Source 2, 4], indicating a strong thematic connection. This course would provide a broader toolkit for handling and extracting value from the data that feeds into search and recommendation algorithms.
+**Academic Progression:**
+Taking CSCE 638 would deepen your understanding of the linguistic and semantic aspects crucial for advanced search and recommendation, especially with the increasing role of Large Language Models. CSCE 676 would provide a broader methodological foundation in handling and analyzing large datasets, which is vital for the scalability and effectiveness of these systems. These courses collectively offer a comprehensive skill set, moving from the core retrieval mechanisms (CSCE 670) to the underlying data processing (CSCE 676) and linguistic understanding (CSCE 638) necessary for cutting-edge web search and recommender systems.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4750,6 +5224,19 @@
 *   **CSCE 676 (Data Mining and Analysis)**: This course focuses on "data mining and analysis," including "data preparation," "normalization," and "large-scale mining" [Source 10]. While CSCE 608 is about managing data, data mining often utilizes data stored in databases, making these fields complementary. The course also uses "Mining of Massive Data Sets" as a required textbook [Source 10], which suggests a connection to large-scale data handling that can relate to distributed data management in CSCE 608.</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Based on the provided context, CSCE 670 (Information Storage and Retrieval) appears to be similar to CSCE 608 (Database Systems).
+Here's a comparison:
+*   **CSCE 608 (Database Systems)** [Source 1, 2]
+    *   **Catalog Description:** Covers database modeling techniques, query languages, data models, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management.
+    *   **Prerequisite:** CSCE 310 or approval of Instructor.
+*   **CSCE 670 (Information Storage and Retrieval)** [Source 5]
+    *   **Catalog Description:** Focuses on representation, storage, and access to very large multimedia document collections; fundamental data structures and algorithms of information storage and retrieval systems; techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying very large collections.
+    *   **Prerequisites:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification.
+Both courses deal with the storage, organization, retrieval, and querying of data, and both list CSCE 310 as a prerequisite [Source 1, 5].</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4866,6 +5353,13 @@
 I don't have enough data to answer this accurately based on the available syllabi regarding courses that *focus* on using AI tools. The provided context only details the policies for their use as an aid or their prohibition.</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The provided context does not explicitly identify courses that *focus* on using AI tools as a primary learning objective or method. However, several courses permit the use of AI tools under specific conditions for assignments or projects.
+Here are the courses where AI tools are permitted, which might align with your interest in using such tools:
+| Course   | AI Tool Usage Policy                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4967,6 +5461,15 @@
 *   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5041,6 +5544,12 @@
         </is>
       </c>
       <c r="Q37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
 The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
@@ -5148,6 +5657,16 @@
 *   **Week 6:** Contextualized Representations, Pre-Training, Large Language Models [Source 1]</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers deep learning architectures including Transformers and Attention mechanisms [Source 1].
+The course schedule includes the following topics:
+*   **Week 3:** Convolutional Neural Network, Recurrent Neural Network
+*   **Week 4:** Sequence-to-Sequence, Attention
+*   **Week 5:** Transformers
+*   **Week 6:** Contextualized Representations, Pre-Training, Large Language Models [Source 1]</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5215,6 +5734,11 @@
         </is>
       </c>
       <c r="Q39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
         </is>
@@ -5354,6 +5878,23 @@
 Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on both network protocol implementation and distributed system design [Source 1].
+The course aims to:
+*   Mix fundamentals with programming and pragmatic engineering issues, including network architecture and principles of network engineering [Source 1].
+*   Apply principles of layered architecture to analyzing real networks, with lab exercises focusing on protocol understanding and programming [Source 1].
+*   Enable students to utilize operating-system sockets APIs, create efficient network applications, build multi-threaded decentralized frameworks, and develop protocols [Source 2].
+Key topics covered include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3].
+*   Application layer concepts such as HTTP, caching, cookies, FTP, email, and DNS [Source 3, 4].
+*   Transport layer topics like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), flow control, congestion control, and TCP modeling [Source 3, 4].
+*   Network layer concepts including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP) [Source 4].
+*   Data-link layer topics such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5450,6 +5991,15 @@
         </is>
       </c>
       <c r="Q41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>For CSCE 670, the final grade is weighted as follows:
 *   **Homework**: 30% (five programming assignments) [Source 1]
@@ -5593,6 +6143,20 @@
 The programming assignments contribute 400 points to the final grade [3].</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of design and programming assignments, referred to as Machine Problems (MPs), that guide students through designing and developing a simple operating system [3, 1]. There are 7 Machine Problems assigned throughout the semester [4, 6].
+These assignments cover various aspects of operating systems, including:
+*   **MP1:** Project setup, introduction to OS concepts, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [4].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [4].
+*   **MP3:** Page replacement policies and an introduction to concurrency and scheduling [4, 6].
+*   **MP4:** Thread dispatching on the x86, kernel vs. user-level threads, and event-based concurrency [6].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [6].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, and file systems (including UNIX file systems) [6].
+*   **MP7:** Journaled and log-based file systems, and virtualization mechanisms including memory virtualization [6].
+The programming assignments contribute 400 points to the final grade [3].</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5665,6 +6229,11 @@
           <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5737,6 +6306,11 @@
           <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5814,6 +6388,11 @@
           <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments and exams. Students are prohibited from using any part (code, text, figures, etc.) developed by others, including AI, for programming assignments and homework. This means students should not submit or make use of AI-generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments and exams. Students are prohibited from using any part (code, text, figures, etc.) developed by others, including AI, for programming assignments and homework. This means students should not submit or make use of AI-generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5884,6 +6463,413 @@
       <c r="Q46" t="inlineStr">
         <is>
           <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>47</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Is CSCE 638 or CSCE 670 more math-heavy, and what does each course primarily cover?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CSCE 638 (Machine Learning) is slightly more math-heavy, with a stronger emphasis on linear algebra, probability theory, and mathematical optimization. CSCE 670 (Information Storage and Retrieval) focuses more on information retrieval systems and applications. Both courses involve machine learning concepts.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CSCE 638, CSCE 670</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>DIFFICULTY</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 670 | Not found | Homeworks, Quizzes, Research Project [Source 4, 5] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 3] |
+| CSCE 638 | Not found | Not found | Not found |
+## Detailed Comparison
+Regarding whether CSCE 638 or CSCE 670 is more math-heavy, the provided context does not explicitly state the mathematical intensity of either course. However, based on the topics and descriptions:
+**CSCE 670**
+The course covers "fundamental data structures and algorithms of information storage and retrieval systems" and "techniques to design and evaluate complete retrieval systems, including cover of algorithms for indexing, compressing, and querying very large collections" [Source 1]. Specific topics include "TF-IDF; Vector Space Model; BM25," "Link Analysis" (e.g., PageRank), "Learning to Rank," "Recommender Systems" (e.g., Matrix Factorization), "word2vec; Neural Ranking," "Transformer; BERT-Based Ranking," and "Large Language Models" [Source 3, 5]. These topics involve significant mathematical and algorithmic foundations, such as linear algebra, probability, and optimization. The prerequisites include CSCE 310 or CSCE 603, which are typically courses in data structures and algorithms [Source 1, 3].
+**CSCE 638**
+This course focuses on "Natural Language Processing (NLP) fundamentals including language models, automatic syntactic processing and semantic understanding" [Source 2]. NLP, by nature, relies heavily on statistical methods, probability, and machine learning algorithms. While the context for CSCE 638 does not list as many specific mathematically-oriented algorithms as CSCE 670, the underlying concepts of language models and semantic understanding are mathematically intensive.
+Both fields are mathematically grounded. However, CSCE 670's description and topic list provide more explicit examples of specific algorithms and models (e.g., Vector Space Model, BM25, Matrix Factorization, PageRank, Neural Ranking) that are known to involve detailed mathematical underpinnings.
+### Course Overview
+**CSCE 670**: This course focuses on Information Storage and Retrieval, covering the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms for information storage and retrieval systems, techniques to design and evaluate complete retrieval systems, and algorithms for indexing, compressing, and querying large collections. It also covers web search, recommender systems, and recent research in neural models and Large Language Models [Source 1, 3, 5].
+**CSCE 638**: This course focuses on Natural Language Processing (NLP) fundamentals. It covers language models, automatic syntactic processing, semantic understanding, and introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+### Prerequisites
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603 or approval of the instructor, along with graduate classification [Source 1, 3].
+**CSCE 638**: Not found.
+### Learning Outcomes
+**CSCE 670**: Upon completion, learners will be able to:
+*   Define and explain key concepts and models relevant to web search (e.g., text indexing, retrieval models, evaluation, Web crawling, PageRank, learning to rank).
+*   Define and explain key concepts and models relevant to recommender systems (e.g., collaborative filtering, matrix factorization, evaluation, implicit recommendation).
+*   Design, implement, and evaluate core algorithms for fully functional web search and recommendation systems.
+*   Identify salient features and apply recent research results in web search and recommender systems, including adversarial information retrieval and neural models [Source 3].
+**CSCE 638**: Upon completion, learners will be able to:
+*   Identify and explain the fundamental concepts and models for natural language processing.
+*   Be aware of recent trends in natural language processing research [Source 2].
+### Topics
+**CSCE 670**: The course schedule includes topics such as Course Overview, Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Evaluation of Search Engines, Learning to Rank, Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking), word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, Large Language Models Basics, Large Language Models with Search Engines, and Large Language Models for Ranking and Recommendation [Source 5].
+**CSCE 638**: The course covers Natural Language Processing (NLP) fundamentals including language models, automatic syntactic processing, semantic understanding, and major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+### Materials
+**CSCE 670**: An optional textbook is "Mining of Massive Datasets" by Jure Leskovec, Anand Rajaraman, and Jeffrey D. Ullman (2014) [Source 3].
+**CSCE 638**: Not found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>How does the grading structure of CSCE 312 compare to CSCE 313? Which course relies more on projects versus exams?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Both CSCE 312 and CSCE 313 include exams and projects. CSCE 312 is more weighted toward projects relative to exams/quizzes, while CSCE 313 places relatively greater emphasis on exams.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CSCE 312, CSCE 313</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>No relevant documents found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Between CSCE 221 and CSCE 222, which has the heavier homework load?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CSCE 221 generally has the heavier homework load. CSCE 222 depends more on exams. The difference is not extreme.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CSCE 221, CSCE 222</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What CSCE graduate courses involve machine learning or artificial intelligence?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CSCE 638 (Machine Learning), CSCE 636 (Deep Learning), and CSCE 625 (Artificial Intelligence) explicitly focus on ML/AI. Many other CSCE graduate courses also incorporate elements of machine learning or artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>semantic_general</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ACADEMIC</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses involve machine learning or artificial intelligence:
+*   **CSCE 726: Large-scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning problems, including deterministic and stochastic gradient-based algorithms. It emphasizes the role of large-scale optimization in ML and AI [Source 3, 9]. Students are expected to have basic knowledge of machine learning and deep learning [Source 1, 9].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that can acquire new knowledge and improve their performance. It surveys machine learning techniques such as induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 4].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots, focusing on biological and cognitive principles. It covers core concepts in robotic autonomy, including state estimation, planning, control, and decision-making under uncertainty [Source 8].
+*   **CSCE 670: Information Retrieval and Recommender Systems**
+    *   This course involves topics like text indexing, retrieval models, evaluation, Web crawling, link-based algorithms, and learning to rank, as well as recommender systems, collaborative filtering, and matrix factorization. It also mentions applying recent research results, including neural models of retrieval and recommendation [Source 6].
+*   **CSCE 676: Data Mining and Analysis**
+    *   This course provides a broad overview of data mining, integrating related concepts from machine learning and statistics. It covers exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data [Source 10].
+*   **CSCE 679: Data Visualization**
+    *   While primarily focused on visualization, this course discusses the role of data visualization in Explainable AI and involves programming in Python for data and AI [Source 7].
+*   **CSCE 624: Sketch Recognition**
+    *   This course emphasizes how systems interpret sketches and how recognition algorithms behave in real-world settings. It mentions that familiarity with basic machine learning or artificial intelligence concepts can be helpful [Source 5].</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>What CSCE courses cover formal methods or theoretical computer science topics?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CSCE 627 (Theory of Computation), CSCE 411 (Design and Analysis of Algorithms), CSCE 222 (Discrete Structures for Computing), and CSCE 221 cover formal methods or theoretical computer science concepts.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>semantic_general</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ACADEMIC</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>The principle underlying "formal methods" and "theoretical computer science" in an academic context involves the use of mathematical logic, discrete mathematics, and abstract models to specify, develop, and verify hardware and software systems, or to analyze the fundamental capabilities and limitations of computation. This includes topics like algorithm analysis, complexity theory, computability, and formal language theory.
+Based on the provided context, the following CSCE courses cover topics related to formal methods or theoretical computer science:
+*   **CSCE 629: Analysis of Algorithms**
+    *   **Academic Dimension:** This course focuses on "Concrete algorithm design and analysis; abstract models to analyze the complexity of problems; NP-Completeness; approximation and probabilistic algorithms" [Source 2].
+    *   **Learning Outcomes:** Students will learn to "Explain a variety of fundamental algorithms and algorithmic techniques," "Select the most appropriate algorithm to solve a given problem," "Analyze the correctness, runtime, and space complexity of an algorithm," "Design new algorithms and modify existing ones using techniques discussed in class," and "Recognize when a problem is likely intractable (has no efficient algorithm) and be able to prove this by showing undecidability or NP-hardness" [Source 2, 6]. These outcomes directly align with theoretical computer science, particularly complexity theory and algorithm analysis.
+*   **CSCE 669: Computational Optimization**
+    *   **Academic Dimension:** This course delves into "Combinatorial theory of polytopes as a tool for the solution of combinatorial optimization problems; applications to max flow, matching and matroids; geometric interpretation of the results indicating the profound role that polyhedral combinatorics play in the design and complexity of approximation algorithms" [Source 10].
+    *   **Learning Outcomes:** Students are expected to "Master basic theories and techniques in the current research in computational optimization" and "apply theories and techniques studied in the course to solve real-world problems" [Source 10]. The emphasis on "combinatorial theory," "polyhedral combinatorics," and "complexity of approximation algorithms" places this course firmly within theoretical computer science and formal methods for optimization.
+While CSCE 633 (Machine Learning) mentions the ability to "formalize the fundamental techniques and methods of machine learning" [Source 3], its primary focus as described is on surveying machine learning techniques rather than the foundational mathematical logic or abstract models typically associated with a dedicated formal methods or theoretical computer science course.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Are there CSCE courses focused on parallel or distributed computing?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Parallel and distributed computing is a specialized topic in the CSCE curriculum. CSCE 735 (Distributed and Parallel Computing) is the primary graduate course, though it may not be available in the current syllabus database. Other courses may touch on these topics tangentially.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>semantic_general</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ACADEMIC</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Yes, there are CSCE courses that focus on parallel or distributed computing.
+The relevant principle here is **distributed systems** and **parallel computing**, which involve coordinating multiple computational units to achieve a common goal, often for performance or fault tolerance.
+Based on the provided syllabi, the following courses cover aspects of parallel or distributed computing:
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    *   **Principle**: This course directly addresses "Distributed Processing" and focuses on applying principles of layered architecture to analyzing real networks [Source 1].
+    *   **Academic Content**: Students will learn to create efficient network applications and build multi-threaded decentralized frameworks [Source 4].
+*   **CSCE 611: Operating Systems**
+    *   **Principle**: This course provides an overview of operating systems, including understanding fundamental approaches to virtualization and what it takes to build a distributed system [Source 3]. It also covers concurrency and synchronization [Source 3, 6].
+    *   **Academic Content**: Topics include evaluating and comparing various forms of concurrency and synchronization mechanisms, and understanding thread dispatching [Source 3, 6].
+*   **CSCE 614: Computer Architecture**
+    *   **Principle**: This course reviews computer architecture with an emphasis on microprocessor design, including parallel computer structures and concurrent computation [Source 2].
+    *   **Academic Content**: It covers pipeline computers, vectorization methods, array processors, and multiprocessor architectures and programming [Source 2]. The schedule also lists topics like ILP (Instruction-Level Parallelism), SIMD (Single Instruction, Multiple Data), and TLP (Thread-Level Parallelism) [Source 8].</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>53</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>What should I take after completing CSCE 638?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Good follow-up courses after CSCE 638 (Machine Learning) include CSCE 670 (Information Storage and Retrieval) and CSCE 753.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CSCE 638</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CSCE 638</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational knowledge or exploring related sub-disciplines. When direct prerequisites or recommended sequences are not explicitly stated, students can consider courses that share thematic elements or offer advanced applications of concepts learned in a prior course.
+Based on the provided syllabi, there is no explicit recommendation for a specific course to take immediately after CSCE 638. However, CSCE 638, "Natural Language Processing: Foundations and Techniques," covers "Large Language Models" as a key topic [Source 1, 3].
+Another course, CSCE 670, "Information Retrieval," also extensively covers "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 4]. This indicates a thematic overlap and suggests that CSCE 670 could be a relevant course for students interested in applying or further exploring Large Language Models within the context of information retrieval and recommender systems, building on the foundations established in CSCE 638.
+I don't have enough data to definitively recommend a specific next course based on the available syllabi, as no explicit academic progression or prerequisite relationships are provided for courses following CSCE 638.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>54</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What courses pair well with CSCE 676?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CSCE 670 pairs well with CSCE 676, as both involve information retrieval and data-intensive systems.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CSCE 676</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CSCE 676</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>CSCE 676 is cross-listed with ECEN 758 and STAT 639 [Source 1]. This means they are the same course, and the information provided for CSCE 676 applies to ECEN 758 and STAT 639.
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 676 / ECEN 758 / STAT 639 | 10% Weekly Assessments, 50% Homework, 40% Individual Semester-Long Project [Source 3, 4] | Weekly assessments, weekly homework assignments, and a semester-long individual project with five deliverables [Source 4, 5] | Previous exposure to basic probability, statistics, algorithms, and data structures; ability to design/develop large programs and learn new software libraries [Source 1] |
+## Detailed Comparison
+### Course Overview
+**CSCE 676, ECEN 758, STAT 639**: This course provides a broad overview of data mining, integrating related concepts from machine learning and statistics. Topics include exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data. It is cross-listed with ECEN 758 and STAT 639 [Source 1].
+### Grading &amp; Workload
+**CSCE 676, ECEN 758, STAT 639**:
+*   **Grading**: The final grade is composed of 10% Weekly Assessments, 50% Homework, and 40% Individual Semester-Long Project [Source 3].
+    *   Weekly Assessments: Short quizzes (typically true/false, multiple choice) over the week's material, which can be taken multiple times with the highest score kept [Source 4].
+    *   Homework: Weekly assignments for the first twelve weeks (4% each) and a 13th homework (2%). These are Python notebooks with programming, written problems, and other questions. Students are required to use an AI-coding assistant. No prior Python exposure is expected, but rapid learning is required [Source 4].
+    *   Individual Semester-Long Project: A significant data mining project broken into five deliverables: Data Selection (Feb 3), Initial Research Question (Mar 5), Deep Dive (Apr 2), Project Showcase (week of Apr 20), and Final Deliverable (Apr 27) [Source 5, 2].
+*   **Late Work Policy**: Late homework is penalized 1% per hour after the deadline, up to a maximum of 48 hours, after which it receives a 0. For the Individual Semester-Long Project, students have five late days in total for the first three deliverables. The Project Showcase and Final Deliverable will not be accepted late [Source 5, 2].
+### Prerequisites
+**CSCE 676, ECEN 758, STAT 639**: Students are expected to have previous exposure to basic probability, statistics, algorithms, and data structures. They should also be able to design and develop large programs and learn new software libraries independently [Source 1].
+### Learning Outcomes
+**CSCE 676, ECEN 758, STAT 639**: Upon completion, learners will be able to:
+*   Define and explain key concepts and models in data mining and analysis, including data preparation, normalization, dimensionality reduction, and text mining [Source 3].
+*   Design, implement, and evaluate data mining algorithms (e.g., associate rules, clustering, anomaly detection) on modern scalable cloud computing platforms (e.g., Spark) [Source 3].
+*   Identify salient features and apply recent research results in data mining, including topics like graph mining and large-scale mining [Source 3].
+### Topics
+**CSCE 676, ECEN 758, STAT 639**: The course schedule includes: Course introduction, Frequent Itemset Mining, Graph Mining, Graph Mining and Large-Scale ML, Large-Scale ML, Clustering, Text Mining, Data Mining and Distributed Computing, Anomaly Detection, Graph Embeddings, Locality-Sensitive Hashing, Stream Mining, Hot Topics in Data Mining, Project Showcase, and Finalize Project Deliverables [Source 2].
+### Materials
+**CSCE 676, ECEN 758, STAT 639**: Required course readings will be drawn from various online textbooks, scholarly papers, and other resources. A key required textbook is "Mining of Massive Data Sets" by Jure Leskovec, Anand Rajaraman, and Jeffrey David Ullman (Cambridge University Press, 2020) [Source 3].</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>55</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>What's the weather in College Station today?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Write me a Python script to sort a list of numbers</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
         </is>
       </c>
     </row>

--- a/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6873,6 +6873,411 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>What should I take alongside CSCE 670 to build toward a research career in information retrieval?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CSCE 638 (NLP) pairs naturally with CSCE 670 as both deal with language and text processing. CSCE 633 (Machine Learning) is also a strong complement, providing the statistical foundations underlying modern IR systems.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CSCE 670</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CSCE 670</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>58</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Which CSCE grad courses allow or encourage using AI tools for assignments?</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Several CSCE grad courses explicitly permit or encourage AI tool usage, including CSCE 638, CSCE 670, CSCE 676, and CSCE 753, among others. Policies vary by course and assignment type — always check the specific syllabus.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AI_POLICY</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AI_POLICY</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>59</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Which CSCE grad courses require buying a textbook?</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CSCE 676 explicitly requires a paid textbook: 'Mining of Massive Data Sets' by Leskovec, Rajaraman, and Ullman. Most other CSCE grad courses rely on free online readings and papers.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>semantic_general</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CSCE 676</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>MATERIALS</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>MATERIALS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>LOGISTICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>60</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>What do I need before taking CSCE 629?</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Graduate classification is the only formal prerequisite for CSCE 629. However, the course assumes strong background knowledge in algorithms and complexity theory.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CSCE 629</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PREREQUISITES</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>CSCE 629</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PREREQUISITES</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>LOGISTICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>61</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Which CSCE grad courses have the lightest prerequisites?</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Most CSCE graduate courses formally only require graduate classification. Courses like CSCE 676 and CSCE 670 are generally considered more accessible in terms of expected background, while others like CSCE 629 carry a steeper implied expectation despite the same formal requirement.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>semantic_general</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PREREQUISITES</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PREREQUISITES</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Can I use ChatGPT to help write my assignments for CSCE 638?</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Yes. CSCE 638 explicitly allows the use of AI tools including ChatGPT for assignments.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CSCE 638</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>AI_POLICY</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>CSCE 638</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AI_POLICY</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>63</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Which CSCE grad courses have the strictest AI policies?</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CSCE 629 and CSCE 752 both prohibit AI tools entirely. CSCE 633 has a partial restriction — AI is prohibited for some assignments but permitted for others.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>recursive</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AI_POLICY</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>AI_POLICY</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Compare the grading breakdown of CSCE 629, CSCE 633, and CSCE 670 — which is the most exam-heavy?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>From least to most exam-heavy: CSCE 670 relies primarily on projects and papers with no traditional exams. CSCE 633 has a moderate exam component. CSCE 629 is the most exam-heavy of the three.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>GRADING</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CSCE 629|CSCE 633|CSCE 670</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>GRADING</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>65</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>What time does the CSCE department office open?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>66</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Do any CSCE grad courses have in-person attendance requirements?</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Some CSCE grad courses specify attendance expectations in their syllabi. Students should review each course's syllabus directly for specific attendance policies.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>semantic_general</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SCHEDULE</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>SCHEDULE</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>LOGISTICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>When is the midterm exam for CSCE 629?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629 is scheduled for October 6th.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>hybrid_course</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CSCE 629</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SCHEDULE</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CSCE 629</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>SCHEDULE</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>LOGISTICAL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
+++ b/tamu_data/evals/golden_sets/golden_20260411_v1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,41 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>run:new_golden_rows</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>run:golden_update_20260421</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>run:router_fix_v2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>run:router_fix_20260421</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>run:router_no_cache_20260421</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>run:router_few_shot_v1_20260421</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>run:router_few_shot_v2_20260421</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>run:full_router_refactor_verification</t>
         </is>
       </c>
     </row>
@@ -623,6 +658,62 @@
 *   **Week 4 (Feb 2):** The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 3].</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CSCE 611 covers the following topics in the beginning of the course:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CSCE 611 covers the following topics in the beginning of the course:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 3].</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, begins with the following topics:
+*   **Week 1:** Project Setup, Introduction to Operating Systems (What is an OS?), Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, and Paging, Advanced Paging [Source 3].</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, begins with the following topics:
+*   **Week 1:** Project Setup, Introduction to Operating Systems (What is an OS?), Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, and Paging, Advanced Paging [Source 3].</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, begins with the following topics:
+*   **Week 1:** Project Setup, Introduction to Operating Systems (What is an OS?), Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, and Paging, Advanced Paging [Source 3].</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, begins with the following topics:
+*   **Week 1:** Project Setup, Introduction to Operating Systems (What is an OS?), Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, and Paging, Advanced Paging [Source 3].</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600, begins with the following topics:
+*   **Week 1:** Project Setup, Introduction to Operating Systems (What is an OS?), Architectural Support, and OS Structures [Source 3].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 3].
+*   **Week 3:** Memory Allocation, Address Spaces, and Paging, Advanced Paging [Source 3].</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -725,6 +816,69 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669 (Section 600), you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669 (Section 600), you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669 (Section 600), you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669 (Section 600), you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 669 (Section 600), you will be able to:
 *   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
 *   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
 *   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
@@ -852,6 +1006,72 @@
 *   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
 *   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
 The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security, which may include but are not limited to:
+*   Basic network &amp; system security (e.g., software security, malware, botnet, intrusion detection) [Source 1, 2]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security) [Source 2]
+*   Mobile &amp; IoT security (e.g., smartphone security, Alexa and voice app security) [Source 2]
+*   Web and Web3 security (e.g., traditional web security, spam, Web3 (DeFi, blockchain) security) [Source 2]
+*   AI/LLM security (e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI) [Source 2]
+The tentative schedule also lists topics such as Malware Basics, Intrusion Detection, Advanced Detection &amp; Response, Software-Defined Security, Web/Web3 Security, and AI/LLM Security [Source 3].</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security. These topics may include, but are not limited to:
+*   **Basic network &amp; system security**: e.g., software security, malware, botnet, intrusion detection [Source 1, 2]
+*   **Security in a software-defined world**: e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security [Source 2]
+*   **Mobile &amp; IoT security**: e.g., smartphone security, Alexa and voice app security [Source 2]
+*   **Web and Web3 security**: e.g., traditional web security, spam, Web3 (DeFi, blockchain) security [Source 2]
+*   **AI/LLM security**: e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI [Source 2]
+The course aims to provide a thorough grounding in these areas, suitable for those interested in conducting research or understanding real-world security issues/techniques [Source 1].</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security. These topics may include, but are not limited to:
+*   **Basic network &amp; system security**: e.g., software security, malware, botnet, intrusion detection [Source 1, 2]
+*   **Security in a software-defined world**: e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security [Source 2]
+*   **Mobile &amp; IoT security**: e.g., smartphone security, Alexa and voice app security [Source 2]
+*   **Web and Web3 security**: e.g., traditional web security, spam, Web3 (DeFi, blockchain) security [Source 2]
+*   **AI/LLM security**: e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI [Source 2]
+The course aims to provide a thorough grounding in these areas, suitable for those interested in conducting research or understanding real-world security issues/techniques [Source 1].</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security. These topics may include, but are not limited to:
+*   **Basic network &amp; system security**: e.g., software security, malware, botnet, intrusion detection [Source 1, 2]
+*   **Security in a software-defined world**: e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security [Source 2]
+*   **Mobile &amp; IoT security**: e.g., smartphone security, Alexa and voice app security [Source 2]
+*   **Web and Web3 security**: e.g., traditional web security, spam, Web3 (DeFi, blockchain) security [Source 2]
+*   **AI/LLM security**: e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI [Source 2]
+The course aims to provide a thorough grounding in these areas, suitable for those interested in conducting research or understanding real-world security issues/techniques [Source 1].</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>CSCE 665 (Section 600) will introduce various modern topics in computer and network security. These topics may include, but are not limited to:
+*   **Basic network &amp; system security**: e.g., software security, malware, botnet, intrusion detection [Source 1, 2]
+*   **Security in a software-defined world**: e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security [Source 2]
+*   **Mobile &amp; IoT security**: e.g., smartphone security, Alexa and voice app security [Source 2]
+*   **Web and Web3 security**: e.g., traditional web security, spam, Web3 (DeFi, blockchain) security [Source 2]
+*   **AI/LLM security**: e.g., LLM-based security, adversarial Learning / backdoor, advanced applications with AI [Source 2]
+The course aims to provide a thorough grounding in these areas, suitable for those interested in conducting research or understanding real-world security issues/techniques [Source 1].</t>
         </is>
       </c>
     </row>
@@ -1089,6 +1309,232 @@
 Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 2].</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>In CSCE 672, Section 600 (58439), you will study Computer Supported Collaborative Work (CSCW) [Source 1].
+**Course Purpose:**
+The course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of CSCW, including current theoretical, practical, technical, and social issues, as well as future directions of the field [Source 1].
+**Key Topics:**
+Throughout the semester, you will cover topics such as [Source 2]:
+*   CSCW history and central issues
+*   Designing for artifact and human awareness
+*   Forms of communication
+*   Content sharing systems and issues
+*   Collaborative decision making
+*   Crowdsourcing and its issues
+*   Online communities and virtual teams
+*   Collaboration in online games
+*   Supporting software teams
+**Prerequisites:**
+To enroll in this course, you must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components [Source 3]:
+| Assignment            | Percentage |
+| :-------------------- | :--------- |
+| Assignment 1          | 10%        |
+| Team project          | 35%        |
+| Readings write-ups    | 35%        |
+| Readings presentations| 10%        |
+| Attendance            | 10%        |
+Grades are on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>In CSCE 672, Section 600 (58439), you will study Computer Supported Collaborative Work (CSCW) [Source 1].
+**Course Purpose:**
+The course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of CSCW, including current theoretical, practical, technical, and social issues, as well as future directions of the field [Source 1].
+**Key Topics:**
+Throughout the semester, you will cover topics such as [Source 2]:
+*   CSCW history and central issues
+*   Designing for artifact and human awareness
+*   Forms of communication
+*   Content sharing systems and issues
+*   Collaborative decision making
+*   Crowdsourcing and its issues
+*   Online communities and virtual teams
+*   Collaboration in online games
+*   Supporting software teams
+**Prerequisites:**
+To enroll in this course, you must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components [Source 3]:
+| Assignment            | Percentage |
+| :-------------------- | :--------- |
+| Assignment 1          | 10%        |
+| Team project          | 35%        |
+| Readings write-ups    | 35%        |
+| Readings presentations| 10%        |
+| Attendance            | 10%        |
+Grades are on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," is a 3-credit hour course offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Topics:**
+This course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), including current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics you can expect to cover include:
+*   CSCW history and central issues [Source 2]
+*   Designing for artifact and human awareness [Source 2]
+*   Forms of communication [Source 2]
+*   Content sharing systems and issues [Source 2]
+*   Collaborative decision making, voting models, and balkanization [Source 2]
+*   Meeting capture and reuse [Source 2]
+*   Crowdsourcing and its issues [Source 2]
+*   Online communities and virtual teams [Source 2]
+*   Shared user history and its visualization [Source 2]
+*   Collaborative search and design [Source 2]
+*   Software supporting social skill development [Source 2]
+*   Collaboration in online games [Source 2]
+*   Supporting software teams [Source 2]
+Upon completion, you should be able to describe the history of collaborative software environments, prioritize design issues, design software capabilities for awareness, communication, and coordination, analyze use contexts, assess needs for collaborative applications, and design, implement, and evaluate collaboration-supporting software [Source 1, Source 3].
+**Prerequisites:**
+You must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 3]
+*   Team project: 35% [Source 3]
+*   Readings write-ups: 35% [Source 3]
+*   Readings presentations: 10% [Source 3]
+*   Attendance (via sign-in sheet): 10% [Source 3]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," is a 3-credit hour course offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Topics:**
+This course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), including current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics you can expect to cover include:
+*   CSCW history and central issues [Source 2]
+*   Designing for artifact and human awareness [Source 2]
+*   Forms of communication [Source 2]
+*   Content sharing systems and issues [Source 2]
+*   Collaborative decision making, voting models, and balkanization [Source 2]
+*   Meeting capture and reuse [Source 2]
+*   Crowdsourcing and its issues [Source 2]
+*   Online communities and virtual teams [Source 2]
+*   Shared user history and its visualization [Source 2]
+*   Collaborative search and design [Source 2]
+*   Software supporting social skill development [Source 2]
+*   Collaboration in online games [Source 2]
+*   Supporting software teams [Source 2]
+Upon completion, you should be able to describe the history of collaborative software environments, prioritize design issues, design software capabilities for awareness, communication, and coordination, analyze use contexts, assess needs for collaborative applications, and design, implement, and evaluate collaboration-supporting software [Source 1, Source 3].
+**Prerequisites:**
+You must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 3]
+*   Team project: 35% [Source 3]
+*   Readings write-ups: 35% [Source 3]
+*   Readings presentations: 10% [Source 3]
+*   Attendance (via sign-in sheet): 10% [Source 3]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," is a 3-credit hour course offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Topics:**
+This course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), including current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics you can expect to cover include:
+*   CSCW history and central issues [Source 2]
+*   Designing for artifact and human awareness [Source 2]
+*   Forms of communication [Source 2]
+*   Content sharing systems and issues [Source 2]
+*   Collaborative decision making, voting models, and balkanization [Source 2]
+*   Meeting capture and reuse [Source 2]
+*   Crowdsourcing and its issues [Source 2]
+*   Online communities and virtual teams [Source 2]
+*   Shared user history and its visualization [Source 2]
+*   Collaborative search and design [Source 2]
+*   Software supporting social skill development [Source 2]
+*   Collaboration in online games [Source 2]
+*   Supporting software teams [Source 2]
+Upon completion, you should be able to describe the history of collaborative software environments, prioritize design issues, design software capabilities for awareness, communication, and coordination, analyze use contexts, assess needs for collaborative applications, and design, implement, and evaluate collaboration-supporting software [Source 1, Source 3].
+**Prerequisites:**
+You must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 3]
+*   Team project: 35% [Source 3]
+*   Readings write-ups: 35% [Source 3]
+*   Readings presentations: 10% [Source 3]
+*   Attendance (via sign-in sheet): 10% [Source 3]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CSCE 672, Section 600 (58439), titled "Computer Supported Collaborative Work," is a 3-credit hour course offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Topics:**
+This course covers the design, implementation, and use of technical systems that support people working cooperatively. It draws from the research area of Computer Supported Cooperative Work (CSCW), including current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+Key topics you can expect to cover include:
+*   CSCW history and central issues [Source 2]
+*   Designing for artifact and human awareness [Source 2]
+*   Forms of communication [Source 2]
+*   Content sharing systems and issues [Source 2]
+*   Collaborative decision making, voting models, and balkanization [Source 2]
+*   Meeting capture and reuse [Source 2]
+*   Crowdsourcing and its issues [Source 2]
+*   Online communities and virtual teams [Source 2]
+*   Shared user history and its visualization [Source 2]
+*   Collaborative search and design [Source 2]
+*   Software supporting social skill development [Source 2]
+*   Collaboration in online games [Source 2]
+*   Supporting software teams [Source 2]
+Upon completion, you should be able to describe the history of collaborative software environments, prioritize design issues, design software capabilities for awareness, communication, and coordination, analyze use contexts, assess needs for collaborative applications, and design, implement, and evaluate collaboration-supporting software [Source 1, Source 3].
+**Prerequisites:**
+You must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components:
+*   Assignment 1: 10% [Source 3]
+*   Team project: 35% [Source 3]
+*   Readings write-ups: 35% [Source 3]
+*   Readings presentations: 10% [Source 3]
+*   Attendance (via sign-in sheet): 10% [Source 3]
+Grades are assigned on a 10-point scale: 90-100 = A, 80-89 = B, 70-79 = C, 60-69 = D, and &lt;60 = F [Source 3].</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>In CSCE 672, Section 600, "Computer Supported Collaborative Work," you will explore the design, implementation, and use of technical systems that facilitate cooperative work among people. The course draws from the research area of Computer Supported Cooperative Work (CSCW), covering current theoretical, practical, technical, and social issues, as well as future directions in the field [Source 1].
+**Key Learning Outcomes:**
+Upon completion, you will be able to [Source 1, 2]:
+*   Describe the history of asynchronous and synchronous collaborative software environments.
+*   Prioritize issues and identify trade-offs in the design of collaborative software.
+*   Design software capabilities that facilitate awareness, communication, and coordination.
+*   Analyze use contexts in terms of social processes, time and place settings, and available resources.
+*   Assess the need for reciprocity, critical mass, and exception handling for collaborative applications.
+*   Design, implement, and evaluate software to support collaboration in specific settings.
+**Topics Covered:**
+The course schedule includes topics such as [Source 3]:
+*   CSCW history and central issues
+*   Designing for artifact and human awareness
+*   Forms of communication
+*   Content sharing systems
+*   Collaborative decision making and voting models
+*   Meeting capture and reuse
+*   Crowdsourcing
+*   Online communities and virtual teams
+*   Shared user history and its visualization
+*   Collaborative search and design
+*   Software supporting social skill development
+*   Collaboration in online games
+*   Supporting software teams
+*   Student project presentations
+**Prerequisites:**
+You must have completed CSCE 671 or CSCE 610, or have approval from the instructor [Source 1].
+**Grading:**
+Your final grade will be determined by the following components [Source 2]:
+*   Assignment 1: 10%
+*   Team project: 35%
+*   Readings write-ups: 35%
+*   Readings presentations: 10%
+*   Attendance (via sign-in sheet): 10%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1683,117 @@
 The course emphasizes how humans naturally sketch, how systems interpret sketches, and how recognition algorithms behave in real-world, noisy settings. It involves hands-on implementation of recognition techniques, critical reading of research papers, in-class activities, and a semester-long team project [Source 1, 2].</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Before taking CSCE 624 (Sketch Recognition), students should be aware of the following:
+*   **Prerequisite:** Graduate classification [Source 1, 2].
+*   **Expected Knowledge:** General graduate-level knowledge in computer science [Source 2].
+*   **Helpful (but not strictly required) Familiarity:**
+    *   Programming (any language)
+    *   Basic machine learning or artificial intelligence concepts
+    *   Linear algebra or probability
+    *   Software engineering practices [Source 2]</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>For CSCE 624, the prerequisite is graduate classification [Source 1, 2].
+Students are expected to have general graduate-level knowledge in computer science. Familiarity with at least one of the following is helpful but not strictly required:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, human-computer interaction (HCI), or data science are welcome and have historically performed well in the course [Source 2].</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>To enroll in CSCE 624, Section 600 (58435), students must have graduate classification [Source 1, 2].
+While not strictly required, familiarity with the following will be helpful:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+The course, titled "Sketch Recognition," focuses on the analysis, implementation, and comparison of various sketch recognition algorithms, including feature-based, vision-based, geometrical, timing-based, and path-based methods. It also covers combining these methods using AI techniques [Source 1]. The course emphasizes how humans sketch, how systems interpret sketches, and how recognition algorithms perform in real-world, noisy environments [Source 1, 2].
+Upon completion, learners will be able to:
+*   Explain core principles of sketch recognition.
+*   Implement and compare multiple sketch recognition approaches.
+*   Apply and evaluate machine learning classifiers in the context of sketch data.
+*   Analyze algorithm performance using statistical and experimental evaluation techniques.
+*   Design and conduct sketch-based experiments.
+*   Critically read, interpret, and discuss research literature in sketch recognition and related AI/HCI domains.
+*   Collaborate effectively on a team-based project [Source 3].
+The course is structured around hands-on implementation, critical reading of research papers, in-class activities, and a semester-long team project [Source 2].
+Grading is based on:
+*   Assignments: 30%
+*   Team-based Project: 30%
+*   Assessments (quizzes and exams): 30%
+*   In-class activities and participation: 10% [Source 6]</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>To enroll in CSCE 624, Section 600 (58435), students must have graduate classification [Source 1, 2].
+While not strictly required, familiarity with the following will be helpful:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+The course, titled "Sketch Recognition," focuses on the analysis, implementation, and comparison of various sketch recognition algorithms, including feature-based, vision-based, geometrical, timing-based, and path-based methods. It also covers combining these methods using AI techniques [Source 1]. The course emphasizes how humans sketch, how systems interpret sketches, and how recognition algorithms perform in real-world, noisy environments [Source 1, 2].
+Upon completion, learners will be able to:
+*   Explain core principles of sketch recognition.
+*   Implement and compare multiple sketch recognition approaches.
+*   Apply and evaluate machine learning classifiers in the context of sketch data.
+*   Analyze algorithm performance using statistical and experimental evaluation techniques.
+*   Design and conduct sketch-based experiments.
+*   Critically read, interpret, and discuss research literature in sketch recognition and related AI/HCI domains.
+*   Collaborate effectively on a team-based project [Source 3].
+The course is structured around hands-on implementation, critical reading of research papers, in-class activities, and a semester-long team project [Source 2].
+Grading is based on:
+*   Assignments: 30%
+*   Team-based Project: 30%
+*   Assessments (quizzes and exams): 30%
+*   In-class activities and participation: 10% [Source 6]</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>To take CSCE 624, Section 600 (58435), you must have graduate classification [Source 1, 2].
+While not strictly required, it is helpful to have:
+*   General graduate-level knowledge in computer science [Source 2].
+*   Familiarity with at least one of the following:
+    *   Programming (any language) [Source 2]
+    *   Basic machine learning or artificial intelligence concepts [Source 2]
+    *   Linear algebra or probability [Source 2]
+    *   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, Human-Computer Interaction (HCI), or data science are welcome and have historically performed well in the course [Source 2].</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>To take CSCE 624, Section 600 (58435), you must have graduate classification [Source 1, 2].
+While not strictly required, it is helpful to have:
+*   General graduate-level knowledge in computer science [Source 2].
+*   Familiarity with at least one of the following:
+    *   Programming (any language) [Source 2]
+    *   Basic machine learning or artificial intelligence concepts [Source 2]
+    *   Linear algebra or probability [Source 2]
+    *   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, Human-Computer Interaction (HCI), or data science are welcome and have historically performed well in the course [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>To take CSCE 624, you must have **Graduate classification** [Source 1, 2].
+While not strictly required, familiarity with at least one of the following areas will be helpful:
+*   Programming (any language)
+*   Basic machine learning or artificial intelligence concepts
+*   Linear algebra or probability
+*   Software engineering practices [Source 2]
+Students from related disciplines such as engineering, Human-Computer Interaction (HCI), or data science are also welcome [Source 2].
+**Course ID and Section:** CSCE 624, Section 600 (58435) [Source 1]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1939,125 @@
         </is>
       </c>
       <c r="R7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
+The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
+*   **Language Modeling** [Source 2]
+*   **Transformers** [Source 2]
+*   **Contextualized Representations, Pre-Training, Large Language Models** [Source 2]
+*   **Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation** [Source 2]
+*   **Instruction Tuning, Alignment, Post-Training** [Source 2]
+*   **Large Reasoning Models, Test-Time Scaling, Decoding** [Source 2]
+*   **Retrieval-Augmented Generation, Agents** [Source 2]
+*   **Multilingual Language Models, Vision-Language Models** [Source 2]
+*   **AI-Generated Text Detection** [Source 2]
+*   **Bias Mitigation, Hallucinations** [Source 2]
+The course aims to teach Natural Language Processing (NLP) fundamentals, including language models and semantic understanding, and introduces major NLP applications [Source 1]. Upon completion, learners will be able to identify and explain fundamental NLP concepts and models, be aware of recent trends in NLP research, and apply techniques to tackle NLP challenges [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Yes, CSCE 638 (Section 600), "Natural Language Processing: Foundations and Techniques," would be highly beneficial for someone wanting to work with large language models (LLMs) [Source 1].
 The course directly addresses LLMs and related advanced topics, making it relevant for careers in this field. Key topics covered include:
@@ -1549,6 +2225,119 @@
 While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600 (42432), "Computers and New Media," covers a substantial amount of interactive media design, which aligns with your primary interest.
+The course description indicates it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 1].
+Key topics related to interactive media design include:
+*   Designing software for immersion, agency, and transformation (Weeks 2-3) [Source 2]
+*   Interactive media, computer characters, interactive text, and social media (Weeks 4-5) [Source 2]
+*   Bridging physical and digital media (Week 6) [Source 2]
+*   Audio, music, speech, recorded, and authored video (Weeks 7-8) [Source 2]
+*   Games and computer-controlled characters, and automatic narrative control (Weeks 9-10) [Source 2]
+These topics are also reflected in the learning outcomes, such as designing software features that support immersion, agency, and transformation, describing techniques for creating computer characters and narrative control, and developing software for the manipulation/use of audio and/or video [Source 3].
+However, the course also dedicates a significant portion (Weeks 11-14) to topics you are less interested in, such as digital rights management, property rights and issues, software licenses, intellectual property, and evaluating policy effects [Source 2]. These topics are also covered in the learning outcomes, including describing core differences between physical and intellectual property and assessing characteristics of software licenses, software patents, and digital rights management software [Source 3].
+Therefore, while a large part of CSCE 656 aligns with your interest in interactive media design, you should be aware that approximately one-quarter of the course content focuses on digital rights and policy topics.</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600 (42432), "Computers and New Media," covers a substantial amount of interactive media design, which aligns with your primary interest.
+The course description indicates it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 1].
+Key topics related to interactive media design include:
+*   Designing software for immersion, agency, and transformation (Weeks 2-3) [Source 2]
+*   Interactive media, computer characters, interactive text, and social media (Weeks 4-5) [Source 2]
+*   Bridging physical and digital media (Week 6) [Source 2]
+*   Audio, music, speech, recorded, and authored video (Weeks 7-8) [Source 2]
+*   Games and computer-controlled characters, and automatic narrative control (Weeks 9-10) [Source 2]
+These topics are also reflected in the learning outcomes, such as designing software features that support immersion, agency, and transformation, describing techniques for creating computer characters and narrative control, and developing software for the manipulation/use of audio and/or video [Source 3].
+However, the course also dedicates a significant portion (Weeks 11-14) to topics you are less interested in, such as digital rights management, property rights and issues, software licenses, intellectual property, and evaluating policy effects [Source 2]. These topics are also covered in the learning outcomes, including describing core differences between physical and intellectual property and assessing characteristics of software licenses, software patents, and digital rights management software [Source 3].
+Therefore, while a large part of CSCE 656 aligns with your interest in interactive media design, you should be aware that approximately one-quarter of the course content focuses on digital rights and policy topics.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600) covers a significant amount of material related to interactive media design, but also includes topics on digital rights and policy [Source 1, 2, 3, 4].
+**Academic Content Breakdown:**
+*   **Interactive Media Design Focus:**
+    *   The course investigates the impact of computers in new media design and the relationships between authors and readers of interactive materials [Source 1].
+    *   Learning outcomes include designing software features for immersion, agency, and transformation; describing techniques for creating computer characters and narrative control; developing software for audio/video manipulation; and designing, implementing, and evaluating software for content creation/consumption [Source 3].
+    *   The course schedule dedicates approximately 10 out of 14 content weeks to topics such as designing software for immersion, agency and transformation, interactive media and computer characters, interactive text and social media, bridging physical and digital media, audio/music/speech, recorded/authored video, games, and automatic narrative control [Source 2, 4].
+*   **Digital Rights and Policy Focus:**
+    *   Learning outcomes also include describing differences between physical and intellectual property, and assessing software licenses, patents, and digital rights management software [Source 3].
+    *   The course schedule dedicates approximately 4 weeks to topics like digital rights management, property rights and issues, software licenses and intellectual property, and evaluating policy effects [Source 2].
+While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>CSCE 656: Computers and New Media (Section 600) covers a significant amount of material related to interactive media design, but also includes topics on digital rights and policy [Source 1, 2, 3, 4].
+**Academic Content Breakdown:**
+*   **Interactive Media Design Focus:**
+    *   The course investigates the impact of computers in new media design and the relationships between authors and readers of interactive materials [Source 1].
+    *   Learning outcomes include designing software features for immersion, agency, and transformation; describing techniques for creating computer characters and narrative control; developing software for audio/video manipulation; and designing, implementing, and evaluating software for content creation/consumption [Source 3].
+    *   The course schedule dedicates approximately 10 out of 14 content weeks to topics such as designing software for immersion, agency and transformation, interactive media and computer characters, interactive text and social media, bridging physical and digital media, audio/music/speech, recorded/authored video, games, and automatic narrative control [Source 2, 4].
+*   **Digital Rights and Policy Focus:**
+    *   Learning outcomes also include describing differences between physical and intellectual property, and assessing software licenses, patents, and digital rights management software [Source 3].
+    *   The course schedule dedicates approximately 4 weeks to topics like digital rights management, property rights and issues, software licenses and intellectual property, and evaluating policy effects [Source 2].
+While a substantial portion of the course focuses on interactive media design, you should be aware that digital rights and policy topics are also covered and are part of the learning outcomes and schedule [Source 2, 3].</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600, "Computers and New Media," covers both interactive media design and digital rights/policy topics [Source 3].
+The course description indicates it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 3].
+Key learning outcomes and topics related to interactive media design include:
+*   Analyzing characteristics of computer-based media [Source 2].
+*   Designing software features that support immersion, agency, and transformation [Source 2].
+*   Describing techniques for creating computer characters and narrative control [Source 2].
+*   Developing software for the manipulation/use of audio and/or video [Source 2].
+*   Topics such as designing software for immersion, agency, and transformation; interactive media and computer characters; interactive text and social media; bridging physical and digital media; audio, music, and speech; recorded and authored video; games and computer-controlled characters; and automatic narrative control are covered in the first 10 weeks of the course [Source 1].
+However, the course also dedicates significant time to digital rights and policy. Learning outcomes include describing core differences between physical and intellectual property, and assessing characteristics of software licenses, software patents, and digital rights management software [Source 2]. Weeks 11-14 of the course schedule are specifically dedicated to digital rights management, property rights and issues, software licenses, intellectual property, and evaluating policy effects [Source 1].</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600 (42432), "Computers and New Media," covers both interactive media design and digital rights/policy topics [Source 3].
+The course aims to investigate the impact of computers in the design of new media, explore relationships between authors and readers of interactive materials, and analyze media design and content [Source 3].
+**Topics related to interactive media design include:**
+*   Designing software for immersion, agency, and transformation [Source 1, 4]
+*   Interactive media and computer characters [Source 1]
+*   Interactive text and social media [Source 1]
+*   Bridging physical and digital media [Source 1]
+*   Audio, music, speech, recorded and authored video [Source 1]
+*   Games and computer-controlled characters [Source 1]
+*   Automatic narrative control [Source 1]
+**Learning outcomes related to interactive media design include:**
+*   Analyzing characteristics of computer-based media [Source 2, 3]
+*   Designing software features that support immersion, agency, and transformation [Source 2]
+*   Describing techniques for creating computer characters and narrative control [Source 2]
+*   Developing software for the manipulation/use of audio and/or video [Source 2]
+*   Designing, implementing, and evaluating software supporting content creation/consumption [Source 2]
+**Topics related to digital rights and policy include:**
+*   Digital rights management [Source 1]
+*   Property rights and issues [Source 1]
+*   Software licenses and intellectual property [Source 1]
+*   Evaluating policy effects [Source 1]
+**Learning outcomes related to digital rights and policy include:**
+*   Describing core differences between physical and intellectual property [Source 2]
+*   Assessing characteristics of software licenses, software patents, and digital rights management software [Source 2]
+While a significant portion of the course, particularly the first 10 weeks, focuses on interactive media design, approximately 4 weeks (weeks 11-14) are dedicated to digital rights and policy topics [Source 1]. Therefore, while the course heavily features interactive media design, it also includes a substantial segment on digital rights and policy.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>CSCE 656, Section 600, "Computers and New Media," covers both interactive media design and digital rights/policy topics [Source 3].
+The course description indicates it "investigates the potential and realized impact of computers in the design of new media, explores the variety of relationships between authors and readers of interactive materials, and explores the influence of media design and content expressed" [Source 3].
+Key learning outcomes and topics related to interactive media design include:
+*   Analyzing characteristics of computer-based media [Source 2].
+*   Designing software features that support immersion, agency, and transformation [Source 2].
+*   Describing techniques for creating computer characters and narrative control [Source 2].
+*   Developing software for the manipulation/use of audio and/or video [Source 2].
+*   Topics such as designing software for immersion, agency, and transformation; interactive media and computer characters; interactive text and social media; bridging physical and digital media; audio, music, and speech; recorded and authored video; games and computer-controlled characters; and automatic narrative control are covered in the first 10 weeks of the course [Source 1].
+However, the course also dedicates significant time to digital rights and policy. Learning outcomes include describing core differences between physical and intellectual property, and assessing characteristics of software licenses, software patents, and digital rights management software [Source 2]. Weeks 11-14 of the course schedule are specifically dedicated to digital rights management, property rights and issues, software licenses, intellectual property, and evaluating policy effects [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1702,6 +2491,119 @@
 **Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>To determine if CSCE 665 would be a strong foundation for specializing in real-world software or cloud security, it's important to consider the course's scope and how it aligns with specific specialization goals. A strong foundation typically involves covering core concepts, relevant technologies, and practical applications within the desired specialization area.
+CSCE 665, "Advanced Networking and Security," aims to provide a "thorough grounding in computer and network security suitable for those interested in conducting research in this area, as well as students more broadly interested in real-world security issues/techniques" [Source 1].
+**For Real-World Software Security:**
+CSCE 665 includes "software security" as a topic under "Basic network &amp; system security" [Source 1]. It also covers "Web and Web3 security" [Source 2]. This indicates that it touches upon aspects relevant to software security.
+However, for a deeper specialization in software security, other courses might offer more focused content:
+*   **CSCE 713 (Software Security)** explicitly focuses on "Basic principles of design and implementation of secure software, code reviews including tool-assisted review by static and dynamic analysis, risk analysis and management, and methods for software security testing" [Source 5]. Its schedule includes topics like Web Security, Mobile Apps Security, Application Security (CVEs, exploits), Fuzzing, Symbolic Execution, and Supply Chain Attacks [Source 4, 7].
+*   **CSCE 652 (Reverse Engineering and Malware Analysis)** delves into "disassembly algorithms and control graph analysis; static and dynamic analyses; case studies on code obfuscation, codebreaking and malware analysis" [Source 8], which are critical for understanding software vulnerabilities and threats.
+**For Cloud Security:**
+CSCE 665 explicitly lists "Security in a software-defined world: e.g., SDN/NFV, Cloud, 5G/Edge, Vehicle security" as a topic [Source 2]. This directly addresses cloud security, suggesting it would provide relevant foundational knowledge in this area.
+**Academic Progression and Planning:**
+CSCE 665 could serve as a valuable broad foundation in advanced networking and security, covering various modern topics, including an introduction to software security and specific mention of cloud security [Source 1, 2]. If your goal is a broad understanding of real-world security with an emphasis on networking and distributed systems, it would be a strong choice.
+For a deeper specialization in **software security**, you might consider supplementing CSCE 665 with courses like CSCE 713 or CSCE 652, which appear to offer more in-depth coverage of software-specific vulnerabilities, analysis, and defense mechanisms. For **cloud security**, CSCE 665's explicit inclusion of "Cloud" security topics suggests it would provide a good starting point for that specialization.
+I don't have enough data to answer this accurately based on the available syllabi regarding how these courses are typically sequenced or recommended for specific specialization tracks within the curriculum.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 665, "Advanced Networking and Security," Section 600, appears to offer a strong foundation for specializing in real-world software or cloud security [Source 1].
+The course aims to provide a thorough grounding in computer and network security, suitable for students interested in real-world security issues and techniques [Source 1].
+Key topics directly relevant to your interest include:
+*   **Software security** [Source 1, 2]
+*   **Security in a software-defined world**, specifically mentioning **Cloud** security [Source 2]
+*   **Web and Web3 security** [Source 2]
+Upon completion, learners will be able to:
+*   Analyze complex trade-offs and architectural tensions in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles to design robust defenses against sophisticated threat models [Source 2].
+*   Demonstrate practical working knowledge of offensive and/or defensive techniques [Source 2].
+The course emphasizes practical application through a significant mini research project (65% of the grade), which can further enhance practical skills relevant to industry [Source 3].
+**Prerequisites:** Graduate classification and approval of the instructor are required [Source 1, 2].</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1859,6 +2761,111 @@
 *   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
 *   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
 The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to computer graphics, focusing on physically based rendering with an emphasis on Monte Carlo techniques [Source 1, 2]. It covers the representation of 3-dimensional objects, techniques for hidden surface/edge removal, volume rendering, illumination, shading, antialiasing, ray tracing, radiosity, and animation [Source 1].
+The curriculum includes:
+*   **Practical Experience:** Students gain "practical experience with state-of-the-art graphics hardware and software" [Source 1].
+*   **Modern Algorithms:** The course studies how image formation is mathematically formulated and solved using "modern rendering algorithms," focusing on "application in practical image synthesis systems" [Source 2].
+*   **Core Skills:** Learning outcomes include understanding physical and mathematical principles of light transport and image formation, implementing core rendering algorithms like ray tracing, direct illumination, and global illumination methods, and designing/implementing a physically based rendering system or component [Source 2].
+*   **Hands-on Implementation:** The course involves programming assignments in C++ and a final project where students implement additional rendering features [Source 5].
+These topics and practical skills are directly applicable and highly valued in the game and graphics development industries.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, and covers how light interacts with objects in the real world and how image formation is mathematically formulated and solved using modern rendering algorithms [Source 1, 2].
+Key topics and skills directly relevant to game and graphics development include:
+*   **Representation of 3-dimensional objects** (polyhedral, curved surfaces, volumetric, CSG models) [Source 1]
+*   **Techniques for hidden surface/edge removal and volume rendering** [Source 1]
+*   **Illumination and shading** [Source 1]
+*   **Antialiasing, ray tracing, and radiosity** [Source 1]
+*   **Animation** [Source 1]
+*   **Practical experience with state-of-the-art graphics hardware and software** [Source 1]
+*   **Implementing core rendering algorithms** such as ray tracing, direct illumination, and global illumination methods [Source 2]
+*   **Designing and implementing a physically based rendering system or rendering component** [Source 2]
+The course focuses on both the theoretical foundations of rendering and their application in practical image synthesis systems [Source 2]. Students will gain practical experience through programming assignments in C++ and a final project where they implement additional rendering features [Source 3]. These skills are fundamental for roles in game engine development, real-time graphics, visual effects, and other areas of computer graphics.</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 641 would be a beneficial course for someone aiming for a career in game or graphics development.
+The course provides an in-depth introduction to physically based rendering, with an emphasis on Monte Carlo techniques, which are fundamental to modern graphics [Source 1]. Students will study how light interacts with objects, image formation, and how these are solved using modern rendering algorithms [Source 1].
+Key topics and skills directly relevant to these careers include:
+*   **Physically Based Rendering (PBR)**: Understanding the physical and mathematical principles underlying light transport, image formation, and PBR, including radiometric quantities and the rendering equation [Source 1]. PBR is a standard in game engines and graphics applications.
+*   **Core Rendering Algorithms**: Implementing algorithms such as ray tracing, direct illumination, and global illumination methods [Source 1]. Ray tracing, in particular, is a cutting-edge technology in real-time graphics and games.
+*   **Practical Implementation**: The course focuses on both theoretical foundations and their application in practical image synthesis systems [Source 1]. Students will design and implement a physically based rendering system or component [Source 1].
+*   **3D Graphics Concepts**: The catalog description mentions representation of 3-dimensional objects, hidden surface/edge removal, volume rendering, illumination, shading, antialiasing, radiosity, and animation [Source 2]. These are all core components of game and graphics engines.
+*   **Practical Experience**: The course offers "practical experience with state-of-the-art graphics hardware and software" [Source 2].
+The programming assignments (70% of the grade) and a final project (30% of the grade) involve implementing rendering features, providing hands-on experience crucial for development roles [Source 4].</t>
         </is>
       </c>
     </row>
@@ -2054,6 +3061,153 @@
 **Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor [Source 1]</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 672 (Section 600) appears to be a worthwhile course if you are interested in the practical aspects of building collaborative applications.
+The course covers the design, implementation, and use of technical systems that support people working cooperatively [Source 1].
+Key learning outcomes include the ability to:
+*   Prioritize issues and identify trade-offs in the design of collaborative software [Source 1, 2].
+*   Design software capabilities that facilitate awareness, communication, and coordination [Source 1, 2].
+*   Design, implement, and evaluate software to support collaboration in specific settings [Source 2].
+Topics covered throughout the semester include:
+*   Designing for artifact and human awareness [Source 3].
+*   Content sharing systems and issues [Source 3].
+*   Collaborative decision making [Source 3].
+*   Crowdsourcing and its issues [Source 3].
+*   Online communities and virtual teams [Source 3].
+*   Collaborative search and design [Source 3].
+*   Software supporting social skill development [Source 3].
+*   Collaboration in online games [Source 3].
+*   Supporting software teams [Source 3].
+A significant portion of the grade (35%) is dedicated to a team project, which often involves practical application [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2201,6 +3355,141 @@
 *   Concurrency control [Source 3]
 *   Index structures [Source 3]
 *   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems.
+The course aims for learners to:
+*   **Develop database systems for applications** [Source 2].
+*   **Master efficient query processing techniques** [Source 2].
+*   **Deal with system issues related to database systems** [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Expressiveness in query languages [Source 1]
+*   Relational database design theory [Source 1]
+*   Query processing [Source 1]
+*   Transaction management and recovery [Source 1]
+*   Distributed data management [Source 1]
+*   SQL [Source 3]
+*   Constraints and triggers [Source 3]
+*   Query optimization [Source 3]
+*   Index structures [Source 3]
+*   System crash recovery [Source 3]
+*   Concurrency control [Source 4]
+*   Transaction processing [Source 4]
+*   Bigdata [Source 4]
+The course includes 3 homework assignments and 2 course projects, which likely involve practical application of these concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems.
+The course aims for learners to:
+*   **Develop database systems for applications** [Source 2].
+*   **Master efficient query processing techniques** [Source 2].
+*   **Deal with system issues related to database systems** [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Expressiveness in query languages [Source 1]
+*   Relational database design theory [Source 1]
+*   Query processing [Source 1]
+*   Transaction management and recovery [Source 1]
+*   Distributed data management [Source 1]
+*   SQL [Source 3]
+*   Constraints and triggers [Source 3]
+*   Query optimization [Source 3]
+*   Index structures [Source 3]
+*   System crash recovery [Source 3]
+*   Concurrency control [Source 4]
+*   Transaction processing [Source 4]
+*   Bigdata [Source 4]
+The course includes 3 homework assignments and 2 course projects, which likely involve practical application of these concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608, Database Systems, covers practical skills relevant to building and managing database systems in the real world.
+The course aims for learners to be able to:
+*   Understand the fundamentals of database design [Source 1, 2]
+*   Develop database systems for applications [Source 2]
+*   Master efficient query processing techniques [Source 2]
+*   Deal with system issues related to database systems [Source 2]
+Key topics covered that are directly applicable to industry include:
+*   Database modeling techniques [Source 1]
+*   Expressiveness in query languages, including SQL [Source 1, 4]
+*   Relational database design theory [Source 1]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 4]
+*   Transaction management and recovery [Source 1, 4]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3, 4]
+*   Bigdata [Source 3, 4]
+These skills are essential for roles involving database development, administration, and data management in various industries.</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608, Database Systems, covers practical skills relevant to building and managing database systems in the real world.
+The course aims for learners to be able to:
+*   Understand the fundamentals of database design [Source 1, 2]
+*   Develop database systems for applications [Source 2]
+*   Master efficient query processing techniques [Source 2]
+*   Deal with system issues related to database systems [Source 2]
+Key topics covered that are directly applicable to industry include:
+*   Database modeling techniques [Source 1]
+*   Expressiveness in query languages, including SQL [Source 1, 4]
+*   Relational database design theory [Source 1]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 4]
+*   Transaction management and recovery [Source 1, 4]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3, 4]
+*   Bigdata [Source 3, 4]
+These skills are essential for roles involving database development, administration, and data management in various industries.</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 covers practical skills relevant to building and managing database systems in the real world. The course aims for learners to be able to develop database systems for applications, master efficient query processing techniques, and deal with system issues related to database systems [Source 2].
+Key topics covered include:
+*   Database modeling techniques [Source 1]
+*   Relational database design theory [Source 1]
+*   Query languages (including SQL) [Source 1, 3]
+*   Physical data organization [Source 1]
+*   Query processing and optimization [Source 1, 3]
+*   Transaction management and recovery [Source 1, 3]
+*   Distributed data management [Source 1]
+*   Concurrency control [Source 3]
+*   Index structures [Source 3]
+*   Bigdata [Source 3]</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 608 (Section 600) covers practical skills relevant to building and managing database systems in the real world.
+The course focuses on:
+*   **Database modeling techniques** and **relational database design theory** [Source 1].
+*   **Expressiveness in query languages**, including **SQL**, and **manipulation languages data models** [Source 1, 3].
+*   **Physical data organization**, **query processing**, **transaction management and recovery**, and **distributed data management** [Source 1].
+*   **System issues related to database systems**, **concurrency control**, and **Bigdata** [Source 2, 3, 4].
+Upon completion, learners will be able to "develop database systems for applications" and "deal with system issues related to database systems" [Source 2]. The course includes two projects, which likely involve practical application of these concepts [Source 2, 3, 4].</t>
         </is>
       </c>
     </row>
@@ -2385,6 +3674,95 @@
     *   CSCE 632 calculates a completion rate for group class activities and adds 15% (capped at 100%) to the score, allowing students to miss some activities without negative impact [Source 10].</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Yes, there are several instances in the provided course information where a student's final grade is not solely based on a simple calculated average of all scores. The principle at play is that while a numerical average often forms the foundation, many courses incorporate specific policies that can adjust, modify, or even override a straightforward calculation to determine the final grade.
+Here are examples from the context:
+*   **Instructor Discretion/Modification:**
+    *   In CSCE 632, the instructor can modify a student's multiplier for peer evaluations at their discretion, which directly impacts the final project score [Source 3].
+    *   For CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 3].
+*   **Prerequisites for Passing:**
+    *   In CSCE 681, to pass the course, students must not only achieve an average score of 80% or higher but also "complete the syllabus quiz on canvas with a grade of 100%" [Source 4]. Furthermore, any course requirements completed before passing this syllabus quiz will not be considered [Source 4].
+*   **Dropping Lowest Grades:**
+    *   CSCE 629 drops the lowest grade for quizzes/exercises and the lowest homework grade [Source 1, 8].
+    *   CSCE 681 calculates the final grade as "the statistical mean of the top 75% of the individual quiz grades," meaning the lowest 25% of quiz grades do not count [Source 5].
+*   **Curving:**
+    *   CSCE 629 states that "a slight curve might be applied if the course average is low" [Source 8].
+*   **Specific Calculation Methods:**
+    *   For group class activities in CSCE 632, a completion rate is calculated, and "15% capped at 100%" is added to the score, allowing for missed activities without negative impact [Source 9].
+*   **Extra Credit:**
+    *   CSCE 713 offers "Independent-Study Reports" as an optional component that can add "+10%" to the final grade [Source 2].
+These examples demonstrate that final grades can be influenced by factors beyond a simple arithmetic mean of all graded components, including instructor judgment, specific prerequisites, grade dropping policies, curving, and extra credit opportunities.</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Yes, there are instances where a student's final grade is not solely based on their calculated average, due to specific course policies or instructor discretion.
+For example, in **CSCE 632**, the instructor may assign a failing grade regardless of a student's computed final score. Additionally, failing to complete work can lead to letter grade reductions even if a zero for that work would still mathematically result in a higher letter grade [Source 2, 6].
+In **CSCE 681**, to pass the course, students must complete a syllabus quiz on Canvas with a 100% grade and receive an average score of 80% or higher. Any course requirements completed before passing the syllabus quiz will not be considered [Source 7]. This means a student could have a high numerical average but still not pass if they don't meet the syllabus quiz requirement.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Yes, there are several instances in the provided course information where a student's final grade may not be solely based on a direct calculated average of their scores. The principle at play is that instructors may implement course-specific grading policies that include prerequisites, discretionary adjustments, or alternative calculation methods to determine the final letter grade.
+Here are examples from the provided context:
+*   **Instructor Discretion/Overrides:** In CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted. Additionally, "failing to complete work can lead to letter grade reductions even if having a zero would still mathematically result in a higher letter grade" [Source 2, 10].
+*   **Prerequisites for Passing:** For CSCE 681, to pass the course, students must not only achieve an average score of 80% or higher but also "complete the syllabus quiz on canvas with a grade of 100%." Any work completed before passing this quiz will not be considered [Source 4].
+*   **Adjustments based on Peer Evaluation and Participation:** In CSCE 632, project scores can be modified by an instructor-assigned multiplier based on team peer evaluations and active participation. For example, a student's project score could be reduced if they are not actively participating with their group [Source 2]. Individual assignment scores can also be based on peer evaluations [Source 7].
+*   **Dropping Lowest Grades:** CSCE 629 drops the lowest grade for quizzes/exercises and homework components [Source 6]. Similarly, CSCE 681 calculates the final grade using the statistical mean of the top 75% of individual quiz grades, meaning the lowest 25% of quiz grades do not count [Source 5].
+*   **Curves:** CSCE 629 states that "a slight curve might be applied if the course average is low" [Source 6].
+*   **Completion Rate Adjustments:** CSCE 632 calculates a completion rate for group class activities and adds 15% (capped at 100%) to the score, allowing students to miss some activities without negatively impacting their grade [Source 7].</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided course information, there are instances where a final grade at Texas A&amp;M University might not be solely based on a straightforward calculated average of all components.
+Here are some examples:
+*   **Instructor Discretion for Failing Grades:** In CSCE 632, the instructor may assign a failing grade regardless of a student's computed final score if warranted. Additionally, failing to complete work can lead to letter grade reductions even if a zero would mathematically result in a higher letter grade [Source 2, 10].
+*   **Curving:** In CSCE 629, a slight curve might be applied if the course average is low, which would adjust final grades beyond a direct calculation [Source 6].
+*   **Dropping Lowest Grades:**
+    *   CSCE 629 drops the lowest grade in quizzes and exercises, and the lowest homework grade [Source 1, 6].
+    *   CSCE 681 calculates the final grade as the statistical mean of the top 75% of individual quiz grades, meaning the lowest 25% of quiz grades do not count [Source 5].
+*   **Prerequisites for Grading:** In CSCE 681, to pass the course, students must complete a syllabus quiz on Canvas with a 100% grade. Any course requirements completed before passing this quiz will not be considered [Source 4].
+*   **Peer Evaluation Multipliers:** In CSCE 632, a student's project score can be affected by a multiplier based on team peer evaluations, which the instructor can modify at their discretion [Source 2].
+*   **Optional Grade Boosters:** In CSCE 713, students have the option to submit "Independent-Study Reports" for an additional +10% to their grade [Source 3].</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided context, there are several Texas A&amp;M University courses where the final grade is not solely based on a simple calculated average of all scores. These courses incorporate principles such as dropping lowest grades, applying curves, or having specific prerequisites for passing.
+Here are examples from the provided syllabi:
+*   **CSCE 629**:
+    *   The lowest grade for quizzes and exercises is dropped [Source 1].
+    *   The lowest homework grade is dropped [Source 7].
+    *   A slight curve might be applied if the course average is low [Source 7].
+*   **CSCE 681**:
+    *   To pass the course, students must complete a syllabus quiz with a 100% grade and receive an average score of 80% or higher [Source 3]. Any course requirements completed before passing the syllabus quiz will not be considered [Source 3].
+    *   The final grade is calculated as the statistical mean of the top 75% of individual quiz grades, meaning the lowest 25% of quiz grades do not count [Source 4].
+*   **CSCE 713**:
+    *   This course offers optional "Independent-Study Reports" which can provide an additional +10% to the final grade, allowing the final grade to exceed the sum of the weighted required components [Source 2].</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Yes, there are instances where a final grade in a Texas A&amp;M University course may not be solely based on a calculated average, due to specific course policies or instructor discretion.
+Here are examples from the provided context:
+*   **Instructor Discretion to Assign Failing Grade:** In CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [Source 5, 6]. Additionally, "failing to complete work can lead to letter grade reductions even if having a zero would still mathematically result in a higher letter grade" [Source 6].
+*   **Mandatory Requirements:** In CSCE 681, to pass the course, students must "complete the syllabus quiz on canvas with a grade of 100%" and "receive an average score of 80% or higher." Any course requirements completed before passing the syllabus quiz with 100% will not be considered [Source 2].
+*   **Academic Integrity Violations:** In CSCE 681, evidence of plagiarism or fabricated information can lead to a recommendation for an F* grade, regardless of other scores [Source 4].
+*   **Peer Evaluation Multipliers:** In CSCE 632, for peer-graded assignments, the instructor can establish and modify a multiplier based on team peer evaluations, which directly impacts an individual's score even if the group's project score is high [Source 5].
+*   **Course-wide Curves:** In CSCE 629, a "slight curve might be applied if the course average is low," which would adjust final grades from the raw calculated average [Source 10].</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes, based on the provided context, there are instances where a final grade in a Texas A&amp;M University course may not be solely based on a student's calculated numerical average. This can occur due to specific course policies, academic integrity violations, or instructor discretion.
+Here are examples from the provided syllabi:
+*   **Instructor Discretion to Assign Failing Grade**: In CSCE 632, the instructor "may assign a failing grade regardless of a student’s computed final score" if warranted [6, 8]. Additionally, "Failing to complete work can lead to letter grade reductions even if having a zero would still mathematically result in a higher letter grade" [8].
+*   **Academic Integrity Violations**: In CSCE 681, evidence of plagiarism or fabricated information can lead to a recommendation for an F* for the course, regardless of the student's computed final score [5].
+*   **Specific Passing Conditions**: In CSCE 681, to pass the course, students must not only receive an average score of 80% or higher but also "complete the syllabus quiz on canvas with a grade of 100%" [2]. Any course requirements completed before passing this syllabus quiz will not be considered [2].</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2484,6 +3862,64 @@
         <is>
           <t>Based on the provided context, the course CSCE 672: Computer Supported Collaborative Work explicitly covers topics such as crowdsourcing, online communities, and collaboration in online games [Source 1, Source 2].
 However, I cannot find information about *other* courses at TAMU that cover these specific topics in the provided context. I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>I cannot find information about other courses at TAMU that cover topics like crowdsourcing, online communities, or collaboration in games in the provided context. The context only details the CSCE 672 course [Source 1, 2, 3].</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>I cannot find information about other courses at TAMU that cover topics like crowdsourcing, online communities, or collaboration in games in the provided context. The context only details the CSCE 672 course [Source 1, 2, 3].</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>To identify courses covering specific academic topics like crowdsourcing, online communities, or collaboration in games, one must examine the course's stated content, such as its catalog description, course schedule, or learning outcomes.
+Based on the provided syllabi:
+**CSCE 672: Computer Supported Collaborative Work** explicitly covers these topics in its course schedule [Source 1]:
+*   **Crowdsourcing**: Week 8 includes "crowdsourcing and its issues" [Source 1].
+*   **Online Communities**: Week 9 covers "online communities and virtual teams" [Source 1].
+*   **Collaboration in Games**: Week 13 addresses "collaboration in online games" [Source 1].
+The course's catalog description also broadly covers the design, implementation, and use of technical systems that support people working cooperatively, including current theoretical, practical, technical, and social issues in Computer Supported Cooperative Work (CSCW) [Source 3].
+The provided context for other courses (CSCE 632, CSCE 624, CSCE 676, CSCE 670) does not explicitly mention crowdsourcing, online communities, or collaboration in games within their course descriptions, schedules, or learning outcomes [Source 4, 5, 6, 7, 8, 9].
+Therefore, based on the available context, **CSCE 672** is the only course that explicitly covers topics such as crowdsourcing, online communities, or collaboration in games. I don't have enough data to identify other courses that cover these topics accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the course that covers topics such as crowdsourcing, online communities, or collaboration in games is **CSCE 672: Computer Supported Collaborative Work** [Source 1, 3].
+Specifically, the course schedule for CSCE 672 includes:
+*   **Week 8:** Crowdsourcing and its issues [Source 1]
+*   **Week 9:** Online communities and virtual teams [Source 1]
+*   **Week 13:** Collaboration in online games [Source 1]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, CSCE 672: Computer Supported Collaborative Work explicitly covers topics such as "crowdsourcing and its issues," "online communities and virtual teams," and "collaboration in online games" [Source 1].
+I cannot find information about other courses at Texas A&amp;M University that cover these specific topics in the provided context. I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the course **CSCE 672: Computer Supported Collaborative Work** covers topics such as crowdsourcing, online communities, and collaboration in online games [Source 1].
+Specifically, the course schedule for CSCE 672 includes:
+*   Week 8: crowdsourcing and its issues [Source 1]
+*   Week 9: online communities and virtual teams [Source 1]
+*   Week 13: collaboration in online games [Source 1]
+I cannot find information in the provided context about other courses at Texas A&amp;M University that cover these specific topics.</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Based on the provided context, CSCE 672 (Computer Supported Collaborative Work) covers topics such as crowdsourcing, online communities, and collaboration in online games [Source 1].
+Specifically, the course schedule for CSCE 672 includes:
+*   **Week 8:** Crowdsourcing and its issues [Source 1]
+*   **Week 9:** Online communities and virtual teams [Source 1]
+*   **Week 13:** Collaboration in online games [Source 1]
+I cannot find information about other courses at Texas A&amp;M University that cover these specific topics in the provided context. I don't have enough data to answer this accurately based on the available syllabi.</t>
         </is>
       </c>
     </row>
@@ -2654,6 +4090,105 @@
     *   Weeks 11-15: AI/LLM Security [Source 10]</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following courses cover advanced topics in AI like transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   This course covers "Transformers" in Week 5 and "Contextualized Representations, Pre-Training, Large Language Models" in Week 6 [Source 1].
+    *   Its catalog description mentions a focus on NLP fundamentals and an awareness of recent trends in natural language processing research [Source 3].
+*   **CSCE 624: Sketch Recognition**
+    *   This course mentions "Hidden Markov Models, LLMs, and related techniques" in Weeks 8-9 [Source 5].
+*   **CSCE 665**
+    *   This course includes "AI/LLM Security" as a topic in Weeks 11, 13, and 14 [Source 10].
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   While its primary focus is optimization, it mentions "Stochastic Optimization for Deep Learning" in Week 10 and requires some foundations in Machine Learning and Deep Learning, including familiarity with basic deep learning methods [Source 2, 7, 9]. It also lists CSCE 636 (Deep Learning) as a recommended background course [Source 9].
+**Note:** CSCE 633 (Machine Learning) is a foundational course that covers general machine learning techniques and is a prerequisite for CSCE 726, but its catalog description does not explicitly mention transformers or large language models [Source 8].</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following courses cover advanced topics in AI such as Transformers and Large Language Models (LLMs):
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Topics:** Transformers (Week 5), Contextualized Representations, Pre-Training, Large Language Models (Week 6), Instruction Tuning, Alignment, Post-Training (Week 8), Large Reasoning Models (Week 9), Multilingual Language Models, Vision-Language Models (Week 11) [Source 1]
+    *   **Catalog Description:** Focuses on NLP fundamentals including language models, automatic syntactic processing, semantic understanding, and major NLP applications [Source 7].
+*   **CSCE 624: Foundations of Sketch Recognition**
+    *   **Topics:** Hidden Markov Models, LLMs, and related techniques (Weeks 8-9) [Source 4]
+*   **CSCE 670: Information Retrieval and Web Search**
+    *   **Topics:** Transformer; BERT-Based Ranking (Week 10), Large Language Models Basics (Week 12), Large Language Models with Search Engines (Week 13), Large Language Models for Ranking and Recommendation (Week 14) [Source 2]
+*   **CSCE 665: Advanced Topics in Security**
+    *   **Topics:** AI/LLM Security (Weeks 11, 13, 14, 15) [Source 9]</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Several courses at Texas A&amp;M cover advanced topics in AI, including Transformers and Large Language Models (LLMs):
+*   **CSCE 670** (term 202611)
+    *   Week 10: Transformer; BERT-Based Ranking [Source 1]
+    *   Week 12: Large Language Models Basics [Source 1]
+    *   Week 13: Large Language Models with Search Engines [Source 1]
+    *   Week 14: Large Language Models for Ranking and Recommendation [Source 1]
+*   **CSCE 638** (term 202611)
+    *   Week 5: Transformers [Source 2]
+    *   Week 6: Contextualized Representations, Pre-Training, Large Language Models [Source 2]
+    *   Week 9: Large Reasoning Models, Test-Time Scaling, Decoding [Source 2]
+*   **CSCE 624** (term 202611)
+    *   Weeks 8-9: Mathematical and Sequential Models, including Hidden Markov Models, LLMs, and related techniques [Source 4]
+*   **CSCE 665** (term 202611)
+    *   Weeks 11-14: AI/LLM Security [Source 7]</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Several courses at Texas A&amp;M cover advanced topics in AI, including Transformers and Large Language Models (LLMs):
+*   **CSCE 670** (Information Retrieval and Web Search) covers Transformers and BERT-Based Ranking in Week 10, Large Language Models Basics in Week 12, Large Language Models with Search Engines in Week 13, and Large Language Models for Ranking and Recommendation in Week 14 [Source 1].
+*   **CSCE 638** (Natural Language Processing) includes topics such as Transformers in Week 5, Contextualized Representations, Pre-Training, and Large Language Models in Week 6, and Large Reasoning Models in Week 9 [Source 2].
+*   **CSCE 624** (Sketch Recognition) mentions Hidden Markov Models, LLMs, and related techniques in Weeks 8-9 [Source 4].
+*   **CSCE 665** (Computer Security) dedicates several weeks to AI/LLM Security, specifically in Weeks 11, 13, and 14 [Source 7].</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Several courses at Texas A&amp;M cover advanced topics in AI, including transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   This course covers "Large Language Models" in Week 6, "Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation" in Week 7, "Instruction Tuning, Alignment, Post-Training" in Week 8, and "Large Reasoning Models, Test-Time Scaling, Decoding" in Week 9 [Source 2]. The catalog description also mentions "language models" and "semantic understanding" [Source 4].
+*   **CSCE 670: Information Retrieval**
+    *   This course includes "Transformer; BERT-Based Ranking" in Week 10, "Large Language Models Basics" in Week 12, "Large Language Models with Search Engines" in Week 13, and "Large Language Models for Ranking and Recommendation" in Week 14 [Source 3].
+*   **CSCE 624: Sketch Recognition**
+    *   This course mentions "Hidden Markov Models, LLMs, and related techniques" in Weeks 8-9 [Source 7].
+These courses demonstrate how advanced AI topics are integrated into the curriculum, allowing students to specialize in areas like Natural Language Processing, Information Retrieval, and Sketch Recognition. Students interested in these areas should consider the prerequisites for each course, such as CSCE 633 or CSCE 636 for CSCE 726, or general graduate classification [Source 6].</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, here are the courses that cover advanced topics in AI such as transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques** [Source 1, 3]
+    *   **Topics include:** Transformers (Week 5), Contextualized Representations, Pre-Training, Large Language Models (Week 6), Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation (Week 7), Instruction Tuning, Alignment, Post-Training (Week 8), Large Reasoning Models, Test-Time Scaling, Decoding (Week 9), Retrieval-Augmented Generation, Agents (Week 10), Multilingual Language Models, Vision-Language Models (Week 11), Bias Mitigation, Hallucinations (Week 14) [Source 1].
+    *   This course focuses on NLP fundamentals and major NLP applications [Source 3].
+*   **CSCE 670: Information Retrieval** [Source 2]
+    *   **Topics include:** Transformer (Week 10), BERT-Based Ranking (Week 10), Large Language Models Basics (Week 12), Large Language Models with Search Engines (Week 13), Large Language Models for Ranking and Recommendation (Week 14) [Source 2].
+*   **CSCE 726: Large-Scale Optimization for Machine Learning** [Source 4, 5]
+    *   While its primary focus is on optimization algorithms for machine learning, it includes "Stochastic Optimization for Deep Learning" (Week 10) [Source 4]. The course description also mentions its role in machine learning (ML) and artificial intelligence (AI) [Source 5]. It requires foundational knowledge in machine learning and deep learning [Source 8].
+*   **CSCE 624: Sketch Recognition** [Source 7]
+    *   **Topics include:** Hidden Markov Models, LLMs, and related techniques (Weeks 8-9) [Source 7].
+**Academic Progression:**
+These courses are graduate-level (CSCE 6xx and 7xx) and delve into specialized areas within Artificial Intelligence.
+*   **CSCE 638** and **CSCE 670** are directly focused on Natural Language Processing and Information Retrieval, respectively, with significant coverage of modern LLM architectures like Transformers. These would be crucial for students specializing in NLP, text analytics, or AI applications involving language.
+*   **CSCE 726** provides the mathematical and algorithmic backbone for large-scale machine learning, including deep learning, which is essential for understanding the underlying mechanisms of LLMs and other advanced AI models. It is a prerequisite for CSCE 726 to have taken CSCE 633 or CSCE 636 [Source 5, 8].
+*   **CSCE 624** offers a unique application of LLMs within the context of sketch recognition, indicating the broad applicability of these models across different AI subfields.
+Taking these courses would provide a comprehensive understanding of both the theoretical foundations and practical applications of advanced AI models, particularly large language models and transformers, preparing students for research or industry roles in these rapidly evolving fields.</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following courses cover advanced topics in AI like transformers and large language models:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   This course covers "Transformers" (Week 5), "Contextualized Representations, Pre-Training, Large Language Models" (Week 6), "Large Reasoning Models" (Week 9), "Multilingual Language Models, Vision-Language Models" (Week 11), and "Bias Mitigation, Hallucinations" (Week 14) [Source 1]. Its catalog description also mentions "language models" [Source 4].
+*   **CSCE 624: Sketch Recognition**
+    *   This course includes "LLMs, and related techniques" in its Week 8 topics [Source 5].
+*   **CSCE 670: Information Retrieval**
+    *   This course covers "Transformer; BERT-Based Ranking" (Week 10), "Large Language Models Basics" (Week 12), "Large Language Models with Search Engines" (Week 13), and "Large Language Models for Ranking and Recommendation" (Week 14) [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2769,6 +4304,93 @@
 *   **CSCE 635**: In this course, students are expected to submit short reviews of research papers, articulating their understanding of main contributions, providing critical analysis of strengths and limitations, and discussing open research questions or potential extensions. Students also lead class discussions on assigned papers, preparing slides or discussion prompts to facilitate conversation around methodology, results, and broader implications [Source 3].
 *   **CSCE 632**: This course requires students to compile a literature review on an accessibility topic, based on at least 10 peer-reviewed conference or journal papers. The literature review must clearly lay out themes and gaps in research, supported by evidence. Students also give a "Current Research Presentation" based on their literature review [Source 9].
 *   **CSCE 665**: This course includes a "Paper mini-review" component and emphasizes "Class participation and presentation" [Source 10].</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>To identify courses that help students improve at preparing research reports and discussing technical articles, we look for courses with learning outcomes or activities explicitly focused on these skills.
+The relevant principle is to match the user's desired skill development (research reports, technical discussions) with the stated academic objectives and activities of the courses.
+Based on the provided context, the following courses would be recommended:
+*   **CSCE 681 (Seminar)**: This course's purpose is to expose students to current and seminal research topics. A key learning outcome is for students to "be able to prepare reports and discuss research works and selected published technical articles" [Source 1]. Students are required to write reports for each lecture [Source 2, 5].
+*   **CSCE 635**: In this course, students are expected to submit "short review[s]... based on two papers," which involves articulating understanding, providing critical analysis, and discussing open research questions. Students also "Lead Paper Discussions" to engage classmates and facilitate conversation around papers' methodology, results, and broader implications [Source 4].</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, students should seek courses that emphasize critical analysis of existing literature, structured writing, and oral presentation of research findings. This involves understanding research methodologies, identifying key contributions, evaluating strengths and limitations, and articulating future research directions.
+Based on the provided context, **CSCE 635** is a course that would be highly beneficial for developing these skills:
+*   **Paper Reviews and Critical Analysis**: Students are required to submit short reviews of research papers. These reviews involve articulating the main contributions of the papers, providing a critical analysis of their strengths and limitations, and discussing open research questions or potential extensions [Source 3]. This directly addresses the preparation of reports and critical engagement with technical articles.
+*   **Leading Paper Discussions**: Students sign up to lead class discussions on assigned papers. This responsibility includes preparing slides or discussion prompts to engage classmates and facilitating meaningful conversation around the papers’ methodology, results, and broader implications [Source 3]. This activity hones skills in discussing technical articles and presenting research effectively.
+*   **Project Proposal and Presentation**: The course includes a project proposal which requires a short written proposal outlining goals, motivation, and expected contributions, accompanied by a brief in-class presentation to gather feedback [Source 3]. This develops skills in structuring research proposals and presenting them orally.
+While CSCE 681 also focuses on preparing reports and discussing research works and technical articles [Source 1], the question asks for *other* recommendations. CSCE 635 provides a structured approach to these academic communication skills through its assignments and discussion formats.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, you should look for courses that emphasize critical analysis of research, written communication of findings, and oral presentation or discussion of technical content. These skills are fundamental to academic progression, especially in graduate studies, as they prepare students for thesis/dissertation work, conference presentations, and publishing research.
+Based on the provided context, here are some Texas A&amp;M CS courses that would help you develop these skills:
+*   **CSCE 681 (Seminar)**: This course's purpose is to expose students to current and seminal research topics. Upon completion, students should be able to "prepare reports and discuss research works and selected published technical articles" [Source 2]. The grading policy specifically requires writing a report for each lecture, which includes sections like background, problem statement, proposed solution, results, and critique, helping you structure and analyze research effectively [Source 1]. You also discuss research works and selected published technical articles [Source 1].
+*   **CSCE 635**: In this course, students are expected to select ten weeks to submit a "short review (within 2 pages) based on two papers from that week’s list." These reviews require articulating understanding of main contributions, providing critical analysis of strengths and limitations, and discussing open research questions or potential extensions [Source 4]. Additionally, students lead class discussions on assigned papers, preparing slides or discussion prompts to facilitate conversation around methodology, results, and broader implications [Source 4].
+These courses directly address the skills you're looking to develop by integrating report writing, critical analysis of technical articles, and discussion facilitation into their core activities.</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, you should consider courses that incorporate these activities into their structure.
+Based on the provided context, the following Texas A&amp;M CS courses would be beneficial:
+*   **CSCE 681 (Seminar)**: This course's purpose is to expose students to current and seminal research topics. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 2]. Students are expected to attend lectures and write a report for each, which includes sections like background, problem statement, proposed solution, results, and critique [Source 1]. They also discuss research works and selected published technical articles [Source 1].
+*   **CSCE 635**: In this course, students are expected to select ten weeks to submit a short review (within 2 pages) based on two papers from that week's list. Each review should articulate the student’s understanding of the papers’ main contributions, provide a critical analysis of their strengths and limitations, and discuss open research questions or potential extensions. Students also lead class discussions on assigned papers, preparing slides or discussion prompts and facilitating conversation around methodology, results, and broader implications [Source 4].
+These courses directly address the development of skills in analyzing, summarizing, critiquing, and discussing research and technical articles, which are crucial for academic progression in a research-oriented field. CSCE 681 focuses on regular reporting and discussion of research, while CSCE 635 emphasizes critical analysis through written reviews and leading discussions.</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, the relevant academic principle is **research communication and scholarly engagement**. This involves actively participating in the academic discourse by critically analyzing existing research and effectively presenting one's own findings or interpretations.
+Based on the provided context, **CSCE 681 (Seminar)** is the most directly relevant course for developing these skills [Source 1, 2, 5].
+**Course Recommendation:**
+*   **CSCE 681: Seminar**
+**Why this course is recommended:**
+*   **Directly Aligned Learning Outcomes:** The primary purpose of CSCE 681 is to "expose students to a broad range of current and seminal research topics in computer science and related fields." Upon completion, students "should be able to prepare reports and discuss research works and selected published technical articles" [Source 1].
+*   **Practical Application:** Students in CSCE 681 are expected to "write a report for each" lecture or lecture recording [Source 2, 5]. These reports require students to synthesize information from the lectures, which are based on current research and technical articles.
+*   **Discussion and Analysis:** The course's catalog description explicitly mentions "Reports and discussion of current research and of selected published technical articles," indicating an emphasis on engaging with scholarly work [Source 1].
+**How this course fits into your academic progression:**
+CSCE 681 is designed for graduate students, requiring "Graduate classification" as a prerequisite [Source 1]. It is a 0 to 1 credit hour course and can be taken once in a master's degree program and up to twice in a PhD program [Source 1]. This structure suggests it's intended as a recurring opportunity for graduate students to continuously engage with and practice communicating about cutting-edge research throughout their studies.
+I cannot find information on other courses in the provided context that explicitly focus on preparing research reports and discussing technical articles as a core learning outcome or activity.</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>To improve skills in preparing research reports and discussing technical articles, students should seek courses that integrate these activities into their learning outcomes, assignments, and class structure. These types of courses often emphasize critical analysis, synthesis of information, and effective communication of complex ideas.
+Based on the provided context, the following Texas A&amp;M University CS courses would be beneficial:
+*   **CSCE 681 (Seminar)**
+    *   **Principle:** This course is specifically designed to develop skills in engaging with current research.
+    *   **Application:** The purpose of CSCE 681 is to expose students to a broad range of current and seminal research topics. Upon completion, students are expected to "prepare reports and discuss research works and selected published technical articles" [Source 1]. Students are required to write reports for each lecture, which involves sections like background, problem statement, proposed solution, results, and critique [Source 2].
+    *   **Planning Dimension:** As a seminar course, CSCE 681 (1 credit hour) can be a foundational experience for graduate students to regularly practice summarizing and critiquing research, which is crucial for thesis/dissertation work and future academic or industry research roles. It can be taken once in a master's program and twice in a PhD program [Source 1].
+*   **CSCE 624**
+    *   **Principle:** This course fosters critical engagement with research literature and interactive discussion.
+    *   **Application:** CSCE 624 involves "critical reading of classic and contemporary research papers" and is described as "discussion-driven and interactive." Students are expected to "actively engage with readings, participate in in-class activities, and reflect on tradeoffs between algorithmic approaches" [Source 3].
+    *   **Planning Dimension:** This course would be valuable for students who benefit from an interactive environment to refine their understanding and articulation of research concepts. The emphasis on critical reading and discussion directly supports the development of skills needed for report writing and article discussion.
+*   **CSCE 635**
+    *   **Principle:** This course provides structured opportunities for in-depth paper review, critical analysis, and leading academic discussions.
+    *   **Application:** In CSCE 635, students are required to "submit a short review (within 2 pages) based on two papers from that week’s list." These reviews must "articulate the student’s understanding of the papers’ main contributions, provide a critical analysis of their strengths and limitations, and discuss open research questions or potential extensions." Additionally, students "Lead Paper Discussions" twice during the semester, which includes preparing prompts and facilitating conversation [Source 5].
+    *   **Planning Dimension:** This course offers a hands-on approach to developing both written and oral communication skills related to research. The structured reviews and discussion leadership roles are excellent preparation for presenting research findings and engaging in academic discourse, which are essential for graduate studies and research careers.
+These courses directly address the skills of preparing research reports and discussing technical articles through their stated objectives and assignments.</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Based on the provided context, here are some Texas A&amp;M CS courses that would help students get better at preparing research reports and discussing technical articles:
+*   **CSCE 681: Seminar**
+    *   **Principle:** This course is explicitly designed to expose students to current and seminal research topics and to develop skills in discussing and reporting on research.
+    *   **Application:** The purpose of CSCE 681 is to expose students to a broad range of current and seminal research topics in computer science. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1].
+        *   For Section 600, students are expected to attend lectures and write a report for each, which includes sections like background, problem statement, proposed solution, results, and critique [Source 2].
+        *   For Section 700, students watch lecture recordings and write reports for each, typically in the form of report quizzes with multiple-choice/multiple-answer questions related to the lecture content [Source 4].
+    *   **Academic Progression:** This course is a seminar, often a requirement or highly recommended for graduate students (master's or PhD) to engage with ongoing research and develop critical analysis and communication skills essential for academic and research careers [Source 1].
+*   **CSCE 635**
+    *   **Principle:** This course involves in-depth analysis and discussion of research papers, requiring students to critically evaluate and present their understanding.
+    *   **Application:** Students are expected to select ten weeks to submit a short review (within 2 pages) based on two papers from that week's list. Each review should articulate the student’s understanding of the papers’ main contributions, provide a critical analysis of their strengths and limitations, and discuss open research questions or potential extensions. Students also lead two class discussions on assigned papers, which includes preparing slides or discussion prompts to engage classmates and facilitating meaningful conversation around the papers’ methodology, results, and broader implications [Source 3].
+    *   **Academic Progression:** This course, likely a graduate-level elective, directly contributes to developing advanced research analysis, critical thinking, and presentation skills, which are crucial for conducting independent research and contributing to the academic community.
+I cannot find information on other courses in the provided context that specifically focus on preparing research reports and discussing technical articles.</t>
         </is>
       </c>
     </row>
@@ -2967,6 +4589,152 @@
 Understanding this end-of-semester convergence is crucial for your academic progression. By proactively mapping out your major assignments from all courses, you can strategically distribute your workload, identify potential conflicts, and avoid overwhelming periods. This allows you to produce higher quality work, reduce stress, and ensure you meet all academic requirements effectively.</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>The principle underlying effective end-of-semester workload management is **proactive planning and strategic time allocation**, especially when multiple significant academic deliverables converge.
+Based on the provided course schedules, it is evident that many final projects, reports, and exams are concentrated in late April and early May. For example:
+*   **CSCE 672**: Final project presentations are due April 27-28, with final project reports due May 1 [Source 3].
+*   **CSCE 633**: The Final Project is due Monday, May 4 [Source 4].
+*   **CSCE 652**: The Final Project is due April 28 [Source 5].
+*   **CSCE 635**: Final Project Reports are due April 27, with presentations and feedback scheduled for April 17, 20, and 22 [Source 6].
+*   **CSCE 656**: Final project presentations are due between April 20-28, and both final project reports and a survey paper are due May 1 [Source 2].
+*   **CSCE 611**: The Final Exam is on May 5 [Source 1].
+*   **CSCE 752**: The Final Exam is on May 1 [Source 10].
+*   **CSCE 648**: Final Integration and Presentation occurs in Week 14, which is late April [Source 7].
+Given this concentration of major deliverables, effective strategies for managing the end-of-semester workload at TAMU include:
+1.  **Early Identification of Deadlines**: Students should identify all final project, paper, and exam due dates from their syllabi at the beginning of the semester to understand the scope of the end-of-semester crunch [Source 1, 2, 3, 4, 5, 6, 10].
+2.  **Proactive Project Planning**: Recognizing that multiple courses will have final projects and reports due around the same time (e.g., late April to early May), students should begin working on these assignments well in advance of their due dates to avoid last-minute rushes [Source 2, 3, 4, 5, 6].
+3.  **Staggered Workload Distribution**: Break down large assignments into smaller, manageable tasks and distribute them across the semester, rather than attempting to complete them all in the final weeks. This is especially important for courses with weekly activities or smaller project components leading up to a final deliverable [Source 2, 3].
+4.  **Prioritization**: With multiple deadlines converging, students should prioritize tasks based on their weight in the overall grade and complexity, allocating time accordingly.</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Effectively managing the end-of-semester workload, especially when multiple final projects, papers, and exams converge, relies on the principle of **proactive workload management and time allocation**.
+Many courses, such as CSCE 632, CSCE 633, CSCE 608, CSCE 672, and CSCE 611, schedule significant deliverables like final presentations, reports, projects, and exams around the same time at the end of the semester [Source 4, 6, 8, 10, 2]. For instance, CSCE 632 has a Final Presentation and Final Report/Video Demo due in late April [Source 4], while CSCE 633 has a Final Project due in early May [Source 6]. Similarly, CSCE 608 has a course project due in late April and a final exam in early May [Source 8], and CSCE 672 has final project presentations and reports due around the same time [Source 10]. CSCE 611 also has a Machine Problem and Final Exam due in early May [Source 2].
+To effectively manage these concurrent deadlines and ensure successful academic progression, consider the following strategies based on course syllabi:
+*   **Start Early:** Begin working on assignments as soon as they are assigned [Source 8, 9]. This is particularly important for larger projects and papers that require significant time.
+*   **Stay Informed and Up-to-Date:** Regularly check course announcements, materials, and due dates daily to avoid falling behind [Source 8]. Consistent engagement, including regular class attendance, is essential [Source 7, 8].
+*   **Seek Assistance Promptly:** If you encounter difficulties, contact your instructor or TA as early as possible. Waiting until closer to the deadline may make it harder to obtain timely help [Source 9].
+*   **Understand Absence Policies:** Be aware of the university's Student Rule 7 regarding excused absences and the specific course policies. For example, in CSCE 681, missed reports without an approved excused absence will receive a zero [Source 5]. For make-up exams, documentation may be required and arrangements often need to be made weeks in advance [Source 9].
+By adopting these proactive strategies, students can better plan their academic progression throughout the semester, distribute their workload more evenly, and mitigate the stress of multiple converging deadlines.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Managing the end-of-semester workload, especially when multiple final projects and papers are due, is a critical aspect of academic success. The underlying principle is effective **time management and proactive workload planning**. This involves understanding all course requirements and deadlines well in advance and allocating sufficient time to each task to avoid last-minute stress and ensure quality submissions.
+Based on the provided course information, here are some strategies for managing your end-of-semester workload at Texas A&amp;M:
+1.  **Track All Deadlines and Major Deliverables Early:**
+    *   Courses like CSCE 611 have multiple "Machine Problems" (MPs) spread throughout the semester, with MP7 due very close to the final exam [Source 1].
+    *   CSCE 632 lists several significant assignments and projects (Court Case Summary Infographic, Final Presentation, Elevator Pitch, Final Report, Video Demo) all scheduled in April, leading up to the end of the semester [Source 2].
+    *   Create a comprehensive calendar or planner that includes all due dates for assignments, projects, reports, and exams from all your courses.
+2.  **Prioritize and Start Major Projects Proactively:**
+    *   The cluster of final projects in CSCE 632 (Final Presentation, Final Report, Video Demo) suggests these are substantial tasks that cannot be completed in a single sitting [Source 2]. Begin working on these well before their due dates, breaking them down into smaller, manageable steps.
+    *   Similarly, the "Machine Problems" in CSCE 611 are likely complex and require dedicated time [Source 1].
+3.  **Maintain Consistent Effort Throughout the Semester:**
+    *   Some courses, like CSCE 681, require consistent engagement, such as completing reports for *each* lecture, due at the end of the lecture [Source 3]. Falling behind on these smaller, regular tasks can quickly accumulate into a large, unmanageable workload by the end of the semester.
+4.  **Understand and Adhere to Strict Deadlines:**
+    *   Be aware that some deadlines are "hard," as explicitly stated for MP7 in CSCE 611, which is due on May 3 to allow for timely grading [Source 1]. Missing such deadlines can have significant academic consequences.
+5.  **Prepare Necessary Technology and Tools in Advance:**
+    *   Courses may require specific technology for submissions, such as creating sketches/diagrams for electronic submission, video demos, or using specific browsers like LockDown Browser for quizzes [Source 2, Source 3]. Ensure you have access to and are proficient with these tools before deadlines.
+**Academic Progression Dimension:**
+Effectively managing your end-of-semester workload is crucial for your academic progression at Texas A&amp;M. It directly impacts your ability to successfully complete courses, achieve good grades, and maintain academic standing. By planning ahead and consistently working on assignments, you can reduce stress, deepen your understanding of course material, and develop essential project management skills that are valuable for future academic and professional endeavors.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Managing the end-of-semester workload, characterized by multiple final projects and papers, relies on **proactive planning, effective time management, and strategic task breakdown**. This approach helps students distribute their effort evenly and avoid last-minute rushes.
+Based on the provided course information, here are some strategies for managing your end-of-semester workload at Texas A&amp;M:
+1.  **Identify and Calendar All Major Deliverables Early:**
+    *   Courses like CSCE 632 clearly outline multiple final components in the last weeks of the semester, including a "Court Case Summary Infographic" (Apr 19), "Final Presentation" (Apr 21 &amp; 23), "Elevator Pitch for Accessibility" (Apr 26), and a "Final Report" and "Video Demo" (Apr 28) [Source 2].
+    *   Other courses, such as CSCE 611, have a final "Machine Problem" (MP7) due on May 3, just before the final exam on May 5 [Source 1].
+    *   Plotting all these deadlines on a single calendar at the beginning of the semester allows you to visualize potential overlaps and plan accordingly.
+2.  **Maintain Consistent Progress on Ongoing Assignments:**
+    *   For courses like CSCE 681, which require continuous engagement through "reports for each lecture" that must be completed during the lecture time [Source 3], staying on top of these regular tasks prevents them from accumulating.
+    *   Similarly, CSCE 611 has weekly "Machine Problems" [Source 1]. Completing these as they are assigned helps manage the overall workload and builds a foundation for later, more complex tasks.
+3.  **Break Down Large Projects into Smaller, Manageable Steps:**
+    *   A "Final Report" or "Final Presentation" [Source 2] can be daunting. Break these down into stages like research, outlining, drafting, and revising. Start working on these stages well in advance of the due date.
+4.  **Prioritize and Allocate Time Strategically:**
+    *   With multiple deadlines converging, prioritize tasks based on their weight in the final grade, complexity, and strictness of the deadline. For instance, MP7 in CSCE 611 is explicitly noted as "hard" for its due date [Source 1], indicating it should be a high priority.
+    *   Allocate dedicated time blocks in your schedule for each major project, especially in the weeks leading up to the end of the semester.
+5.  **Understand Technology Requirements and Prepare in Advance:**
+    *   Some assignments may require specific technology, such as a personal computer meeting TAMU requirements, an HDMI cable for presentations, or a wireless device for in-class submissions [Source 2]. Ensure you have access to and are familiar with these tools to avoid last-minute technical issues.
+    *   For reports requiring LockDown Browser, as in CSCE 681 [Source 3], ensure your setup is ready.
+**Academic Progression Planning:**
+By proactively identifying and managing end-of-semester workloads, you ensure that you can dedicate sufficient time and effort to each course's final requirements. This not only helps in achieving better grades but also reinforces good academic habits essential for success in future courses and your overall academic progression at Texas A&amp;M. Understanding the demands of different course types (e.g., project-heavy vs. continuous assignment-heavy) allows you to make informed decisions when registering for future semesters, balancing your course load effectively.</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>To effectively manage the end-of-semester workload, especially when multiple final projects and papers are due, the core principle is **proactive time management and strategic prioritization**. This involves understanding all deadlines, starting work early, and being aware of course-specific policies.
+Here are some effective strategies based on the provided course information:
+1.  **Start Working Early and Consistently:** Many courses emphasize the importance of starting assignments as soon as they are assigned and not falling behind. For example, CSCE 608 advises, "Start working on assignments as soon as they are assigned" [Source 8], and CSCE 614 suggests, "The correct approach is to start working on assignments as early as possible" [Source 9]. This helps distribute the workload and allows time to seek assistance if difficulties arise [Source 9].
+2.  **Regularly Check Course Platforms (Canvas):** Due dates and course announcements are frequently updated on Canvas. It is crucial to check Canvas daily for updates, course materials, and due dates [Source 3, Source 6, Source 8]. CSCE 633 explicitly states, "Always refer to the due date listed on Canvas" [Source 6].
+3.  **Understand and Prioritize Based on Late Work Policies:** Late work policies vary significantly between courses, which can impact how you prioritize your tasks:
+    *   **No Late Assignments Accepted:** Some courses, like CSCE 633, state "No Late Assignments will be accepted" [Source 6]. CSCE 614 also notes, "Late assignments are not going to be accepted in general, unless a University sanctioned excuse is provided ahead of time" [Source 9].
+    *   **Strict Deductions:** CSCE 672 has a tiered deduction policy for late write-ups and a 10% per day deduction for other assignments, up to a week [Source 10].
+    *   **Hard Deadlines:** For CSCE 611, the due date for MP7 is explicitly stated as "hard" to allow for timely grading [Source 2].
+    Knowing these policies helps you prioritize assignments with strict or "hard" deadlines to avoid penalties.
+4.  **Identify and Track Major End-of-Semester Deliverables:** Create a comprehensive list of all final projects, reports, and exams across your courses. Examples from the context include:
+    *   **CSCE 632:** Final Presentation, Final Report, and Video Demo due April 28 [Source 4].
+    *   **CSCE 633:** Final Project due May 4 [Source 6].
+    *   **CSCE 648:** Final project presentations and critique in Week 14 [Source 7].
+    *   **CSCE 608:** Course project #2 due April 27, Final exam on May 4 [Source 8].
+    *   **CSCE 672:** Final project presentations due April 27-28, Final project reports due May 1 [Source 10].
+    *   **CSCE 611:** MP7 due May 3, Final Exam on May 5 [Source 2].
+    *   **CSCE 629:** Midterm and comprehensive final exam [Source 3].
+5.  **Understand Excused Absence Procedures:** While not a strategy for general workload management, knowing the process for excused absences (following Student Rule 7) is important for unforeseen circumstances. Requests must typically be made prior to the absence or within two business days with an explanation [Source 5]. Missed work due to an approved excused absence is not considered late work [Source 6].
+**Planning Dimension:**
+By implementing these strategies, students can create a detailed academic plan for the semester. This involves mapping out all major deadlines, allocating dedicated time slots for each project and exam, and adjusting priorities based on the specific late work policies of each course. Proactive planning helps to prevent the overwhelming feeling of multiple converging deadlines, allowing for a more balanced and effective approach to academic progression.</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>To effectively manage the end-of-semester workload at Texas A&amp;M University, especially with multiple final projects and papers due, a key principle is **proactive planning and consistent engagement**. This involves staying organized, understanding course-specific policies, and utilizing available resources.
+Based on the provided course information, here are some effective strategies:
+*   **Start Early and Plan Ahead**
+    *   Begin working on assignments as soon as they are assigned, rather than waiting until closer to the deadline [Source 6, 7].
+    *   Plan your time, including potential travel, in accordance with the course schedule for all assignments, projects, and exams [Source 8].
+    *   Be aware that some courses have projects due approximately every two weeks, requiring continuous effort [Source 8].
+*   **Utilize Canvas for Up-to-Date Information**
+    *   Check Canvas daily for course announcements, materials, and assignment due dates [Source 6].
+    *   Always refer to the due date listed on Canvas, as this is the definitive source [Source 3].
+    *   All assignments and projects are typically submitted electronically via Canvas [Source 6, 7].
+*   **Understand and Adhere to Strict Due Dates and Late Policies**
+    *   Many courses have strict "No Late Assignments" policies, meaning deliverables submitted after the established deadline will not be accepted [Source 3, 7].
+    *   For courses that do accept late work, significant deductions may apply (e.g., 20% per day, or a maximum possible score decreasing over time) [Source 8, 9].
+    *   Some deadlines, especially for final projects or machine problems, are "hard" to ensure timely grading [Source 2].
+*   **Seek Assistance Promptly**
+    *   If you encounter difficulties with assignments, contact the instructor or TA as early as possible. Waiting until closer to the deadline may make it harder to receive help [Source 7].
+*   **Prioritize and Track All Deliverables**
+    *   Keep track of all significant due dates, including homework, project presentations, final project reports, and final exams across all your courses [Source 3, 4, 6, 9]. For example, CSCE 633 has a Final Project due May 4 [Source 3], CSCE 672 has Final project presentations April 27-28 and reports May 1 [Source 9], and CSCE 611 has MP7 due May 3 and a Final Exam May 5 [Source 2].
+By proactively managing your schedule, staying informed through Canvas, and understanding the strictness of deadlines, you can better navigate the demanding end-of-semester period.</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>To effectively manage the end-of-semester workload, especially when facing multiple final projects and papers, the underlying principle is **proactive academic planning and diligent adherence to course-specific requirements and deadlines**. This involves understanding each course's structure, anticipating peak workload periods, and utilizing available university policies.
+Based on the provided syllabi, here are some effective strategies:
+*   **Start Early and Check Daily:** Many courses emphasize the importance of starting assignments as soon as they are assigned and regularly checking Canvas for announcements, materials, and due dates [Source 8, 9]. For example, CSCE 614 advises starting assignments early to allow time to contact instructors or TAs for assistance [Source 9].
+*   **Understand and Adhere to Strict Due Dates and Late Policies:** Be aware that many courses have very strict late work policies.
+    *   Some courses, like CSCE 633 and CSCE 614, state that "No Late Assignments will be accepted" or "Late assignments are not going to be accepted in general" unless a University-sanctioned excuse is provided ahead of time [Source 6, 9].
+    *   CSCE 672 has a specific tiered late policy, deducting 10% per day late for some assignments and significantly reducing the maximum possible grade for others if submitted late [Source 10].
+    *   CSCE 611 explicitly states that the due date for MP7 is "hard" to allow for timely grading [Source 2].
+    *   CSCE 681 requires lecture reports to be completed within the lecture time frame, with missed reports without an excused absence receiving an automatic zero [Source 1].
+*   **Utilize Excused Absence Policies Proactively:** Familiarize yourself with Student Rule 7 for excused absences. For courses like CSCE 681, requesting an excused absence requires following specific steps, including providing advance notice or notification within two business days after the absence, with supporting documentation [Source 5]. This can prevent zeros for missed assignments or lectures.
+*   **Prioritize and Plan Around Major Deliverables:** Identify significant due dates for final projects, presentations, and exams across all your courses.
+    *   For example, CSCE 632 has a Final Presentation on April 21 &amp; 23, and a Final Report &amp; Video Demo due April 28 [Source 4].
+    *   CSCE 672 has Final project presentations due April 27-28 and Final project reports due May 1 [Source 10].
+    *   CSCE 608 has Course project #2 due in Week 16 (April 27) and a Final exam on May 4 [Source 8].
+    *   CSCE 633 has a Final Project due May 4 [Source 6].
+    *   CSCE 611 has MP7 due May 3 and a Final Exam on May 5 [Source 2].
+    *   Mapping these dates will help you allocate time effectively.
+*   **Attend Lectures and Seminars Regularly:** Several courses emphasize the importance of attendance. CSCE 681 requires attendance for all lectures, and you must bring your TAMU ID for verification [Source 1]. CSCE 648 states that "regular class attendance is essential" [Source 7], and CSCE 608 "strongly recommended" attendance, noting students are responsible for missed material [Source 8].
+*   **Be Mindful of Academic Integrity and AI Policies:** Strict policies against plagiarism and the use of AI tools are in place. CSCE 681 states that reports with machine-generated text will be submitted to the Aggie Honors Office, potentially leading to an F* for the course [Source 5]. CSCE 608 explicitly states, "The use of AI is strictly prohibited in this course" [Source 8]. Ensure all submitted work is your own and adheres to these guidelines.
+By proactively planning, understanding each course's specific requirements and deadlines, and adhering to university policies, students can better manage their academic progression and reduce stress during the intensive end-of-semester period.
+I don't have enough data to provide a comprehensive guide to end-of-semester workload management, as the context only includes specific course syllabi and not general university-wide advice on this topic. However, the strategies above are derived directly from the provided course information.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3100,6 +4868,99 @@
 Based on the available syllabi, while not every course follows this model, at least one course (CSCE 679) explicitly features a single, tool-specific project (D3.js) for graduate students that accounts for 50% of the final grade [Source 1]. Another course (CSCE 713) also has a significant individual, tool-related component ("Vulnerabilities PoC") weighted at 50% [Source 3].</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>The grading policy for a course outlines the weight assigned to various components, such as projects, exams, assignments, and participation, to determine a student's final grade. This structure reflects the instructor's emphasis on different learning activities and outcomes [Source 1, 3, 4, 7, 8, 9].
+In CSCE 679, the course project accounts for 50% of the final grade, and graduate students are specifically required to implement their project using the D3.js visualization library [Source 1]. This aligns with the course's learning outcomes, which include gaining practical skills for crafting interactive visualizations through hands-on tutorials in D3 and Vega-Lite [Source 5].
+Looking at other graduate CS courses in the provided context:
+*   **CSCE 713** has an individual component called "Vulnerabilities PoC" (Proof of Concept) that accounts for 50% of the grade. Students are required to deliver source code and a video demonstrating exploitation for vulnerabilities explained in class [Source 3]. While not explicitly tied to a single named tool like D3.js, it is a single, technically-specific deliverable with a high weight.
+*   **CSCE 648** allocates 36% of the grade to projects, which are split across six equally weighted projects, meaning no single project accounts for 50% [Source 4, 6].
+*   **CSCE 652** assigns 30% of the grade to a final project, with homework accounting for 60% [Source 7].
+*   **CSCE 629** primarily uses exams (60%) and homework (30%), with no specific projects listed [Source 8].
+*   **CSCE 748** has "Programming assignments" worth 50%, but this is distributed across five assignments, not a single project. The final project is 20% [Source 9].
+Based on the available syllabi, while CSCE 679 explicitly features a single, tool-specific project (D3.js) for 50% of the grade [Source 1], CSCE 713 also has a single, high-weighted individual technical deliverable ("Vulnerabilities PoC") at 50% [Source 3]. Other courses either distribute project weight across multiple assignments or have different grading structures. Therefore, it is not universally common across all provided examples, but it does appear in more than one instance for a significant individual component.
+I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>The question pertains to the structure of grading policies in academic courses, specifically the weighting and nature of major assignments like projects.
+Based on the provided syllabi for Texas A&amp;M University graduate CS courses:
+*   In **CSCE 679**, the course project accounts for 50% of the final grade, and graduate students are specifically required to implement their project using the D3.js visualization library [Source 1]. This aligns with your description of a single, tool-specific project counting for half of the final grade.
+*   In **CSCE 648**, projects contribute 36% to the final grade, but this is distributed across six equally weighted projects, not a single one [Source 4, 6].
+*   In **CSCE 713**, "Vulnerabilities PoC" is an individual component worth 50% of the grade. While significant, its description ("PoCs for the vulnerabilities explained in class") suggests it may involve multiple proofs of concept rather than a single, monolithic project, and it is not explicitly tool-specific in the same way D3.js is [Source 7].
+*   In **CSCE 676**, an "Individual Semester-Long Project" accounts for 40% of the final grade [Source 9]. This is a single project, but it does not constitute 50% of the grade.
+*   In **CSCE 748**, programming assignments collectively make up 50% of the grade, but these are five separate assignments, not a single project. A final project is also included, but it is weighted at 20% [Source 10].
+Therefore, based on the available syllabi, this specific grading structure—where a single, tool-specific project accounts for 50% of the final grade—is explicitly observed in **CSCE 679** [Source 1]. Other courses have different project weighting schemes or distribute project grades across multiple assignments. It does not appear to be a common practice across all the listed TAMU graduate CS courses in this context.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the commonality of a single, tool-specific project counting for half of your final grade varies among Texas A&amp;M University graduate CS courses.
+The principle underlying this question relates to the structure and weighting of major academic components, specifically projects, within a course's grading policy. These projects often serve as a primary mechanism for students to demonstrate mastery of course learning outcomes.
+In **CSCE 679**, graduate students are required to complete a course project using the D3.js visualization library, which accounts for 50% of their final grade [Source 1]. This project is a central component for students to apply concepts learned in the course, such as analyzing diverse data types and crafting interactive visualizations, with hands-on tutorials provided for D3 and Vega-Lite [Source 4].
+However, other courses show different approaches:
+*   **CSCE 676** includes an "Individual Semester-Long Project" that accounts for 40% of the final grade [Source 10]. While a single project, its weight is slightly less than 50%.
+*   **CSCE 748** has a "Final project" worth 20% of the grade, in addition to five programming assignments that collectively make up 50% [Source 9].
+*   **CSCE 648** requires students to complete six projects, each contributing 1/6th of the 36% allocated for projects, meaning no single project accounts for a large portion of the grade [Source 3, 7].
+*   **CSCE 629** does not list projects as a component in its grading policy, focusing instead on exams, quizzes/exercises, and homework [Source 8].
+*   **CSCE 632** mentions a "Final Presentation" and "Final Report" for a project but does not specify its weight in the grading policy [Source 5].
+Therefore, while a 50% weighted, tool-specific project is present in CSCE 679 [Source 1], it is not a universally common structure across all graduate CS courses in the provided context. Other courses either distribute project weight across multiple assignments, assign a lower percentage to a single project, or do not feature projects as a primary grading component.</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>In Texas A&amp;M University graduate CS courses, grading policies vary, and while projects are a common component, the specific weighting and nature of a single, tool-specific project counting for half of the final grade is not uniformly observed across the provided syllabi.
+For **CSCE 679**, graduate students are required to complete a course project using the D3.js visualization library, which accounts for 50% of their final grade [Source 1]. This project involves hands-on tutorials in D3 and Vega-Lite, and later in web programming, to craft interactive visualizations [Source 4].
+In contrast, other courses show different structures:
+*   **CSCE 648** allocates 36% of the grade to projects, which are six equally weighted projects [Source 3, Source 7].
+*   **CSCE 629** bases grades on exams (60%), homework (30%), and quizzes/exercises (10%), with no large project component mentioned [Source 8].
+*   **CSCE 748** has programming assignments (50%) and a final project (20%) [Source 9]. The 50% for programming assignments is distributed across five assignments, not a single project [Source 9].
+*   **CSCE 676** includes an Individual Semester-Long Project worth 40% of the grade [Source 10].
+Based on the available context, CSCE 679 is the only course explicitly detailing a single, tool-specific project (D3.js for graduate students) that constitutes 50% of the final grade. Other courses either have multiple projects contributing to a similar or lower percentage, or a single project with a lower weighting.
+I don't have enough data to definitively state how common this specific grading structure is across *all* TAMU graduate CS courses, as only a limited number of syllabi were provided.</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Based on the provided context, it does not appear to be common for a single, tool-specific project like D3.js to count for half of your final grade in other TAMU graduate CS courses.
+Here's a breakdown of project-based grading from the available syllabi:
+*   **CSCE 679:** Graduate students must implement their project using the D3.js visualization library, which accounts for 50% of the final grade [Source 3]. This is the specific instance you referenced.
+*   **CSCE 713:** This course has a "Vulnerabilities PoC" (Proof of Concept) worth 50% of the grade, which is an individual component requiring students to deliver source code and a video demonstrating exploitation of vulnerabilities explained in class. While it's a single component worth 50%, it's focused on demonstrating exploitation skills rather than a specific visualization library [Source 1].
+*   **CSCE 748:** This course has "Programming assignments" worth 50%, but these consist of 5 assignments in Python, not a single project. There is also a "Final project" worth 20% [Source 7].
+*   **CSCE 752:** This course includes "Projects using ROS" (Robotics Operating System) which account for 34% of the grade. However, these are described as "approximately six assignments," some individual and some group, rather than a single project [Source 9].
+*   **CSCE 669:** This course has a "Course project" worth 35% of the final grade [Source 10].
+*   **CSCE 681 &amp; CSCE 629:** These courses do not have a single project component of this magnitude [Source 2, 4, 5].
+While some courses have significant project components or single assessment items worth 50%, the specific combination of a *single, tool-specific project* accounting for 50% of the final grade appears to be unique to CSCE 679 among the provided examples.</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Based on the provided syllabi for Texas A&amp;M University graduate CS courses:
+In **CSCE 679**, graduate students are required to implement a course project using the D3.js visualization library, which accounts for 50% of their final grade [Source 3]. This fits the description of a single, tool-specific project counting for half the grade.
+Looking at other courses:
+*   **CSCE 713** includes a "Vulnerabilities PoC" (Proof of Concept) component, which is individual and accounts for 50% of the grade. Students are expected to deliver source code and a video demonstrating exploitation using security tools on their own machines [Source 1]. While not explicitly called a "project," it is a single, high-weighted, tool-dependent deliverable.
+*   **CSCE 676** lists "Homework" as 50% of the grade, but this consists of weekly assignments (13 in total), not a single project [Source 8]. An "Individual Semester-Long Project" in this course is worth 40% [Source 8].
+*   Other courses, such as **CSCE 624**, **CSCE 612**, **CSCE 629**, **CSCE 638**, and **CSCE 669**, distribute grades across multiple components like assignments, projects, exams, quizzes, and participation, with no single project or tool-specific component reaching 50% of the final grade [Source 4, 5, 6, 7, 9, 10]. For example, the team-based project in CSCE 624 is 30% [Source 4], and the course project in CSCE 669 is 35% [Source 9, 10].
+Therefore, while **CSCE 679** explicitly features a single, tool-specific project (D3.js) worth 50% [Source 3], and **CSCE 713** has a single, tool-dependent individual component (Vulnerabilities PoC) also worth 50% [Source 1], this grading structure is not common across all the provided TAMU graduate CS course syllabi.</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Based on the provided syllabi for Texas A&amp;M University graduate CS courses, it is not common for a single, tool-specific project like D3.js to count for half of your final grade.
+Here's a breakdown of project weighting in the available courses:
+*   **CSCE 713:** The "Vulnerabilities PoC (Individual)" component accounts for 50% of the grade. While this is a single, significant individual component, it involves demonstrating exploits for vulnerabilities explained in class, rather than a specific visualization tool like D3.js [Source 1]. There are also a First Project (25%) and Final Project (25%) [Source 1].
+*   **CSCE 748:** "Programming assignments" collectively account for 50% of the grade, but this consists of 5 separate assignments, not a single project [Source 2]. A separate "Final project" is worth 20% [Source 2].
+*   **CSCE 652:** The Final Project is 30% of the grade [Source 4].
+*   **CSCE 638:** The Course Project is 26% of the grade [Source 5].
+*   **CSCE 669:** The Course project is 35% of the grade [Source 8].
+*   **CSCE 672:** The Team project is 35% of the grade [Source 10].
+*   **CSCE 612:** Homework assignments (multiple) account for 40% of the grade [Source 9].
+*   **CSCE 629:** This course does not explicitly list a "project" component, with grades based on exams (60%), quizzes/exercises (10%), and homework (30%) [Source 7].
+While some courses have significant project components, none of the provided syllabi explicitly describe a *single, tool-specific project* (like one focused solely on D3.js) that constitutes 50% of the final grade. The closest are CSCE 713's PoC component and CSCE 748's programming assignments, but these are not described as tool-specific in the way your question implies.
+I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3174,6 +5035,41 @@
       <c r="R19" t="inlineStr">
         <is>
           <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [3].</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600 (54978), is scheduled for Thursday, February 26th, in class [Source 1, Source 3].</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [1, 2].</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [1, 2].</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [1, 3].</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26, in class [1, 3].</t>
         </is>
       </c>
     </row>
@@ -3258,6 +5154,41 @@
           <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608 is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. Its ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. The ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009 (ISBN: 978-0-13-187325-4) [Source 1].</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608, Section 600, is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009 (ISBN: 978-0-13-187325-4) [Source 1].</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>The required textbook for CSCE 608 is "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom, 2nd Edition, published by Pearson Prentice Hall in 2009. Its ISBN is 978-0-13-187325-4 [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3332,6 +5263,41 @@
       <c r="R21" t="inlineStr">
         <is>
           <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>For CSCE 633, the permitted programming language is Python. It must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>The programming language permitted for CSCE 633 is Python, and it must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>The programming language permitted for CSCE 633 is Python, and it must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>The programming language permitted for CSCE 633 is Python, and it must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>The programming language permitted for CSCE 633 is Python, and it must be executable on CS unix hosts or other public systems in the department lab [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>The programming language permitted for CSCE 633, Section 601, is Python, and it must be executable on CS Unix hosts or other public systems in the department lab [Source 2, Source 3].</t>
         </is>
       </c>
     </row>
@@ -3440,6 +5406,69 @@
 *   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
 *   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
 *   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to [Source 1, Source 2]:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection.
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches.
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning.
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, Source 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, Source 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, Source 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, Source 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 633, students are expected to be able to:
+*   Formalize the fundamental techniques and methods of machine learning, including methods, data processing, and model selection [Source 1, 2].
+*   Analyze and compare the strengths and weaknesses of commonly used machine learning approaches [Source 2].
+*   Evaluate the underlying mathematical relationships within and across advanced machine learning algorithms and the paradigms of supervised and unsupervised learning [Source 2].
+*   Design, implement, and apply various advanced machine learning algorithms in a range of real-world applications [Source 2].</t>
         </is>
       </c>
     </row>
@@ -3563,6 +5592,77 @@
 The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques learned in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids [Source 1]. The geometric interpretation of these results highlights the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1].
+**Career Relevance:**
+The ability to master current research techniques, apply them to real-world problems, and conduct research in computational optimization directly prepares students for careers in advanced research, development, and problem-solving roles within industries that rely on complex optimization, algorithm design, and data analysis. This includes fields such as operations research, artificial intelligence, machine learning, logistics, and software engineering, where efficient algorithms and optimization strategies are critical for system performance and decision-making [Source 1, 2]. The course also provides a strong foundation for further academic pursuits in these areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, you will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>After completing CSCE 669, you will be able to:
+*   Master basic theories and techniques in the current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization, and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>After completing CSCE 669, you will be able to:
+*   Master basic theories and techniques in the current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization, and other related research areas [Source 2].</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, students will be able to:
+*   Master basic theories and techniques in current research in computational optimization [Source 1, 2].
+*   Apply these theories and techniques to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and related areas [Source 2].
+This course, CSCE 669 Section 600, focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids [Source 1]. The geometric interpretation of these results highlights the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1].
+**Career Relevance:** The course directly prepares students for advanced research in computational optimization, indicating its relevance for academic and R&amp;D careers. The ability to apply theories and techniques to "real-world problems" suggests its utility in industry roles that involve complex problem-solving, algorithm design, and optimization in fields like logistics, data science, machine learning, and operations research [Source 1, 2]. The course project, which involves reading recent published papers and conducting research on current problems, further enhances skills valuable for innovation and problem-solving in professional settings [Source 2].
+The prerequisite for this course is CSCE 629 [Source 1]. Grading is based on homework assignments (30%), a course project (35%), and a final exam (35%) [Source 2].</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, section 600, you will be able to:
+*   Master basic theories and techniques in the current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].
+This course focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, with applications to max flow, matching, and matroids. It also covers the geometric interpretation of these results, highlighting the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1]. The course content, including topics like approximation algorithms, parameterized algorithms, and exact algorithms for NP-hard problems, directly relates to industry applications and career paths in areas requiring advanced problem-solving, algorithm design, and optimization techniques for complex computational challenges [Source 1, 4].</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Upon completing CSCE 669, section 600, you will be able to:
+*   Master basic theories and techniques in the current research in computational optimization [Source 1, 2].
+*   Apply theories and techniques studied in the course to solve real-world problems in computational optimization [Source 1, 2].
+*   Use appropriate technologies to communicate, collaborate, and conduct research in the area of computational optimization [Source 2].
+*   Gain a solid background and preparation for advanced research in computational optimization and other related research areas [Source 2].
+This course focuses on the combinatorial theory of polytopes for solving combinatorial optimization problems, with applications to max flow, matching, and matroids. It also covers the geometric interpretation of these results, highlighting the role of polyhedral combinatorics in designing and understanding the complexity of approximation algorithms [Source 1]. The course content, including topics like approximation algorithms, parameterized algorithms, and exact algorithms for NP-hard problems, directly relates to industry applications and career paths in areas requiring advanced problem-solving, algorithm design, and optimization techniques for complex computational challenges [Source 1, 4].</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3671,6 +5771,69 @@
 *   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665 (Section 600), students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665, students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665, students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665, students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 1].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 1].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 1].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 1].</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665, students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 1].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 1].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 1].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 1].</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Upon completion of CSCE 665, students will be able to:
+*   Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks [Source 2].
+*   Synthesize fundamental security principles and mechanisms to design robust defenses against sophisticated threat models [Source 2].
+*   Critique state-of-the-art security literature to identify open problems, methodological flaws, and emerging trends in the field [Source 2].
+*   Demonstrate a practical working knowledge of offensive and/or defensive techniques to contextualize theoretical concepts [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3745,6 +5908,41 @@
       <c r="R25" t="inlineStr">
         <is>
           <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608, Section 600, will be posted in Canvas [Source 2]. Students should check course announcements, course material, and due dates daily [Source 2].</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas [Source 3]. You should check your course announcements, course material, and due dates daily [Source 3]. The course uses the Canvas Learning Management System, and students submit their homework and projects via Canvas [Source 3].</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas [3]. Students should check course announcements, course material, and due dates daily [3].</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas [3]. Students should check course announcements, course material, and due dates daily [3].</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas. Students should check Canvas daily for announcements, course material, and due dates. Homework and projects are also submitted via Canvas [Source 4].</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas. Students should check Canvas daily for announcements, course material, and due dates. Homework and projects are also submitted via Canvas [Source 4].</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>All course information for CSCE 608 will be posted in Canvas [3]. Students should check course announcements, course material, and due dates daily [3].</t>
         </is>
       </c>
     </row>
@@ -3844,6 +6042,67 @@
           <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
 The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
 To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course explicitly states that "Upon completion of the course, students should be able to prepare reports and discuss research works and selected published technical articles" [Source 1, Source 2].
+To achieve this, students in Section 600 are expected to attend all lectures and write a report for each. These reports are structured to include sections such as background, problem statement, proposed solution, results, and critique, directly supporting the development of report preparation and research discussion skills [Source 2]. Students in Section 700 also write reports for each lecture, which are in the form of quizzes related to the lecture content [Source 4].</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course's purpose is to expose students to current and seminal research topics, and upon completion, students are expected to "prepare reports and discuss research works and selected published technical articles" [Source 1].
+The course structure supports this through:
+*   **Reports:** Students are required to write a report for each lecture [Source 2, 4]. For Section 600, these reports are structured with sections such as background, problem statement, proposed solution, results, and critique, which directly align with the components of discussing research [Source 2]. For Section 700, reports are in the form of quizzes related to lecture content [Source 4].
+*   **Discussion:** The catalog description mentions "Reports and discussion of current research and of selected published technical articles" [Source 1]. While the context doesn't detail the "discussion" aspect beyond the reports, the act of preparing structured reports on research topics inherently involves engaging with and discussing the research.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 (Section 600 and 700) seem attainable for preparing reports and discussing research.
+The purpose of the course is to expose students to current and seminal research topics in computer science. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1].
+For Section 600, students are expected to attend all lectures and write a report for each. These reports are structured with five sections: background, problem statement, proposed solution, results, and critique, which directly supports the objective of preparing reports on research [Source 2].
+For Section 700, students watch lecture recordings and write a report for each, consisting of multiple-choice and multiple-answer questions related to the lecture content [Source 3].
+Both sections require students to engage with research content and produce reports, directly addressing the learning outcomes.</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 (Section 600 and 700) seem attainable for preparing reports and discussing research.
+The purpose of the course is to expose students to current and seminal research topics in computer science. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1].
+For Section 600, students are expected to attend all lectures and write a report for each. These reports are structured with five sections: background, problem statement, proposed solution, results, and critique, which directly supports the objective of preparing reports on research [Source 2].
+For Section 700, students watch lecture recordings and write a report for each, consisting of multiple-choice and multiple-answer questions related to the lecture content [Source 3].
+Both sections require students to engage with research content and produce reports, directly addressing the learning outcomes.</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 seem attainable for preparing reports and discussing research.
+The course's purpose is to expose students to current and seminal research topics, and upon completion, students are expected to "prepare reports and discuss research works and selected published technical articles" [Source 1].
+The course structure supports this through:
+*   **Reports:** Students are required to write a report for each lecture [Source 2, 4]. For Section 600, these reports are structured with sections such as background, problem statement, proposed solution, results, and critique, which directly align with the components of discussing research [Source 2]. For Section 700, reports are in the form of quizzes related to lecture content [Source 4].
+*   **Discussion:** The catalog description mentions "Reports and discussion of current research and of selected published technical articles" [Source 1]. While the context doesn't detail the "discussion" aspect beyond the reports, the act of preparing structured reports on research topics inherently involves engaging with and discussing the research.</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 (Section 600 and 700) seem attainable for preparing reports and discussing research.
+The purpose of the course is to expose students to current and seminal research topics in computer science. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1].
+For Section 600, students are expected to attend all lectures and write a report for each. These reports are structured with five sections: background, problem statement, proposed solution, results, and critique, which directly supports the objective of preparing reports on research [Source 2].
+For Section 700, students watch lecture recordings and write a report for each, consisting of multiple-choice and multiple-answer questions related to the lecture content [Source 3].
+Both sections require students to engage with research content and produce reports, directly addressing the learning outcomes.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Yes, the learning objectives for CSCE 681 (Section 600 and 700) seem attainable for preparing reports and discussing research.
+The purpose of the course is to expose students to current and seminal research topics in computer science. Upon completion, students should be able to prepare reports and discuss research works and selected published technical articles [Source 1].
+For Section 600, students are expected to attend all lectures and write a report for each. These reports are structured with five sections: background, problem statement, proposed solution, results, and critique, which directly supports the objective of preparing reports on research [Source 2].
+For Section 700, students watch lecture recordings and write a report for each, consisting of multiple-choice and multiple-answer questions related to the lecture content [Source 3].
+Both sections require students to engage with research content and produce reports, directly addressing the learning outcomes.</t>
         </is>
       </c>
     </row>
@@ -4098,6 +6357,208 @@
 |      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
 | 5    | Tue | Page Replacement Policies I                                        |
 |      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), is an Operating Systems course offered in Spring 2026 [Source 3].
+**Course Purpose:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will leverage knowledge from previous courses in Computer Architecture and Computer Systems to understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. A significant component involves implementing a simple operating system capable of booting and running on a bare PC [Source 2].
+**Prerequisites:**
+CSCE 313 and graduate classification are required [Source 2, 3].
+**Grading Policy:**
+The course grading is based on the following components [Source 7]:
+*   Midterm: 200 points
+*   Final Exam: 200 points
+*   Design and Programming Assignments (Machine Problems): 400 points
+*   Daily Quizzes: 100 points
+*   Homework Assignments: 100 points
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 7].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule outlines the following topics for the initial weeks [Source 1]:
+| Week | Day | Topic                                                              |
+| :--- | :-- | :----------------------------------------------------------------- |
+| 1    | Tue | Project Setup, Intro: What is an OS?                               |
+|      | Thu | Architectural Support, OS Structures                               |
+| 2    | Tue | System Calls                                                       |
+|      | Thu | Interrupts and Exceptions on the x86                               |
+| 3    | Tue | Memory: Memory Allocation, Address Spaces                          |
+|      | Thu | Paging, Advanced Paging                                            |
+| 4    | Tue | The TLB, Paging on the x86                                         |
+|      | Thu | Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms    |
+| 5    | Tue | Page Replacement Policies I                                        |
+|      | Thu | Page Replacement Policies II, Recursive Page Table Lookup          |</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), titled "Operating Systems," is offered in Spring 2026 at College Station [Source 3].
+**Course Purpose and Overview:**
+This course provides an overview of the general architecture and important components of modern operating systems. Students will leverage knowledge from previous computer architecture and systems courses to understand and implement aspects of operating systems, including memory management, persistent storage, file systems, threading, scheduling, and resource management. It covers fundamental approaches to virtualization and what is required to build a distributed system. A key component is implementing a simple operating system that can boot and run on a bare PC [Source 2].
+**Key Topics:**
+The course covers the evolution of computer architecture hardware/software leading to contemporary operating systems, basic operating system concepts, methods of operating system design and construction, algorithms for CPU scheduling, memory and general resource allocation, process coordination and management, and case studies of various operating systems [Source 3].
+**Prerequisites:**
+To enroll in CSCE 611, students must have completed CSCE 313 and have graduate classification [Source 2, 3].
+**Grading:**
+The course includes a midterm and a final exam, totaling 400 points, in addition to a series of design and programming assignments [Source 5].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule details the following topics in the early weeks:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 1].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 1].
+*   **Week 3:** Memory management, including Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 1].
+*   **Week 4:** Further memory management topics such as The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 1].
+*   **Week 5:** Page Replacement Policies I and II, and Recursive Page Table Lookup [Source 1].</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), titled "Operating Systems," is offered in Spring 2026 at College Station [Source 3].
+**Course Purpose and Overview:**
+This course provides an overview of the general architecture and important components of modern operating systems. Students will leverage knowledge from previous computer architecture and systems courses to understand and implement aspects of operating systems, including memory management, persistent storage, file systems, threading, scheduling, and resource management. It covers fundamental approaches to virtualization and what is required to build a distributed system. A key component is implementing a simple operating system that can boot and run on a bare PC [Source 2].
+**Key Topics:**
+The course covers the evolution of computer architecture hardware/software leading to contemporary operating systems, basic operating system concepts, methods of operating system design and construction, algorithms for CPU scheduling, memory and general resource allocation, process coordination and management, and case studies of various operating systems [Source 3].
+**Prerequisites:**
+To enroll in CSCE 611, students must have completed CSCE 313 and have graduate classification [Source 2, 3].
+**Grading:**
+The course includes a midterm and a final exam, totaling 400 points, in addition to a series of design and programming assignments [Source 5].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule details the following topics in the early weeks:
+*   **Week 1:** Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 1].
+*   **Week 2:** System Calls, and Interrupts and Exceptions on the x86 [Source 1].
+*   **Week 3:** Memory management, including Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 1].
+*   **Week 4:** Further memory management topics such as The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 1].
+*   **Week 5:** Page Replacement Policies I and II, and Recursive Page Table Lookup [Source 1].</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), titled "Operating Systems," is offered in Spring 2026 in College Station [Source 3].
+**Course Purpose and Overview:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will apply knowledge from Computer Architecture and Computer Systems to understand and implement aspects such as memory management, persistent storage, file systems, threading, scheduling, and resource management. It also covers fundamental approaches to virtualization and distributed systems. A significant part of the course involves implementing a simple operating system that can boot and run on a bare PC [Source 1, 3].
+**Prerequisites:**
+The prerequisites for CSCE 611 are CSCE 313 and graduate classification [Source 1, 3].
+**Key Topics and Learning Outcomes:**
+The course covers a range of topics including:
+*   Operating system architecture and major components [Source 1].
+*   Exception and interrupt handling [Source 1].
+*   Memory management, including virtual memory, paging, and address spaces [Source 1, 2].
+*   Concurrency mechanisms, synchronization, and threading [Source 1, 4].
+*   Persistent storage, file systems, and device drivers [Source 1, 4].
+*   Virtualization approaches [Source 1, 4].
+Upon completion, learners will be able to:
+*   Describe and compare the role, architecture, and major components of an operating system [Source 1].
+*   Implement components of a virtual memory manager for a paged system [Source 1, 4].
+*   Evaluate and compare various forms of concurrency and synchronization mechanisms [Source 1, 4].
+*   Implement components of a threading system, simple device driver, and simple file system [Source 4].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule for the early weeks focuses on foundational operating system concepts and memory management:
+*   **Week 1**: Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 2].
+*   **Week 3**: Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 2].
+*   **Week 4**: The Translation Lookaside Buffer (TLB), Paging on the x86 architecture, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 2].
+*   **Week 5**: Page Replacement Policies I and II, and Recursive Page Table Lookup [Source 2].
+**Grading Policy:**
+The grading for CSCE 611 is based on:
+*   Midterm and Final Exam: 400 points total [Source 4, 6].
+*   Design and Programming Assignments (Machine Problems): 400 points [Source 4, 6].
+*   Daily Quizzes: 100 points [Source 6].
+*   Homework Assignments: 100 points [Source 6].
+A standard letter grading scale is used: A (90%+), B (80%+), C (70%+), D (60%+), F (less than 60%) [Source 6].</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), titled "Operating Systems," is offered in Spring 2026 in College Station [Source 3].
+**Course Purpose and Overview:**
+This course provides an overview of the general architecture and key components of modern operating systems. Students will apply knowledge from Computer Architecture and Computer Systems to understand and implement aspects such as memory management, persistent storage, file systems, threading, scheduling, and resource management. It also covers fundamental approaches to virtualization and distributed systems. A significant part of the course involves implementing a simple operating system that can boot and run on a bare PC [Source 1, 3].
+**Prerequisites:**
+The prerequisites for CSCE 611 are CSCE 313 and graduate classification [Source 1, 3].
+**Key Topics and Learning Outcomes:**
+The course covers a range of topics including:
+*   Operating system architecture and major components [Source 1].
+*   Exception and interrupt handling [Source 1].
+*   Memory management, including virtual memory, paging, and address spaces [Source 1, 2].
+*   Concurrency mechanisms, synchronization, and threading [Source 1, 4].
+*   Persistent storage, file systems, and device drivers [Source 1, 4].
+*   Virtualization approaches [Source 1, 4].
+Upon completion, learners will be able to:
+*   Describe and compare the role, architecture, and major components of an operating system [Source 1].
+*   Implement components of a virtual memory manager for a paged system [Source 1, 4].
+*   Evaluate and compare various forms of concurrency and synchronization mechanisms [Source 1, 4].
+*   Implement components of a threading system, simple device driver, and simple file system [Source 4].
+**Early Week Topics (OS Structures and Memory Management):**
+The course schedule for the early weeks focuses on foundational operating system concepts and memory management:
+*   **Week 1**: Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 2].
+*   **Week 3**: Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 2].
+*   **Week 4**: The Translation Lookaside Buffer (TLB), Paging on the x86 architecture, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 2].
+*   **Week 5**: Page Replacement Policies I and II, and Recursive Page Table Lookup [Source 2].
+**Grading Policy:**
+The grading for CSCE 611 is based on:
+*   Midterm and Final Exam: 400 points total [Source 4, 6].
+*   Design and Programming Assignments (Machine Problems): 400 points [Source 4, 6].
+*   Daily Quizzes: 100 points [Source 6].
+*   Homework Assignments: 100 points [Source 6].
+A standard letter grading scale is used: A (90%+), B (80%+), C (70%+), D (60%+), F (less than 60%) [Source 6].</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>CSCE 611, Section 600 (50668), titled "Operating Systems," is offered in Spring 2026 in College Station [Source 3].
+**Course Purpose and Content:**
+This course provides an overview of the general architecture and most important components of modern operating systems. It leverages knowledge from previous courses on Computer Architecture and Computer Systems to help students understand and implement aspects of operating systems, including memory management, persistent storage and file systems, threading, scheduling, and resource management. The course covers fundamental approaches to virtualization and what is required to build a distributed system. Students will also implement a simple operating system [Source 2].
+**Key Learning Outcomes include:**
+*   Describing and comparing the role, architecture, and major components of an operating system [Source 2].
+*   Describing the role and operation of exception and interrupt handling in modern operating systems [Source 2].
+*   Implementing components of a virtual memory manager for a paged system [Source 2, 4].
+*   Evaluating and comparing various forms of concurrency and synchronization mechanisms [Source 2, 4].
+**Early Week Topics:**
+The course schedule details the following topics for the initial weeks, focusing on OS structures and memory management:
+*   **Week 1**: Project Setup, Introduction to Operating Systems, Architectural Support, and OS Structures [Source 1].
+*   **Week 2**: System Calls, and Interrupts and Exceptions on the x86 [Source 1].
+*   **Week 3**: Memory Allocation, Address Spaces, Paging, and Advanced Paging [Source 1].
+*   **Week 4**: The Translation Lookaside Buffer (TLB), Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 1].
+*   **Week 5**: Page Replacement Policies I and II, and Recursive Page Table Lookup [Source 1, 5].
+**Prerequisites:**
+The prerequisites for CSCE 611 are CSCE 313 and graduate classification [Source 2, 3].
+**Grading Policy:**
+The final grade is determined by:
+*   Midterm and Final Exam: 400 points total [Source 6].
+*   Design and Programming Assignments (Machine Problems): 400 points [Source 6].
+*   Daily Quizzes: 100 points [Source 6].
+*   Homework Assignments: 100 points [Source 6].
+A standard letter grading scale is used: A = 90% and above, B = 80% and above, C = 70% and above, D = 60% and above, F = less than 60% [Source 6].
+**Late Work Policy:**
+Deadlines for online quizzes and homework are hard, and late submissions will not be accepted. Machine problems are penalized 1/5 of earned points per calendar day for late submissions (1/3 during 10-week summer courses). No make-up work submissions will be accepted [Source 1].</t>
         </is>
       </c>
     </row>
@@ -4281,6 +6742,246 @@
 | Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600 (46627) in Spring 2026, effective time management will be crucial due to the distribution of assignments and the significant group project.
+Here's a breakdown to help you plan:
+**Course Overview:**
+*   **Course ID:** CSCE 670, Section 600 (46627) [Source 4]
+*   **Term:** Spring 2026 [Source 4]
+*   **Credit Hours:** 3 [Source 4]
+*   **Instructor:** Yu Zhang (yuzhang@tamu.edu) [Source 4]
+*   **Meeting Times:** MWF, 1:50 PM - 2:40 PM in HRBB 113 [Source 4]
+*   **Prerequisites:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 4]
+**Grading Breakdown:**
+*   **Homework:** 30% (5 assignments) [Source 2]
+*   **Quizzes:** 20% (4 quizzes) [Source 2]
+*   **Group Project:** 20% [Source 2]
+*   **Final Exam:** 30% [Source 2]
+**Key Components and Planning Advice:**
+1.  **Homeworks (30%):**
+    *   There are five programming assignments, all in Python. The first is introductory [Source 2].
+    *   **Due Dates:**
+        *   Homework 0: Jan 26 [Source 1, 3]
+        *   Homework 1: Feb 9 [Source 1, 3]
+        *   Homework 2: Mar 2 [Source 1, 3]
+        *   Homework 3: Mar 30 [Source 1, 3]
+        *   Homework 4: Apr 20 [Source 1, 3]
+    *   **Planning:** These are individual assignments, though discussing approaches (without sharing code) is encouraged. You must acknowledge all help [Source 2, 5]. You have a total of five late days, each an indivisible 24-hour unit. After using these, late assignments receive a 0 [Source 3, 5]. Start early on these, especially as they progress in weight (2% for HW0, then 7% each for the rest) [Source 2].
+2.  **Quizzes (20%):**
+    *   There will be four brief in-class quizzes [Source 2].
+    *   **Dates:**
+        *   Quiz 1: Feb 6 [Source 1, 3]
+        *   Quiz 2: Feb 27 [Source 1, 3]
+        *   Quiz 3: Mar 25 [Source 1]
+        *   Quiz 4: Apr 15 [Source 1]
+    *   **Planning:** These are spread throughout the semester, each contributing 5% to your grade [Source 2]. Regular review of course material, especially before the quiz dates, will be beneficial.
+3.  **Group Project (20%):**
+    *   You will work in teams of 3 or 4 on a mini-research project [Source 2].
+    *   **Key Dates:**
+        *   Proposal: due Mar 7 [Source 1]
+        *   Presentation: Apr 20, Apr 22, Apr 24, and Apr 27 [Source 1]
+        *   Report: due May 2 [Source 1]
+    *   **Planning:** This project has multiple deliverables spread across the latter half of the semester. Begin forming groups and brainstorming ideas early. The proposal is due in early March, followed by presentations in late April and the final report in early May. Consistent teamwork and progress tracking will be essential to manage this significant component.
+4.  **Final Exam (30%):**
+    *   A comprehensive final exam will be held on May 4, from 3:30 PM - 5:30 PM in HRBB 113 [Source 2].
+    *   **Planning:** Allocate dedicated study time for the final exam, as it is a substantial portion of your grade.
+**Overall Planning:**
+*   **Weekly Schedule:** Review the course schedule [Source 3] to align your study with the topics covered each week, which include Boolean Retrieval, TF-IDF, Link Analysis, Recommender Systems, Neural Ranking, Transformers, and Large Language Models [Source 3].
+*   **Late Days:** Use your five late days strategically for homeworks if unexpected circumstances arise, but be mindful that they are a limited resource [Source 3, 5].
+*   **AI Policy:** You may use AI-generated code if properly documented with the prompt and significant parts of the response. However, you are responsible for identifying errors and improving the code [Source 1].
+*   **Regrade Policy:** You have seven days to request a regrade in writing after receiving a graded assignment [Source 5].
+By proactively managing these components and adhering to deadlines, you can effectively navigate CSCE 670.</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600 (46627), effective time management will be crucial due to the distribution of assignments throughout the semester [Source 4].
+Here's a breakdown of the major components and their deadlines to help you plan:
+**Grading Breakdown:**
+*   **Homeworks:** 30%
+*   **Quizzes:** 20%
+*   **Final:** 30%
+*   **Group Project:** 20% [Source 2]
+**Key Components and Dates:**
+| Assignment Type | Component      | Due Date/Class Date                               | Weighting (of total grade) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>To plan your time effectively for CSCE 670, Section 600, consider the following components and their respective deadlines and weights:
+**Course Overview:**
+*   **Course ID:** CSCE 670, Section 600 (46627) [Source 2]
+*   **Term:** Spring 2026 [Source 2]
+*   **Instructor:** Yu Zhang [Source 2]
+*   **Meeting Times:** MWF, 1:50 PM - 2:40 PM, HRBB 113 [Source 2]
+**Grading Breakdown:**
+*   Homework: 30%
+*   Quizzes: 20%
+*   Final Exam: 30%
+*   Group Project: 20% [Source 1]
+**Key Components for Time Planning:**
+1.  **Homeworks (30% of grade):**
+    *   There are five programming assignments, all in Python, with the first one designed to familiarize you with Jupyter Notebook [Source 1].
+    *   **Due Dates:**
+        *   Homework 0: January 26
+        *   Homework 1: February 9
+        *   Homework 2: March 2
+        *   Homework 3: March 30
+        *   Homework 4: April 20 [Source 3, 4]
+    *   **Late Policy:** You have five late days total, each an indivisible 24-hour unit. Once used, late assignments receive a grade of 0 [Source 4, 5].
+    *   **Collaboration:** Homeworks are individual assignments. You should write your own code. While discussing approaches is encouraged, sharing code, pair programming, or working through specific problems in code together is inappropriate. All help must be acknowledged [Source 1, 5].
+    *   **Planning Tip:** Start early on homeworks, especially given their individual nature and the programming involved. Utilize the five late days strategically if unexpected issues arise, but do not rely on them.
+2.  **Quizzes (20% of grade):**
+    *   There will be four brief in-class quizzes, each worth 5% [Source 1].
+    *   **Dates:**
+        *   Quiz 1: February 6
+        *   Quiz 2: February 27
+        *   Quiz 3: March 25
+        *   Quiz 4: April 15 [Source 3, 4]
+    *   **Planning Tip:** These are spread throughout the semester, so consistent review of course material is crucial to be prepared for each in-class quiz.
+3.  **Group Project (20% of grade):**
+    *   You will work in teams of 3 or 4 on a mini-research project [Source 1].
+    *   **Key Deadlines:**
+        *   Proposal: due March 7
+        *   Presentations: April 20, April 22, April 24, and April 27 classes
+        *   Report: due May 2 [Source 3]
+    *   **Planning Tip:** This project has multiple stages, requiring sustained effort. Begin forming your group and brainstorming ideas early. Distribute tasks effectively among team members and ensure regular communication to meet the proposal, presentation, and final report deadlines.
+4.  **Final Exam (30% of grade):**
+    *   A comprehensive final exam will be held on May 4, from 3:30 PM - 5:30 PM in HRBB 113 [Source 1].
+    *   **Planning Tip:** Allocate sufficient time for review leading up to the final exam, as it is a significant portion of your grade.
+**Overall Academic Progression:**
+This course covers topics such as Boolean Retrieval, TF-IDF, Vector Space Model, Link Analysis, Recommender Systems, word2vec, Neural Ranking, Transformers, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models [Source 4]. The prerequisites are CSCE 310 or CSCE 603 or instructor approval, along with graduate classification [Source 2]. Given the breadth of topics and the programming-heavy assignments, consistent engagement with lectures and hands-on practice will be essential for success.</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>To plan your time effectively for CSCE 670, Section 600, consider the following components and their respective deadlines and weights:
+**Course Overview:**
+*   **Course ID:** CSCE 670, Section 600 (46627) [Source 2]
+*   **Term:** Spring 2026 [Source 2]
+*   **Instructor:** Yu Zhang [Source 2]
+*   **Meeting Times:** MWF, 1:50 PM - 2:40 PM, HRBB 113 [Source 2]
+**Grading Breakdown:**
+*   Homework: 30%
+*   Quizzes: 20%
+*   Final Exam: 30%
+*   Group Project: 20% [Source 1]
+**Key Components for Time Planning:**
+1.  **Homeworks (30% of grade):**
+    *   There are five programming assignments, all in Python, with the first one designed to familiarize you with Jupyter Notebook [Source 1].
+    *   **Due Dates:**
+        *   Homework 0: January 26
+        *   Homework 1: February 9
+        *   Homework 2: March 2
+        *   Homework 3: March 30
+        *   Homework 4: April 20 [Source 3, 4]
+    *   **Late Policy:** You have five late days total, each an indivisible 24-hour unit. Once used, late assignments receive a grade of 0 [Source 4, 5].
+    *   **Collaboration:** Homeworks are individual assignments. You should write your own code. While discussing approaches is encouraged, sharing code, pair programming, or working through specific problems in code together is inappropriate. All help must be acknowledged [Source 1, 5].
+    *   **Planning Tip:** Start early on homeworks, especially given their individual nature and the programming involved. Utilize the five late days strategically if unexpected issues arise, but do not rely on them.
+2.  **Quizzes (20% of grade):**
+    *   There will be four brief in-class quizzes, each worth 5% [Source 1].
+    *   **Dates:**
+        *   Quiz 1: February 6
+        *   Quiz 2: February 27
+        *   Quiz 3: March 25
+        *   Quiz 4: April 15 [Source 3, 4]
+    *   **Planning Tip:** These are spread throughout the semester, so consistent review of course material is crucial to be prepared for each in-class quiz.
+3.  **Group Project (20% of grade):**
+    *   You will work in teams of 3 or 4 on a mini-research project [Source 1].
+    *   **Key Deadlines:**
+        *   Proposal: due March 7
+        *   Presentations: April 20, April 22, April 24, and April 27 classes
+        *   Report: due May 2 [Source 3]
+    *   **Planning Tip:** This project has multiple stages, requiring sustained effort. Begin forming your group and brainstorming ideas early. Distribute tasks effectively among team members and ensure regular communication to meet the proposal, presentation, and final report deadlines.
+4.  **Final Exam (30% of grade):**
+    *   A comprehensive final exam will be held on May 4, from 3:30 PM - 5:30 PM in HRBB 113 [Source 1].
+    *   **Planning Tip:** Allocate sufficient time for review leading up to the final exam, as it is a significant portion of your grade.
+**Overall Academic Progression:**
+This course covers topics such as Boolean Retrieval, TF-IDF, Vector Space Model, Link Analysis, Recommender Systems, word2vec, Neural Ranking, Transformers, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models [Source 4]. The prerequisites are CSCE 310 or CSCE 603 or instructor approval, along with graduate classification [Source 2]. Given the breadth of topics and the programming-heavy assignments, consistent engagement with lectures and hands-on practice will be essential for success.</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600, "Information Storage and Retrieval" in Spring 2026, effective time management will be crucial given the various assignments and project work [Source 5].
+Here's a breakdown of key components and their deadlines to help you plan:
+**Course Overview:**
+*   **Course ID:** CSCE 670, Section 600 [Source 5]
+*   **Term:** Spring 2026 [Source 5]
+*   **Meeting Times:** MWF, 1:50 PM - 2:40 PM [Source 5]
+*   **Prerequisites:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5]. This indicates the course expects a foundational understanding of computer science concepts, which you should leverage in your planning.
+**Grading Breakdown:**
+*   **Homework:** 30% (five programming assignments in Python) [Source 2]
+*   **Quizzes:** 20% (four brief in-class quizzes) [Source 2]
+*   **Group Project:** 20% (mini-research project in teams of 3-4) [Source 2]
+*   **Final Exam:** 30% [Source 2]
+**Important Dates &amp; Planning Considerations:**
+| Assignment Type | Item           | Due Date/Time                               | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>To plan your time effectively for CSCE 670, Section 600 (46627), "Information Storage and Retrieval," in Spring 2026, consider the following key components and their deadlines:
+**Course Overview:**
+This course covers representation, storage, and access to very large multimedia document collections, including fundamental data structures and algorithms for information storage and retrieval systems. It also teaches techniques to design and evaluate complete retrieval systems, covering algorithms for indexing, compressing, and querying large collections [Source 5].
+**Prerequisites:**
+You should have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 5].
+**Instructor:**
+Yu Zhang (yuzhang@tamu.edu), Office: PETR 222. Office Hours: Mondays 3:30 – 4:30 PM [Source 5].
+**Grading Breakdown:**
+*   Homework: 30%
+*   Quizzes: 20%
+*   Group Project: 20%
+*   Final Exam: 30% [Source 2]
+**Key Dates and Planning Considerations:**
+**1. Homeworks (30% of grade):**
+There are five programming assignments, all in Python. The first is introductory (2%), and the subsequent four are 7% each [Source 2].
+*   **Homework 0:** Due Jan 26 [Source 1, 3]
+*   **Homework 1:** Due Feb 9 [Source 1, 3]
+*   **Homework 2:** Due Mar 2 [Source 1, 3]
+*   **Homework 3:** Due Mar 30 [Source 1, 3]
+*   **Homework 4:** Due Apr 20 [Source 1, 3]
+*   **Planning Tip:** Homeworks are individual assignments, but discussion about approaches is encouraged (without sharing code). You must acknowledge all help. You may use AI-generated code if properly documented with the prompt and significant parts of the response [Source 1, 2, 4].
+*   **Late Work Policy:** You have five late days total for homeworks, which are indivisible 24-hour units. Once used, late assignments receive a grade of 0 [Source 3, 4].
+**2. Quizzes (20% of grade):**
+There will be four brief in-class quizzes, each worth 5% [Source 2].
+*   **Quiz 1:** In the Feb 6 class [Source 1, 3]
+*   **Quiz 2:** In the Feb 27 class [Source 1, 3]
+*   **Quiz 3:** In the Mar 25 class [Source 1]
+*   **Quiz 4:** In the Apr 15 class [Source 1]
+*   **Planning Tip:** These are in-class, so ensure you are prepared for the material covered up to those dates.
+**3. Group Project (20% of grade):**
+Students will work in teams of 3 or 4 on a mini-research project [Source 2].
+*   **Proposal:** Due Mar 7 [Source 1]
+*   **Presentation:** In the Apr 20, Apr 22, Apr 24, and Apr 27 classes [Source 1]
+*   **Report:** Due May 2 [Source 1]
+*   **Planning Tip:** Start forming groups and brainstorming project ideas early. The proposal is due in early March, and presentations/reports are at the very end of the semester, requiring sustained effort.
+**4. Final Exam (30% of grade):**
+*   **Date:** May 4, 3:30 - 5:30 PM in HRBB 113 [Source 1, 2]
+*   **Planning Tip:** This is a comprehensive final exam, so consistent review of course material throughout the semester will be beneficial.
+**Course Schedule Overview (Subject to Change):**
+The course progresses through topics such as Boolean Retrieval, TF-IDF, Link Analysis, Evaluation of Search Engines, Learning to Rank, Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization), word2vec, Neural Ranking, Transformers, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 3].
+By keeping these dates and policies in mind, you can effectively manage your workload for CSCE 670.</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For CSCE 670, Section 600, "Information Storage and Retrieval" in Spring 2026, effective time management will be crucial given the various assignments and project work [Source 5].
+Here's a breakdown of key components and their deadlines to help you plan:
+**Course Overview:**
+*   **Course ID:** CSCE 670, Section 600 [Source 5]
+*   **Term:** Spring 2026 [Source 5]
+*   **Meeting Times:** MWF, 1:50 PM - 2:40 PM [Source 5]
+*   **Prerequisites:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5]. This indicates the course expects a foundational understanding of computer science concepts, which you should leverage in your planning.
+**Grading Breakdown:**
+*   **Homework:** 30% (five programming assignments in Python) [Source 2]
+*   **Quizzes:** 20% (four brief in-class quizzes) [Source 2]
+*   **Group Project:** 20% (mini-research project in teams of 3-4) [Source 2]
+*   **Final Exam:** 30% [Source 2]
+**Important Dates &amp; Planning Considerations:**
+| Assignment Type | Item           | Due Date/Time                               | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4524,6 +7225,182 @@
 *   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Each student/team has a limited number of "late days" they may use by request. Work submitted as makeup for an excused absence is exempt from the late work policy [Source 7].</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSCE 632, Section 600 (54784), is titled "Accessible Computing" and is offered in Spring 2026. This graduate-level course explores traditionally disenfranchised user populations due to disability, reviews ethical and legal motivations for accessible technology, and covers universal design principles for developing, evaluating, designing, and implementing equitable and inclusive software and computer-based solutions. It also includes the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+**Prerequisites:**
+*   Graduate classification [Source 5].
+**Grading Components and Weights:**
+The final grade for CSCE 632 is determined by the following components:
+| Component                     | Weight | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>CSCE 632, Section 600 (54784), titled "Accessible Computing," is a 3-credit hour graduate-level course offered in Spring 2026 [Source 5].
+**Course Purpose and Topics:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and covers universal design and its role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will also apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 5].
+**Learning Outcomes:**
+Students will learn to:
+*   Develop accessible technologies, documents, and presentations that comply with established standards and evaluate their effectiveness [Source 7].
+*   Critique technology, identify insufficient accessibility standards, and propose design alternatives [Source 7].
+*   Design, implement, and evaluate solutions for equitable interaction, mediating challenges for specific disabilities, and justify design choices within universal design principles [Source 7].
+**Prerequisites:**
+The prerequisite for CSCE 632 is graduate classification [Source 5].
+**Grading Breakdown for CSCE 632:**
+The final grade is determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 2]
+*   **Group Class Activities**: 10% [Source 2]
+*   **Assignments**: 25% [Source 1]
+*   **Quick Applications**: 20% [Source 1]
+*   **Literature Review**: 10% [Source 1, 4]
+*   **Current Research Presentation**: 5% [Source 4]
+*   **Team Project**: 25% [Source 4]
+**Grading Scale:**
+Grades will be rounded to the nearest whole number and assigned as follows [Source 3]:
+*   **A**: ≥ 90 (excellent)
+*   **B**: &lt; 90 and ≥ 80 (good)
+*   **C**: &lt; 80 and ≥ 70 (satisfactory)
+*   **D**: &lt; 70 and ≥ 60 (passing)
+*   **F**: &lt; 60 (failing)
+**Important Grading Notes:**
+*   **Completion Rate Adjustment**: For Pre-Class Engagement and Group Class Activities, a completion rate is calculated, and 15% (capped at 100%) is added to allow for missed activities without negative impact [Source 1, 2].
+*   **Peer Grading**: Some assignments, the Literature Review, Current Research Presentation, and parts of the Team Project will be peer graded. Your score will be based on peer evaluations and your evaluation of other student assignments. Points can be lost for grading significantly differently than peers or giving all students the same scores [Source 1, 3, 4].
+*   **Team Project Multiplier**: The instructor may establish a multiplier based on team peer evaluations, which can be modified at their discretion, potentially impacting individual scores [Source 3].
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 3, 6].
+*   **Grade Challenges**: Any grading challenges must be made within one week of the grade's publication. The course reserves the right to audit grades, which may result in scores being decreased or increased [Source 2, 7].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Students have a limited number of "late days" they may use by request [Source 6].</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>CSCE 632, Section 600 (54784), titled "Accessible Computing," is a 3-credit hour graduate-level course offered in Spring 2026 at College Station [Source 5].
+**Course Purpose and Topics:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and the role of universal design in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Key topics include the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+**Prerequisites:**
+The prerequisite for CSCE 632 is graduate classification [Source 5].
+**Grading Breakdown:**
+Final grades are determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 2]
+*   **Group Class Activities**: 10% [Source 2, 1]
+*   **Assignments**: 25% (may be individual or group, some peer-graded) [Source 1]
+*   **Quick Applications**: 20% (timed assignments applying class materials) [Source 1]
+*   **Literature Review**: 10% (compiling a review on an accessibility topic with at least 10 peer-reviewed papers) [Source 3, 1]
+*   **Current Research Presentation**: 5% (based on the Literature Review, peer-graded) [Source 3]
+*   **Team Project**: 25% (designing and implementing a technology-based solution for a barrier faced by people with disabilities, parts are peer-graded) [Source 3, 4]
+**Grading Policies:**
+*   **Peer Grading**: Several components, including Assignments, Current Research Presentation, and parts of the Team Project, are peer-graded. Scores are based on peer evaluations and your evaluation of other students' work. You can lose points for grading significantly differently than your peers or giving all students the same scores [Source 1, 3, 4].
+*   **Completion Rate Adjustment**: For Pre-Class Engagement and Group Class Activities, a completion rate is calculated, and 15% is added, capped at 100%. This allows for missing some activities without negative impact [Source 2, 1].
+*   **Team Project Multiplier**: The instructor may establish a multiplier based on team peer evaluations, which can modify individual scores [Source 4].
+*   **Grading Scale**: Grades are rounded to the nearest whole number [Source 4].
+    *   A: ≥ 90
+    *   B: &lt; 90 and ≥ 80
+    *   C: &lt; 80 and ≥ 70
+    *   D: &lt; 70 and ≥ 60
+    *   F: &lt; 60 [Source 4]
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 4, 7].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Students have a limited number of "late days" they can use by request [Source 7].</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>CSCE 632, Section 600 (54784), titled "Accessible Computing," is a 3-credit hour graduate-level course offered in Spring 2026 at College Station [Source 5].
+**Course Purpose and Topics:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and the role of universal design in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Key topics include the application of accessibility standards and the compilation of a literature review on a current topic in accessible computing [Source 5].
+**Prerequisites:**
+The prerequisite for CSCE 632 is graduate classification [Source 5].
+**Grading Breakdown:**
+Final grades are determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 2]
+*   **Group Class Activities**: 10% [Source 2, 1]
+*   **Assignments**: 25% (may be individual or group, some peer-graded) [Source 1]
+*   **Quick Applications**: 20% (timed assignments applying class materials) [Source 1]
+*   **Literature Review**: 10% (compiling a review on an accessibility topic with at least 10 peer-reviewed papers) [Source 3, 1]
+*   **Current Research Presentation**: 5% (based on the Literature Review, peer-graded) [Source 3]
+*   **Team Project**: 25% (designing and implementing a technology-based solution for a barrier faced by people with disabilities, parts are peer-graded) [Source 3, 4]
+**Grading Policies:**
+*   **Peer Grading**: Several components, including Assignments, Current Research Presentation, and parts of the Team Project, are peer-graded. Scores are based on peer evaluations and your evaluation of other students' work. You can lose points for grading significantly differently than your peers or giving all students the same scores [Source 1, 3, 4].
+*   **Completion Rate Adjustment**: For Pre-Class Engagement and Group Class Activities, a completion rate is calculated, and 15% is added, capped at 100%. This allows for missing some activities without negative impact [Source 2, 1].
+*   **Team Project Multiplier**: The instructor may establish a multiplier based on team peer evaluations, which can modify individual scores [Source 4].
+*   **Grading Scale**: Grades are rounded to the nearest whole number [Source 4].
+    *   A: ≥ 90
+    *   B: &lt; 90 and ≥ 80
+    *   C: &lt; 80 and ≥ 70
+    *   D: &lt; 70 and ≥ 60
+    *   F: &lt; 60 [Source 4]
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can also lead to letter grade reductions [Source 4, 7].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Students have a limited number of "late days" they can use by request [Source 7].</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSCE 632, Section 600 (54784), titled "Accessible Computing," is a 3-credit hour graduate-level course offered in Spring 2026 at College Station [Source 6].
+**Course Purpose and Topics:**
+The course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and covers universal design's role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 6].
+**Learning Outcomes:**
+Upon completion, students should be able to:
+*   Develop accessible technologies, documents, and presentations that comply with established standards and evaluate their effectiveness for people with disabilities and other populations [Source 7].
+*   Critique technology, identify instances where accessibility standards may be insufficient, and propose design alternatives that fulfill the underlying goals of accessibility [Source 7].
+*   Design, implement, and evaluate solutions that enable equitable interaction, mediating challenges and barriers for specific disabilities, and justify design choices within the framework of universal design principles [Source 7].
+**Prerequisites:**
+The prerequisite for CSCE 632 is graduate classification [Source 6].
+**Grading Breakdown:**
+Final grades are determined by the following components for CSCE 632:
+| Component                       | Weight (CSCE 632) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>CSCE 632, Section 600 (54784), titled "Accessible Computing," is a 3-credit hour graduate-level course offered in Spring 2026 [Source 7].
+**Course Overview:**
+This course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, focusing on universal design and its role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 7].
+**Learning Outcomes:**
+Students will learn to:
+*   Develop accessible technologies, documents, and presentations that comply with established standards and evaluate their effectiveness for people with disabilities and other populations [Source 6].
+*   Critique technology, identify instances where accessibility standards may be insufficient, and propose design alternatives that fulfill the underlying goals of accessibility [Source 6].
+*   Design, implement, and evaluate solutions that enable equitable interaction, mediating challenges and barriers for specific disabilities, and justify design choices within the framework of universal design principles [Source 6].
+**Prerequisites:**
+The prerequisite for CSCE 632 is graduate classification [Source 7].
+**Grading Breakdown:**
+Final grades are determined by the following components:
+*   **Pre-Class Engagement**: 5% [Source 2]
+*   **Group Class Activities**: 10% [Source 2]
+*   **Assignments**: 25% [Source 1]
+*   **Quick Applications**: 20% [Source 1]
+*   **Literature Review**: 10% [Source 1, 4]
+*   **Current Research Presentation**: 5% [Source 4]
+*   **Team Project**: 25% [Source 4]
+**Grading Scale:**
+Grades will be rounded to the nearest whole number and assigned as follows [Source 3]:
+*   **A**: ≥ 90 (excellent)
+*   **B**: &lt; 90 and ≥ 80 (good)
+*   **C**: &lt; 80 and ≥ 70 (satisfactory)
+*   **D**: &lt; 70 and ≥ 60 (passing)
+*   **F**: &lt; 60 (failing)
+**Important Grading Policies:**
+*   **Peer Grading**: Some assignments, the Current Research Presentation, and parts of the Team Project will be peer-graded. Your score will be based on peer evaluations and your evaluation of other student assignments. You can lose points for grading significantly differently than your peers or giving all students the same scores [Source 1, 3, 4].
+*   **Instructor Modifications**: The instructor may assign a failing grade regardless of a student’s computed final score if warranted. Failing to complete work can lead to letter grade reductions even if a zero would mathematically result in a higher letter grade [Source 3, 5].
+*   **Grade Challenges**: If you wish to challenge any grading, you must do so within one week of when the grade is published. The instructor reserves the right to audit grades, which could result in scores being decreased or increased [Source 6, 2].
+*   **Late Work Policy**: Penalties for unexcused late submissions are 5% per calendar day, unless specified otherwise. Students have a limited number of "late days" they may use by request [Source 5].</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSCE 632, Section 600 (54784), titled "Accessible Computing," is a 3-credit hour graduate-level course offered in Spring 2026 at College Station [Source 6].
+**Course Purpose and Topics:**
+The course explores traditionally disenfranchised user populations due to disability, including discrimination and population characteristics. It reviews ethical and legal motivations for creating accessible technology, and covers universal design's role in the development, evaluation, design, and implementation of equitable and inclusive software and computer-based solutions. Students will apply accessibility standards and compile a literature review on a current topic in accessible computing [Source 6].
+**Learning Outcomes:**
+Upon completion, students should be able to:
+*   Develop accessible technologies, documents, and presentations that comply with established standards and evaluate their effectiveness for people with disabilities and other populations [Source 7].
+*   Critique technology, identify instances where accessibility standards may be insufficient, and propose design alternatives that fulfill the underlying goals of accessibility [Source 7].
+*   Design, implement, and evaluate solutions that enable equitable interaction, mediating challenges and barriers for specific disabilities, and justify design choices within the framework of universal design principles [Source 7].
+**Prerequisites:**
+The prerequisite for CSCE 632 is graduate classification [Source 6].
+**Grading Breakdown:**
+Final grades are determined by the following components for CSCE 632:
+| Component                       | Weight (CSCE 632) | Notes                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4670,6 +7547,178 @@
 *   **C:** 60-70% [Source 1, 2]
 *   **F:** 0-59% [Source 1, 2]
 No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), is a Computational Optimization course offered in Spring 2026 [Source 4].
+The grading breakdown for the course is as follows:
+*   **Homework:** 30% (3 assignments, 10% each) [Source 1, 2]
+*   **Course project:** 35% [Source 1, 2]
+*   **Final exam:** 35% [Source 1, 2]
+The grading scale is:
+*   **A:** 90-100% [Source 1, 2]
+*   **B:** 70-89% [Source 1, 2]
+*   **C:** 60-70% [Source 1, 2]
+*   **F:** 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and projects, but unusual circumstances can be discussed with the instructor in advance [Source 1]. The final exam is comprehensive [Source 2].</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), titled "Computational Optimization," is offered in Spring 2026 [Source 4].
+**Course Purpose and Content:**
+This course focuses on the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems. It covers applications to max flow, matching, and matroids, and explores the geometric interpretation of results in the design and complexity of approximation algorithms [Source 4].
+Key topics include:
+*   Algorithmic background review [Source 1]
+*   Maximum flow and graph matching [Source 1]
+*   Linear programming [Source 1]
+*   NP-completeness theory and approximation algorithms (FPTAS, PTAS, APX) [Source 1]
+*   Inapproximability results and the PCP theorem [Source 1, 3]
+*   Parameterized algorithms [Source 1, 3]
+*   ETH and Computational lower bounds [Source 3]
+*   Exact algorithms for NP-hard problems [Source 3]
+Upon completion, students should be able to master basic theories and techniques in computational optimization, apply them to real-world problems, use appropriate technologies for research, and gain a solid background for advanced research in the area [Source 2, 4].
+**Prerequisites:**
+The prerequisite for CSCE 669 is CSCE 629 [Source 4].
+**Grading Breakdown:**
+Your overall grade in CSCE 669 is determined by the following components:
+*   **Homework:** 30% (3 assignments, each worth 10%) [Source 1, 2]
+*   **Course Project:** 35% [Source 1, 2]
+*   **Final Exam:** 35% [Source 1, 2]
+The grading scale is as follows:
+*   A = 90-100%
+*   B = 70-89%
+*   C = 60-70%
+*   F = 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and the project, unless unusual circumstances are discussed in advance with the instructor [Source 1]. The use of AI is strictly prohibited in this course [Source 3].</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), titled "Computational Optimization," is offered in Spring 2026 [Source 4].
+**Course Purpose and Content:**
+This course focuses on the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems. It covers applications to max flow, matching, and matroids, and explores the geometric interpretation of results in the design and complexity of approximation algorithms [Source 4].
+Key topics include:
+*   Algorithmic background review [Source 1]
+*   Maximum flow and graph matching [Source 1]
+*   Linear programming [Source 1]
+*   NP-completeness theory and approximation algorithms (FPTAS, PTAS, APX) [Source 1]
+*   Inapproximability results and the PCP theorem [Source 1, 3]
+*   Parameterized algorithms [Source 1, 3]
+*   ETH and Computational lower bounds [Source 3]
+*   Exact algorithms for NP-hard problems [Source 3]
+Upon completion, students should be able to master basic theories and techniques in computational optimization, apply them to real-world problems, use appropriate technologies for research, and gain a solid background for advanced research in the area [Source 2, 4].
+**Prerequisites:**
+The prerequisite for CSCE 669 is CSCE 629 [Source 4].
+**Grading Breakdown:**
+Your overall grade in CSCE 669 is determined by the following components:
+*   **Homework:** 30% (3 assignments, each worth 10%) [Source 1, 2]
+*   **Course Project:** 35% [Source 1, 2]
+*   **Final Exam:** 35% [Source 1, 2]
+The grading scale is as follows:
+*   A = 90-100%
+*   B = 70-89%
+*   C = 60-70%
+*   F = 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and the project, unless unusual circumstances are discussed in advance with the instructor [Source 1]. The use of AI is strictly prohibited in this course [Source 3].</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), titled "Computational Optimization," is offered in Spring 2026 [Source 4].
+**Course Purpose and Content:**
+This course focuses on the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems. It covers applications to max flow, matching, and matroids, and explores the geometric interpretation of results in the design and complexity of approximation algorithms [Source 4].
+Key topics include:
+*   Algorithmic background review [Source 1]
+*   Maximum flow and graph matching [Source 1]
+*   Linear programming [Source 1]
+*   NP-completeness theory and approximation algorithms (FPTAS, PTAS, APX) [Source 1]
+*   Inapproximability results and the PCP theorem [Source 1, 3]
+*   Parameterized algorithms [Source 1, 3]
+*   ETH and Computational lower bounds [Source 3]
+*   Exact algorithms for NP-hard problems [Source 3]
+Upon completion, students should be able to master basic theories and techniques in computational optimization, apply them to real-world problems, use appropriate technologies for research, and gain a solid background for advanced research in the area [Source 2, 4].
+**Prerequisites:**
+The prerequisite for CSCE 669 is CSCE 629 [Source 4].
+**Grading Breakdown:**
+Your overall grade in CSCE 669 is determined by the following components:
+*   **Homework:** 30% (3 assignments, each worth 10%) [Source 1, 2]
+*   **Course Project:** 35% [Source 1, 2]
+*   **Final Exam:** 35% [Source 1, 2]
+The grading scale is as follows:
+*   A = 90-100%
+*   B = 70-89%
+*   C = 60-70%
+*   F = 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and the project, unless unusual circumstances are discussed in advance with the instructor [Source 1]. The use of AI is strictly prohibited in this course [Source 3].</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438), titled "Computational Optimization," is offered in Spring 2026 [Source 4].
+**Course Purpose and Content:**
+This course focuses on the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems. It covers applications to max flow, matching, and matroids, and explores the geometric interpretation of results in the design and complexity of approximation algorithms [Source 4].
+Key topics include:
+*   Algorithmic background review [Source 1]
+*   Maximum flow and graph matching [Source 1]
+*   Linear programming [Source 1]
+*   NP-completeness theory and approximation algorithms (FPTAS, PTAS, APX) [Source 1]
+*   Inapproximability results and the PCP theorem [Source 1, 3]
+*   Parameterized algorithms [Source 1, 3]
+*   ETH and Computational lower bounds [Source 3]
+*   Exact algorithms for NP-hard problems [Source 3]
+Upon completion, students should be able to master basic theories and techniques in computational optimization, apply them to real-world problems, use appropriate technologies for research, and gain a solid background for advanced research in the area [Source 2, 4].
+**Prerequisites:**
+The prerequisite for CSCE 669 is CSCE 629 [Source 4].
+**Grading Breakdown:**
+Your overall grade in CSCE 669 is determined by the following components:
+*   **Homework:** 30% (3 assignments, each worth 10%) [Source 1, 2]
+*   **Course Project:** 35% [Source 1, 2]
+*   **Final Exam:** 35% [Source 1, 2]
+The grading scale is as follows:
+*   A = 90-100%
+*   B = 70-89%
+*   C = 60-70%
+*   F = 0-59% [Source 1, 2]
+No late submissions will be accepted for assignments and the project, unless unusual circumstances are discussed in advance with the instructor [Source 1]. The use of AI is strictly prohibited in this course [Source 3].</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>CSCE 669, Section 600 (58438) - Computational Optimization, is offered in Spring 2026 [Source 4].
+This course aims to help students:
+*   Master basic theories and techniques in current research in computational optimization.
+*   Apply these theories and techniques to solve real-world problems.
+*   Use appropriate technologies for communication, collaboration, and research in the field.
+*   Gain a solid background for advanced research in computational optimization and related areas [Source 1, 4].
+Key topics covered include the combinatorial theory of polytopes, applications to max flow, matching, and matroids, geometric interpretation of results, and the role of polyhedral combinatorics in the design and complexity of approximation algorithms [Source 4]. The course schedule details topics such as algorithmic background review, maximum flow and graph matching, linear programming, NP-completeness theory, various approximation algorithms (FPTAS, PTAS, APX), inapproximability results, parameterized algorithms, and exact algorithms for NP-hard problems [Source 2, 3].
+The prerequisite for this course is CSCE 629 [Source 4].
+Your overall grade in CSCE 669 is determined by the following components:
+*   **Homework:** There are 3 homework assignments, each contributing 10% to the final grade, for a total of 30% [Source 1, 2].
+*   **Course Project:** The course research project accounts for 35% of the final grade [Source 1, 2].
+*   **Final Exam:** The comprehensive final exam contributes 35% to the final grade [Source 1, 2].
+The grading scale is as follows:
+*   A = 90-100%
+*   B = 70-89%
+*   C = 60-70%
+*   F = 0-59% [Source 1, 2]
+All assignments and the project are due on their designated dates at the beginning of class, and no late submissions will be accepted unless unusual circumstances are discussed in advance with the instructor [Source 2]. The use of AI is strictly prohibited in this course [Source 3].</t>
         </is>
       </c>
     </row>
@@ -4836,6 +7885,161 @@
 The instructor for this course is Yu Zhang [Source 1].</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, "Information Storage and Retrieval," is offered in Spring 2026 [Source 1].
+**Course Purpose and Topics:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+Key topics and algorithms covered include:
+*   **Web Search**: Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems**: Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics**: Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models**: Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, and for ranking/recommendation) [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have instructor approval, and be of graduate classification [Source 1, 3].
+**Grading (Late Work Policy):**
+For homework assignments, students are allotted five late days in total. A late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 2].
+The instructor for this course is Yu Zhang [Source 1].</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600, "Information Storage and Retrieval" (Spring 2026), here's what you should know:
+**Course Purpose:**
+This course covers the representation, storage, and access to very large multimedia document collections. It focuses on the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems [Source 1].
+**Key Topics, Data Structures, and Algorithms:**
+The course will cover:
+*   **Fundamental data structures and algorithms** of information storage and retrieval systems [Source 1].
+*   **Algorithms for indexing, compressing, and querying** very large collections [Source 1].
+*   **Specific topics** include:
+    *   Boolean Retrieval [Source 3]
+    *   TF-IDF; Vector Space Model; BM25 [Source 3]
+    *   Link Analysis [Source 3]
+    *   Evaluation of Search Engines [Source 3]
+    *   Learning to Rank [Source 3]
+    *   Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, Neural Collaborative Filtering, Sequential Recommendation) [Source 3]
+    *   word2vec; Neural Ranking [Source 3]
+    *   Transformer; BERT-Based Ranking [Source 3]
+    *   Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 3]
+**Prerequisites:**
+CSCE 310 or CSCE 603, or approval of the instructor; graduate classification is also required [Source 1, Source 2].
+**Grading (Late Work Policy):**
+Students receive five late days total for homework assignments. Each late day is an indivisible 24-hour unit. Once these five late days are used, any subsequent late assignment will receive a grade of 0 [Source 3, Source 4]. Homeworks are individual assignments, but discussion about approaches is encouraged, provided all help is acknowledged [Source 4].</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600 (46627), titled "Information Storage and Retrieval," is offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Overview:**
+This course focuses on the representation, storage, and access of very large multimedia document collections. It covers the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems [Source 1].
+**Key Topics and Academic Content:**
+The course delves into algorithms for indexing, compressing, and querying large collections [Source 1]. Upon completion, learners will be able to define and explain key concepts and models relevant to:
+*   **Web Search:** Including text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems:** Including collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+Specific topics covered in the course schedule include:
+*   Boolean Retrieval, TF-IDF, Vector Space Model, BM25 [Source 2]
+*   Link Analysis, Evaluation of Search Engines, Learning to Rank [Source 2]
+*   Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, Neural Collaborative Filtering, Sequential Recommendation) [Source 2]
+*   Neural Models: word2vec, Neural Ranking, Transformer, BERT-Based Ranking [Source 2]
+*   Large Language Models: Basics, integration with Search Engines, and application for Ranking and Recommendation [Source 2]
+**Prerequisites:**
+Students must have CSCE 310 or CSCE 603, or approval of the instructor, and graduate classification [Source 1, 3].
+The provided context does not include detailed information on grading policies or components beyond the listing of homeworks and quizzes [Source 2].</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600 (46627), titled "Information Storage and Retrieval," is offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Overview:**
+This course focuses on the representation, storage, and access of very large multimedia document collections. It covers the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems [Source 1].
+**Key Topics and Academic Content:**
+The course delves into algorithms for indexing, compressing, and querying large collections [Source 1]. Upon completion, learners will be able to define and explain key concepts and models relevant to:
+*   **Web Search:** Including text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems:** Including collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+Specific topics covered in the course schedule include:
+*   Boolean Retrieval, TF-IDF, Vector Space Model, BM25 [Source 2]
+*   Link Analysis, Evaluation of Search Engines, Learning to Rank [Source 2]
+*   Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, Neural Collaborative Filtering, Sequential Recommendation) [Source 2]
+*   Neural Models: word2vec, Neural Ranking, Transformer, BERT-Based Ranking [Source 2]
+*   Large Language Models: Basics, integration with Search Engines, and application for Ranking and Recommendation [Source 2]
+**Prerequisites:**
+Students must have CSCE 310 or CSCE 603, or approval of the instructor, and graduate classification [Source 1, 3].
+The provided context does not include detailed information on grading policies or components beyond the listing of homeworks and quizzes [Source 2].</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, titled "Information Storage and Retrieval," focuses on the representation, storage, and access of very large multimedia document collections [Source 1].
+**Course Purpose and Content:**
+The course covers fundamental data structures and algorithms used in information storage and retrieval systems, including techniques for designing and evaluating complete retrieval systems, indexing, compressing, and querying large collections [Source 1].
+**Key Topics and Algorithms:**
+Upon completion, learners will be able to define and explain key concepts and models relevant to:
+*   **Web Search:** Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 2].
+*   **Recommender Systems:** Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 2].
+*   **Recent Research:** Adversarial information retrieval and neural models of retrieval and recommendation [Source 2].
+Specific algorithms and models covered in the course schedule include:
+*   Boolean Retrieval, TF-IDF, Vector Space Model, BM25 [Source 3]
+*   Link Analysis, Learning to Rank [Source 3]
+*   Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking) [Source 3]
+*   word2vec, Neural Ranking, Transformer, BERT-Based Ranking [Source 3]
+*   Neural Collaborative Filtering, Sequential Recommendation [Source 3]
+*   Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 3]
+**Prerequisites:**
+Students must have CSCE 310 or CSCE 603, or approval of the instructor, and graduate classification [Source 1, Source 2].
+**Grading Policy:**
+The final grade is determined by:
+*   Homework: 30% (five programming assignments) [Source 5]
+*   Quizzes: 20% (four in-class quizzes) [Source 5]
+*   Final: 30% (comprehensive final exam) [Source 5]
+*   Group Project: 20% (mini-research project in teams of 3 or 4) [Source 5]</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600, titled "Information Storage and Retrieval," is a 3-credit hour graduate-level course offered in Spring 2026 by instructor Yu Zhang [Source 1].
+**Course Purpose and Content:**
+The course focuses on the representation, storage, and access of very large multimedia document collections. It covers the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems [Source 1].
+Key topics and algorithms covered include:
+*   **Retrieval Models:** Boolean Retrieval, TF-IDF, Vector Space Model, BM25 [Source 3].
+*   **Web Search:** Text indexing, Web crawling, Link Analysis (e.g., PageRank), Learning to Rank, Evaluation of Search Engines [Source 2, Source 3].
+*   **Recommender Systems:** Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, Neural Collaborative Filtering, Sequential Recommendation [Source 2, Source 3].
+*   **Advanced Topics:** word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Large Language Models (basics, with search engines, for ranking and recommendation) [Source 3].
+*   **Core Algorithms:** Algorithms for indexing, compressing, and querying very large collections [Source 1].
+**Learning Outcomes:**
+Upon completion, students will be able to define and explain key concepts and models relevant to web search and recommender systems, design, implement, and evaluate core algorithms for these systems, and apply recent research results in these fields [Source 2].
+**Prerequisites:**
+Students must have CSCE 310 or CSCE 603, or obtain approval from the instructor, and have graduate classification [Source 1, Source 2].
+**Grading Policy:**
+The final grade is determined by:
+*   Homework: 30% (five programming assignments) [Source 5]
+*   Quizzes: 20% (four in-class quizzes) [Source 5]
+*   Final Exam: 30% [Source 5]
+*   Group Project: 20% (mini-research project) [Source 5]
+The grading scale is A: &gt;=90%, B: &gt;=80%, C: &gt;=70%, D: &gt;=60%, F: &lt;60% [Source 5].</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>CSCE 670, Section 600 (46627), titled "Information Storage and Retrieval," is offered in Spring 2026 at College Station [Source 1].
+**Course Purpose and Content:**
+This course focuses on the representation, storage, and access of very large multimedia document collections. It covers the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. This includes algorithms for indexing, compressing, and querying large collections [Source 1].
+**Key Topics and Algorithms Covered:**
+Upon completion, learners will be able to define and explain key concepts and models relevant to web search and recommender systems. Specific topics and algorithms include:
+*   **Web Search:** Text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank [Source 3].
+*   **Recommender Systems:** Collaborative filtering, matrix factorization, recommender system evaluation, and implicit recommendation [Source 3].
+*   **Advanced Topics:** Adversarial information retrieval, neural models of retrieval and recommendation [Source 3].
+*   **Specific Algorithms/Models from Schedule:** Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Content-Based Recommender Systems, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models for search, ranking, and recommendation [Source 2].
+**Prerequisites:**
+Students must have completed CSCE 310 or CSCE 603, or have approval from the instructor, and must have graduate classification [Source 1, 3].
+**Grading Policy:**
+The final grade is determined by the following components:
+*   Homework: 30% (five programming assignments in Python) [Source 5]
+*   Quizzes: 20% (four in-class quizzes) [Source 5]
+*   Final Exam: 30% (comprehensive final exam) [Source 5]
+*   Group Project: 20% (mini-research project in teams of 3 or 4) [Source 5]
+The grading scale is A: &gt;=90%, B: &gt;=80% and &lt; 90%, C: &gt;=70% and &lt; 80%, D: &gt;=60% and &lt; 70%, F: &lt; 60% [Source 5].</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4953,6 +8157,91 @@
     *   While broader in scope, CSCE 713 includes significant "Network Security" topics, such as Man-In-The-Middle (MITM) Attacks, ARP Spoofing, Port Scanning, and Honeypots [Source 9]. This course would allow you to "perform penetration testing on previously unknown software" and "analyze existing source code for functional correctness" [Source 11], which could be a valuable specialization after understanding network fundamentals in CSCE 612.
 **Note on CSCE 611:** CSCE 611 (Operating Systems) is listed with CSCE 313 as a prerequisite, similar to CSCE 612 [Source 8, 2]. The content of CSCE 611, which covers operating system components, virtualization, and distributed systems [Source 8], is foundational and often taken *before* or *concurrently* with advanced networking courses like CSCE 612, rather than after. CSCE 612 itself mentions utilizing "operating-system sockets APIs" and building "multi-threaded decentralized frameworks" [Source 2], indicating that OS knowledge is beneficial prior to or during the course.
 I don't have enough data to provide a comprehensive list of all possible follow-up courses based on the available syllabi, but CSCE 665 and CSCE 713 are strong candidates for academic progression after CSCE 612.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>When considering what to take after CSCE 612, a common academic progression principle is to build upon foundational knowledge by exploring more specialized or advanced topics within the same domain. CSCE 612, "Applied Networks and Distributed Processing," provides fundamentals in network design, protocol analysis, and network engineering [Source 1].
+Based on the available course descriptions, **CSCE 665: Advanced Networking and Security** appears to be a logical next step if you wish to delve deeper into networking with a focus on security. This course specifically covers "Security aspects of various network protocols" and introduces "modern topics in computer and network security" [Source 6]. Its topics include basic network and system security, security in software-defined environments, mobile and IoT security, Web and Web3 security, and AI/LLM security [Source 7]. This directly extends the networking foundation established in CSCE 612 by adding a critical security dimension.
+While CSCE 713: Advanced Topics in Security also focuses on security, its learning outcomes lean more towards general security principles, secure software development, penetration testing, and analyzing software defects [Source 9]. This suggests a broader security focus rather than a direct continuation of advanced networking protocols as explicitly as CSCE 665.
+Therefore, to continue your academic progression in networking with an added specialization, CSCE 665 is a strong candidate.
+**Course Comparison for Post-CSCE 612 Progression:**
+| Course | Focus | Connection to CSCE 612 |
+| :------------------- | :----------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>CSCE 612, "Applied Networks and Distributed Processing," focuses on the fundamentals of network design, protocol analysis, and network engineering, including programming and pragmatic views of engineering issues. It covers applying layered architecture principles to real networks, with lab exercises on protocol understanding and programming [Source 1]. A key learning outcome is the ability to analyze network performance and security, develop protocols, and build multi-threaded decentralized frameworks [Source 2].
+Based on this foundation, courses that delve deeper into networking, network security, or the underlying systems that support distributed processing would be logical next steps:
+*   **CSCE 665: Advanced Networking and Security**
+    *   **Relevance:** This course directly builds on networking fundamentals by exploring "security aspects of various network protocols" and "modern topics in computer and network security" [Source 6]. It covers areas like basic network &amp; system security, security in software-defined environments, mobile &amp; IoT security, and Web/Web3 security [Source 7]. This aligns well with CSCE 612's learning outcome of analyzing network security [Source 2].
+    *   **Prerequisites:** Graduate classification and approval of instructor [Source 6, 7].
+*   **CSCE 713: Advanced Topics in Security**
+    *   **Relevance:** While broader in security, this course includes significant network security components, such as Man-In-The-Middle (MITM) attacks, port scanning, and honeypots [Source 9]. It also covers web security, application security, and malware, which are often network-related. This course would deepen the security analysis skills gained in CSCE 612 [Source 9, 10].
+    *   **Prerequisites:** Not explicitly stated in the provided context, but it is a graduate-level course.
+*   **CSCE 611: Advanced Operating Systems**
+    *   **Relevance:** This course provides an overview of operating system architecture and components, including memory management, persistent storage, threading, scheduling, and resource management. It also covers virtualization and what is required to build a distributed system [Source 11]. While not directly a networking course, understanding advanced operating systems is crucial for building robust distributed processing systems, a component of CSCE 612 [Source 1, 11].
+    *   **Prerequisites:** CSCE 313; graduate classification [Source 11].
+For academic planning, if your interest lies in specializing in network security, CSCE 665 and CSCE 713 would be highly relevant. If you are more interested in the foundational systems that enable distributed computing, CSCE 611 would be a valuable choice.
+I don't have enough data to provide a comprehensive list of all possible "next steps" or official course pathways based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational knowledge by taking more specialized or advanced courses in related fields. Given that CSCE 612 focuses on "Applied Networks and Distributed Processing," including network design, protocol analysis, and the analysis of network performance and security [Source 1, 2], a logical next step would be courses that delve deeper into advanced networking concepts or the security aspects of networks.
+Based on the provided context, here are courses that could be considered after CSCE 612:
+*   **CSCE 665: Advanced Networking and Security**
+    *   This course directly builds on networking concepts by focusing on "Security aspects of various network protocols" and "modern topics in computer and network security" [Source 6]. It covers topics such as basic network &amp; system security, security in a software-defined world, mobile &amp; IoT security, Web and Web3 security, and AI/LLM security [Source 7]. This aligns well with CSCE 612's learning outcome of analyzing network security [Source 2].
+    *   **Prerequisites:** Graduate classification and approval of instructor [Source 6, 7].
+*   **CSCE 713: Advanced Topics in Security**
+    *   While broader in scope, this course includes "Network Security" as a topic [Source 8] and aims for learners to "identify specific principles that have been violated in common security failures" and "perform penetration testing on previously unknown software" [Source 10]. Given CSCE 612's mention of analyzing network security [Source 2], CSCE 713 could be a suitable follow-up for students interested in a deeper dive into security, including network security.
+    *   **Prerequisites:** Graduate classification and approval of instructor (implied by the course level and typical graduate course structure, though not explicitly stated in the provided snippets for CSCE 713, it is for CSCE 665 which is also a graduate course).
+These courses would allow you to expand on the networking and security foundations established in CSCE 612, providing a more in-depth understanding of advanced network protocols and security mechanisms. For planning, ensure you meet the prerequisites for any chosen course, such as graduate classification and instructor approval [Source 6, 7].</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>When considering what to take after a course, a helpful principle is to look for courses that either build upon the foundational knowledge acquired or delve deeper into specialized topics introduced. This allows for academic progression and specialization within a field.
+Based on the provided context, CSCE 612 focuses on "Applied Networks and Distributed Processing," covering fundamentals like network design, protocol analysis, and the security of networks [Source 1, 2]. While the context does not explicitly list recommended follow-up courses for CSCE 612, CSCE 665: Advanced Networking and Security appears to be a thematically related course that could serve as a logical next step.
+CSCE 665 delves into "Security aspects of various network protocols" and aims for students to "Analyze the complex trade-offs and architectural tensions inherent in securing modern distributed systems and networks" and "Synthesize fundamental security principles and mechanisms" [Source 6, 7]. This course directly expands on the "security of networks" aspect mentioned in CSCE 612's learning outcomes [Source 2].
+Therefore, if you are interested in specializing further in network security, CSCE 665 could be a suitable progression after CSCE 612.
+I don't have enough data to definitively state a required or officially recommended sequence of courses based on the available syllabi, as no explicit "next course" information is provided for CSCE 612.</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>To plan your academic progression, it's helpful to identify courses that build upon the foundational knowledge and skills acquired in a previous course. CSCE 612, "Applied Networks and Distributed Processing," focuses on network design, protocol analysis, network architecture, and principles of network engineering, including the analysis of network performance and security [Source 1, 2].
+Based on the course descriptions provided, the following courses could be logical next steps or complementary studies after completing CSCE 612:
+*   **CSCE 665: Advanced Networking and Security**
+    This course directly builds on networking concepts by focusing on "Security aspects of various network protocols" and providing a "thorough grounding in computer and network security" [Source 6]. Its topics include "Basic network &amp; system security," which aligns well with CSCE 612's objective to "analyze performance and security of networks" [Source 2, 7].
+*   **CSCE 713: Introduction to Security**
+    While a broader security course, CSCE 713 includes "Network Security" as a specific topic [Source 9]. This would allow you to delve deeper into the security aspects of networks, which is an area introduced in CSCE 612 [Source 2].
+I cannot find information in the provided context that explicitly states required or recommended follow-up courses for CSCE 612. However, based on the content, CSCE 665 and CSCE 713 appear to be relevant options for further study in networking and security.</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational knowledge gained in earlier courses. To determine what you should take after CSCE 612, we can look for courses that expand on its core topics.
+CSCE 612, "Applied Networks and Distributed Processing," focuses on fundamentals of network design, protocol analysis, and network architecture, with an emphasis on applying layered architecture principles to real networks. Its learning outcomes include analyzing the performance and security of networks, and developing protocols [Source 1, 2].
+Based on this, **CSCE 665: Advanced Networking and Security** appears to be a suitable follow-up course. CSCE 665 specifically addresses "Security aspects of various network protocols" and involves "investigation and tool development using 'live' machines and networks" [Source 6]. This directly builds upon CSCE 612's coverage of network fundamentals and its learning outcome related to analyzing network security [Source 2, 6].
+CSCE 665 covers topics such as:
+*   Basic network &amp; system security (e.g., malware, intrusion detection) [Source 7]
+*   Security in a software-defined world (e.g., SDN/NFV, Cloud) [Source 7]
+*   Mobile &amp; IoT security [Source 7]
+*   Web and Web3 security [Source 7]
+*   AI/LLM security [Source 7]
+The prerequisites for CSCE 665 are graduate classification and approval of the instructor [Source 6, 7]. This course would allow you to deepen your understanding of network security, applying the foundational networking knowledge gained in CSCE 612 to advanced security challenges.</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>After completing CSCE 612 (Applied Networks and Distributed Processing), which covers network design, protocol analysis, and computer communications, including programming with operating-system sockets APIs and multi-threaded decentralized frameworks [Source 1, 2], you might consider the following courses to further your knowledge in related advanced areas:
+*   **CSCE 665: Advanced Networking and Security**
+    *   This course directly builds upon networking fundamentals by focusing on the "security aspects of various network protocols" [Source 6]. It involves investigating and developing tools using live machines and networks, covering topics such as basic network &amp; system security, security in a software-defined world, mobile &amp; IoT security, and Web/Web3 security [Source 6, 7]. This course is a natural progression for students looking to apply their networking knowledge to security challenges.
+*   **CSCE 713: Advanced Topics in Security**
+    *   This course delves into various security topics, including "Network Security," "Web Security," "Mobile Apps Security," and "Application Security" [Source 8]. While broader in scope than CSCE 665, the significant focus on network security and related application security makes it a strong follow-up for students interested in the security implications and vulnerabilities within networked and distributed systems.
+These courses allow you to deepen your understanding of network systems by moving from fundamental design and analysis (covered in CSCE 612) to advanced security considerations and practical applications in securing networks and distributed systems.</t>
         </is>
       </c>
     </row>
@@ -5107,6 +8396,135 @@
 Taking CSCE 638 would deepen your understanding of the linguistic and semantic aspects crucial for advanced search and recommendation, especially with the increasing role of Large Language Models. CSCE 676 would provide a broader methodological foundation in handling and analyzing large datasets, which is vital for the scalability and effectiveness of these systems. These courses collectively offer a comprehensive skill set, moving from the core retrieval mechanisms (CSCE 670) to the underlying data processing (CSCE 676) and linguistic understanding (CSCE 638) necessary for cutting-edge web search and recommender systems.</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>For academic progression, students often benefit from courses that either provide foundational knowledge for specialized topics or delve deeper into related advanced areas. CSCE 670, "Information Storage and Retrieval," focuses on specialized applications like web search and recommender systems [Source 1, 2]. To complement this, courses that provide a broader understanding of data analysis, machine learning, or the underlying optimization techniques would be beneficial.
+Based on the provided context, the following courses would go well with CSCE 670 for someone interested in web search or recommender systems:
+1.  **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** CSCE 676 provides a broad overview of data mining, including concepts from machine learning and statistics, with applications to scientific and online data [Source 7]. Many techniques used in recommender systems and large-scale web search (e.g., pattern mining, clustering, text mining, graph mining, large-scale ML) are covered in CSCE 676 [Source 6, 9]. Notably, "Mining of Massive Data Sets" is a required textbook for CSCE 676 and an optional resource for CSCE 670, indicating a strong thematic overlap [Source 2, 4, 9].
+    *   **Planning Dimension:** This course would provide a broader toolkit of data analysis techniques that can be applied to the specific problems of information retrieval and recommendation.
+2.  **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 covers advanced topics like "Learning to Rank," "Neural Ranking," "BERT-Based Ranking," "Neural Collaborative Filtering," and "Large Language Models for Ranking and Recommendation" [Source 3]. These topics are heavily reliant on machine learning principles. CSCE 633 surveys fundamental machine learning techniques, which would provide a strong theoretical and practical foundation for understanding the ML-driven aspects of CSCE 670 [Source 8].
+    *   **Planning Dimension:** This course would build foundational knowledge in machine learning, which is increasingly critical for understanding and developing modern web search and recommender systems. CSCE 633 is also a prerequisite for CSCE 726 [Source 11].
+3.  **CSCE 726: Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** This course focuses on "classic deterministic optimization and modern large-scale stochastic optimization algorithms for solving ML/AI problems" [Source 10]. Given CSCE 670's coverage of neural and BERT-based ranking, and large language models [Source 3], a deeper understanding of the optimization algorithms that power these advanced machine learning models would be highly valuable.
+    *   **Planning Dimension:** This course is more advanced, requiring CSCE 633 (or CSCE 636) as a prerequisite [Source 11]. It would allow a student to delve into the mathematical and algorithmic underpinnings of the sophisticated ML techniques applied in web search and recommender systems.
+These courses offer either foundational knowledge (CSCE 633) or complementary advanced techniques (CSCE 676, CSCE 726) that would enhance a student's understanding and skill set in the areas of web search and recommender systems beyond what is covered in CSCE 670.</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>To enhance your understanding and application of concepts in web search and recommender systems, complementary courses often provide foundational knowledge or specialized techniques that build upon or integrate with the topics covered in CSCE 670.
+Based on the provided syllabi, here are courses that would go well with CSCE 670, especially for someone interested in web search or recommender systems:
+*   **CSCE 676: Data Mining and Analysis** [Source 11]
+    *   **Why it fits:** This course offers a broad overview of data mining, integrating concepts from machine learning and statistics, including exploratory data analysis, pattern mining, clustering, and classification [Source 11]. CSCE 670 covers topics like "Learning to Rank" and "Recommender Systems" [Source 3], which heavily rely on data mining and machine learning principles. Both courses also list "Mining of Massive Datasets" as a resource, with CSCE 676 requiring it and CSCE 670 listing it as optional [Source 4, 7]. This indicates a strong thematic overlap in handling and extracting insights from large datasets.
+    *   **Academic Progression:** This course would provide a broader context and deeper dive into the data-driven techniques that underpin modern search and recommendation systems.
+*   **CSCE 633: Machine Learning** [Source 10]
+    *   **Why it fits:** Machine learning is the study of self-modifying computer systems that acquire knowledge and improve performance [Source 10]. CSCE 670 explicitly covers "Learning to Rank," "Neural Ranking," and "neural models of retrieval and recommendation" [Source 2, 3]. A strong foundation in machine learning is crucial for understanding and developing these advanced techniques.
+    *   **Academic Progression:** This course would serve as a foundational course, providing the core machine learning algorithms and theories necessary to fully grasp and innovate within the web search and recommender systems domain.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques** [Source 9]
+    *   **Why it fits:** This course focuses on NLP fundamentals, including language models, syntactic processing, and semantic understanding, with applications like information extraction and text summarization [Source 9]. CSCE 670 delves into "word2vec," "Transformer," "BERT-Based Ranking," and "Large Language Models Basics," as well as their application in search engines and for ranking/recommendation [Source 3]. Understanding NLP is essential for processing and interpreting the textual content that forms the basis of most web search and many recommender systems.
+    *   **Academic Progression:** This course would provide specialized knowledge in text processing, directly supporting the understanding and implementation of advanced retrieval and recommendation models that rely on natural language.
+These courses offer either foundational knowledge (Machine Learning) or specialized, complementary skills (Data Mining, Natural Language Processing) that are highly relevant to the advanced topics covered in CSCE 670, particularly for students interested in the practical and research aspects of web search and recommender systems.</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>For students interested in web search or recommender systems, selecting complementary courses can significantly deepen your understanding and practical skills. The principle here is to identify courses that provide foundational knowledge, advanced techniques, or related application areas that build upon the core concepts of CSCE 670.
+CSCE 670, "Information Storage and Retrieval," covers key concepts in web search (text indexing, retrieval models, evaluation, Web crawling, PageRank, learning to rank) and recommender systems (collaborative filtering, matrix factorization, evaluation) [Source 2]. It also delves into modern topics like neural ranking, large language models for search and recommendation, and BERT-based ranking [Source 3].
+Based on this, the following courses would go well with CSCE 670:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it complements CSCE 670:** CSCE 638 focuses on NLP fundamentals, including language models, syntactic processing, and semantic understanding, with applications like information extraction and text summarization [Source 6]. This directly supports advanced topics in CSCE 670 such as "word2vec," "Transformer; BERT-Based Ranking," and "Large Language Models" for search and recommendation, which rely heavily on NLP techniques [Source 3]. Understanding NLP is crucial for processing and interpreting textual data in both web search and content-based recommender systems.
+    *   **Academic Progression:** This course provides foundational knowledge in a critical area that underpins many modern search and recommendation algorithms.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** CSCE 676 provides a broad overview of data mining, including exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data [Source 8]. These techniques are highly relevant for analyzing user behavior, identifying patterns in large datasets for recommender systems, and optimizing search results.
+    *   **Academic Progression:** This course offers a broader set of analytical tools that can be applied to the large datasets encountered in information retrieval and recommendation.
+*   **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 633 surveys various machine learning techniques, including induction from examples, clustering, and genetic algorithms [Source 9]. Since CSCE 670 explicitly covers "Learning to Rank" and various neural models for ranking and recommendation [Source 3], a strong foundation in machine learning is essential for understanding and developing these advanced systems.
+    *   **Academic Progression:** This is a foundational course that provides the theoretical and practical basis for many of the advanced algorithms used in modern web search and recommender systems.
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** This course focuses on classical and large-scale stochastic optimization algorithms for solving ML/AI problems [Source 11]. Given that CSCE 670 mentions "Neural Ranking," "Neural Collaborative Filtering," and "BERT-Based Ranking" [Source 3], understanding the optimization techniques used to train these complex models is highly beneficial. The course also emphasizes proficiency in Python and PyTorch for deep learning [Source 7].
+    *   **Academic Progression:** This course offers a more advanced, specialized skill set for those looking to deeply understand and improve the performance of machine learning models used in search and recommendation.
+*   **CSCE 681: Seminar**
+    *   **Why it complements CSCE 670:** While not a technical course, CSCE 681 involves reports and discussions of current research and published technical articles [Source 10]. This can expose students to the latest advancements and cutting-edge research in web search, information retrieval, and recommender systems, complementing the foundational and applied knowledge gained in CSCE 670.
+    *   **Academic Progression:** This course helps students stay current with research trends and develop critical analysis skills for academic literature in the field.</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>To identify courses that complement CSCE 670, especially for interests in web search or recommender systems, we look for courses with overlapping topics, shared prerequisites, or recommended backgrounds that align with the content of CSCE 670. This approach helps students build a cohesive academic progression in related fields.
+Based on the provided context, here are courses that would go well with CSCE 670:
+*   **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 covers "Learning to Rank" and "Neural Ranking," as well as "Neural Collaborative Filtering" [Source 3]. Machine Learning (CSCE 633) provides the fundamental techniques and methods of machine learning, including data processing, model selection, and various advanced algorithms [Source 11]. This foundational knowledge would be highly beneficial for understanding and implementing the machine learning aspects of web search and recommender systems. CSCE 633 also covers supervised and unsupervised learning paradigms [Source 11], which are relevant to many retrieval and recommendation tasks.
+    *   **Academic Progression:** Taking CSCE 633 would provide a strong theoretical and practical foundation in machine learning, which is increasingly integral to advanced web search and recommender systems. This would allow a student to delve deeper into the algorithms and models mentioned in CSCE 670.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it complements CSCE 670:** CSCE 670 deals with "Information Storage and Retrieval" of "very large multimedia document collections" and covers topics like "Boolean Retrieval," "TF-IDF," "word2vec," "Transformer," "BERT-Based Ranking," and "Large Language Models" [Source 1, 3]. Natural Language Processing (CSCE 638) focuses on NLP fundamentals, including language models, automatic syntactic processing, and semantic understanding, and introduces major NLP applications like information extraction and text summarization [Source 8]. Understanding NLP is crucial for processing and understanding textual content in web search and for many modern recommender systems.
+    *   **Academic Progression:** CSCE 638 would provide the necessary background in how text is processed and understood, which is directly applicable to improving the relevance and effectiveness of search engines and content-based recommender systems discussed in CSCE 670.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** CSCE 670 involves techniques to "design and evaluate complete retrieval systems" and covers "fundamental data structures and algorithms of information storage and retrieval systems" [Source 1]. Data Mining and Analysis (CSCE 676) offers a broad overview of data mining, integrating concepts from machine learning and statistics, including exploratory data analysis, pattern mining, clustering, and classification [Source 9]. These data analysis and mining techniques are essential for understanding user behavior, extracting patterns from large datasets, and evaluating the performance of both search and recommender systems.
+    *   **Academic Progression:** CSCE 676 would equip students with skills to analyze the vast amounts of data generated by user interactions with search engines and recommender systems, providing a data-driven perspective that enhances the algorithmic knowledge gained from CSCE 670.
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 mentions "Learning to Rank" and various neural models [Source 3]. CSCE 726 focuses on deterministic and large-scale stochastic optimization algorithms for solving Machine Learning/AI problems [Source 7]. Many of the advanced ranking and recommendation algorithms, especially those involving neural networks, rely heavily on optimization techniques. CSCE 726 also recommends proficiency in Python and PyTorch [Source 6], which are relevant for the programming assignments in CSCE 670 [Source 4].
+    *   **Academic Progression:** For students interested in the underlying mathematical and algorithmic improvements of machine learning models used in search and recommendation, CSCE 726 would provide a deep dive into the optimization methods, allowing them to design and improve these systems.
+*   **CSCE 679: Data Visualization**
+    *   **Why it complements CSCE 670:** While not directly about algorithms, CSCE 670 involves evaluating systems [Source 1, 2]. CSCE 679 focuses on analyzing diverse data types and crafting interactive visualizations, including innovative areas like data storytelling and the role of data visualization in Explainable AI [Source 10]. Visualizing search results, recommender system outputs, and system performance metrics is crucial for understanding, evaluating, and communicating the effectiveness of these systems.
+    *   **Academic Progression:** This course would provide practical skills in presenting and interpreting the complex data and results generated by search and recommender systems, enhancing the ability to communicate insights and evaluate system performance effectively.
+These courses offer a well-rounded academic progression for someone interested in the advanced aspects of web search and recommender systems, building upon the foundations provided by CSCE 670.</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>For someone interested in web search or recommender systems, the principle is to build a strong foundation in related computational and analytical fields that underpin these advanced applications. This includes machine learning, natural language processing, and data mining, as these areas provide the theoretical and practical tools necessary to design, implement, and evaluate sophisticated search and recommendation systems.
+Based on the provided context, the following courses would complement CSCE 670 (Information Storage and Retrieval) well for a student interested in web search or recommender systems:
+*   **CSCE 633: Machine Learning**
+    *   **Why it complements CSCE 670:** CSCE 670 covers topics like "Learning to Rank," "Neural Ranking," and "Neural Collaborative Filtering" [Source 3], as well as "neural models of retrieval and recommendation" [Source 2]. CSCE 633 provides a foundational understanding of machine learning techniques, which are essential for developing and optimizing these advanced retrieval and recommendation models [Source 10].
+    *   **Academic Progression:** Taking CSCE 633 would provide the core machine learning knowledge that CSCE 670 applies to specific information retrieval and recommender system problems, allowing for a deeper understanding of the algorithms and their underlying principles.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it complements CSCE 670:** CSCE 670 delves into "word2vec; Neural Ranking," "Transformer; BERT-Based Ranking," "Large Language Models Basics," and "Large Language Models with Search Engines" [Source 3]. These are all core topics within Natural Language Processing. CSCE 638 focuses on NLP fundamentals, including language models, syntactic processing, and semantic understanding, which are crucial for understanding how search engines process and interpret textual queries and documents [Source 11].
+    *   **Academic Progression:** This course would provide the necessary NLP background to fully grasp and innovate on the text-based aspects of web search and recommendation systems introduced in CSCE 670.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670:** CSCE 676 provides a broad overview of data mining, including "exploratory data analysis, pattern mining, clustering and classification" [Source 8], and "Text Mining" [Source 6]. Many of these techniques are directly applicable to analyzing user behavior, content, and system performance in web search and recommender systems. Notably, "Mining of Massive Datasets" is an optional textbook for CSCE 670 [Source 2, 4] and a required textbook for CSCE 676 [Source 7], indicating a strong thematic overlap.
+    *   **Academic Progression:** This course would broaden your toolkit for handling and extracting insights from the large datasets common in web search and recommender systems, complementing the specific retrieval and recommendation algorithms learned in CSCE 670.
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Why it complements CSCE 670:** While CSCE 670 applies machine learning techniques, CSCE 726 focuses on the "classic deterministic optimization and modern large-scale stochastic optimization algorithms for solving ML/AI problems" [Source 9]. Understanding these optimization algorithms is critical for improving the efficiency and performance of the "Learning to Rank" and "Neural Ranking" models discussed in CSCE 670.
+    *   **Academic Progression:** This course offers a deeper, more theoretical understanding of how machine learning models, particularly those used in search and recommendation, are trained and optimized, which can be valuable for research or advanced development roles.
+These courses would provide a comprehensive academic progression, moving from the application-specific knowledge of CSCE 670 to the foundational theories and broader techniques that enable innovation in web search and recommender systems.</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>For someone interested in web search or recommender systems, selecting complementary courses involves identifying those that provide foundational knowledge, advanced techniques, or related applications that enhance the understanding and practical skills gained from CSCE 670. This approach ensures a well-rounded academic progression in these specialized areas.
+Based on the provided context, the following courses would go well with CSCE 670 (Information Storage and Retrieval) for someone interested in web search or recommender systems:
+*   **CSCE 633: Machine Learning**
+    *   **Relevance:** CSCE 670 covers topics like "Learning to Rank," "Recommender Systems," "Neural Ranking," and "Neural Collaborative Filtering" [Source 3]. Machine Learning (CSCE 633) provides the fundamental techniques and methods that underpin these advanced topics [Source 6]. Understanding machine learning principles is crucial for designing and implementing effective search and recommendation algorithms.
+    *   **Academic Progression:** This course would serve as a strong foundational course, providing the necessary theoretical and practical background in machine learning that is applied in CSCE 670. It is also a prerequisite for more advanced courses like CSCE 726 [Source 10].
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Relevance:** CSCE 670 includes modules on "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 3]. CSCE 638 focuses on "NLP fundamentals including language models, automatic syntactic processing and semantic understanding" and major NLP applications [Source 7]. This course directly supports a deeper understanding of the language-based aspects of search and recommendation systems, especially those leveraging modern LLMs.
+    *   **Academic Progression:** This course would provide specialized knowledge in a rapidly evolving area that is increasingly integrated into information retrieval and recommender systems, building on the concepts introduced in CSCE 670 regarding LLMs.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Relevance:** This course offers a "broad overview of data mining, integrating related concepts from machine learning and statistics" and covers "exploratory data analysis, pattern mining, clustering and classification" [Source 9]. Its schedule includes "Text Mining" and "Large-Scale ML" [Source 8], which are highly relevant to processing and analyzing the massive datasets typically involved in web search and recommender systems.
+    *   **Academic Progression:** This course complements CSCE 670 by providing broader skills in handling and extracting insights from large datasets, which is essential for both web search and recommender systems.
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Relevance:** This course focuses on "classic deterministic optimization and modern large-scale stochastic optimization algorithms for solving ML/AI problems" [Source 11]. Given that CSCE 670 delves into "neural models of retrieval and recommendation" [Source 2] and "neural ranking" [Source 3], understanding the optimization techniques taught in CSCE 726 would be invaluable for developing, training, and fine-tuning these complex models.
+    *   **Academic Progression:** This is a more advanced course, building on the machine learning foundations (CSCE 633 is a prerequisite [Source 10]). It provides the mathematical and algorithmic depth necessary for research and development in cutting-edge search and recommendation systems.
+**Academic Progression:**
+These courses offer a structured path for students interested in web search and recommender systems. CSCE 633 provides the fundamental machine learning background. CSCE 676 offers broader data analysis skills. CSCE 638 provides specialized knowledge in Natural Language Processing, which is critical for understanding and applying large language models in these domains. Finally, CSCE 726 offers advanced optimization techniques essential for developing and improving the performance of complex machine learning models used in search and recommendation. Taking these courses in conjunction with or after CSCE 670 would provide a comprehensive skill set for this field.</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>For someone interested in web search or recommender systems, several courses at Texas A&amp;M would complement CSCE 670 (Information Storage and Retrieval) by providing deeper foundational knowledge or related application areas:
+1.  **CSCE 676: Data Mining and Analysis**
+    *   **Why it fits:** This course provides a broad overview of data mining, integrating concepts from machine learning and statistics, with applications to online data [Source 9]. It covers topics like data preparation, text mining, graph mining, and large-scale mining [Source 8]. The required textbook for CSCE 676, "Mining of Massive Data Sets," is also listed as an optional resource for CSCE 670, indicating a strong thematic overlap in handling large datasets crucial for web search and recommender systems [Source 2, 4, 8].
+    *   **Planning Dimension:** Taking CSCE 676 would provide a robust understanding of how to extract valuable insights and patterns from large datasets, which is directly applicable to improving search engine relevance and recommender system accuracy.
+2.  **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it fits:** CSCE 670 delves into modern techniques like word2vec, Neural Ranking, Transformers, BERT-Based Ranking, and Large Language Models (LLMs) for search engines, ranking, and recommendation [Source 3]. CSCE 638 focuses on NLP fundamentals, including language models, syntactic processing, semantic understanding, and applications like information extraction and sentiment analysis [Source 10]. This course would provide a deeper theoretical and practical foundation for the NLP components used in advanced information retrieval and recommender systems.
+    *   **Planning Dimension:** This course is ideal for students who want to specialize in the linguistic and semantic aspects of information retrieval, understanding how search engines and recommenders process and understand human language.
+3.  **CSCE 633: Machine Learning**
+    *   **Why it fits:** CSCE 670 applies various machine learning concepts, such as learning to rank and different recommender system models (e.g., collaborative filtering, matrix factorization) [Source 2, 3]. CSCE 633 offers a comprehensive survey of machine learning techniques, including induction from examples, conceptual clustering, and genetic algorithms [Source 11]. This course would strengthen your foundational understanding of the machine learning algorithms that underpin many modern web search and recommender systems.
+    *   **Planning Dimension:** As a foundational course, CSCE 633 would equip you with a broader toolkit of machine learning methods, enabling you to design and implement more sophisticated algorithms for information retrieval and recommendation tasks.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5237,6 +8655,97 @@
 Both courses deal with the storage, organization, retrieval, and querying of data, and both list CSCE 310 as a prerequisite [Source 1, 5].</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>To determine course similarity, one must compare the catalog descriptions, learning outcomes, and core topics of the courses to identify significant thematic or content overlap.
+Based on the provided context:
+*   **CSCE 608: Database Systems** focuses on database modeling techniques, query languages, data models, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management [Source 1]. Its learning outcomes include understanding database design fundamentals, developing database systems, understanding relational database theory, mastering efficient query processing, and dealing with system issues [Source 2].
+*   **CSCE 670: Information Storage and Retrieval** covers the representation, storage, and access to very large multimedia document collections. It also includes fundamental data structures and algorithms for information storage and retrieval systems, and techniques for designing and evaluating retrieval systems, including indexing, compressing, and querying large collections [Source 5].
+While CSCE 670 is specifically about information retrieval, it shares conceptual similarities with CSCE 608 in the areas of storing and querying large collections of data. No other courses in the provided context show a direct or significant thematic overlap with CSCE 608.
+Therefore, **CSCE 670 (Information Storage and Retrieval)** is the most similar course to CSCE 608 based on the available information [Source 5].</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Based on the provided context, CSCE 608 focuses on **Database Systems**, covering topics such as database modeling, query languages, relational database theory, query processing, transaction management, and distributed data management [Source 1, 2].
+Another course mentioned is **CSCE 670: Information Storage and Retrieval**. While related, it has a distinct focus on the representation, storage, and access to very large multimedia document collections. It covers fundamental data structures and algorithms for information storage and retrieval systems, including techniques for indexing, compressing, and querying large collections [Source 6].
+**CSCE 681: Seminar** is a graduate seminar course focused on discussing current research and published technical articles in computer science, rather than a specific technical domain like database systems [Source 5].
+Therefore, while CSCE 670 shares some high-level concepts like storage and querying, its specific academic content differs from CSCE 608's focus on core database systems. I cannot find another course that is directly similar in its primary academic content to CSCE 608 within the provided context.</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>To determine course similarity, we look for overlapping academic content, learning outcomes, and prerequisites.
+**CSCE 608: Database Systems**
+This course focuses on database modeling techniques, expressiveness in query languages, data models, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management [Source 1]. Its learning outcomes include understanding database design fundamentals, developing database systems, understanding relational database theory, mastering efficient query processing, and dealing with system issues [Source 2]. A prerequisite is CSCE 310 or instructor approval [Source 1].
+Based on the provided context, **CSCE 670: Information Storage and Retrieval** shares significant similarities with CSCE 608.
+**Similarities with CSCE 670:**
+*   **Core Concepts:** Both courses deal with the fundamental principles of storing, organizing, and retrieving information. CSCE 608 covers "physical data organization" and "query processing" [Source 1], while CSCE 670 covers "representation, storage, and access to very large multimedia document collections" and "algorithms for indexing, compressing, and querying very large collections" [Source 5].
+*   **Querying:** CSCE 608 emphasizes "expressiveness in query languages" and "query processing" [Source 1]. CSCE 670 also includes "querying very large collections" and "web search" concepts like "text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, and learning to rank" [Source 5, 10].
+*   **Prerequisites:** Both courses list CSCE 310 (or an alternative for CSCE 670) as a prerequisite, indicating a similar foundational knowledge base [Source 1, 5].
+**Differences:**
+While both deal with data, CSCE 608 focuses on traditional "Database Systems" including relational theory and transaction management [Source 1, 2], whereas CSCE 670 specializes in "Information Storage and Retrieval" for large, often unstructured, data collections, including web search and recommender systems [Source 5, 10].
+**CSCE 679: Data Visualization**
+This course focuses on analyzing diverse data types and mapping visual analytical tasks to appropriate visual marks and encoding channels, applying visualization design models, and developing data visualization projects [Source 6, 7]. While it deals with data, its academic dimension is distinct, focusing on the visual representation and analysis of data rather than its underlying storage, retrieval mechanisms, or database theory. Therefore, CSCE 679 is not similar to CSCE 608 in its core academic content.
+In summary, **CSCE 670: Information Storage and Retrieval** is the most similar course to CSCE 608 based on the shared academic focus on data storage, organization, and querying mechanisms.</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Based on the provided context, here are courses with similarities to CSCE 608 (Database Systems):
+*   **CSCE 670 (Information Storage and Retrieval)**
+    *   **Similarities:** Both courses deal with the fundamental aspects of data. CSCE 670 focuses on the "representation, storage, and access to very large multimedia document collections," including "fundamental data structures and algorithms of information storage and retrieval systems" and "techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying very large collections" [Source 5]. This aligns with CSCE 608's coverage of "database modeling techniques," "physical data organization," "query processing," and "distributed data management" [Source 1]. Both courses also list CSCE 310 as a prerequisite [Source 1, 5].
+*   **CSCE 713 (Security)**
+    *   **Similarities:** While CSCE 713 is a security course, its schedule includes topics directly relevant to database systems. Specifically, "SQL Injection" is listed as a topic, which is a security vulnerability related to database query languages [Source 8]. Additionally, the course introduces "ACID Properties" (Atomicity, Consistency, Isolation, Durability) in its first week, which are foundational concepts for transaction management and reliability in database systems, a core topic in CSCE 608 [Source 1, 8].</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>To determine course similarity, we can look at shared prerequisites and overlapping topics in their catalog descriptions. This helps understand how courses build upon foundational knowledge and cover related subject areas, aiding in academic planning.
+Based on the provided context:
+**CSCE 608: Database Systems**
+*   **Prerequisite:** CSCE 310 or approval of Instructor [Source 1]
+*   **Core Topics:** Database modeling, query languages, data models, physical data organization, relational database design, query processing, transaction management, recovery, distributed data management [Source 1].
+**CSCE 670: Information Storage and Retrieval**
+*   **Prerequisite:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5]
+*   **Core Topics:** Representation, storage, and access to very large multimedia document collections; fundamental data structures and algorithms of information storage and retrieval systems; techniques to design and evaluate complete retrieval systems, including indexing, compressing, and querying large collections [Source 5].
+**Similarity Analysis:**
+CSCE 670 (Information Storage and Retrieval) shares a common prerequisite with CSCE 608 (Database Systems), specifically CSCE 310 [Source 1, Source 5]. Both courses deal with aspects of data management, storage, and querying. While CSCE 608 focuses broadly on database systems, including design, theory, and transaction management, CSCE 670 specializes in the storage, retrieval, and querying of very large, potentially multimedia, document collections [Source 1, Source 5]. Therefore, CSCE 670 is the most similar course in the provided context due to its shared prerequisite and related focus on data handling and querying.
+**Academic Progression:**
+If you have completed CSCE 310, you meet the prerequisite for both CSCE 608 and CSCE 670, allowing you to pursue either course. CSCE 608 provides a foundational understanding of database systems, while CSCE 670 delves into specialized techniques for information storage and retrieval, which could be a natural progression or a complementary area of study if your interests lie in managing and accessing large data collections [Source 1, Source 5].</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>To determine course similarity, we can look at shared prerequisites, overlapping catalog descriptions, and comparable learning outcomes. These elements indicate foundational knowledge and developed skills, which are key indicators of academic relatedness.
+**CSCE 608: Database Systems**
+*   **Prerequisite:** CSCE 310 or approval of Instructor [Source 1, 2].
+*   **Catalog Description:** Covers database modeling, query languages, data models, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management [Source 1].
+*   **Learning Outcomes:** Focuses on understanding database design fundamentals, developing database systems, relational database theory, efficient query processing, and system issues related to databases [Source 2].
+Based on the provided context, **CSCE 670: Information Storage and Retrieval** shares the most similarities with CSCE 608.
+**CSCE 670: Information Storage and Retrieval**
+*   **Prerequisite:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5, 10]. This directly overlaps with CSCE 608's prerequisite of CSCE 310.
+*   **Catalog Description:** Focuses on the representation, storage, and access to very large multimedia document collections, including fundamental data structures and algorithms for information storage and retrieval systems, and techniques for designing and evaluating retrieval systems (indexing, compressing, querying) [Source 5].
+*   **Learning Outcomes:** Includes defining and explaining key concepts for web search (text indexing, retrieval models, web crawling, PageRank, learning to rank) and recommender systems (collaborative filtering, matrix factorization), as well as designing, implementing, and evaluating algorithms for search and recommendation systems [Source 10].
+**Comparison and Planning Dimension:**
+Both CSCE 608 and CSCE 670 require CSCE 310 as a prerequisite, indicating a shared foundational knowledge in computer science. While CSCE 608 focuses on structured database systems, CSCE 670 extends these concepts to the storage, retrieval, and querying of large, often unstructured, information collections like web documents.
+For a student, understanding this similarity is valuable for academic planning:
+*   If you have completed CSCE 608 and enjoyed the topics of data storage, organization, and efficient querying, CSCE 670 would be a logical progression to explore how these principles apply to broader information retrieval contexts, such as web search engines and recommender systems.
+*   These courses collectively build a strong foundation in data management and information systems, which are crucial for careers in data science, software engineering, and information architecture. They allow you to specialize in how data is stored, accessed, and made useful, whether in structured databases or vast document collections.</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Based on the provided context, **CSCE 670: Information Storage and Retrieval** is a course similar to CSCE 608: Database Systems [Source 5].
+Here's how CSCE 670 relates to CSCE 608 and how it might fit into your academic progression:
+*   **Focus on Large Data Collections**: Both courses deal with the management and querying of large data collections. While CSCE 608 focuses on database systems, relational theory, and transaction management, CSCE 670 delves into the "representation, storage, and access to very large multimedia document collections" and the "fundamental data structures and algorithms of information storage and retrieval systems" [Source 1, 5].
+*   **Querying and Indexing**: CSCE 670 covers "algorithms for indexing, compressing, and querying very large collections," which complements the "query processing" and "physical data organization" topics in CSCE 608 [Source 1, 5].
+*   **Big Data Concepts**: CSCE 608 includes "Bigdata" in its course summary [Source 3]. CSCE 670 extends this by exploring modern techniques like "Large Language Models with Search Engines" and "Large Language Models for Ranking and Recommendation," and uses "Mining of Massive Datasets" as an optional textbook [Source 7, 9].
+*   **Prerequisites**: Both courses share CSCE 310 as a prerequisite, indicating a foundational knowledge in computer science is expected for both [Source 1, 5].
+**Academic Planning Dimension:**
+If you have completed CSCE 608 and wish to deepen your understanding of how large-scale data is organized, accessed, and retrieved, particularly in the context of search engines, recommender systems, and modern AI applications, CSCE 670 would be a logical next step. It builds upon the data management fundamentals learned in CSCE 608 by focusing on specialized techniques for information retrieval from massive, often unstructured, datasets. This course could be beneficial for students interested in careers involving search technologies, data mining, or large-scale information systems.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5360,6 +8869,112 @@
 | Course   | AI Tool Usage Policy                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Based on the provided context, here are courses that permit or generally accept the use of AI tools:
+*   **CSCE 624** (Sketch Recognition): AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, 9, 11].
+*   **CSCE 632**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments for brainstorming ideas or providing feedback, but should not complete the work. Students must cite any AI-generated content that informs their work, and no more than 30% of any assignment should consist of AI-generated text [Source 6].
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to get started with ideas or to provide feedback. Students must cite any AI-generated material that informed their work, and no more than 30% of an assignment should come directly from text generated from an AI tool [Source 8].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts and evaluation, and must cite their use. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct [Source 12].
+*   **CSCE 713**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible to allow the instructor to evaluate the student rationale to solve the problem [Source 13].
+**Note:** CSCE 726 prohibits the use of AI tools such as large language models for completing homework assignments, exams, or the course project, but it is acceptable for tasks like editing writing or debugging code [Source 7]. CSCE 665 prohibits AI tools for paper mini-review writing, but the course schedule includes "AI/LLM Security" topics [Source 10]. CSCE 612 strictly prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 14].</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>CSCE 629 strictly prohibits the use of AI tools [Source 2]. If you are looking for courses that focus on using AI tools, you might consider the following:
+*   **CSCE 624**
+    *   AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including what tool was used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, Source 9, Source 11].
+*   **CSCE 632**
+    *   The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct. Students must cite the use of Generative AI tools and document their contributions [Source 12].
+*   **CSCE 633**
+    *   The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct. Students must cite the use of Generative AI tools and document what they have contributed to an assignment [Source 12].
+*   **CSCE 614**
+    *   Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to help with ideas or provide feedback. Students must cite any AI-generated material that informed their work, and no more than 30% of an assignment should come directly from text generated by an AI tool. Using an AI tool to generate content without proper attribution qualifies as academic dishonesty [Source 8].
+*   **CSCE 665**
+    *   This course has specific restrictions. While it mentions "AI/LLM Security" as a topic [Source 10], it explicitly states that "No AI tools such as ChatGPT are allowed to use in the review writing" for the paper mini-review component [Source 10].
+*   **CSCE 713**
+    *   The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible to allow the instructor to evaluate the student's rationale to solve the problem [Source 13].
+*   **CSCE 726**
+    *   The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing your writing or assisting in debugging your code [Source 7].
+**Note:** CSCE 612 explicitly prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 14].
+When planning your academic progression, consider that policies on AI tool usage can vary significantly between courses. Always review the specific AI statement in each course's syllabus to understand the expectations and requirements for documentation and attribution.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Given that AI is strictly prohibited in CSCE 629 [Source 2], you have several other options for courses that permit or focus on the use of AI tools:
+*   **CSCE 624** (Spring 2026): AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, Source 9, Source 12].
+*   **CSCE 632** (Spring 2026): You are permitted to use generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) to assist with assignments. These tools can help with brainstorming ideas or providing feedback, but should not complete your work. You must cite any AI-generated content that informs your work, and no more than 30% of any assignment should consist of AI-generated text [Source 6].
+*   **CSCE 614** (Spring 2026): Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to help with ideas or provide feedback. You must cite any AI-generated material that informed your work, and generally, no more than 30% of an assignment should come directly from AI-generated text [Source 7].
+*   **CSCE 633** (Spring 2026): The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts and evaluation methods. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct, so students must cite the use of Generative AI tools and document their contribution to an assignment [Source 11].
+*   **CSCE 713** (Spring 2026): The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible, to allow the instructor to evaluate the student's rationale [Source 14].
+**Courses with Restrictions or Prohibitions on AI Tools:**
+*   **CSCE 612** (Spring 2026): Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F\* [Source 13].
+*   **CSCE 726** (Spring 2026): The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing your writing or assisting in debugging your code [Source 8].
+*   **CSCE 665** (Spring 2026): No AI tools such as ChatGPT are allowed to use in the review writing [Source 10].
+When planning your academic progression, consider these policies carefully. Courses like CSCE 624, CSCE 632, CSCE 614, CSCE 633, and CSCE 713 offer opportunities to engage with AI tools, often with specific documentation and attribution requirements, which can be valuable for developing skills in using emerging technologies responsibly. Conversely, CSCE 612, CSCE 726, and CSCE 665 have stricter policies regarding AI use for graded assignments.</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>CSCE 629 strictly prohibits the use of AI tools [Source 2]. However, several other courses permit or even encourage the use of AI tools, often with specific guidelines for their use and attribution.
+Here are some courses where AI tools are mentioned as being usable:
+*   **CSCE 624**
+    *   AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, Source 9, Source 11].
+*   **CSCE 632**
+    *   The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts provided and how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct. Students must cite the use of Generative AI tools and document their contribution to an assignment [Source 12].
+*   **CSCE 633**
+    *   Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments. These tools can help brainstorm ideas or provide feedback but should not complete the work. Students must cite any AI-generated content that informs their work, and failure to properly attribute AI-generated material is considered academic dishonesty. No more than 30% of any assignment should consist of AI-generated text [Source 6].
+*   **CSCE 614**
+    *   Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments. AI is not intended to do all the work but to get students started with ideas or provide feedback. Students must cite any AI-generated material that informed their work, and using an AI tool to generate content without proper attribution qualifies as academic dishonesty. No more than 30% of an assignment should come directly from text generated from an AI tool [Source 8].
+*   **CSCE 713**
+    *   The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible, to allow the instructor to evaluate the student's rationale to solve the problem [Source 13].
+**Courses where AI tools are prohibited or have specific restrictions:**
+*   **CSCE 612**: Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F* [Source 14].
+*   **CSCE 665**: No AI tools such as ChatGPT are allowed to be used in the paper mini-review writing [Source 10].
+*   **CSCE 726**: The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 7].
+When planning your academic progression, consider these policies to choose courses that align with your interest in using AI tools for learning and assignments. Always review the specific syllabus for the most up-to-date AI policy for any course you plan to take.</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>CSCE 629 strictly prohibits the use of AI tools [Source 2].
+If you are looking for courses that allow or focus on the use of AI tools, you might consider the following:
+*   **CSCE 624**: AI tools may be used when explicitly permitted for assignments or projects, with clear documentation required for what tool was used, how it was used, and how the output was validated or modified [Source 5, Source 9, Source 11].
+*   **CSCE 632**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts and evaluation methods. However, submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct [Source 12].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated [Source 12].
+*   **CSCE 614**: Generative AI tools are permitted on assignments to help with ideas or provide feedback, but not to do all the work. Any AI-generated material must be cited, and no more than 30% of an assignment should come directly from AI-generated text [Source 8].
+*   **CSCE 665**: This course includes topics on "AI/LLM Security" in weeks 11, 13, and 14, suggesting a focus on AI technologies themselves, though it explicitly states "No AI tools such as ChatGPT are allowed to use in the review writing" for the paper mini-review [Source 10].
+*   **CSCE 713**: AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to allow the instructor to evaluate the student rationale [Source 13].
+**Courses where AI is strictly prohibited or has specific restrictions:**
+*   **CSCE 612**: Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating [Source 14].
+*   **CSCE 726**: The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 7].
+When planning your academic progression, consider that policies on AI tool usage can vary significantly between courses. It's important to review the specific AI statement in each course's syllabus to understand the expectations and requirements for attribution and usage.</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>AI policies vary significantly across courses. While CSCE 629 strictly prohibits the use of AI [Source 2], several other courses permit or even encourage the use of AI tools under specific conditions.
+Here are some courses where AI tools are mentioned as being usable:
+*   **CSCE 624**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 5, Source 9, Source 11].
+*   **CSCE 632**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts provided and how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct. Students must cite the use of Generative AI tools and document their contributions [Source 12].
+*   **CSCE 633**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments. These tools can help brainstorm ideas or provide feedback but should not complete the work. Students must cite any AI-generated content that informs their work, and failure to properly attribute AI-generated material is considered academic dishonesty. No more than 30% of any assignment should consist of AI-generated text [Source 6].
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to get started with ideas or provide feedback. Students must cite any AI-generated material that informed their work, and using an AI tool to generate content without proper attribution qualifies as academic dishonesty. No more than 30% of an assignment should come directly from text generated from an AI tool [Source 8].
+*   **CSCE 713**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible to allow the instructor to evaluate the student's rationale to solve the problem [Source 13].
+*   **CSCE 726**: The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 7].
+**Note**: CSCE 665 explicitly states that "No AI tools such as ChatGPT are allowed to use in the review writing" for the paper mini-review component [Source 10]. CSCE 612 strictly prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 14].
+When planning your academic progression, consider the specific AI policies of each course, as they vary from strict prohibition to conditional allowance with documentation and citation requirements.</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>While CSCE 629 strictly prohibits the use of AI [Source 2], several other courses permit or encourage the use of AI tools for various academic tasks. If you are looking for courses where you can integrate AI tools into your work, consider the following:
+*   **CSCE 633**: In this course, the use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated the AI's output. This approach helps students engage with creative tasks while maintaining academic integrity by citing AI contributions [Source 11]. This course could help you develop skills in ethically integrating AI into your creative and problem-solving processes.
+*   **CSCE 624**: AI tools may be used for assignments or projects when explicitly permitted. Any AI assistance must be clearly documented, detailing the tool used, how it was used, and how the student validated or modified the output. This course provides an opportunity to apply AI tools in practical project settings, enhancing your ability to leverage AI while ensuring accountability and understanding of its contributions [Source 5, Source 12].
+*   **CSCE 632**: This course permits the use of generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) to assist with assignments. These tools can be used for brainstorming ideas or providing feedback, but they should not complete your work entirely. You are required to cite any AI-generated content that informs your work, and no more than 30% of any assignment should consist of AI-generated text. This course helps you learn to use emerging technologies ethically and effectively for idea generation and feedback in your academic progression [Source 6].</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5470,6 +9085,99 @@
 *   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **Week 8:** word2vec; Neural Ranking [Source 2]
+*   **Week 10:** Transformer; BERT-Based Ranking [Source 2]
+*   **Week 11:** Neural Collaborative Filtering; Sequential Recommendation [Source 2]
+*   **Week 12-14:** Large Language Models (Basics, with Search Engines, for Ranking and Recommendation) [Source 2]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>CSCE 670 (Section 600) covers the following information retrieval algorithms and models in the second half of the course:
+*   word2vec [Source 3]
+*   Neural Ranking [Source 3]
+*   Transformer [Source 3]
+*   BERT-Based Ranking [Source 3]
+*   Neural Collaborative Filtering [Source 3]
+*   Sequential Recommendation [Source 3]
+*   Large Language Models Basics [Source 3]
+*   Large Language Models with Search Engines [Source 3]
+*   Large Language Models for Ranking and Recommendation [Source 3]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **word2vec** [Source 2]
+*   **Neural Ranking** [Source 2]
+*   **Transformer** [Source 2]
+*   **BERT-Based Ranking** [Source 2]
+*   **Neural Collaborative Filtering** [Source 2]
+*   **Sequential Recommendation** [Source 2]
+*   **Large Language Models Basics** [Source 2]
+*   **Large Language Models with Search Engines** [Source 2]
+*   **Large Language Models for Ranking and Recommendation** [Source 2]</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   **word2vec** [Source 2]
+*   **Neural Ranking** [Source 2]
+*   **Transformer** [Source 2]
+*   **BERT-Based Ranking** [Source 2]
+*   **Neural Collaborative Filtering** [Source 2]
+*   **Sequential Recommendation** [Source 2]
+*   **Large Language Models Basics** [Source 2]
+*   **Large Language Models with Search Engines** [Source 2]
+*   **Large Language Models for Ranking and Recommendation** [Source 2]</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   word2vec [Source 3]
+*   Neural Ranking [Source 3]
+*   Transformer [Source 3]
+*   BERT-Based Ranking [Source 3]
+*   Neural Collaborative Filtering [Source 3]
+*   Sequential Recommendation [Source 3]
+*   Large Language Models Basics [Source 3]
+*   Large Language Models with Search Engines [Source 3]
+*   Large Language Models for Ranking and Recommendation [Source 3]</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following specific information retrieval algorithms and models:
+*   word2vec [Source 3]
+*   Neural Ranking [Source 3]
+*   Transformer [Source 3]
+*   BERT-Based Ranking [Source 3]
+*   Neural Collaborative Filtering [Source 3]
+*   Sequential Recommendation [Source 3]
+*   Large Language Models Basics [Source 3]
+*   Large Language Models with Search Engines [Source 3]
+*   Large Language Models for Ranking and Recommendation [Source 3]</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>In the second half of CSCE 670, the course covers the following information retrieval algorithms and models:
+*   word2vec [Source 1]
+*   Neural Ranking [Source 1]
+*   Transformer [Source 1]
+*   BERT-Based Ranking [Source 1]
+*   Neural Collaborative Filtering [Source 1]
+*   Sequential Recommendation [Source 1]
+*   Large Language Models Basics [Source 1]
+*   Large Language Models with Search Engines [Source 1]
+*   Large Language Models for Ranking and Recommendation [Source 1]</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5553,6 +9261,47 @@
         <is>
           <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
 The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [3].
+The provided context does not explicitly mention whether ensemble methods are covered [1, 3].</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [Source 3]. The course also surveys various machine learning techniques and aims for students to apply advanced machine learning algorithms [Source 1, 2]. However, the provided context does not explicitly mention whether ensemble methods are covered.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [Source 2].
+The provided context does not explicitly mention whether ensemble methods are covered [Source 1, 2, 3].</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [Source 2].
+The provided context does not explicitly mention whether ensemble methods are covered [Source 1, 2, 3].</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [Source 2].
+The provided context does not explicitly mention whether ensemble methods are covered.</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [Source 2].
+The provided context does not explicitly mention whether ensemble methods are covered [Source 1, 2, 3].</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 633 covers regularization techniques, as indicated by the "Logistic Regression &amp; Regularization" module in the course schedule [Source 2].
+The provided context does not explicitly mention whether ensemble methods are covered [Source 1, 2, 3].</t>
         </is>
       </c>
     </row>
@@ -5667,6 +9416,74 @@
 *   **Week 6:** Contextualized Representations, Pre-Training, Large Language Models [Source 1]</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers several deep learning architectures, including:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Sequence-to-Sequence models [Source 1]
+The course specifically includes **Attention** mechanisms (Week 4) and **Transformers** (Week 5) [Source 1].</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 638 covers several deep learning architectures, including:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Sequence-to-Sequence models [Source 1]
+The course specifically includes **Attention** mechanisms (Week 4) and **Transformers** (Week 5) [Source 1].</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>CSCE 638 (Section 600) covers the following deep learning architectures:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Attention mechanisms [Source 1]
+*   Transformers [Source 1]
+Yes, the course specifically includes Transformers and Attention mechanisms in its curriculum [Source 1].</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>CSCE 638 (Section 600) covers the following deep learning architectures:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Attention mechanisms [Source 1]
+*   Transformers [Source 1]
+Yes, the course specifically includes Transformers and Attention mechanisms in its curriculum [Source 1].</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>CSCE 638 covers the following deep learning architectures:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Attention mechanisms [Source 1]
+*   Transformers [Source 1]
+Specifically, attention mechanisms are covered in Week 4, and Transformers are covered in Week 5 of the course schedule [Source 1].</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>CSCE 638 covers the following deep learning architectures:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Attention mechanisms [Source 1]
+*   Transformers [Source 1]
+Specifically, attention mechanisms are covered in Week 4, and Transformers are covered in Week 5 of the course schedule [Source 1].</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>CSCE 638 covers the following deep learning architectures:
+*   Convolutional Neural Networks (CNN) [Source 1]
+*   Recurrent Neural Networks (RNN) [Source 1]
+*   Attention mechanisms [Source 1]
+*   Transformers [Source 1]
+Specifically, attention mechanisms are covered in Week 4, and Transformers are covered in Week 5 of the course schedule [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5741,6 +9558,41 @@
       <c r="R39" t="inlineStr">
         <is>
           <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2]. The course description and topics for CSCE 665 focus on advanced networking and security, including areas like software security, malware, botnets, intrusion detection, and web/AI security, but do not specifically mention cryptographic concepts or protocols.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context. The course focuses on advanced networking and security topics such as software security, malware, botnets, intrusion detection, software-defined security, web/Web3 security, and AI/LLM security [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context. The course focuses on advanced networking and security topics such as software security, malware, botnets, intrusion detection, software-defined security, web/Web3 security, and AI/LLM security [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context. The course focuses on advanced networking and security topics such as software security, malware, botnets, intrusion detection, software-defined security, web/Web3 security, and AI/LLM security [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context. The course focuses on advanced networking and security topics such as software security, malware, botnets, intrusion detection, software-defined security, web/Web3 security, and AI/LLM security [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>I cannot find information about specific cryptographic concepts and protocols covered in CSCE 665 in the provided context. The course focuses on advanced networking and security topics such as software security, malware, botnets, intrusion detection, software-defined security, web/Web3 security, and AI/LLM security [Source 1, Source 2].</t>
         </is>
       </c>
     </row>
@@ -5895,6 +9747,97 @@
 Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>CSCE 612, Applied Networks and Distributed Processing, focuses on both network protocol implementation and distributed system design [Source 1, 2].
+Key systems-level topics include:
+*   **Network Protocol Implementation**: The course involves programming and pragmatic views of engineering issues, with lab exercises focusing on protocol understanding and programming. Students will learn to utilize operating-system sockets APIs and create efficient network applications [Source 1, 2]. The schedule includes topics like "Sockets, threads, synchronization" [Source 3].
+*   **Distributed System Design**: The course covers "Applied Networks and Distributed Processing" and aims for students to "build multi-threaded decentralized frameworks" [Source 1, 2].
+The course also emphasizes applying principles of layered architecture to analyzing real networks, network design, protocol analysis, and principles of network engineering [Source 1]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on both network protocol implementation and distributed system design [Source 1].
+The course aims to:
+*   Mix fundamentals with programming and pragmatic engineering issues, including network architecture and principles of network engineering [Source 1].
+*   Apply principles of layered architecture to analyzing real networks, with lab exercises focusing on protocol understanding and programming [Source 1].
+*   Enable students to utilize operating-system sockets APIs, create efficient network applications, build multi-threaded decentralized frameworks, and develop protocols [Source 2].
+Key topics covered include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3].
+*   Application layer concepts such as HTTP, caching, cookies, FTP, email, and DNS [Source 3, 4].
+*   Transport layer topics like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), flow control, congestion control, and TCP modeling [Source 3, 4].
+*   Network layer concepts including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP) [Source 4].
+*   Data-link layer topics such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring submissions to compile in Visual Studio 2022 [Source 3, 4]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>CSCE 612, "Applied Networks and Distributed Processing," focuses on systems-level topics including network protocol implementation and distributed system design.
+Specifically, the course aims for students to:
+*   Utilize operating-system sockets APIs [Source 2].
+*   Create efficient network applications [Source 2].
+*   Build multi-threaded decentralized frameworks [Source 2].
+*   Develop protocols [Source 2].
+*   Construct models of their system [Source 2].
+The curriculum covers fundamentals of network design and protocol analysis, mixing these with programming and pragmatic engineering views. Lab exercises emphasize protocol understanding and programming, applying principles of layered architecture to analyze real networks [Source 1]. Key topics include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3, 4].
+*   Application layer protocols such as HTTP, FTP, email, and DNS, including DNS vulnerabilities and P2P [Source 3, 4].
+*   Transport layer concepts like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), timeouts, flow control, congestion control, and TCP modeling [Source 4].
+*   Network layer topics including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP, multicast) [Source 4].
+*   Data-link layer aspects such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring compilation in Visual Studio 2022 [Source 3, 4]. The course requires a prerequisite of CSCE 313 and is intended for graduate classification [Source 2].</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>CSCE 612, "Applied Networks and Distributed Processing," focuses on systems-level topics including network protocol implementation and distributed system design.
+Specifically, the course aims for students to:
+*   Utilize operating-system sockets APIs [Source 2].
+*   Create efficient network applications [Source 2].
+*   Build multi-threaded decentralized frameworks [Source 2].
+*   Develop protocols [Source 2].
+*   Construct models of their system [Source 2].
+The curriculum covers fundamentals of network design and protocol analysis, mixing these with programming and pragmatic engineering views. Lab exercises emphasize protocol understanding and programming, applying principles of layered architecture to analyze real networks [Source 1]. Key topics include:
+*   Sockets, threads, and synchronization [Source 3].
+*   Internet structure, topology, delay, and loss [Source 3, 4].
+*   Application layer protocols such as HTTP, FTP, email, and DNS, including DNS vulnerabilities and P2P [Source 3, 4].
+*   Transport layer concepts like multiplexing, UDP, reliable data transfer (stop &amp; wait, Go-back-N, Selective Repeat), timeouts, flow control, congestion control, and TCP modeling [Source 4].
+*   Network layer topics including switching, IP header, NAT, and routing protocols (link-state, distance vector, RIP, OSPF, BGP, multicast) [Source 4].
+*   Data-link layer aspects such as error detection/correction, CSMA, Ethernet, hubs, and switches [Source 4].
+Homework assignments involve implementation and reports, requiring compilation in Visual Studio 2022 [Source 3, 4]. The course requires a prerequisite of CSCE 313 and is intended for graduate classification [Source 2].</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on systems-level topics including network protocol implementation and distributed system design [Source 1, 2].
+Specifically, the course covers:
+*   **Network Protocol Implementation:** Students will learn to utilize operating-system sockets APIs, create efficient network applications, and develop protocols. Lab exercises emphasize protocol understanding and programming [Source 1, 2]. The course schedule includes topics such as Internet structure, application types (HTTP, FTP, email, DNS, P2P), transport layer protocols (UDP, reliable data transfer, Go-back-N, Selective Repeat, TCP modeling, congestion control), and network layer concepts (IP header, routing protocols like RIP, OSPF, BGP) [Source 3, 4].
+*   **Distributed System Design:** The course aims for students to be able to build multi-threaded decentralized frameworks [Source 1]. Early lectures cover "Sockets, threads, synchronization" [Source 3].
+The course mixes fundamentals with programming and pragmatic engineering views, applying principles of layered architecture to analyze real networks [Source 2].</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on systems-level topics including network protocol implementation and distributed system design [Source 1, 2].
+Specifically, the course covers:
+*   **Network Protocol Implementation:** Students will learn to utilize operating-system sockets APIs, create efficient network applications, and develop protocols. Lab exercises emphasize protocol understanding and programming [Source 1, 2]. The course schedule includes topics such as Internet structure, application types (HTTP, FTP, email, DNS, P2P), transport layer protocols (UDP, reliable data transfer, Go-back-N, Selective Repeat, TCP modeling, congestion control), and network layer concepts (IP header, routing protocols like RIP, OSPF, BGP) [Source 3, 4].
+*   **Distributed System Design:** The course aims for students to be able to build multi-threaded decentralized frameworks [Source 1]. Early lectures cover "Sockets, threads, synchronization" [Source 3].
+The course mixes fundamentals with programming and pragmatic engineering views, applying principles of layered architecture to analyze real networks [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>CSCE 612: Applied Networks and Distributed Processing (Section 600) focuses on systems-level topics including network protocol implementation and distributed system design [Source 1, 2].
+Specifically, the course covers:
+*   **Network Protocol Implementation:** Students will learn to utilize operating-system sockets APIs, create efficient network applications, and develop protocols. Lab exercises emphasize protocol understanding and programming [Source 1, 2]. The course schedule includes topics such as Internet structure, application types (HTTP, FTP, email, DNS, P2P), transport layer protocols (UDP, reliable data transfer, Go-back-N, Selective Repeat, TCP modeling, congestion control), and network layer concepts (IP header, routing protocols like RIP, OSPF, BGP) [Source 3, 4].
+*   **Distributed System Design:** The course aims for students to be able to build multi-threaded decentralized frameworks [Source 1]. Early lectures cover "Sockets, threads, synchronization" [Source 3].
+The course mixes fundamentals with programming and pragmatic engineering views, applying principles of layered architecture to analyze real networks [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6006,6 +9949,69 @@
 *   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
 *   **Final Exam**: 30% [Source 1]
 *   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four brief in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, the final grade is weighted as follows:
+*   **Homework**: 30% (five programming assignments) [Source 1]
+*   **Quizzes**: 20% (four in-class quizzes) [Source 1]
+*   **Final Exam**: 30% [Source 1]
+*   **Group Project**: 20% [Source 1]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600, the final grade is weighted as follows [1]:
+*   **Homework:** 30% (five programming assignments)
+*   **Quizzes:** 20% (four brief in-class quizzes)
+*   **Final Exam:** 30%
+*   **Group Project:** 20%</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600, the final grade is weighted as follows [1]:
+*   **Homework:** 30% (five programming assignments)
+*   **Quizzes:** 20% (four brief in-class quizzes)
+*   **Final Exam:** 30%
+*   **Group Project:** 20%</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600, the final grade is weighted as follows [1]:
+*   **Homework:** 30% (five programming assignments)
+*   **Quizzes:** 20% (four brief in-class quizzes)
+*   **Final Exam:** 30%
+*   **Group Project:** 20%</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600, the final grade is weighted as follows [1]:
+*   **Homework:** 30% (five programming assignments)
+*   **Quizzes:** 20% (four brief in-class quizzes)
+*   **Final Exam:** 30%
+*   **Group Project:** 20%</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>For CSCE 670, Section 600, the final grade is weighted as follows [1]:
+*   **Homework:** 30% (five programming assignments)
+*   **Quizzes:** 20% (four brief in-class quizzes)
+*   **Final Exam:** 30%
+*   **Group Project:** 20%</t>
         </is>
       </c>
     </row>
@@ -6157,6 +10163,92 @@
 The programming assignments contribute 400 points to the final grade [3].</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of seven programming assignments, referred to as machine problems (MPs) [Source 4, 5]. These assignments are designed to guide students through the process of designing and developing a simple operating system that can boot and run on a bare PC [Source 1, 4].
+The machine problems cover various aspects of operating systems, including:
+*   **MP1**: Project setup, introduction to OS concepts, architectural support, OS structures, system calls, and interrupt/exception handling on the x86 architecture [Source 3].
+*   **MP2**: Memory management, including allocation, address spaces, paging, advanced paging, TLB, segmentation, and virtual memory mechanisms [Source 3].
+*   **MP3**: Page replacement policies, recursive page table lookup, concurrency introduction, and scheduling [Source 3, 5].
+*   **MP4**: Thread dispatching on x86, kernel vs. user-level threads, event-based concurrency, and an introduction to synchronization [Source 5].
+*   **MP5**: Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [Source 5].
+*   **MP6**: I/O management, device drivers, disks, RAID, flash memory, and file systems (including allocation, UNIX file systems, and UNIX Fast File System) [Source 5].
+*   **MP7**: Journaled and log-based file systems, and virtualization mechanisms including memory virtualization [Source 5].
+Through these projects, students will implement components such as a virtual memory manager for a paged system, a threading system, a simple device driver, and a simple file system [Source 1, 6].</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>In CSCE 611, there are 7 programming projects, referred to as Machine Problems (MPs) [3, 4, 5]. These assignments guide students through the design and development of a simple operating system that can boot and run on a bare PC [1, 3].
+The Machine Problems cover the following topics:
+*   **MP1:** Project setup, introduction to operating systems, architectural support, and OS structures [4].
+*   **MP2:** Memory management, including allocation, address spaces, paging, advanced paging, TLB, x86 paging, segmentation, and virtual memory mechanisms [4].
+*   **MP3:** Page replacement policies, recursive page table lookup, concurrency introduction, and scheduling [4, 5].
+*   **MP4:** Thread dispatching on x86, kernel vs. user-level threads, and event-based concurrency [5].
+*   **MP5:** Software and hardware solutions to the critical section problem, concurrent data structures, and atomic transactions [5].
+*   **MP6:** I/O management, device drivers, disks, RAID, flash memory, and file systems (intro, allocation, UNIX file system, UNIX fast file system) [5].
+*   **MP7:** Journaled and log-based file systems, and virtualization (introduction, mechanisms, memory virtualization) [5].</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of seven programming assignments, referred to as Machine Problems (MPs), which guide students through designing and developing a simple operating system [Source 6].
+The topics covered by these MPs are:
+*   **MP1:** Project Setup, Introduction to OS, Architectural Support, OS Structures, System Calls, Interrupts and Exceptions on the x86 [Source 2].
+*   **MP2:** Memory Allocation, Address Spaces, Paging, Advanced Paging, The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms [Source 2].
+*   **MP3:** Page Replacement Policies I &amp; II, Recursive Page Table Lookup, Concurrency Introduction, Scheduling [Source 2, 4].
+*   **MP4:** Thread Dispatching on the x86, Kernel vs. User level Threads, Event-based Concurrency [Source 4].
+*   **MP5:** SW Solutions to Critical Section Problem, HW Solutions to Critical Section Problem, Concurrent Data Structures, Atomic Transactions [Source 4].
+*   **MP6:** I/O Introduction, I/O Management and Device Drivers, Disks, RAID, Flash Memory, File Systems Introduction, File Allocation, UNIX File System, UNIX Fast File System [Source 4].
+*   **MP7:** Journaled and Log-Based File Systems, Virtualization Introduction, Virtualization Mechanisms, Memory Virtualization [Source 4].</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>CSCE 611 includes a series of seven programming assignments, referred to as Machine Problems (MPs), which guide students through designing and developing a simple operating system [Source 6].
+The topics covered by these MPs are:
+*   **MP1:** Project Setup, Introduction to OS, Architectural Support, OS Structures, System Calls, Interrupts and Exceptions on the x86 [Source 2].
+*   **MP2:** Memory Allocation, Address Spaces, Paging, Advanced Paging, The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, Virtual Memory Mechanisms [Source 2].
+*   **MP3:** Page Replacement Policies I &amp; II, Recursive Page Table Lookup, Concurrency Introduction, Scheduling [Source 2, 4].
+*   **MP4:** Thread Dispatching on the x86, Kernel vs. User level Threads, Event-based Concurrency [Source 4].
+*   **MP5:** SW Solutions to Critical Section Problem, HW Solutions to Critical Section Problem, Concurrent Data Structures, Atomic Transactions [Source 4].
+*   **MP6:** I/O Introduction, I/O Management and Device Drivers, Disks, RAID, Flash Memory, File Systems Introduction, File Allocation, UNIX File System, UNIX Fast File System [Source 4].
+*   **MP7:** Journaled and Log-Based File Systems, Virtualization Introduction, Virtualization Mechanisms, Memory Virtualization [Source 4].</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>In CSCE 611, there are seven programming projects, referred to as Machine Problems (MPs) [Source 1, 4]. These assignments are designed to guide students through the process of designing and developing a simple operating system that can boot and run on a bare PC [Source 3, 6].
+Specifically, the projects cover implementing components such as:
+*   A virtual memory manager for a paged system [Source 5].
+*   A threading system for a single-processor system [Source 5].
+*   A simple device driver [Source 5].
+*   A simple file system [Source 5].</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>In CSCE 611, there are seven programming projects, referred to as Machine Problems (MPs) [Source 1, 3, 5]. These assignments are designed to guide students through the process of designing and developing a simple operating system [Source 5].
+The topics covered by these machine problems are:
+*   **MP1:** Project Setup, Introduction to Operating Systems, Architectural Support, OS Structures, System Calls, and Interrupts and Exceptions on the x86 [Source 1].
+*   **MP2:** Memory management, including Memory Allocation, Address Spaces, Paging, Advanced Paging, The TLB, Paging on the x86, Segmentation, Beyond Physical Memory, and Virtual Memory Mechanisms [Source 1].
+*   **MP3:** Page Replacement Policies, Recursive Page Table Lookup, Concurrency Introduction, and Scheduling [Source 1, 3].
+*   **MP4:** Thread Dispatching on the x86, Kernel vs. User-level Threads, Event-based Concurrency, and Synchronization Introduction [Source 3].
+*   **MP5:** Software and Hardware Solutions to the Critical Section Problem, Concurrent Data Structures, and Atomic Transactions [Source 3].
+*   **MP6:** I/O management (Intro, I/O Management and Device Drivers, Disks, RAID, Flash Memory), and File Systems (Intro, File Allocation, UNIX File System, UNIX Fast File System) [Source 3].
+*   **MP7:** Journaled and Log-Based File Systems, Virtualization Introduction, Virtualization Mechanisms, and Memory Virtualization [Source 3].</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>In CSCE 611, there are seven programming projects, referred to as Machine Problems (MPs) [Source 1, 4]. These assignments are designed to guide students through the process of designing and developing a simple operating system that can boot and run on a bare PC [Source 3, 6].
+Specifically, the projects cover implementing components such as:
+*   A virtual memory manager for a paged system [Source 5].
+*   A threading system for a single-processor system [Source 5].
+*   A simple device driver [Source 5].
+*   A simple file system [Source 5].</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6234,6 +10326,41 @@
           <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1]. Work submitted as makeup for an excused absence is exempt from this policy [Source 1].</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1].</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1].</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1].</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1].</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1].</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>For CSCE 633, no late assignments will be accepted. Late assignments are defined as any deliverables submitted after the established deadline [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6311,6 +10438,41 @@
           <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The prerequisites listed for CSCE 633 are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2, Source 3]. The prerequisites listed are CSCE 420 or CSCE 625 [Source 1].</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The context lists course prerequisites as CSCE 420 or CSCE 625, but does not specify the mathematical background expected [Source 1].</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The context lists course prerequisites as CSCE 420 or CSCE 625, but does not specify the mathematical background expected [Source 1].</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The context lists CSCE 420 or CSCE 625 as prerequisites for CSCE 633, but does not specify the mathematical background expected [Source 1].</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The context lists CSCE 420 or CSCE 625 as prerequisites for CSCE 633, but it does not specify the mathematical background expected beyond these course prerequisites [Source 1].</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The context lists CSCE 420 or CSCE 625 as prerequisites for CSCE 633, but does not specify the mathematical background expected [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6393,6 +10555,51 @@
           <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments and exams. Students are prohibited from using any part (code, text, figures, etc.) developed by others, including AI, for programming assignments and homework. This means students should not submit or make use of AI-generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments.
+For programming assignments, students are not to submit or make use of AI generated solutions [Source 1]. Similarly, for homework, students are not to submit or make use of AI generated solutions [Source 1]. For exams, AI tools are listed as disallowed sources of information [Source 2]. The course states that it will use code-similarity detection tools and automated plagiarism detection tools, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments.
+For programming assignments, students are instructed: "Do not submit or make use of AI generated solutions" [Source 1]. Similarly, for homework, the policy states: "Do not submit or make use of AI generated solutions" [Source 1]. For exams, students are prohibited from using "AI tools" [Source 2]. The course also notes that "code-similarity detection tools and automated plagiarism detection tools" will be used, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments.
+For programming assignments, students are instructed: "Do not submit or make use of AI generated solutions" [Source 1]. Similarly, for homework, the policy states: "Do not submit or make use of AI generated solutions" [Source 1]. For exams, students are prohibited from using "AI tools" [Source 2]. The course also notes that "code-similarity detection tools and automated plagiarism detection tools" will be used, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments.
+For programming assignments, students are instructed: "Do not submit or make use of AI generated solutions" [Source 1]. Similarly, for homework, the policy states: "Do not submit or make use of AI generated solutions" [Source 1]. For exams, students are prohibited from using "AI tools" [Source 2]. The course also notes that "code-similarity detection tools and automated plagiarism detection tools" will be used, and if a tool flags a submission, it will be treated as a potential violation [Source 2].</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy regarding the use of AI tools or generative AI for assignments and exams.
+For programming assignments and homework, students are explicitly told: "Do not submit or make use of AI generated solutions" [Source 1].
+For exams, AI tools are listed as disallowed sources of information [Source 2].</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments and exams.
+For programming assignments, students are explicitly told: "Do not submit or make use of AI generated solutions" [Source 1]. Similarly, for homework, the policy states: "Do not submit or make use of AI generated solutions" [Source 1]. For exams, students are not allowed to use "AI tools" as sources of information [Source 2].
+The course emphasizes that the solution handed in must be the student's own work, and using any part developed by others, including AI, is prohibited [Source 1]. The course will use code-similarity detection tools and automated plagiarism detection tools, and any flagged submission will be treated as a potential violation and reported to the Aggie Honor System Office [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Yes, CSCE 611 has an explicit policy on the use of AI tools or generative AI for assignments and exams.
+For programming assignments, students are explicitly told: "Do not submit or make use of AI generated solutions" [Source 1]. Similarly, for homework, the policy states: "Do not submit or make use of AI generated solutions" [Source 1]. For exams, students are not allowed to use "AI tools" as sources of information [Source 2].
+The course emphasizes that the solution handed in must be the student's own work, and using any part developed by others, including AI, is prohibited [Source 1]. The course will use code-similarity detection tools and automated plagiarism detection tools, and any flagged submission will be treated as a potential violation and reported to the Aggie Honor System Office [Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6468,6 +10675,41 @@
       <c r="R46" t="inlineStr">
         <is>
           <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 3]. Knowledge of UNIX and C programming is helpful but not required [Source 1].</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, homework submissions must compile in Visual Studio 2022 [Source 3]. Knowledge of UNIX and C programming is helpful, but not required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>For CSCE 612 assignments, all homework submissions must compile in Visual Studio 2022 [Source 3]. Knowledge of UNIX and C programming is helpful, but not required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>For CSCE 612 assignments, all homework submissions must compile in Visual Studio 2022 [Source 3]. Knowledge of UNIX and C programming is helpful, but not required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>For CSCE 612, homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 5]. Knowledge of UNIX and C programming is helpful, but not required [Source 1, 3].</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>For CSCE 612 assignments, all homework submissions must compile in Visual Studio 2022 [Source 3]. Knowledge of UNIX and C programming is helpful, but not required [Source 1, 2].</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>For CSCE 612 assignments, all homework submissions must compile in Visual Studio 2022 in both debug and release mode [Source 4, 2]. Solutions with missing files, incorrect project options, or dependency on non-standard libraries (e.g., boost) will not be graded [Source 4, 2]. Knowledge of UNIX and C programming is helpful, but not required [Source 1, 3]. The use of AI, copilot, or LLMs is prohibited and will be treated as cheating [Source 2].</t>
         </is>
       </c>
     </row>
@@ -6536,6 +10778,178 @@
 **CSCE 638**: Not found.</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>The context does not provide information on which course is more math-heavy.
+| Course | Grading | Workload | Prerequisites |
+| :----- | :------ | :------- | :------------ |
+| CSCE 638 | Not found | Not found | Not found |
+| CSCE 670 | Not found | Not found | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 3] |
+## Detailed Comparison
+### Course Overview
+**CSCE 638**: This course focuses on the fundamentals and techniques of Natural Language Processing (NLP). It covers language models, automatic syntactic processing, semantic understanding, and introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: This course covers the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms of information storage and retrieval systems, including techniques to design and evaluate complete retrieval systems. Topics include algorithms for indexing, compressing, and querying very large collections [Source 1].
+### Prerequisites
+**CSCE 638**: Not found.
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603 or approval of the instructor, along with graduate classification [Source 1, 3].
+### Learning Outcomes
+**CSCE 638**: Upon completion, learners will be able to identify and explain key concepts and models for natural language processing and be aware of recent trends in NLP research [Source 2].
+**CSCE 670**: Upon completion, learners will be able to:
+*   Define and explain key concepts and models relevant to web search (e.g., text indexing, retrieval models, evaluation, Web crawling, PageRank, learning to rank) [Source 3].
+*   Define and explain key concepts and models relevant to recommender systems (e.g., collaborative filtering, matrix factorization, evaluation, implicit recommendation) [Source 3].
+*   Design, implement, and evaluate core algorithms for fully functional web search and recommendation systems [Source 3].
+*   Identify salient features and apply recent research results in web search and recommender systems, including adversarial information retrieval and neural models [Source 3].
+### Topics
+**CSCE 638**: The course covers NLP fundamentals including language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: The course schedule includes topics such as:
+*   Boolean Retrieval, TF-IDF, Vector Space Model, BM25 [Source 5].
+*   Link Analysis, Evaluation of Search Engines, Learning to Rank [Source 5].
+*   Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking) [Source 5].
+*   word2vec, Neural Ranking, Transformer, BERT-Based Ranking [Source 5].
+*   Neural Collaborative Filtering, Sequential Recommendation [Source 5].
+*   Large Language Models Basics, Large Language Models with Search Engines, Large Language Models for Ranking and Recommendation [Source 5].
+### Materials
+**CSCE 670**: An optional textbook is "Mining of Massive Datasets" by Jure Leskovec, Anand Rajaraman, and Jeffrey D. Ullman, published in 2014 [Source 3].</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Here's a comparison of CSCE 638 and CSCE 670:
+| Course | Grading | Workload | Prerequisites |
+| :------ | :-------- | :--------- | :------------ |
+| CSCE 638 | Not found | Not found | Not found |
+| CSCE 670 | Not found | Not found | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1] |
+## Detailed Comparison
+### Course Overview
+The context does not explicitly state which course is more "math-heavy."
+**CSCE 638**: This course primarily focuses on the fundamentals of Natural Language Processing (NLP), including language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: This course primarily covers the representation, storage, and access of very large multimedia document collections. It delves into the fundamental data structures and algorithms used in information storage and retrieval systems, as well as techniques for designing and evaluating complete retrieval systems. Topics include algorithms for indexing, compressing, and querying large collections [Source 1].
+### Prerequisites
+**CSCE 638**: Not found.
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603, or approval of the instructor, along with graduate classification [Source 1].</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Here's a comparison of CSCE 638 and CSCE 670:
+| Course | Grading | Workload | Prerequisites |
+| :----- | :------ | :------- | :------------ |
+| CSCE 638 | Assignments (0-3), Quizzes (1-4), Project (Proposal, Presentation, Report) [Source 5] | 4 assignments, 4 quizzes, 3 project deliverables [Source 5] | Not found |
+| CSCE 670 | Homeworks (0-4), Quizzes (1-2), Research Project [Source 3, 4] | 5 homeworks, 2 quizzes, 1 research project [Source 3, 4] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 6] |
+## Detailed Comparison
+### Course Overview
+**CSCE 638**: This course focuses on Natural Language Processing (NLP) fundamentals, including language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: This course covers information storage and retrieval, including the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms for information storage and retrieval systems, and techniques to design and evaluate complete retrieval systems. Topics include algorithms for indexing, compressing, and querying large collections [Source 1].
+### Math-Heavy Comparison
+Both courses involve significant mathematical and algorithmic concepts due to their focus on advanced computational models and systems.
+**CSCE 638**: This course is inherently math-heavy as it covers "Machine Learning Basics" and various neural network architectures like Convolutional Neural Networks, Recurrent Neural Networks, Transformers, and Large Language Models [Source 5]. These topics rely heavily on linear algebra, calculus, probability, and optimization techniques.
+**CSCE 670**: This course is also math-heavy, explicitly mentioning "fundamental data structures and algorithms" and "algorithms for indexing, compressing, and querying" [Source 1]. It covers "retrieval models," "link-based algorithms like PageRank," "matrix factorization," and "neural models" [Source 6]. The prerequisite of CSCE 310 or CSCE 603 (Data Structures and Algorithms) further indicates a strong algorithmic and mathematical foundation is expected [Source 1, 6].
+It is difficult to definitively state which is *more* math-heavy without more specific detail on the depth of mathematical treatment in each, but both require a strong background in computational mathematics and algorithms. CSCE 638's focus on modern deep learning architectures implies a heavy reliance on linear algebra and optimization, while CSCE 670's focus on algorithms and data structures for retrieval implies a strong foundation in discrete mathematics and algorithm analysis.
+### Grading &amp; Workload
+**CSCE 638**: The course includes Assignments (Assignment 0, 1, 2, 3), Quizzes (Quiz 1, 2, 3, 4), and a Course Project with a Proposal, Presentation, and Report. Late submissions for Assignments 1-3, Project Proposal, and Project Report incur penalties: 10% for 1 day late, up to 100% for 5 or more days late. Assignment 0 and Project Presentation do not allow late submissions [Source 5].
+**CSCE 670**: The course involves Homeworks (Homework 0, 1, 2, 3, 4), Quizzes (Quiz 1, 2), and a research project [Source 3, 4]. Students receive five late days total for homeworks, with each late day being an indivisible 24-hour unit. Once these late days are used, late assignments receive a grade of 0 [Source 3, 4].
+### Prerequisites
+**CSCE 638**: Not found.
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603 or approval of the instructor, along with graduate classification [Source 1, 6].
+### Learning Outcomes
+**CSCE 638**: Upon completion, learners will be able to identify and explain the fundamental concepts and models for natural language processing and be aware of recent trends in NLP research [Source 2].
+**CSCE 670**: Upon completion, learners will be able to define and explain key concepts and models for web search (e.g., text indexing, retrieval models, evaluation, PageRank, learning to rank) and recommender systems (e.g., collaborative filtering, matrix factorization). They will also be able to design, implement, and evaluate core algorithms for web search and recommendation systems, and apply recent research results in these areas, including neural models [Source 6].
+### Topics
+**CSCE 638**: Topics include Machine Learning Basics, Word Representations, Language Modeling, Convolutional Neural Networks, Recurrent Neural Networks, Sequential Labeling, Sequence-to-Sequence, Attention, Transformers, Contextualized Representations, Pre-Training, Large Language Models, Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation, Instruction Tuning, Alignment, Post-Training, Large Reasoning Models, Test-Time Scaling, Decoding, Text Similarity, Retrieval-Augmented Generation, Agents, Multilingual Language Models, Vision-Language Models, Adversarial Attack and Defense, AI-Generated Text Detection, Non-Autoregressive Generation, Bias Mitigation, and Hallucinations [Source 5].
+**CSCE 670**: Topics include Course Overview, Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Evaluation of Search Engines, Learning to Rank, Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking), word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, Large Language Models (Basics, with Search Engines, for Ranking and Recommendation), and Project Presentations [Source 3].</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|:-------|:--------|:---------|:--------------|
+| CSCE 638 | Not found | 4 Assignments, 4 Quizzes, Course Project (Proposal, Presentation, Report) [Source 5] | Not found |
+| CSCE 670 | Not found | 5 Homeworks, 2 Quizzes, Research Project [Source 3, 4] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 6] |
+## Detailed Comparison
+### Course Overview
+**CSCE 638**: This course focuses on Natural Language Processing (NLP) fundamentals, including language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: This course covers Information Storage and Retrieval, including the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms of information storage and retrieval systems, as well as techniques to design and evaluate complete retrieval systems, with a focus on algorithms for indexing, compressing, and querying large collections [Source 1].
+### Math-Heavy Comparison &amp; Primary Coverage
+Both CSCE 638 and CSCE 670 involve significant algorithmic and model-based content, which inherently relies on mathematical concepts. The context does not explicitly state which course is "more math-heavy," but both delve into areas with strong mathematical foundations.
+**CSCE 638**: Primarily covers Natural Language Processing (NLP) [Source 2]. Its topics include various neural network architectures like Convolutional Neural Networks (CNN), Recurrent Neural Networks (RNN), and Transformers, as well as Large Language Models (LLMs), which are mathematically intensive [Source 5]. Other topics include word representations, language modeling, sequential labeling, attention mechanisms, contextualized representations, parameter-efficient fine-tuning, model distillation, instruction tuning, alignment, large reasoning models, text similarity, retrieval-augmented generation, and bias mitigation [Source 5].
+**CSCE 670**: Primarily covers Information Storage and Retrieval [Source 1]. Its topics include models and algorithms such as TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, and various Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking). It also covers neural ranking, Transformers, BERT-Based Ranking, and the application of Large Language Models to search engines, ranking, and recommendation [Source 3]. The course emphasizes designing, implementing, and evaluating core algorithms for web search and recommendation systems [Source 6].
+### Grading &amp; Workload
+**CSCE 638**: The workload includes 4 assignments, 4 quizzes, and a course project which involves a proposal, presentation, and report. A late work policy is in place for assignments and the project, with penalties ranging from 10% for 1 day late to 100% for 5 or more days late. Assignment 0 and the project presentation do not allow late submissions [Source 5]. Specific grading percentages are not provided.
+**CSCE 670**: The workload includes 5 homework assignments, 2 quizzes, and a research project [Source 3, 4]. Students are granted five late days total for homeworks, with each late day being an indivisible 24-hour unit. Once these late days are used, late assignments receive a grade of 0 [Source 3, 4]. Homeworks are individual assignments, but discussion of approaches is encouraged, with strict rules against sharing code or pair programming [Source 4]. A regrade policy allows seven days to request a regrade with a written explanation [Source 4]. Specific grading percentages are not provided.
+### Prerequisites
+**CSCE 638**: Prerequisites are not found in the provided context.
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603 or approval of the instructor, along with graduate classification [Source 1, 6].
+### Learning Outcomes
+**CSCE 638**: Upon completion, learners will be able to identify and explain the fundamental concepts and models for natural language processing and be aware of recent trends in NLP research [Source 2].
+**CSCE 670**: Upon completion, learners will be able to define and explain key concepts and models for web search (e.g., text indexing, retrieval models, evaluation, PageRank, learning to rank) and recommender systems (e.g., collaborative filtering, matrix factorization, evaluation). They will also be able to design, implement, and evaluate core algorithms for web search and recommendation systems, and apply recent research results in these areas, including neural models [Source 6].
+### Topics
+**CSCE 638**: Topics include Machine Learning Basics, Word Representations, Language Modeling, Convolutional Neural Networks, Recurrent Neural Networks, Sequential Labeling, Sequence-to-Sequence, Attention, Transformers, Contextualized Representations, Pre-Training, Large Language Models, Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation, Instruction Tuning, Alignment, Post-Training, Large Reasoning Models, Test-Time Scaling, Decoding, Text Similarity, Retrieval-Augmented Generation, Agents, Multilingual Language Models, Vision-Language Models, Adversarial Attack and Defense, AI-Generated Text Detection, Non-Autoregressive Generation, Bias Mitigation, and Hallucinations [Source 5].
+**CSCE 670**: Topics include Course Overview, Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Evaluation of Search Engines, Learning to Rank, Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking), word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, Large Language Models (Basics, with Search Engines, for Ranking and Recommendation), and Project Presentations [Source 3].</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Here's a comparison of CSCE 638 and CSCE 670:
+| Course | Grading | Workload | Prerequisites |
+| :----- | :------ | :------- | :------------ |
+| CSCE 638 | Not found | Not found | Not found |
+| CSCE 670 | Not found | Not found | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 5] |
+## Detailed Comparison
+### Course Overview
+**CSCE 638**: This course focuses on Natural Language Processing (NLP) foundations and techniques. It covers NLP fundamentals such as language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications like information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2]. Topics include Machine Learning Basics, various neural network architectures (CNN, RNN, Transformers), contextualized representations, pre-training, Large Language Models (LLMs), parameter-efficient fine-tuning, model distillation, evaluation, instruction tuning, alignment, post-training, large reasoning models, text similarity, Retrieval-Augmented Generation, agents, multilingual and vision-language models, adversarial attacks, AI-generated text detection, non-autoregressive generation, bias mitigation, and hallucinations [Source 6].
+**CSCE 670**: This course is about Information Storage and Retrieval. It covers the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms for information storage and retrieval systems, as well as techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying large collections [Source 1]. Key topics include Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Evaluation of Search Engines, Learning to Rank, Recommender Systems (Content-Based, Collaborative Filtering, Matrix Factorization, Bayesian Personalized Ranking), word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, and Large Language Models (basics, with search engines, for ranking and recommendation) [Source 3].
+### Mathematical Intensity
+The provided context does not explicitly state which course is "more math-heavy." However, based on the topics covered, both courses involve advanced algorithmic and model-based concepts that typically have significant mathematical underpinnings.
+**CSCE 638**: This course covers topics like Language Modeling, Convolutional Neural Networks, Recurrent Neural Networks, Transformers, and Large Language Models [Source 6]. These concepts are built upon mathematical frameworks from linear algebra, calculus, probability, and optimization, which are fundamental to understanding their internal workings and theoretical guarantees.
+**CSCE 670**: This course covers "fundamental data structures and algorithms" [Source 1], and specific models like TF-IDF, Vector Space Model, BM25, Link Analysis, Learning to Rank, Matrix Factorization, Bayesian Personalized Ranking, word2vec, Neural Ranking, Transformer, and BERT-Based Ranking [Source 3]. These topics also rely heavily on mathematical concepts, including linear algebra, probability, statistics, and optimization, for their design, analysis, and evaluation.</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| **CSCE 638** | Assignments (0-3), Quizzes (1-4), Project (Proposal, Presentation, Report) [Source 5] | Assignments, Quizzes, Course Project [Source 5] | Not found |
+| **CSCE 670** | Homeworks, Research project [Source 4] | Homeworks, Research project [Source 4] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1, 3] |
+## Detailed Comparison
+### Course Overview
+**CSCE 638**: This course focuses on Natural Language Processing (NLP) fundamentals, including language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: This course covers information storage and retrieval, specifically the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms for information storage and retrieval systems, and techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying large collections [Source 1].
+### Grading &amp; Workload
+**CSCE 638**: The course includes Assignment 0, Assignment 1, Assignment 2, Assignment 3, Quiz 1, Quiz 2, Quiz 3, Quiz 4, a Project Proposal, Project Presentation, and a Project Report. Late submissions for Assignments 1-3, Project Proposal, and Project Report incur penalties (10% for 1 day late, up to 100% for 5 or more days late). Assignment 0 and Project Presentation do not allow late submissions [Source 5].
+**CSCE 670**: The workload includes homework assignments and a research project. Homeworks are individual assignments, but students are encouraged to discuss approaches. Each student receives five late days for homeworks, with a late day being an indivisible 24-hour unit [Source 4].
+### Prerequisites
+**CSCE 638**: Not found.
+**CSCE 670**: Prerequisites are CSCE 310 or CSCE 603 or approval of the instructor, and graduate classification [Source 1, 3].
+### Learning Outcomes
+**CSCE 638**: Upon completion, learners will be able to identify and explain fundamental concepts and models for natural language processing and be aware of recent trends in NLP research [Source 2].
+**CSCE 670**: Upon completion, learners will be able to define and explain key concepts and models relevant to web search (e.g., text indexing, retrieval models, PageRank, learning to rank) and recommender systems (e.g., collaborative filtering, matrix factorization). They will also be able to design, implement, and evaluate core algorithms for web search and recommendation systems, and apply recent research results in these areas, including adversarial information retrieval and neural models [Source 3].
+### Topics
+**CSCE 638**: Topics include Overview and Machine Learning Basics, Word Representations, Language Modeling, Convolutional Neural Network, Recurrent Neural Network, Transformers, Contextualized Representations, Pre-Training, Large Language Models, Parameter-Efficient Fine-Tuning, Model Distillation, Evaluation, Instruction Tuning, Alignment, Post-Training, Large Reasoning Models, Test-Time Scaling, Decoding, Text Similarity, Retrieval-Augmented Generation, Agents, Multilingual Language Models, Vision-Language Models, Adversarial Attack and Defense, AI-Generated Text Detection, Non-Autoregressive Generation, Bias Mitigation, and Hallucinations [Source 5].
+**CSCE 670**: Topics include web search concepts (text indexing, retrieval models, evaluation, Web crawling, link-based algorithms like PageRank, learning to rank) and recommender systems concepts (collaborative filtering, matrix factorization, evaluation, implicit recommendation). It also covers recent research in adversarial information retrieval and neural models of retrieval and recommendation [Source 3].
+### Math-Heaviness and Primary Coverage
+Both courses involve significant algorithmic and model-based understanding, which typically implies a mathematical foundation.
+**CSCE 638**: Primarily covers Natural Language Processing (NLP). Its topics include various neural network architectures (Convolutional, Recurrent, Transformers), Large Language Models, and techniques like Parameter-Efficient Fine-Tuning and Retrieval-Augmented Generation [Source 5]. These areas rely heavily on linear algebra, calculus, and probability/statistics for understanding and implementing the underlying models and algorithms.
+**CSCE 670**: Primarily covers Information Storage and Retrieval, with a focus on web search and recommender systems. It involves "fundamental data structures and algorithms," "algorithms for indexing, compressing, and querying," and specific algorithms like PageRank, collaborative filtering, and matrix factorization, as well as neural models [Source 1, 3]. These topics also require a strong grasp of algorithms, data structures, and mathematical concepts, particularly in areas like graph theory (for PageRank), linear algebra (for matrix factorization), and optimization.
+Based on the descriptions, both courses involve complex algorithms and models, suggesting a substantial mathematical component. The context does not explicitly state which course is "more math-heavy."</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 638 | Not found | Not found | Not found |
+| CSCE 670 | Not found | Homework late day policy: Each student gets five late days total. A late day is an indivisible 24-hour unit. [Source 3] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1] |
+## Detailed Comparison
+### Course Overview
+**CSCE 638**: This course focuses on teaching Natural Language Processing (NLP) fundamentals, including language models, automatic syntactic processing, and semantic understanding. It also introduces major NLP applications such as information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 2].
+**CSCE 670**: This course covers the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms of information storage and retrieval systems, as well as techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying very large collections [Source 1].
+### Math-Heaviness
+The provided context does not contain information to determine which course, CSCE 638 or CSCE 670, is more math-heavy.
+### Prerequisites
+**CSCE 638**: Not found.
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603 or approval of the instructor, along with graduate classification [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6569,6 +10983,41 @@
           <t>No relevant documents found.</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>No relevant documents found.</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>No relevant documents found.</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>No relevant documents found.</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>No relevant documents found.</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>No relevant documents found.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6598,6 +11047,41 @@
         <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Not found.</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -6646,6 +11130,137 @@
     *   This course emphasizes how systems interpret sketches and how recognition algorithms behave in real-world settings. It mentions that familiarity with basic machine learning or artificial intelligence concepts can be helpful [Source 5].</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses involve machine learning or artificial intelligence:
+*   **CSCE 726: Large-scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning problems, including deterministic and stochastic gradient-based algorithms. It emphasizes the role of large-scale optimization in ML and AI [Source 3, 9]. Students will need basic knowledge of machine learning and deep learning, including methods like linear regression, logistic regression, support vector machines, and regularization [Source 1, 9].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that acquire new knowledge and improve performance. It surveys machine learning techniques such as induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 4].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots, focusing on biological and cognitive principles for unmanned systems. Learning outcomes include understanding core concepts in robotic autonomy, state estimation, planning, control, and decision-making under uncertainty [Source 8].
+*   **CSCE 670: Information Retrieval and Recommender Systems**
+    *   This course involves topics like text indexing, retrieval models, evaluation, Web crawling, link-based algorithms (e.g., PageRank), learning to rank, collaborative filtering, matrix factorization, and recommender system evaluation. It also covers recent research results, including neural models of retrieval and recommendation [Source 6].
+*   **CSCE 676: Data Mining and Analysis**
+    *   This course offers a broad overview of data mining, integrating concepts from machine learning and statistics. Topics include exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data [Source 10].
+*   **CSCE 679: Data Visualization**
+    *   While not solely focused on ML/AI, this course discusses the role of data visualization in Explainable AI (XAI) and involves programming in Python for data and AI [Source 7].
+*   **CSCE 624: Sketch Recognition**
+    *   This course emphasizes how systems interpret sketches and how recognition algorithms behave in real-world, noisy settings. It involves hands-on implementation of recognition techniques and assumes familiarity with basic machine learning or artificial intelligence concepts is helpful [Source 5].</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following CSCE graduate courses involve Machine Learning or Artificial Intelligence:
+*   **CSCE 726: Large-scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning and artificial intelligence problems. It covers deterministic and stochastic gradient-based algorithms, adaptive gradient-based methods, and momentum-based methods, with applications to real-world ML/AI problems [Source 3, 9]. Students are expected to have basic knowledge of machine learning and deep learning [Source 1, 9].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that acquire new knowledge and improve performance. It surveys machine learning techniques including induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 4].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots, focusing on biological and cognitive principles for unmanned systems. Learning outcomes include understanding core concepts in robotic autonomy, state estimation, planning, control, and decision making under uncertainty [Source 8].
+*   **CSCE 670: Information Retrieval and Recommender Systems**
+    *   This course involves topics like learning to rank and identifying salient features and applying recent research results in web search and recommender systems, including neural models of retrieval and recommendation [Source 6].
+*   **CSCE 676: Data Mining and Analysis**
+    *   This course provides a broad overview of data mining, integrating related concepts from machine learning and statistics. It covers exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data [Source 10].
+*   **CSCE 679: Data Visualization**
+    *   This course discusses the role of data visualization in Explainable AI and involves programming in Python for data and AI [Source 7].
+*   **CSCE 624: Sketch Recognition**
+    *   This course emphasizes how systems interpret sketches and how recognition algorithms behave in real-world, noisy settings. Familiarity with basic machine learning or artificial intelligence concepts is helpful but not strictly required [Source 5].</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses involve machine learning or artificial intelligence:
+*   **CSCE 726: Large-scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms for solving machine learning problems, including deterministic and stochastic gradient-based algorithms, adaptive gradient-based methods, and momentum-based methods. It also covers their application to real-world machine learning and artificial intelligence problems [Source 1]. Students will learn to name, analyze, evaluate, compare, and design optimization algorithms for ML/AI problems [Source 2].
+    *   Prerequisites include CSCE 633 or CSCE 636, or instructor approval, and graduate classification [Source 1, Source 4]. Recommended background includes proficiency in Python, PyTorch, and foundations of Machine Learning and Deep Learning [Source 4].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that can acquire new knowledge and improve their own performance. It surveys machine learning techniques such as induction from examples, conceptual clustering, explanation-based learning, exemplar learning and analogy, discovery, and genetic algorithms [Source 3].
+    *   Upon completion, students are expected to formalize the fundamental techniques and methods of machine learning [Source 3].
+*   **CSCE 635: AI Robotics**
+    *   This course introduces and surveys artificial intelligence methods for mobile robots, focusing on biological and cognitive principles [Source 5].
+    *   Prerequisite: Graduate classification [Source 5].
+*   **CSCE 670: Web Search and Recommender Systems**
+    *   This course involves topics relevant to recommender systems, including collaborative filtering, matrix factorization, and recommender system evaluation [Source 6]. It also covers identifying salient features and applying recent research results in web search and recommender systems, including neural models of retrieval and recommendation [Source 6].
+*   **CSCE 679: Data Visualization**
+    *   This course discusses the role of data visualization in Explainable AI [Source 7]. It also involves programming in Python for data and AI [Source 7].
+*   **CSCE 624: Sketch Recognition**
+    *   This course mentions basic machine learning or artificial intelligence concepts as helpful, though not strictly required, background [Source 8].
+*   **CSCE 676: Data Mining and Analysis**
+    *   This course provides a broad overview of data mining, integrating related concepts from machine learning and statistics [Source 9].</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses involve machine learning or artificial intelligence:
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning problems, including deterministic and stochastic gradient-based algorithms, adaptive gradient-based methods, and momentum-based methods. It also covers the implementation and application of these algorithms to real-world machine learning and artificial intelligence problems [Source 1]. Students will learn to name classical stochastic optimization algorithms, analyze their convergence, evaluate and compare performance, apply tuning strategies, and design new optimization algorithms for large-scale problems [Source 2]. Prerequisites include CSCE 633 or CSCE 636, or instructor approval, and graduate classification [Source 1, 4].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that can acquire new knowledge and improve their own performance. It surveys machine learning techniques such as induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 3]. Students are expected to formalize fundamental techniques and methods of machine learning [Source 3]. Prerequisites include CSCE 420 or CSCE 625 [Source 3].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots, focusing on biological and cognitive principles. It covers core concepts in robotic autonomy, including state estimation, planning, control, and decision-making under uncertainty [Source 5]. Prerequisites include graduate classification [Source 5].
+*   **CSCE 670: Web Search and Recommender Systems**
+    *   This course involves topics like learning to rank in web search and recommender systems [Source 6].
+*   **CSCE 679: Data Visualization**
+    *   This course discusses the role of data visualization in Explainable AI [Source 7].
+*   **CSCE 624: Sketch Recognition**
+    *   This course mentions basic machine learning or artificial intelligence concepts as helpful background, though not strictly required [Source 8].
+*   **CSCE 676: Data Mining and Analysis**
+    *   This course provides a broad overview of data mining, integrating related concepts from machine learning and statistics [Source 9].</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following CSCE graduate courses involve Machine Learning or Artificial Intelligence:
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning problems. It covers advanced machine learning methods and stochastic gradient-based algorithms, and students will implement these for real-world ML/AI problems [Source 3, 9]. It also lists "Some Foundations of Machine Learning and Deep Learning" as recommended background [Source 1, 2].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that acquire new knowledge and improve performance, surveying machine learning techniques such as induction from examples, conceptual clustering, and genetic algorithms [Source 4]. Students are expected to formalize, analyze, and apply various advanced machine learning algorithms [Source 10].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots, focusing on biological and cognitive principles [Source 5].
+*   **CSCE 624: Sketch Recognition**
+    *   While not exclusively ML/AI, this course mentions that familiarity with basic machine learning or artificial intelligence concepts is helpful, though not strictly required [Source 8].
+*   **CSCE 679: Data Visualization**
+    *   This course discusses the role of data visualization in Explainable AI and involves programming in Python for data and AI [Source 7].
+**Planning Dimension:**
+For students interested in Machine Learning or Artificial Intelligence, CSCE 633 serves as a foundational course in the field. CSCE 726 builds upon this foundation by focusing on the optimization techniques critical for large-scale ML/AI problems. CSCE 635 offers a specialized application of AI in robotics. CSCE 624 and CSCE 679 incorporate ML/AI concepts as part of their broader topics, providing opportunities to see these principles applied in specific domains like sketch recognition and data visualization.</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following CSCE graduate courses involve Machine Learning or Artificial Intelligence:
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning problems. It covers advanced machine learning methods and stochastic gradient-based algorithms, and students will implement these for real-world ML/AI problems [Source 3, 9]. Large-scale optimization plays an important role in machine learning (ML) and artificial intelligence (AI) [Source 3, 9].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that can acquire new knowledge and improve their performance, surveying machine learning techniques such as induction from examples, conceptual clustering, and genetic algorithms [Source 4]. Students are expected to formalize, analyze, evaluate, design, implement, and apply various advanced machine learning algorithms [Source 10].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots, focusing on biological and cognitive principles [Source 5].
+*   **CSCE 624: Sketch Recognition**
+    *   While not exclusively ML/AI, this course mentions that familiarity with basic machine learning or artificial intelligence concepts will be helpful, though not strictly required [Source 8]. It involves hands-on implementation of recognition techniques and understanding how recognition algorithms behave [Source 8].
+*   **CSCE 679: Data Visualization**
+    *   This course discusses the role of data visualization in Explainable AI [Source 7]. It also involves programming in Python for data and AI [Source 7].
+**Planning Dimension:**
+For students planning their academic progression, CSCE 633 (Machine Learning) is a foundational course, often serving as a prerequisite or recommended background for more specialized courses like CSCE 726 (Large-Scale Optimization for Machine Learning) [Source 1, 2]. CSCE 726 also lists CSCE 636 (Deep Learning) as a recommended background course, indicating a progression in specialized ML/AI topics [Source 2]. Courses like CSCE 635 (AI Robotics) and CSCE 679 (Data Visualization) apply ML/AI concepts to specific domains, while CSCE 624 (Sketch Recognition) can benefit from a basic understanding of ML/AI.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Based on the provided context, here are the CSCE graduate courses that involve machine learning or artificial intelligence:
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    *   This course focuses on fundamental optimization algorithms and their analysis for solving machine learning problems. It covers advanced machine learning methods and algorithms, and students will implement them to solve real-world ML/AI problems [Source 3, 9]. It also mentions that large-scale optimization plays an important role in machine learning (ML) and artificial intelligence (AI) [Source 3, 9].
+*   **CSCE 633: Machine Learning**
+    *   This course is the study of self-modifying computer systems that can acquire new knowledge and improve their performance, surveying machine learning techniques [Source 4]. Students are expected to formalize, analyze, and apply various advanced machine learning algorithms [Source 10].
+*   **CSCE 635: AI Robotics**
+    *   This course provides an introduction and survey of artificial intelligence methods for mobile robots [Source 5].
+*   **CSCE 670: Web Search and Recommender Systems**
+    *   This course involves concepts relevant to recommender systems, including collaborative filtering and matrix factorization, and identifying recent research results in web search and recommender systems, including neural models of retrieval and recommendation [Source 6].
+*   **CSCE 679: Data Visualization**
+    *   This course discusses the role of data visualization in Explainable AI and involves programming in Python for data and AI [Source 7].
+*   **CSCE 624: Sketch Recognition**
+    *   Familiarity with basic machine learning or artificial intelligence concepts is helpful for this course [Source 8].
+For academic planning, students interested in machine learning or artificial intelligence should consider CSCE 633 as a foundational course, as it is a prerequisite for CSCE 726 [Source 1, 3, 4]. CSCE 726 builds upon this foundation by focusing on optimization techniques crucial for large-scale ML/AI problems [Source 3, 9]. Other courses like CSCE 635, CSCE 670, CSCE 679, and CSCE 624 offer specialized applications or related concepts within the broader fields of AI and ML.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6682,6 +11297,107 @@
     *   **Academic Dimension:** This course delves into "Combinatorial theory of polytopes as a tool for the solution of combinatorial optimization problems; applications to max flow, matching and matroids; geometric interpretation of the results indicating the profound role that polyhedral combinatorics play in the design and complexity of approximation algorithms" [Source 10].
     *   **Learning Outcomes:** Students are expected to "Master basic theories and techniques in the current research in computational optimization" and "apply theories and techniques studied in the course to solve real-world problems" [Source 10]. The emphasis on "combinatorial theory," "polyhedral combinatorics," and "complexity of approximation algorithms" places this course firmly within theoretical computer science and formal methods for optimization.
 While CSCE 633 (Machine Learning) mentions the ability to "formalize the fundamental techniques and methods of machine learning" [Source 3], its primary focus as described is on surveying machine learning techniques rather than the foundational mathematical logic or abstract models typically associated with a dedicated formal methods or theoretical computer science course.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>The principle of "formal methods" in computer science involves the application of rigorous mathematical techniques and tools for the specification, design, and verification of software and hardware systems. "Theoretical computer science" encompasses the study of fundamental concepts of computation, algorithms, data structures, complexity theory, and the limits of computation.
+Based on the provided context, the following CSCE courses cover topics related to formal methods or theoretical computer science:
+*   **CSCE 629: Analysis of Algorithms**
+    *   **Academic Dimension:** This course focuses on concrete algorithm design and analysis, abstract models to analyze the complexity of problems, NP-Completeness, approximation, and probabilistic algorithms. Students are expected to analyze the correctness, runtime, and space complexity of algorithms, and recognize when a problem is likely intractable by proving undecidability or NP-hardness [Source 2, 6].
+    *   **Relevance to Formal Methods/Theoretical CS:** The emphasis on algorithm correctness, runtime, space complexity analysis, NP-Completeness, and proofs of intractability directly aligns with theoretical computer science and the rigorous analysis characteristic of formal methods.
+*   **CSCE 669: Computational Optimization**
+    *   **Academic Dimension:** This course delves into the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems, with applications to max flow, matching, and matroids. It also covers the geometric interpretation of results and the role of polyhedral combinatorics in the design and complexity of approximation algorithms. Students will master basic theories and techniques in computational optimization [Source 10].
+    *   **Relevance to Formal Methods/Theoretical CS:** The course's focus on combinatorial theory, polyhedral combinatorics, and the complexity of approximation algorithms places it firmly within theoretical computer science, utilizing formal mathematical structures to analyze and solve optimization problems.
+While **CSCE 633: Machine Learning** mentions "formalize the fundamental techniques and methods of machine learning" in its learning outcomes, its catalog description primarily focuses on the study of self-modifying computer systems and various machine learning techniques, which leans more towards applied machine learning rather than core theoretical computer science or formal methods in the traditional sense [Source 3].</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following CSCE courses cover formal methods or theoretical computer science topics:
+*   **CSCE 629: Analysis of Algorithms**
+    *   **Principle/Framework**: This course focuses on the fundamental principles of algorithm design and analysis, including the theoretical limits of computation. It delves into complexity theory, which is a core area of theoretical computer science.
+    *   **Academic Content**:
+        *   **Catalog Description**: Covers "Concrete algorithm design and analysis; abstract models to analyze the complexity of problems; NP-Completeness; approximation and probabilistic algorithms" [Source 3].
+        *   **Learning Outcomes**: Students will learn to "Analyze the correctness, runtime, and space complexity of an algorithm," "Design new algorithms and modify existing ones," and "Recognize when a problem is likely intractable (has no efficient algorithm) and be able to prove this by showing undecidability or NP-hardness" [Source 1, 3].
+        *   **Topics Covered**: The weekly schedule includes "Lower Bounds," "Divide and Conquer," "Greedy Algorithms," "Dynamic Programming," "Amortized Analysis," "Graph Algorithms," "Randomized Algorithms," "NP Completeness," "Approximation Algorithms," and "Undecidability" [Source 4].
+*   **CSCE 669**
+    *   **Principle/Framework**: This course explores advanced algorithmic techniques and the theoretical underpinnings of computational complexity, particularly concerning intractable problems and methods to address them.
+    *   **Academic Content**:
+        *   **Topics Covered**: The course schedule lists "Algorithmic background review," "Maximum flow and graph matching," "Linear programming," "NP-completeness theory and approximation algorithms," "Approximation algorithms: FPTAS algorithms," "Approximation algorithms: PTAS algorithms," "Inapproximability results, PCP theorem," and "Parameterized algorithms" [Source 6].
+Other courses like CSCE 611 (Operating Systems) and CSCE 612 (Applied Networks and Distributed Processing) focus on more applied aspects of computer science [Source 7, 8]. CSCE 681 (Seminar) is for discussing research but does not inherently teach specific theoretical topics [Source 2].</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>The terms "formal methods" and "theoretical computer science topics" refer to the mathematical foundations of computing, including areas like algorithm analysis, computational complexity theory, computability theory, logic, automata theory, and formal verification. Formal methods involve using mathematical techniques for the specification, development, and verification of software and hardware systems, while theoretical computer science explores the fundamental limits and capabilities of computation.
+Based on the provided context, the following CSCE courses cover formal methods or theoretical computer science topics:
+*   **CSCE 629: Analysis of Algorithms**
+    *   **Academic Dimension:** This course focuses on the concrete design and analysis of algorithms, utilizing abstract models to analyze problem complexity. Key topics include NP-Completeness, approximation algorithms, and probabilistic algorithms [Source 1]. Students will learn to analyze the correctness, runtime, and space complexity of algorithms, and recognize when a problem is intractable, proving this through undecidability or NP-hardness [Source 4].
+    *   **Relevance:** Directly addresses theoretical computer science through algorithm analysis, complexity theory, and computability.
+*   **CSCE 669: Computational Optimization**
+    *   **Academic Dimension:** This course delves into the combinatorial theory of polytopes as a tool for solving combinatorial optimization problems. It covers applications such as max flow, matching, and matroids, and explores the geometric interpretation of results, highlighting the role of polyhedral combinatorics in the design and complexity of approximation algorithms [Source 6].
+    *   **Relevance:** Strongly aligns with theoretical computer science, particularly in the areas of combinatorial optimization, graph theory, and the complexity analysis of algorithms.</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>The principle for identifying courses covering formal methods or theoretical computer science topics involves looking for course descriptions and learning outcomes that emphasize the abstract study of computation, algorithms, complexity, logic, and mathematical structures relevant to computer science.
+Based on the provided context, the following CSCE courses cover formal methods or theoretical computer science topics:
+*   **CSCE 629: Analysis of Algorithms**
+    *   This course focuses on "concrete algorithm design and analysis," "abstract models to analyze the complexity of problems," "NP-Completeness," and "approximation and probabilistic algorithms" [Source 1].
+    *   Learning outcomes include the ability to "analyze the correctness, runtime, and space complexity of an algorithm" and "recognize when a problem is likely intractable (has no efficient algorithm) and be able to prove this by showing undecidability or NP-hardness" [Source 1, 4]. These topics are central to theoretical computer science and formal methods.
+*   **CSCE 669: Computational Optimization**
+    *   The catalog description highlights "combinatorial theory of polytopes as a tool for the solution of combinatorial optimization problems" and discusses "polyhedral combinatorics play in the design and complexity of approximation algorithms" [Source 6].
+    *   Learning outcomes include mastering "basic theories and techniques in the current research in computational optimization" [Source 6]. This course delves into the theoretical underpinnings of optimization and algorithm complexity.
+*   **CSCE 633: Machine Learning**
+    *   While primarily focused on techniques, one of its learning outcomes is to "formalize the fundamental techniques and methods of machine learning" [Source 2]. This suggests an academic dimension that includes understanding the theoretical and formal aspects behind machine learning algorithms.
+*   **CSCE 681: Seminar**
+    *   This course involves "reports and discussion of current research and of selected published technical articles" to "expose students to a broad range of current and seminal research topics in computer science and related fields" [Source 3]. While not exclusively theoretical, it serves as a venue where formal methods and theoretical computer science research topics could be discussed.
+I don't have enough data to definitively state if other courses like CSCE 614, CSCE 652, CSCE 670, CSCE 611, or CSCE 608 cover formal methods or theoretical computer science topics in a significant way, as their descriptions lean more towards applied or systems-level content.</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>The principle for identifying courses related to "formal methods" or "theoretical computer science" involves examining course catalog descriptions, learning outcomes, and schedules for keywords associated with foundational computational concepts, algorithm analysis, complexity theory, and mathematical logic applied to computing.
+Based on the provided context, the following CSCE courses cover topics in theoretical computer science:
+*   **CSCE 629: Analysis of Algorithms**
+    *   This course focuses on concrete algorithm design and analysis, abstract models to analyze the complexity of problems, NP-Completeness, and approximation and probabilistic algorithms [Source 5].
+    *   Students will learn to analyze the correctness, runtime, and space complexity of algorithms, design new algorithms, and recognize intractable problems by proving undecidability or NP-hardness [Source 3, 5].
+    *   The required textbook is "Introduction to Algorithms" [Source 3].
+    *   **Academic Progression:** This course is foundational for understanding the efficiency and limits of computation, which is crucial for advanced studies in many computer science fields. It is also a prerequisite for CSCE 669 [Source 10].
+*   **CSCE 669: Computational Optimization**
+    *   This course explores the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids. It also delves into the design and complexity of approximation algorithms [Source 10].
+    *   Topics covered include algorithmic background, maximum flow and graph matching, linear programming, NP-completeness theory, approximation algorithms (FPTAS, PTAS, APX), inapproximability results (PCP theorem), and parameterized algorithms [Source 4].
+    *   **Academic Progression:** This course builds upon the concepts introduced in CSCE 629, as CSCE 629 is a prerequisite [Source 10]. It is suitable for students interested in advanced algorithmic design, complexity theory, and optimization techniques.</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>To identify CSCE courses covering formal methods or theoretical computer science topics, we look for course descriptions, learning outcomes, and schedules that explicitly mention areas such as algorithm analysis, complexity theory, computability, logic, proofs, verification, and mathematical foundations of computing.
+Based on the provided context, the following courses cover theoretical computer science topics:
+*   **CSCE 629: Analysis of Algorithms**
+    *   **Principle:** This course is foundational in theoretical computer science, focusing on the rigorous analysis of algorithms.
+    *   **Application:** It covers concrete algorithm design and analysis, abstract models for problem complexity, NP-Completeness, and approximation and probabilistic algorithms [Source 4]. Students learn to analyze the correctness, runtime, and space complexity of algorithms, and to recognize and prove the intractability of problems by showing undecidability or NP-hardness [Source 3].
+    *   **Planning Dimension:** This course is essential for students aiming to understand the theoretical limits and efficiency of computation and often serves as a prerequisite for more advanced theoretical courses.
+*   **CSCE 669: Computational Optimization**
+    *   **Principle:** This course delves into advanced theoretical aspects of algorithm design and complexity within the optimization domain.
+    *   **Application:** It explores the combinatorial theory of polytopes for solving combinatorial optimization problems, applications to max flow, matching, and matroids, and the design and complexity of approximation algorithms [Source 9]. The course schedule includes topics like algorithmic background review, maximum flow, graph matching, linear programming, NP-completeness theory, approximation algorithms, inapproximability results, and parameterized algorithms [Source 6].
+    *   **Planning Dimension:** This course builds upon the foundations laid in CSCE 629, as CSCE 629 is a prerequisite [Source 9]. It is suitable for students who have a solid understanding of algorithm analysis and wish to specialize in the theoretical aspects of optimization and complexity.
+I cannot find information about courses specifically covering "formal methods" (e.g., logic, verification, model checking) in the provided context.</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>To identify courses covering formal methods or theoretical computer science topics, we look for academic content related to the mathematical foundations of computing, algorithm analysis, complexity theory, computability, logic, and abstract models.
+Based on the provided context, the following CSCE courses cover formal methods or theoretical computer science topics:
+*   **CSCE 629 - Analysis of Algorithms**
+    *   **Academic Dimension:** This course focuses on concrete algorithm design and analysis, abstract models for problem complexity, NP-Completeness, and approximation and probabilistic algorithms [Source 1].
+    *   **Learning Outcomes:** Students will learn to explain fundamental algorithms, select appropriate algorithms, analyze correctness, runtime, and space complexity, design new algorithms, and recognize and prove when a problem is intractable (e.g., by showing undecidability or NP-hardness) [Source 1, 3].
+*   **CSCE 669 - Computational Optimization**
+    *   **Academic Dimension:** This course explores the combinatorial theory of polytopes for solving combinatorial optimization problems, including applications to max flow, matching, and matroids. It also covers the geometric interpretation of results in polyhedral combinatorics and their role in the design and complexity of approximation algorithms [Source 9].
+    *   **Learning Outcomes:** Students will master basic theories and techniques in computational optimization and apply them to real-world problems [Source 9].
+    *   **Topics Covered:** The course schedule includes algorithmic background review, maximum flow and graph matching, linear programming, NP-completeness theory and approximation algorithms (FPTAS, PTAS, APX), inapproximability results (PCP theorem), and parameterized algorithms [Source 10].</t>
         </is>
       </c>
     </row>
@@ -6725,6 +11441,138 @@
     *   **Academic Content**: It covers pipeline computers, vectorization methods, array processors, and multiprocessor architectures and programming [Source 2]. The schedule also lists topics like ILP (Instruction-Level Parallelism), SIMD (Single Instruction, Multiple Data), and TLP (Thread-Level Parallelism) [Source 8].</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Yes, there are CSCE courses that focus on parallel or distributed computing.
+The relevant principle here is identifying courses that cover specific computing paradigms, such as parallel processing, distributed systems, concurrency, and network-based computation. This involves examining course titles, catalog descriptions, and learning outcomes for keywords and concepts related to these areas.
+Based on the provided context, the following courses address these topics:
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    *   **Focus:** This course explicitly covers "Applied Networks and Distributed Processing" [Source 1]. It mixes fundamentals with programming and pragmatic views of engineering issues, including network architecture and principles of network engineering [Source 1].
+    *   **Learning Outcomes:** Students will be able to "create efficient network applications and build multi-threaded decentralized frameworks" [Source 4].
+    *   **Topics:** Network design, protocol analysis, computer communications, and analyzing real networks using layered architecture principles [Source 1].
+*   **CSCE 611: Operating Systems**
+    *   **Focus:** This course provides an overview of modern operating systems, including understanding fundamental approaches to virtualization and what it takes to build a distributed system [Source 3, Source 5].
+    *   **Learning Outcomes:** Students will be able to "evaluate and compare various forms of concurrency mechanisms" and "evaluate and compare and apply various synchronization mechanisms" [Source 3].
+    *   **Topics:** Process coordination and management, concurrency, thread dispatching, and synchronization [Source 5, Source 6].
+*   **CSCE 614: Computer Architecture**
+    *   **Focus:** This course reviews von Neumann architecture and its limitations, with a strong emphasis on parallel computer structures [Source 2].
+    *   **Topics:** "Parallel computer structures and concurrent computation; pipeline computers and vectorization methods; array processors, multiprocessor architectures and programming; dataflow computers" [Source 2].
+*   **CSCE 608: Database Systems**
+    *   **Focus:** While primarily about database systems, its catalog description mentions "distributed data management" as a topic [Source 7].</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University offers several CSCE courses that focus on parallel or distributed computing:
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    *   **Principle/Framework:** This course focuses on the fundamentals of network design and protocol analysis within the context of computer communications, emphasizing the application of layered architecture principles to real networks [Source 1]. It also covers the engineering issues related to distributed processing.
+    *   **Academic Content:** Topics include network architecture and engineering principles. Students will learn to utilize operating-system sockets APIs, create efficient network applications, and build multi-threaded decentralized frameworks [Source 1, 4]. Knowledge of UNIX and C programming is helpful [Source 1].
+*   **CSCE 611: Operating Systems**
+    *   **Principle/Framework:** This course provides an overview of the general architecture and components of modern operating systems, including fundamental approaches to virtualization and what is required to build a distributed system [Source 3, 5]. It covers concepts like process coordination and management, and algorithms for CPU scheduling and resource allocation [Source 5].
+    *   **Academic Content:** Key topics include memory management, persistent storage and file systems, threading, scheduling, and resource management. Students will understand the role of exception and interrupt handling, implement components of a virtual memory manager, and evaluate various concurrency and synchronization mechanisms [Source 3]. The schedule includes dedicated weeks for Concurrency, Thread Dispatching, Synchronization, and Atomic Transactions [Source 6].
+*   **CSCE 614: Computer Architecture**
+    *   **Principle/Framework:** This course reviews von Neumann architecture and its limitations, then delves into various parallel computer structures and concurrent computation methods [Source 2].
+    *   **Academic Content:** It covers pipeline computers, vectorization methods, array processors, multiprocessor architectures and programming, and dataflow computers [Source 2]. The course aims to provide students with an understanding of computer architecture with an emphasis on microprocessors [Source 2].
+*   **CSCE 608: Database Systems**
+    *   **Principle/Framework:** While primarily a database course, it includes "distributed data management" as a topic [Source 7].
+    *   **Academic Content:** Students will understand database modeling techniques, query languages, physical data organization, relational database design theory, query processing, transaction management, recovery, and distributed data management [Source 7].</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Yes, there are CSCE courses that focus on parallel or distributed computing.
+**Principle/Framework:**
+Parallel computing involves performing multiple computations simultaneously, often on multiple processors, to solve a problem faster. Distributed computing involves using multiple interconnected computers to work on a single problem, where components of the system are located on different networked computers and communicate by passing messages. Both paradigms are crucial for handling complex computational tasks and large datasets.
+**Relevant Courses:**
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    *   **Academic Dimension:** This course directly focuses on "Applied Networks and Distributed Processing." It covers fundamentals of network design and protocol analysis, mixing these with programming and engineering issues. Students will learn to apply layered architecture principles to analyze real networks and develop "multi-threaded decentralized frameworks" and efficient network applications. Knowledge of UNIX and C programming is helpful [Source 1, 4].
+    *   **Learning Outcomes:** Students will be able to utilize operating-system sockets APIs, create efficient network applications, and build multi-threaded decentralized frameworks [Source 4].
+*   **CSCE 611: Operating Systems**
+    *   **Academic Dimension:** This course provides an overview of modern operating systems, including memory management, persistent storage, file systems, threading, scheduling, and resource management. It explicitly covers understanding "what it takes to build a distributed system" and fundamental approaches to virtualization. Topics include concurrency mechanisms, synchronization mechanisms, thread dispatching, and event-based concurrency [Source 3, 5, 6].
+    *   **Learning Outcomes:** Students will be able to evaluate and compare various forms of concurrency mechanisms and apply various synchronization mechanisms [Source 3].
+*   **CSCE 614: Computer Architecture**
+    *   **Academic Dimension:** This course focuses on computer architecture with an emphasis on microprocessors. It reviews von Neumann architecture and its limitations, and delves into "parallel computer structures and concurrent computation; pipeline computers and vectorization methods; array processors, multiprocessor architectures and programming; dataflow computers" [Source 2].
+    *   **Learning Outcomes:** The main objective is for students to learn about computer architecture with an emphasis on microprocessor design [Source 2].
+*   **CSCE 608: Database Systems**
+    *   **Academic Dimension:** While primarily focused on database systems, this course includes "distributed data management" as one of its topics, indicating an aspect of distributed computing within the context of databases [Source 9].</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Yes, there are CSCE courses that focus on parallel or distributed computing paradigms.
+The relevant principle is that computer science courses often specialize in different computing models, including those that involve multiple processors or systems working together (parallel and distributed computing).
+Based on the provided syllabi, the following courses address these areas:
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    *   **Academic Dimension:** This course explicitly covers "Applied Networks and Distributed Processing" [Source 1]. Its catalog description includes "network design and protocol analysis" and "principles of network engineering," focusing on applying layered architecture to real networks [Source 1].
+    *   **Learning Outcomes:** Students will be able to "utilize operating-system sockets APIs, create efficient network applications and build multi-threaded decentralized frameworks, analyze performance and security of networks, develop protocols, and construct models of their system" [Source 4]. This directly relates to distributed computing and concurrent programming.
+*   **CSCE 611: Operating Systems**
+    *   **Academic Dimension:** This course gives an overview of modern operating systems, including understanding "what it takes to build a distributed system" [Source 3].
+    *   **Learning Outcomes:** Students will be able to "Evaluate and compare various forms of concurrency mechanisms" and "Evaluate and compare and apply various synchronization mechanisms" [Source 3]. The course schedule also lists topics such as "Concurrency," "Thread Dispatching," and "Synchronization" [Source 6].
+*   **CSCE 614: Computer Architecture**
+    *   **Academic Dimension:** The catalog description for this course explicitly mentions "parallel computer structures and concurrent computation; pipeline computers and vectorization methods; array processors, multiprocessor architectures and programming; dataflow computers" [Source 2]. This directly addresses various aspects of parallel computing.
+*   **CSCE 608: Database Systems**
+    *   **Academic Dimension:** The catalog description for this course includes "distributed data management" as a topic [Source 9]. This is a specific application area within distributed computing.</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Yes, there are CSCE courses that focus on parallel or distributed computing.
+**Principle: Parallel and Distributed Computing**
+Parallel computing involves performing multiple calculations or processes simultaneously to solve a problem faster, often on a single machine with multiple processors. Distributed computing, a subset of parallel computing, uses multiple interconnected computers (a distributed system) to work on the same problem, coordinating their efforts to achieve a common goal. Both paradigms are crucial for handling large datasets, complex computations, and ensuring high availability and fault tolerance in modern systems.
+**Relevant Courses:**
+*   **CSCE 611: Operating Systems**
+    This course provides an overview of modern operating systems, including understanding "what it takes to build a distributed system" [Source 1]. It covers aspects like "process coordination and management" [Source 8], which are fundamental to distributed environments.
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    The title itself indicates a focus on "Distributed Processing" [Source 2]. The course description highlights "network design and protocol analysis" and "applying principles of layered architecture to analyzing real networks" [Source 2]. Learning outcomes include the ability to "build multi-threaded decentralized frameworks" [Source 3], directly addressing distributed computing concepts.
+*   **CSCE 614: Computer Architecture**
+    This course explicitly covers "parallel computer structures and concurrent computation; pipeline computers and vectorization methods; array processors, multiprocessor architectures and programming; dataflow computers" [Source 4]. Its schedule includes topics like "SIMD" (Single Instruction, Multiple Data) and "TLP" (Thread-Level Parallelism) and "Cache Coherence" [Source 9], which are core concepts in parallel computing architectures.
+*   **CSCE 676: Data Mining**
+    While primarily a data mining course, its schedule includes a week dedicated to "Data Mining and Distributed Computing" [Source 5], indicating that distributed computing principles are applied within the context of data mining.
+**Academic Progression:**
+These courses are typically graduate-level (600-level and above) and build upon foundational undergraduate knowledge (e.g., CSCE 313 for CSCE 611 and 612, CSCE 350/ECEN 350/CSCE 312 for CSCE 614) [Source 1, 3, 4, 8]. Taking these courses can deepen your understanding of how modern computing systems are designed and implemented to handle complex, large-scale problems, which is essential for careers in system architecture, high-performance computing, cloud computing, and large-scale data processing.</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Yes, there are CSCE courses focused on parallel or distributed computing.
+Based on the provided syllabi:
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    This course covers fundamentals of network design and protocol analysis, mixing fundamentals with programming and engineering issues. It includes network architecture and principles of network engineering, focusing on applying layered architecture to real networks. Lab exercises focus on protocol understanding and programming. Knowledge of UNIX and C programming is helpful but not required [Source 1]. Students will be able to build multi-threaded decentralized frameworks [Source 4].
+*   **CSCE 614: Computer Architecture**
+    This course reviews von Neumann architecture and its limitations, and covers parallel computer structures and concurrent computation. It also includes pipeline computers, vectorization methods, array processors, multiprocessor architectures and programming, and dataflow computers [Source 3].
+*   **CSCE 611 (or CSCE 410): Operating Systems**
+    This course gives an overview of modern operating systems, including understanding fundamental approaches to virtualization and what it takes to build a distributed system [Source 2].
+*   **CSCE 676: Data Mining**
+    This course includes "Data Mining and Distributed Computing" as a topic in Week 8 of its schedule [Source 7].
+*   **CSCE 726: Large-Scale Optimization for Machine Learning**
+    This course focuses on fundamental optimization algorithms for solving machine learning problems, including implementation of algorithms and their application to solving real-world machine learning and artificial intelligence problems [Source 8]. While not explicitly "distributed computing," large-scale optimization often involves distributed approaches.
+**Academic Progression:**
+These courses can fit into an academic progression for students interested in various aspects of computing:
+*   **CSCE 614** provides foundational knowledge in computer architecture, which is crucial for understanding how parallel and distributed systems are built at a hardware level [Source 3].
+*   **CSCE 611** offers insights into operating systems, including the principles behind distributed systems, which is essential for software development in such environments [Source 2].
+*   **CSCE 612** directly addresses distributed processing and network applications, providing practical skills in building multi-threaded decentralized frameworks [Source 1, Source 4].
+*   **CSCE 676** touches upon distributed computing within the context of data mining, which could be relevant for students interested in big data processing [Source 7].
+*   **CSCE 726** focuses on large-scale optimization, which often leverages distributed computing techniques for efficiency in machine learning and AI applications [Source 8].
+Students should consider their specific interests (e.g., hardware, operating systems, networking, data processing, AI) to choose the most relevant courses for their academic and career goals.</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University offers several CSCE courses that focus on parallel or distributed computing paradigms. These courses are essential for students looking to understand how to design and implement systems that leverage multiple processors or networked computers to solve complex problems.
+Here are the courses identified:
+*   **CSCE 612: Applied Networks and Distributed Processing**
+    *   **Focus:** This course covers the fundamentals of network design and protocol analysis, integrating programming and engineering perspectives. It includes network architecture and principles of network engineering, with a focus on applying layered architecture to real networks. Students will learn to build multi-threaded decentralized frameworks [Source 1, 4].
+    *   **Prerequisites:** Graduate classification and CSCE 313 [Source 1].
+*   **CSCE 611: Operating Systems**
+    *   **Focus:** This course provides an overview of the general architecture and components of modern operating systems. It includes understanding fundamental approaches to virtualization and what it takes to build a distributed system [Source 3, 7].
+    *   **Prerequisites:** Graduate classification and CSCE 313 [Source 3, 7].
+*   **CSCE 614: Computer Architecture**
+    *   **Focus:** This course reviews von Neumann architecture and its limitations, and delves into parallel computer structures, concurrent computation, pipeline computers, vectorization methods, array processors, multiprocessor architectures, and dataflow computers [Source 2].
+    *   **Prerequisites:** CSCE 350, ECEN 350, or CSCE 312, and a background in undergraduate computer engineering or computer science [Source 2].
+**Academic Planning Dimension:**
+These courses are foundational for students interested in advanced topics such as high-performance computing, cloud computing, network engineering, or designing scalable software systems. They build upon undergraduate computer science fundamentals (like CSCE 313 or 312/350) and are typically intended for graduate students or those with a strong undergraduate background in the field. Taking these courses can prepare students for specialized research or industry roles requiring expertise in concurrent and distributed system design and analysis.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6766,6 +11614,94 @@
 Based on the provided syllabi, there is no explicit recommendation for a specific course to take immediately after CSCE 638. However, CSCE 638, "Natural Language Processing: Foundations and Techniques," covers "Large Language Models" as a key topic [Source 1, 3].
 Another course, CSCE 670, "Information Retrieval," also extensively covers "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 4]. This indicates a thematic overlap and suggests that CSCE 670 could be a relevant course for students interested in applying or further exploring Large Language Models within the context of information retrieval and recommender systems, building on the foundations established in CSCE 638.
 I don't have enough data to definitively recommend a specific next course based on the available syllabi, as no explicit academic progression or prerequisite relationships are provided for courses following CSCE 638.</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>To determine what course might be suitable after completing CSCE 638, we can look for courses that share similar advanced topics or build upon the foundations established in CSCE 638.
+CSCE 638, "Natural Language Processing: Foundations and Techniques," covers topics such as language models, automatic syntactic processing, semantic understanding, information extraction, machine translation, text summarization, dialogue systems, sentiment analysis, Transformers, Large Language Models, and related concepts [Source 1, 3].
+Based on the provided syllabi, CSCE 670, "Information Retrieval," includes several related advanced topics:
+*   **Transformers, BERT-Based Ranking, Large Language Models with Search Engines:** These topics directly align with the advanced NLP concepts covered in CSCE 638 [Source 4].
+*   The course also covers Recommender Systems, Neural Ranking, and Neural Collaborative Filtering, which often leverage techniques from natural language processing and machine learning [Source 4].
+While CSCE 726, "Optimization Algorithms for Machine Learning and Artificial Intelligence," focuses on the mathematical and algorithmic foundations of ML/AI, it requires a background in Machine Learning (CSCE 633 or CSCE 636) [Source 6, 8]. If a student wishes to delve deeper into the optimization algorithms that power many NLP models, this could be a relevant, albeit more foundational, next step, provided they meet the prerequisites.
+Therefore, based on the shared and complementary topics, CSCE 670 appears to be a logical next course for a student interested in applying and extending their knowledge from CSCE 638.
+I don't have enough data to provide a comprehensive list of all potential follow-up courses, as the context only includes a limited set of syllabi.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>The provided context does not explicitly define a recommended sequence of courses or state what course should be taken directly after CSCE 638. However, we can identify related courses based on overlapping advanced topics.
+CSCE 638, "Natural Language Processing: Foundations and Techniques," covers a wide range of topics including "Transformers," "Contextualized Representations," "Pre-Training," "Large Language Models," "Instruction Tuning," "Alignment," "Large Reasoning Models," and "Retrieval-Augmented Generation" [Source 1, 3].
+Considering academic progression, a student might look for courses that either build upon these advanced topics or apply them in specific domains:
+*   **CSCE 670 (Web Search and Recommender Systems)**: This course includes topics such as "Transformer," "BERT-Based Ranking," "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 4]. Given the significant overlap in "Large Language Models" and "Transformers," CSCE 670 could be a logical next step if you are interested in applying your NLP and LLM knowledge to information retrieval and recommender systems.
+*   **CSCE 624 (Sketch Recognition)**: This course also mentions "LLMs" in its schedule [Source 8]. While its primary focus is sketch recognition, it indicates an application of LLMs in a different domain.
+*   **CSCE 726 (Advanced Machine Learning)**: This course focuses on advanced machine learning techniques and optimization [Source 9]. While CSCE 638 covers "Machine Learning Basics" [Source 3], CSCE 726 could provide a deeper theoretical understanding of the underlying algorithms relevant to NLP.
+**Planning Dimension:**
+If your interest lies in applying the advanced concepts of Large Language Models and Transformers learned in CSCE 638 to specific applications like search engines and recommender systems, CSCE 670 appears to be a strong candidate for academic progression. If you are interested in a deeper dive into the theoretical underpinnings of machine learning, CSCE 726 could be beneficial.
+I don't have enough data to definitively recommend a single "next" course based on a structured curriculum path.</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>After completing CSCE 638, which focuses on Natural Language Processing (NLP) fundamentals, including language models, automatic syntactic processing, semantic understanding, and major NLP applications like information extraction, machine translation, and sentiment analysis [Source 1], you might consider courses that build upon these concepts or apply them in specific domains. Academic progression often involves moving from foundational knowledge to more specialized applications or advanced theoretical underpinnings.
+Based on the provided context, here are some courses that could be relevant for your academic progression:
+*   **CSCE 670: Web Search and Recommender Systems**
+    *   **Relevance:** This course directly applies concepts related to Large Language Models (LLMs), which are covered in CSCE 638 [Source 3]. CSCE 670 includes topics such as "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 4]. This would allow you to see how NLP and LLM principles are used in practical information retrieval and recommendation systems.
+    *   **Prerequisites:** Requires CSCE 310 or CSCE 603 or instructor approval, along with graduate classification [Source 5]. Your background from CSCE 638 would be highly beneficial.
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Relevance:** This course focuses on optimization algorithms for solving Machine Learning (ML) and Artificial Intelligence (AI) problems [Source 8]. While CSCE 638 covers "Machine Learning Basics" [Source 3], CSCE 726 requires a stronger foundation in ML and Deep Learning.
+    *   **Prerequisites:** Requires CSCE 633 (Machine Learning) or CSCE 636 (Deep Learning) or instructor approval [Source 9]. If you have not taken CSCE 633 or CSCE 636, you might consider taking one of those first to meet the prerequisites for CSCE 726. CSCE 726 also recommends proficiency in math (linear algebra, probability/statistics, optimization) and Python/PyTorch [Source 9].
+The best choice depends on your specific interests within the field of AI and computing. If you wish to delve deeper into the application of LLMs in specific systems, CSCE 670 appears to be a strong follow-up. If you are interested in the mathematical and algorithmic foundations of machine learning, CSCE 726 (potentially after CSCE 633 or 636) would be a suitable path.
+I don't have enough data to answer this accurately based on the available syllabi for all possible follow-up courses.</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>After completing CSCE 638, which focuses on Natural Language Processing (NLP) foundations and techniques, including language models, automatic syntactic processing, semantic understanding, and major NLP applications like information extraction, machine translation, and sentiment analysis, as well as recent trends like Transformers and Large Language Models (LLMs) [Source 1, 3], you might consider courses that either deepen your specialization in related application areas or strengthen your foundational understanding of the underlying machine learning principles.
+Based on the provided context, here are some courses that align with academic progression after CSCE 638:
+*   **CSCE 670: Information Retrieval**
+    *   **Principle:** Specialization in a related application domain.
+    *   **Application:** CSCE 638 introduces you to LLMs and Transformers [Source 3]. CSCE 670 builds directly on these concepts by covering topics such as "Transformer," "BERT-Based Ranking," "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 4]. This course would allow you to apply your NLP knowledge to the specific domain of information retrieval, search engines, and recommender systems, which are closely related to the information extraction applications mentioned in CSCE 638 [Source 1].
+*   **CSCE 726: Advanced Optimization for Machine Learning**
+    *   **Principle:** Foundational strengthening in underlying mathematical and algorithmic principles.
+    *   **Application:** CSCE 638 involves various advanced NLP models that rely heavily on machine learning and deep learning techniques [Source 3]. CSCE 726 focuses on "large-scale optimization" and "fundamental optimization algorithms and their analysis for solving advanced machine learning problems" [Source 10]. This course would provide a deeper theoretical and practical understanding of the optimization methods (e.g., stochastic gradient descent, AdaGrad) that underpin the training and development of the complex models you encounter in NLP, such as those used for language modeling and contextualized representations [Source 3, 10]. It requires comfort with intensive math and programming, and basic knowledge of machine learning [Source 8, 10].
+These courses offer pathways for either applying your NLP skills to specific, related fields (CSCE 670) or gaining a more profound understanding of the core mathematical and algorithmic underpinnings of modern AI/ML, which are essential for advanced NLP research and development (CSCE 726).</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>When planning your academic progression, it's beneficial to select courses that build upon the foundational knowledge you've acquired or explore related specialized areas. CSCE 638 focuses on Natural Language Processing (NLP) fundamentals, including language models, automatic syntactic processing, semantic understanding, and major NLP applications like information extraction, machine translation, and sentiment analysis [Source 1]. It also covers recent trends such as Large Language Models (LLMs) [Source 3].
+Based on the provided context, a highly relevant course to consider after completing CSCE 638 is **CSCE 670: Web Search and Recommender Systems**. This course directly applies concepts related to Large Language Models (LLMs) to specific domains, with topics including:
+*   Large Language Models Basics [Source 4]
+*   Large Language Models with Search Engines [Source 4]
+*   Large Language Models for Ranking and Recommendation [Source 4]
+This course would allow you to apply and deepen your understanding of modern NLP techniques, particularly LLMs, in practical information retrieval and recommendation contexts.
+While other courses like CSCE 726 (Optimization for Machine Learning) are related to the broader field of AI/ML, CSCE 670 offers a more direct application and extension of the specific NLP and LLM topics covered in CSCE 638.
+I don't have enough data to provide a comprehensive list of all possible follow-up courses based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Academic progression often involves building upon foundational knowledge or exploring related sub-disciplines. CSCE 638, "Natural Language Processing: Foundations and Techniques," focuses on NLP fundamentals, including language models, automatic syntactic processing, semantic understanding, and applications like information extraction, machine translation, and sentiment analysis. It also covers recent topics such as Transformers and Large Language Models (LLMs) [Source 1, 3].
+Based on the provided context, while no course explicitly lists CSCE 638 as a direct prerequisite, CSCE 670, "Information Retrieval," appears to be a strong thematic follow-up. CSCE 670 covers topics that align well with advanced applications of NLP, such as:
+*   **Transformers and Large Language Models:** CSCE 670 includes "Transformer; BERT-Based Ranking," "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 4]. These topics directly build on the LLM and Transformer concepts introduced in CSCE 638 [Source 3].
+*   **Related Applications:** Information Retrieval, search engines, and recommender systems are closely related to the information extraction and semantic understanding aspects of NLP [Source 4, 1].
+For students interested in the mathematical and algorithmic underpinnings of machine learning and AI, CSCE 726, "Optimization for Machine Learning," could be considered. However, it requires prerequisites such as CSCE 633 (Machine Learning) or CSCE 636 (Deep Learning) and focuses on optimization algorithms rather than direct NLP applications [Source 5, 6]. CSCE 633 itself covers fundamental machine learning techniques that are foundational to NLP [Source 8, 9].
+Therefore, for a direct continuation of NLP applications and related fields, CSCE 670 is a suitable next step. I don't have enough data to answer this accurately based on the available syllabi if you are looking for a course that *requires* CSCE 638 as a prerequisite.</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>After completing CSCE 638 (Natural Language Processing: Foundations and Techniques), you might consider the following courses to further your studies in related areas:
+1.  **CSCE 670: Information Retrieval**
+    *   **Why it fits:** CSCE 638 introduces concepts like Text Similarity and Retrieval-Augmented Generation [Source 3]. CSCE 670 directly expands on these by covering topics such as Boolean Retrieval, TF-IDF, Vector Space Model, Learning to Rank, and specifically delves into Large Language Models (LLMs) in the context of search engines, ranking, and recommendation [Source 5]. This course would allow you to apply your NLP knowledge to practical information retrieval systems and understand how LLMs are integrated into these systems.
+    *   **Academic Progression:** This course is a natural progression for students interested in search technologies, recommender systems, and the application of LLMs in information access.
+2.  **CSCE 726: Advanced Optimization for Machine Learning**
+    *   **Why it fits:** While CSCE 638 focuses on the application of machine learning and deep learning techniques to NLP problems, CSCE 726 provides a deeper theoretical and algorithmic understanding of the optimization methods used to train these complex models [Source 9]. It covers classic deterministic and modern large-scale stochastic optimization algorithms for solving ML/AI problems [Source 9]. This would enhance your understanding of the underlying mechanics of the models discussed in CSCE 638, such as Large Reasoning Models and techniques like Parameter-Efficient Fine-Tuning [Source 3].
+    *   **Academic Progression:** This course is suitable for students aiming for research-oriented roles or those who wish to gain a more profound understanding of the mathematical and computational foundations of machine learning and deep learning, building on the practical applications learned in CSCE 638. Note that CSCE 633 or CSCE 636 are prerequisites [Source 6].
+3.  **CSCE 676: Data Mining**
+    *   **Why it fits:** CSCE 676 covers a broad range of techniques for extracting knowledge from data, including "Text Mining" and "Large-Scale ML" [Source 10]. Given that CSCE 638 provides a strong foundation in processing and understanding natural language, CSCE 676 would allow you to apply these skills within a broader data mining context, including working with large datasets and exploring different types of data analysis problems beyond pure NLP.
+    *   **Academic Progression:** This course is ideal for students looking to broaden their skill set in data analysis and apply their machine learning and text processing knowledge to diverse data mining challenges.</t>
         </is>
       </c>
     </row>
@@ -6832,6 +11768,210 @@
 **CSCE 676, ECEN 758, STAT 639**: Required course readings will be drawn from various online textbooks, scholarly papers, and other resources. A key required textbook is "Mining of Massive Data Sets" by Jure Leskovec, Anand Rajaraman, and Jeffrey David Ullman (Cambridge University Press, 2020) [Source 3].</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>When considering courses that "pair well" with another, the principle of **course complementarity and academic progression** is key. This means looking for courses that either provide foundational knowledge, build upon the topics covered, offer different perspectives on related subjects, or teach essential skills for applying the knowledge gained.
+CSCE 676, "Data Mining and Analysis," provides a broad overview of data mining, integrating concepts from machine learning and statistics. It covers topics such as exploratory data analysis, pattern mining, clustering, classification, graph mining, large-scale machine learning, and text mining, with applications to scientific and online data [Source 1, 2, 3]. The course expects students to have exposure to basic probability, statistics, algorithms, and data structures [Source 1].
+Based on the available context, the following courses would pair well with CSCE 676:
+*   **CSCE 633 (Machine Learning):** CSCE 676 explicitly integrates "related concepts from machine learning" [Source 1]. A foundational course like CSCE 633 would provide a deeper understanding of the machine learning algorithms and principles that underpin many data mining techniques, enhancing a student's ability to grasp and apply the concepts taught in CSCE 676.
+*   **CSCE 726 (Optimization for Machine Learning):** This course focuses on fundamental optimization algorithms for solving advanced machine learning problems [Source 12]. Given that CSCE 676 covers "Large-Scale ML" [Source 2], understanding the optimization techniques from CSCE 726 would be highly beneficial for implementing and analyzing the efficiency of data mining algorithms, especially in large-scale contexts. It also lists CSCE 633 as a prerequisite, indicating a natural progression [Source 13].
+*   **CSCE 670 (Web Search and Recommender Systems):** This course shares the "Mining of Massive Datasets" textbook with CSCE 676 [Source 3, 6, 11], indicating a strong thematic overlap. CSCE 670 focuses on specific applications (web search and recommender systems) that heavily rely on data mining techniques for processing and analyzing "online data," which is an application area mentioned in CSCE 676 [Source 1, 11].
+*   **CSCE 679 (Data Visualization):** Data mining often involves exploratory data analysis and the communication of insights. CSCE 679 teaches principles and practical skills for visualizing diverse data types and presenting findings effectively [Source 9]. This course would complement CSCE 676 by providing the tools and techniques necessary to interpret and present the results of data mining and analysis.
+It is also important to note that CSCE 676 is cross-listed with ECEN 758 and STAT 639 [Source 1]. This means these are essentially the same course offered under different departmental designations, rather than complementary courses that would "pair well" in terms of expanding knowledge beyond the scope of CSCE 676.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>ECEN 758 and STAT 639 are cross-listed with CSCE 676, meaning they are the same course offered under different department codes [Source 1]. Therefore, the information below applies to all three courses.
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 676 / ECEN 758 / STAT 639 | Weekly Assessments (10%), Homework (50%), Individual Semester-Long Project (40%) | Weekly quizzes, weekly Python-based homework (programming, written, video/Canvas response, AI-coding assistant required), significant semester-long project with 5 deliverables. | Basic probability, statistics, algorithms, data structures; ability to design/develop large programs and learn new software libraries independently. |
+## Detailed Comparison
+### Course Overview
+**CSCE 676 / ECEN 758 / STAT 639**: This course provides a broad overview of data mining, integrating concepts from machine learning and statistics. Topics include exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data [Source 1].
+### Grading &amp; Workload
+**CSCE 676 / ECEN 758 / STAT 639**:
+*   **Grading Breakdown**: Weekly Assessments (10%), Homework (50%), Individual Semester-Long Project (40%) [Source 3, 4].
+*   **Weekly Assessments**: Consist of one or more short quizzes (typically true/false, multiple choice) over the week's material. These can be taken multiple times, with the highest score kept [Source 4].
+*   **Homework**: Weekly assignments for 13 weeks (first 12 weeks are 4% each, 13th week is 2%). These are Python notebooks combining programming, written problems, and other tasks (e.g., video/Canvas responses). Students are required to use an AI-coding assistant. No prior Python exposure is expected, but rapid learning is required. Late homework is penalized 1% per hour, up to 48 hours, after which it receives a 0 [Source 4, 5].
+*   **Individual Semester-Long Project**: A significant data mining project broken into five deliverables: Data Selection (Feb 3), Initial Research Question (Mar 5), Deep Dive (Apr 2), Project Showcase (week of Apr 20), and Final Deliverable (Apr 27). Students have five late days in total for the first three deliverables; the final two deliverables are not accepted late [Source 5, 2].
+### Prerequisites
+**CSCE 676 / ECEN 758 / STAT 639**: Students are expected to have previous exposure to basic probability, statistics, algorithms, and data structures. They should also be able to design and develop large programs and learn new software libraries independently [Source 1].
+### Learning Outcomes
+**CSCE 676 / ECEN 758 / STAT 639**: Upon completion, learners will be able to:
+*   Define and explain key concepts and models relevant to data mining and analysis, including data preparation, normalization, dimensionality reduction, and text mining [Source 3].
+*   Design, implement, and evaluate data mining algorithms (e.g., associate rules, clustering, anomaly detection) on modern scalable cloud computing platforms (e.g., Spark) [Source 3].
+*   Identify salient features and apply recent research results in data mining, including topics such as graph mining and large-scale mining [Source 3].
+### Topics
+**CSCE 676 / ECEN 758 / STAT 639**: The course schedule includes:
+*   Week 1: Course introduction [Source 2]
+*   Week 2: Frequent Itemset Mining [Source 2]
+*   Week 3: Graph Mining [Source 2]
+*   Week 4: Graph Mining and Large-Scale ML [Source 2]
+*   Week 5: Large-Scale ML [Source 2]
+*   Week 6: Clustering [Source 2]
+*   Week 7: Text Mining [Source 2]
+*   Week 8: Data Mining and Distributed Computing [Source 2]
+*   Week 9: Anomaly Detection [Source 2]
+*   Week 10: Graph Embeddings [Source 2]
+*   Week 11: Locality-Sensitive Hashing [Source 2]
+*   Week 12: Stream Mining [Source 2]
+*   Week 13: Hot Topics in Data Mining [Source 2]
+*   Week 14: Project Showcase [Source 2]
+*   Week 15: Finalize Project Deliverables [Source 2]
+### Materials
+**CSCE 676 / ECEN 758 / STAT 639**:
+*   **Required Readings**: Course readings will be drawn from a variety of online textbooks, scholarly papers, and other resources [Source 3].
+*   **Required Textbook**: "Mining of Massive Data Sets" by Jure Leskovec, Anand Rajaraman, Jeffrey David Ullman (Cambridge University Press, 2020-01-09, ISBN: 9781108476348) [Source 3, 4].</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>CSCE 676 is cross-listed with ECEN 758 and STAT 639 [Source 1]. This means they are the same course offered under different departmental codes. Therefore, they pair well because they are essentially the same course.
+However, detailed information for ECEN 758 and STAT 639 beyond their cross-listing is not available in the provided context. The following comparison focuses on CSCE 676.
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 676 | Weekly Assessments (10%), Homework (50%), Individual Semester-Long Project (40%) | Weekly assessments, weekly homework (Python notebooks), individual semester-long project with 5 deliverables | Previous exposure to basic probability, statistics, algorithms, and data structures; ability to design/develop large programs and learn new software libraries |
+| ECEN 758 | Not found | Not found | Not found |
+| STAT 639 | Not found | Not found | Not found |
+## Detailed Comparison
+### Course Overview
+**CSCE 676**: This course provides a broad overview of data mining, integrating concepts from machine learning and statistics. Topics include exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data. It is cross-listed with ECEN 758 and STAT 639 [Source 1].
+**ECEN 758**: Not found
+**STAT 639**: Not found
+### Grading &amp; Workload
+**CSCE 676**: The grading policy is composed of 10% Weekly Assessments, 50% Homework, and 40% Individual Semester-Long Project [Source 3, Source 4].
+*   **Weekly Assessments**: These are short quizzes (typically true/false, multiple choice) over the week's material, which can be taken multiple times with the highest score kept [Source 4].
+*   **Homework**: There will be weekly homework assignments for the first twelve weeks (4% each) and a 13th homework (2%). All homework assignments are Python notebooks, including programming, written problems, and other questions (e.g., video posts, Canvas discussions). Students are required to use an AI-coding assistant [Source 4]. Late homework is penalized 1% per hour after the deadline, up to 48 hours, after which it receives a 0 [Source 5].
+*   **Individual Semester-Long Project**: This is a significant data mining project broken into five major deliverables: Data Selection (Feb 3), Initial Research Question (Mar 5), Deep Dive (Apr 2), Project Showcase (week of Apr 20), and Final Deliverable (Apr 27) [Source 5, Source 2]. Students have five late days in total for the first three deliverables; the final two deliverables are not accepted late [Source 5, Source 2].
+**ECEN 758**: Not found
+**STAT 639**: Not found
+### Prerequisites
+**CSCE 676**: Students are expected to have previous exposure to basic probability, statistics, algorithms, and data structures. They should also be able to design and develop large programs and learn new software libraries independently [Source 1].
+**ECEN 758**: Not found
+**STAT 639**: Not found
+### Learning Outcomes
+**CSCE 676**: Upon completion, learners will be able to:
+*   Define and explain key concepts and models in data mining and analysis, including data preparation, normalization, dimensionality reduction, and text mining [Source 3].
+*   Design, implement, and evaluate data mining algorithms (e.g., associate rules, clustering, anomaly detection) on modern scalable cloud computing platforms (e.g., Spark) [Source 3].
+*   Identify salient features and apply recent research results in data mining, including topics like graph mining and large-scale mining [Source 3].
+**ECEN 758**: Not found
+**STAT 639**: Not found
+### Topics
+**CSCE 676**: The course schedule includes topics such as Course introduction, Frequent Itemset Mining, Graph Mining (including Large-Scale ML), Large-Scale ML, Clustering, Text Mining, Data Mining and Distributed Computing, Anomaly Detection, Graph Embeddings, Locality-Sensitive Hashing, Stream Mining, and Hot Topics in Data Mining. The semester concludes with a Project Showcase and Final Project Deliverables [Source 2].
+**ECEN 758**: Not found
+**STAT 639**: Not found
+### Materials
+**CSCE 676**: Course readings will be drawn from various online textbooks, scholarly papers, and other resources. A required textbook is "Mining of Massive Data Sets" by Jure Leskovec, Anand Rajaraman, and Jeffrey David Ullman (Cambridge University Press, 2020, ISBN: 9781108476348) [Source 3, Source 4].
+**ECEN 758**: Not found
+**STAT 639**: Not found</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>CSCE 676 is cross-listed with ECEN 758 and STAT 639 [Source 1]. This means they are the same course and share the same syllabus, content, grading, workload, and prerequisites.
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 676 / ECEN 758 / STAT 639 | Weekly Assessments (10%), Homework (50%), Individual Semester-Long Project (40%) | Weekly Assessments, Weekly Homework (Python notebooks), Individual Semester-Long Project (5 deliverables) | Previous exposure to basic probability, statistics, algorithms, and data structures; ability to design and develop large programs and learn new software libraries |
+## Detailed Comparison
+### Course Overview
+**CSCE 676 / ECEN 758 / STAT 639**: This course provides a broad overview of data mining, integrating concepts from machine learning and statistics. Topics include exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data. It is a 3-credit hour course [Source 1].
+### Grading &amp; Workload
+**CSCE 676 / ECEN 758 / STAT 639**: The final grade is determined by:
+*   **Weekly Assessments (10%)**: Short quizzes (typically true/false, multiple choice) over the week's material, which can be taken multiple times with the highest score kept [Source 3, 4].
+*   **Homework (50%)**: Weekly assignments for the first twelve weeks (4% each) and a 13th homework (2%). These are Python notebooks with programming, written problems, and other questions. Students are required to use an AI-coding assistant. Late homework is penalized 1% per hour up to 48 hours, after which it receives a 0 [Source 3, 4, 5].
+*   **Individual Semester-Long Project (40%)**: A significant data mining project broken into five deliverables: Data Selection (Feb 3), Initial Research Question (Mar 5), Deep Dive (Apr 2), Project Showcase (week of Apr 20), and Final Deliverable (Apr 27). Students have five late days in total for the first three deliverables; the final two deliverables are not accepted late [Source 3, 5, 2].
+### Prerequisites
+**CSCE 676 / ECEN 758 / STAT 639**: Students are expected to have previous exposure to basic probability, statistics, algorithms, and data structures. They should also be able to design and develop large programs and learn new software libraries independently [Source 1].
+### Learning Outcomes
+**CSCE 676 / ECEN 758 / STAT 639**: Upon completion, learners will be able to:
+*   Define and explain key concepts and models in data mining and analysis, including data preparation, normalization, dimensionality reduction, and text mining.
+*   Design, implement, and evaluate data mining algorithms (e.g., associate rules, clustering, anomaly detection) on modern scalable cloud computing platforms (e.g., Spark).
+*   Identify salient features and apply recent research results in data mining, such as graph mining and large-scale mining [Source 3].
+### Topics
+**CSCE 676 / ECEN 758 / STAT 639**: The course schedule includes:
+*   Course introduction
+*   Frequent Itemset Mining
+*   Graph Mining (including Large-Scale ML)
+*   Large-Scale ML
+*   Clustering
+*   Text Mining
+*   Data Mining and Distributed Computing
+*   Anomaly Detection
+*   Graph Embeddings
+*   Locality-Sensitive Hashing
+*   Stream Mining
+*   Hot Topics in Data Mining
+*   Project Showcase
+*   Finalize Project Deliverables [Source 2]
+### Materials
+**CSCE 676 / ECEN 758 / STAT 639**: Required readings will be drawn from various online textbooks, scholarly papers, and other resources. A key required textbook is "Mining of Massive Data Sets" by Jure Leskovec, Anand Rajaraman, and Jeffrey David Ullman (Cambridge University Press, 2020, ISBN: 9781108476348) [Source 3, 4].</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>When considering courses that "pair well" with another, it's helpful to look for courses that share foundational knowledge, serve as prerequisites, or build upon similar advanced concepts, creating a cohesive academic progression.
+For CSCE 676, "Data Mining and Analysis," which integrates concepts from machine learning and statistics [Source 1], the following courses would be complementary:
+*   **CSCE 633: Machine Learning**
+    *   **Principle:** CSCE 676 explicitly states it integrates "related concepts from machine learning" [Source 1]. CSCE 633 provides a foundational and comprehensive survey of machine learning techniques, including induction from examples, conceptual clustering, and various algorithms [Source 11].
+    *   **Application:** Taking CSCE 633 would provide a strong theoretical and practical background in machine learning, which is directly applied and integrated into the data mining techniques covered in CSCE 676, such as classification and clustering [Source 1, 3]. Both courses emphasize Python programming [Source 4, 8].
+*   **CSCE 726: Optimization for Machine Learning**
+    *   **Principle:** CSCE 676 covers advanced topics like "large-scale mining" and the use of "modern scalable cloud computing platforms" [Source 3]. CSCE 726 focuses on "large-scale stochastic optimization algorithms for solving ML/AI problems" and advanced machine learning methods [Source 6, 12].
+    *   **Application:** This course builds upon machine learning foundations (CSCE 633 is a prerequisite for CSCE 726 [Source 9]) and would provide deeper insights into the optimization techniques necessary for handling the large-scale data and complex models often encountered in data mining and analysis. Both courses require strong mathematical and programming backgrounds, particularly in Python [Source 1, 9, 12].
+**Planning Dimension:**
+Taking CSCE 633 before or concurrently with CSCE 676 would establish a robust understanding of machine learning principles that are fundamental to data mining. Following up with CSCE 726 would then deepen your expertise in the computational and algorithmic aspects of large-scale machine learning and data analysis, which are critical for advanced work in the field. All these courses share a common need for strong programming skills (especially Python) and a background in probability, statistics, and algorithms [Source 1, 9, 12].
+Additionally, CSCE 676 is cross-listed with ECEN 758 and STAT 639, indicating its interdisciplinary nature and strong ties to statistics [Source 1].</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>The provided context indicates that CSCE 676 is cross-listed with ECEN 758 and STAT 639 [Source 1]. This means they are the same course offered under different departmental designations. Therefore, the information provided for CSCE 676 applies to ECEN 758 and STAT 639.
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 676 | Weekly Assessments (10%), Homework (50%), Individual Semester-Long Project (40%) | Weekly assessments, weekly homework (Python notebooks), individual semester-long project with 5 deliverables | Basic probability, statistics, algorithms, data structures; ability to design/develop large programs and learn new software libraries |
+| ECEN 758 | Same as CSCE 676 [Source 1] | Same as CSCE 676 [Source 1] | Same as CSCE 676 [Source 1] |
+| STAT 639 | Same as CSCE 676 [Source 1] | Same as CSCE 676 [Source 1] | Same as CSCE 676 [Source 1] |
+## Detailed Comparison
+### Course Overview
+**CSCE 676**: This course provides a broad overview of data mining, integrating concepts from machine learning and statistics. Topics include exploratory data analysis, pattern mining, clustering, classification, and applications to scientific and online data. It is cross-listed with ECEN 758 and STAT 639 [Source 1]. The course meets on Tuesdays and Thursdays from 09:35 AM to 10:50 AM in Spring 2026 [Source 1].
+**ECEN 758**: This course is cross-listed with CSCE 676, meaning it covers the same content and structure as CSCE 676 [Source 1].
+**STAT 639**: This course is cross-listed with CSCE 676, meaning it covers the same content and structure as CSCE 676 [Source 1].
+### Grading &amp; Workload
+**CSCE 676**: The grading policy is as follows: Weekly Assessments (10%), Homework (50%), and an Individual Semester-Long Project (40%) [Source 3, 4].
+*   **Weekly Assessments**: These are short quizzes (typically true/false, multiple choice) over the week's material, which can be taken multiple times with the highest score kept [Source 4].
+*   **Homework**: There will be weekly homework assignments. For the first twelve weeks, each is worth 4% of the grade, and the 13th homework is worth 2%. All homework assignments are Python notebooks, including programming, written problems, and other questions (e.g., video posts, Canvas discussions). Students are required to use an AI-coding assistant. No prior Python exposure is expected, but rapid learning is required [Source 4]. Late homework is penalized 1% per hour after the deadline, up to a maximum of 48 hours, after which it receives a 0 [Source 5].
+*   **Individual Semester-Long Project**: This is a significant data mining project broken into five deliverables: Data Selection (Feb 3), Initial Research Question (Mar 5), Deep Dive (Apr 2), Project Showcase (week of Apr 20), and Final Deliverable (Apr 27) [Source 5, 2]. Students have five late days in total for the first three deliverables. The Project Showcase and Final Deliverable will not be accepted late [Source 5, 2].
+**ECEN 758**: The grading and workload are the same as CSCE 676 due to cross-listing [Source 1].
+**STAT 639**: The grading and workload are the same as CSCE 676 due to cross-listing [Source 1].
+### Prerequisites
+**CSCE 676**: Students are expected to have previous exposure to basic probability, statistics, algorithms, and data structures. They should also be able to design and develop large programs and learn new software libraries independently [Source 1].
+**ECEN 758**: The prerequisites are the same as CSCE 676 due to cross-listing [Source 1].
+**STAT 639**: The prerequisites are the same as CSCE 676 due to cross-listing [Source 1].
+### Learning Outcomes
+**CSCE 676**: Upon completion, learners will be able to:
+*   Define and explain key data mining and analysis concepts and models, including data preparation, normalization, dimensionality reduction, and text mining [Source 3].
+*   Design, implement, and evaluate data mining algorithms (e.g., associate rules, clustering, anomaly detection) on modern scalable cloud computing platforms (e.g., Spark) [Source 3].
+*   Identify salient features and apply recent research results in data mining, including topics like graph mining and large-scale mining [Source 3].
+**ECEN 758**: The learning outcomes are the same as CSCE 676 due to cross-listing [Source 1, 3].
+**STAT 639**: The learning outcomes are the same as CSCE 676 due to cross-listing [Source 1, 3].
+### Topics
+**CSCE 676**: The course schedule includes: Course introduction, Frequent Itemset Mining, Graph Mining, Graph Mining and Large-Scale ML, Large-Scale ML, Clustering, Text Mining, Data Mining and Distributed Computing, Anomaly Detection, Graph Embeddings, Locality-Sensitive Hashing, Stream Mining, and Hot Topics in Data Mining. The semester also includes a Project Showcase and time to Finalize Project Deliverables [Source 2].
+**ECEN 758**: The topics covered are the same as CSCE 676 due to cross-listing [Source 1, 2].
+**STAT 639**: The topics covered are the same as CSCE 676 due to cross-listing [Source 1, 2].
+### Materials
+**CSCE 676**: Course readings will be drawn from various online textbooks, scholarly papers, and other resources. A required textbook is "Mining of Massive Data Sets" by Jure Leskovec, Anand Rajaraman, and Jeffrey David Ullman (Cambridge University Press, 2020, ISBN: 9781108476348) [Source 3, 4].
+**ECEN 758**: The materials are the same as CSCE 676 due to cross-listing [Source 1, 3, 4].
+**STAT 639**: The materials are the same as CSCE 676 due to cross-listing [Source 1, 3, 4].</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>CSCE 676, Data Mining and Analysis, is cross-listed with the following courses, meaning they cover the same material and would "pair well" in the sense of being equivalent or highly related:
+*   **ECEN 758** [Source 1]
+*   **STAT 639** [Source 1]
+These courses are essentially the same content offered under different departmental designations, which can be useful for students in different programs who need to fulfill specific course requirements while studying data mining and analysis [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6852,6 +11992,41 @@
           <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6872,6 +12047,41 @@
           <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6907,6 +12117,112 @@
           <t>PLANNING</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>To build toward a research career in information retrieval, it is beneficial to acquire complementary skills in related areas such as data mining, machine learning, and natural language processing. These fields provide foundational knowledge and advanced techniques that are increasingly integrated into modern information retrieval systems.
+Based on the provided course descriptions, here are courses that would complement CSCE 670 (Information Storage and Retrieval) for a research career in this domain:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Relevance:** CSCE 670 covers modern topics like `word2vec`, `Neural Ranking`, `Transformer`, `BERT-Based Ranking`, `Neural Collaborative Filtering`, `Sequential Recommendation`, and `Large Language Models` [Source 3]. CSCE 638 directly focuses on `NLP fundamentals including language models, automatic syntactic processing and semantic understanding`, and `major NLP applications` [Source 8]. Its schedule includes `Word Representations`, `Language Modeling`, `Transformers`, `Contextualized Representations`, `Pre-Training`, `Large Language Models`, `Retrieval-Augmented Generation`, and `Bias Mitigation` [Source 9]. This course would provide a deeper theoretical and practical understanding of the language models and neural techniques that are critical for advanced information retrieval research, especially in areas like semantic search, question answering, and conversational AI.
+    *   **Career Relevance:** A strong background in NLP is essential for research roles in companies developing search engines, recommendation systems, virtual assistants, and any application involving understanding and processing human language at scale. It prepares students for roles such as NLP Scientist, Research Engineer, or Applied Scientist in AI/ML.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Relevance:** CSCE 670 deals with `representation, storage, and access to very large multimedia document collections` and `techniques to design and evaluate complete retrieval systems` [Source 1]. CSCE 676 offers a `broad overview of data mining, integrating related concepts from machine learning and statistics` [Source 7]. Its topics include `Frequent Itemset Mining`, `Graph Mining`, `Large-Scale ML`, `Clustering`, `Text Mining`, `Data Mining and Distributed Computing`, `Anomaly Detection`, `Graph Embeddings`, and `Stream Mining` [Source 6]. These techniques are highly applicable to analyzing large datasets, extracting patterns, and building scalable information retrieval and recommendation systems. The `Text Mining` component is particularly relevant for processing and understanding document collections.
+    *   **Career Relevance:** Data mining skills are crucial for roles in data science, machine learning engineering, and research where analyzing vast amounts of data to discover insights and build predictive models is key. This course would prepare students for positions involving large-scale data analysis, system optimization, and developing new data-driven algorithms for information systems.
+While CSCE 633 (Machine Learning) is foundational, CSCE 670 already incorporates many machine learning concepts specific to information retrieval and recommender systems [Source 3]. CSCE 638 and CSCE 676 offer more specialized and directly complementary knowledge for a research career focused on information retrieval.
+**Summary of Complementary Courses:**
+| Course | Description | Relevance to Information Retrieval Research | Career Relevance |
+| :---------------- | :----------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>To build toward a research career in information retrieval, taking complementary courses that deepen your understanding of related fields like Natural Language Processing (NLP), Machine Learning (ML), and Data Mining would be beneficial alongside CSCE 670.
+Here are some courses that align with a research career in information retrieval:
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Principle:** NLP is fundamental to information retrieval, as search engines and recommendation systems heavily rely on understanding and processing human language.
+    *   **Relevance:** This course focuses on NLP fundamentals, including language models, automatic syntactic processing, semantic understanding, and major NLP applications like information extraction, machine translation, text summarization, dialogue systems, and sentiment analysis [Source 8]. Its schedule includes topics such as Word Representations, Language Modeling, Transformers, Contextualized Representations, Pre-Training, and Large Language Models [Source 9]. These topics are directly applicable to advanced information retrieval research, especially given CSCE 670's coverage of Large Language Models with Search Engines and for Ranking and Recommendation [Source 3].
+    *   **Career Relevance:** A strong background in NLP is crucial for developing cutting-edge search algorithms, improving document understanding, and creating more intelligent retrieval systems. Researchers in this area often work on improving search relevance, developing conversational AI for information access, and building sophisticated content analysis tools.
+*   **CSCE 633: Machine Learning**
+    *   **Principle:** Machine learning provides the algorithms and techniques necessary to build, optimize, and evaluate modern information retrieval and recommendation systems.
+    *   **Relevance:** This course surveys machine learning techniques, including induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 11]. Many of the advanced topics in CSCE 670, such as Learning to Rank, Recommender Systems, and Neural Ranking, are deeply rooted in machine learning principles [Source 3].
+    *   **Career Relevance:** Machine learning skills are indispensable for research in information retrieval. Professionals in this field use ML to develop ranking algorithms, personalize search results, detect patterns in user behavior, and build predictive models for content recommendation. This expertise is highly valued in tech companies, research labs, and academia.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Principle:** Data mining techniques are essential for extracting valuable insights and patterns from large datasets, which is a core task in building effective information retrieval and recommendation systems.
+    *   **Relevance:** This course provides a broad overview of data mining, integrating concepts from machine learning and statistics. It covers exploratory data analysis, pattern mining, clustering, and classification, with applications to scientific and online data [Source 7]. Specific topics include Frequent Itemset Mining, Graph Mining, Large-Scale ML, Clustering, Text Mining, and Anomaly Detection [Source 6]. The course also emphasizes designing, implementing, and evaluating data mining algorithms on modern scalable cloud computing platforms [Source 10]. CSCE 670 also lists "Mining of Massive Datasets" as an optional resource [Source 2, 4], indicating the overlap and complementary nature of these fields.
+    *   **Career Relevance:** Data mining skills are critical for researchers who need to analyze vast amounts of data to understand user behavior, identify trends, and optimize retrieval performance. This includes working with web logs, user interaction data, and large document collections to discover hidden relationships and improve system efficiency and effectiveness.
+By combining CSCE 670 with courses like CSCE 638, CSCE 633, and CSCE 676, you would gain a comprehensive foundation in the theoretical underpinnings, practical techniques, and advanced research trends necessary for a successful research career in information retrieval.</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>To build a strong foundation for a research career in Information Retrieval (IR), it is beneficial to complement core IR knowledge with advanced skills in related disciplines such as machine learning, natural language processing, and large-scale data analysis. These fields provide the theoretical underpinnings and practical techniques essential for developing novel IR systems and conducting cutting-edge research.
+CSCE 670, "Information Storage and Retrieval," provides a comprehensive overview of IR, covering fundamental data structures and algorithms, techniques for designing and evaluating retrieval systems, and modern topics like web search, recommender systems, neural models, and Large Language Models (LLMs) [Source 1, 2, 3]. This course equips students with the ability to define key concepts, design and implement core algorithms, and apply recent research results in IR [Source 2].
+To further enhance your research capabilities alongside CSCE 670, consider the following courses:
+*   **CSCE 633: Machine Learning**
+    *   **Relevance:** Many advanced IR techniques, including learning to rank, neural ranking, and sophisticated recommender systems, are deeply rooted in machine learning [Source 3]. CSCE 633 focuses on formalizing fundamental machine learning techniques, analyzing various approaches, evaluating mathematical relationships within algorithms, and designing/implementing these algorithms for real-world applications [Source 6, 9]. A strong understanding of machine learning is crucial for developing and optimizing modern IR systems.
+    *   **Career Relevance:** Expertise in machine learning is highly sought after in research roles at tech companies (e.g., Google, Amazon, Meta) for improving search algorithms, recommendation engines, and data-driven product features. It's also fundamental for academic research in AI and data science.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Relevance:** Information Retrieval often deals with vast amounts of text data. CSCE 670 covers topics like `word2vec`, `Transformer`, `BERT-Based Ranking`, and `Large Language Models` [Source 3]. CSCE 638 provides the foundational knowledge of NLP, including language models, syntactic processing, semantic understanding, and major NLP applications [Source 11]. This course is essential for understanding how to process, analyze, and leverage textual information effectively in IR research, especially with the rise of LLMs.
+    *   **Career Relevance:** NLP skills are critical for research scientists working on search engines, conversational AI, text analytics, and information extraction. These roles exist in both industry and academia, focusing on making sense of human language data.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Relevance:** Research in IR often involves working with massive datasets. CSCE 676 provides a broad overview of data mining, integrating concepts from machine learning and statistics, and covers exploratory data analysis, pattern mining, clustering, and classification [Source 10]. Topics like `text mining`, `graph mining`, `large-scale ML`, `data mining and distributed computing`, and `Locality-Sensitive Hashing` [Source 7, 12] are directly applicable to handling and extracting insights from the large-scale data encountered in IR. The course also uses "Mining of Massive Datasets," which is an optional resource for CSCE 670 [Source 4, 12].
+    *   **Career Relevance:** Data mining and analysis skills are vital for research scientists and data scientists who need to process, analyze, and derive insights from large, complex datasets. This is applicable in various industries, including e-commerce, social media, and scientific research, where understanding user behavior and data patterns is key.
+By combining CSCE 670 with these complementary courses, you will gain a robust understanding of both the core principles of information retrieval and the advanced techniques from machine learning, natural language processing, and data mining that are critical for conducting impactful research in the field.</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>To build toward a research career in information retrieval, it is beneficial to take courses that provide a strong foundation in core information retrieval concepts, as well as complementary skills in related fields such as machine learning and natural language processing. These areas are crucial for developing advanced retrieval models, understanding data, and working with modern AI techniques in IR.
+Alongside CSCE 670, which covers fundamental data structures and algorithms for information storage and retrieval systems, including web search, recommender systems, and recent advancements like neural models and Large Language Models (LLMs) [Source 1, 2, 3], consider the following courses:
+*   **CSCE 633: Machine Learning**
+    *   **Relevance:** This course focuses on the fundamental techniques and methods of machine learning, including data processing, model selection, and advanced algorithms [Source 6, 9]. A strong understanding of machine learning is essential for research in information retrieval, particularly for developing sophisticated ranking algorithms, recommender systems, and neural retrieval models, which are explicitly covered in CSCE 670 [Source 2, 3]. Machine learning provides the tools to analyze and learn from large datasets to improve retrieval performance.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Relevance:** This course covers NLP fundamentals such as language models, syntactic processing, semantic understanding, and applications like information extraction and text summarization [Source 11]. Given that information retrieval primarily deals with textual data and CSCE 670 includes topics like `word2vec`, `Transformer`, `BERT-Based Ranking`, and `Large Language Models` [Source 3], NLP knowledge is critical. It enables researchers to better process, understand, and generate human language, which is central to advanced IR systems.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Relevance:** This course provides a broad overview of data mining, integrating concepts from machine learning and statistics, covering exploratory data analysis, pattern mining, clustering, and classification [Source 10]. It also delves into topics like graph mining and large-scale mining [Source 12]. These skills are valuable for handling and extracting insights from the massive datasets typical in information retrieval, and for designing scalable solutions for IR problems.
+By combining CSCE 670 with courses in Machine Learning and Natural Language Processing, you will gain a comprehensive skill set that is highly relevant for a research career in information retrieval, enabling you to design, implement, and evaluate cutting-edge retrieval and recommendation systems.</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>To build a strong foundation for a research career in Information Retrieval, it is beneficial to complement your core studies with courses that deepen your understanding of related computational fields, particularly those involving data analysis, machine learning, and natural language processing. These areas provide essential tools and theoretical frameworks that are increasingly integral to advanced Information Retrieval research.
+Based on the provided context, here are courses that would significantly complement CSCE 670 (Information Storage and Retrieval) for a research career:
+1.  **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it's relevant:** CSCE 670 covers topics like `word2vec`, `Neural Ranking`, `Transformer`, `BERT-Based Ranking`, and `Large Language Models` [Source 3]. CSCE 638 directly focuses on `NLP fundamentals including language models, automatic syntactic processing and semantic understanding`, and `major NLP applications` [Source 11]. Its schedule includes `Word Representations`, `Language Modeling`, `Transformers`, `Contextualized Representations`, `Pre-Training`, `Large Language Models`, `Retrieval-Augmented Generation`, and more [Source 8]. This course would provide a deeper theoretical and practical understanding of the language-related technologies that are at the forefront of modern Information Retrieval.
+    *   **Planning Dimension:** Taking CSCE 638 alongside or after CSCE 670 would equip you with specialized knowledge in how language is processed and understood by machines, which is critical for developing advanced search, recommendation, and question-answering systems.
+2.  **CSCE 633: Machine Learning**
+    *   **Why it's relevant:** CSCE 670 incorporates `Learning to Rank`, `Neural Ranking`, and various `Recommender Systems` which are heavily rooted in machine learning principles [Source 3]. CSCE 633 focuses on `fundamental techniques and methods of machine learning`, `analyzing and comparing the strengths and weaknesses of commonly used machine learning approaches`, and `designing, implementing, and applying various advanced machine learning algorithms` [Source 6, 9].
+    *   **Planning Dimension:** A solid background in machine learning from CSCE 633 would enable you to understand, adapt, and innovate on the algorithms used for ranking, recommendation, and other data-driven aspects of Information Retrieval, making you a more versatile researcher.
+3.  **CSCE 676: Data Mining and Analysis**
+    *   **Why it's relevant:** CSCE 670 deals with `storage and retrieval of very large multimedia document collections` [Source 1]. CSCE 676 provides a `broad overview of data mining, integrating related concepts from machine learning and statistics`, covering `exploratory data analysis, pattern mining, clustering and classification` [Source 10]. Its schedule includes `Frequent Itemset Mining`, `Graph Mining`, `Large-Scale ML`, `Clustering`, `Text Mining`, and `Data Mining and Distributed Computing` [Source 7]. Both CSCE 670 and CSCE 676 list "Mining of Massive Datasets" as a resource [Source 2, 4, 12].
+    *   **Planning Dimension:** This course would provide you with skills in handling and extracting insights from large datasets, which is fundamental to Information Retrieval research, especially when dealing with web-scale data or complex user behavior patterns.
+By combining CSCE 670 with these courses, you would gain a comprehensive understanding of the theoretical underpinnings, practical algorithms, and cutting-edge techniques across Information Retrieval, Natural Language Processing, Machine Learning, and Data Mining, which are all crucial for a successful research career in the field.</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>For a research career in information retrieval, it is beneficial to build a strong foundation in related computational fields such as machine learning, natural language processing, and data mining, as these disciplines often provide the theoretical and practical tools necessary for advanced research in IR.
+To complement CSCE 670 (Information Storage and Retrieval) and build toward a research career in this area, you might consider taking the following courses:
+*   **CSCE 633: Machine Learning**
+    *   **Relevance:** CSCE 670 covers topics like "Learning to Rank," "Neural Ranking," "word2vec," and "BERT-Based Ranking" [Source 3], which are deeply rooted in machine learning principles. CSCE 633 focuses on "self-modifying computer systems that can acquire new knowledge and improve their own performance" and surveys various machine learning techniques [Source 6]. A strong understanding of machine learning is crucial for developing and evaluating advanced retrieval and recommendation systems.
+*   **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Relevance:** CSCE 670 extensively discusses "Large Language Models Basics," "Large Language Models with Search Engines," and "Large Language Models for Ranking and Recommendation" [Source 3], as well as "Transformer" and "BERT-Based Ranking" [Source 3]. CSCE 638 focuses on "NLP fundamentals including language models, automatic syntactic processing and semantic understanding" and major NLP applications [Source 8]. Given the increasing role of LLMs and NLP in modern information retrieval, this course would provide essential background.
+*   **CSCE 676: Data Mining and Analysis**
+    *   **Relevance:** CSCE 670 lists "Mining of Massive Datasets" as an optional textbook [Source 4], and its content involves handling "very large multimedia document collections" [Source 1]. CSCE 676 provides a "broad overview of data mining, integrating related concepts from machine learning and statistics," covering "exploratory data analysis, pattern mining, clustering and classification" [Source 9]. Topics like "Text Mining" and "Large-Scale ML" from CSCE 676 [Source 7] directly support the analysis and processing of large datasets common in information retrieval research.
+By taking these courses alongside CSCE 670, you would gain a comprehensive skill set in the theoretical underpinnings and practical applications of machine learning, natural language processing, and data mining, which are all highly relevant for a research career in information retrieval. This multidisciplinary approach will enable you to tackle complex research problems and contribute to the evolving landscape of IR.</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>To build a research career in information retrieval, taking courses that complement CSCE 670 by deepening your understanding of related fields like Natural Language Processing and Data Mining would be highly beneficial.
+Here are two courses you could consider taking alongside CSCE 670:
+1.  **CSCE 638: Natural Language Processing: Foundations and Techniques**
+    *   **Why it complements CSCE 670**: CSCE 670 covers advanced topics like Neural Ranking, BERT-Based Ranking, and Large Language Models (LLMs) in the context of search engines and recommendation systems [Source 3]. CSCE 638 provides a foundational and in-depth understanding of NLP, including language models, transformers, contextualized representations, pre-training, and LLMs [Source 9]. This course would equip you with the core NLP knowledge essential for cutting-edge research in information retrieval, especially with the increasing role of neural methods and LLMs in the field.
+    *   **Planning Dimension**: Taking CSCE 638 would provide the theoretical and practical NLP background that directly supports and enhances the application-focused NLP topics covered in CSCE 670, allowing for a more comprehensive understanding of how language processing techniques are integrated into retrieval systems.
+2.  **CSCE 676: Data Mining and Analysis**
+    *   **Why it complements CSCE 670**: Information retrieval systems often deal with massive datasets. CSCE 676 offers a broad overview of data mining, integrating concepts from machine learning and statistics, and covers techniques like exploratory data analysis, pattern mining, clustering, classification, and text mining [Source 7]. It also delves into topics such as graph mining, large-scale machine learning, and data mining on distributed computing platforms [Source 6, 10]. The "Mining of Massive Datasets" textbook is a required resource for CSCE 676 and an optional resource for CSCE 670, highlighting the strong synergy between the two courses [Source 10, 2].
+    *   **Planning Dimension**: This course would provide you with critical skills in analyzing and extracting insights from large data collections, which is fundamental for designing, evaluating, and improving information retrieval systems. It would also expose you to scalable data processing techniques relevant to real-world IR research.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6924,7 +12240,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>recursive</t>
+          <t>semantic_general</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6940,6 +12256,109 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>POLICY</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses permit or encourage the use of AI tools for assignments, each with specific guidelines:
+*   **CSCE 624 (202611)**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including what tool was used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 1, 2, 3].
+*   **CSCE 713 (202611)**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible, to allow the instructor to evaluate the student's rationale to solve the problem [Source 4].
+*   **CSCE 614 (202611)**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments. AI is intended to help students get started with ideas or provide feedback, not to do all the work. Any AI-generated material must be cited, and using AI without proper attribution is academic dishonesty. No more than 30% of an assignment should come directly from AI-generated text [Source 6].
+*   **CSCE 632 (202611)**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments. These tools can help brainstorm ideas or provide feedback but should not complete the work. AI-generated content must be cited, and failure to attribute is academic dishonesty. No more than 30% of any assignment should consist of AI-generated text [Source 7].
+*   **CSCE 670 (202611)**: AI-generated code, or code based on or derived from AI-generated code, may be submitted as long as its use is properly documented in comments (including the prompt and significant parts of the response). AI tools may help avoid syntax errors, but students are responsible for identifying errors through comprehensive, documented testing. The submission must meet standards of attribution and validation [Source 8].
+*   **CSCE 726 (202611)**: The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 5].
+*   **CSCE 641 (202611)**: The use of large language models (e.g., ChatGPT, Copilot, Claude) is not strictly prohibited but may only be used for debugging or clarification purposes, not for generating code. Students are expected to write all code themselves, and copying or modifying AI-generated code is not permitted. If any AI tool is used, even for conceptual questions, a transcript of the full interaction must be submitted with the work. Failure to adequately explain one's own code will be considered an honor code violation [Source 9].</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses permit or generally accept the use of AI tools for assignments, often with specific guidelines for documentation and attribution:
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL-E 2) are permitted on assignments. Students must cite any AI-generated material that informed their work, and generally, no more than 30% of an assignment should come directly from AI-generated text [Source 2].
+*   **CSCE 624**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including what tool was used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 1, 6, 10].
+*   **CSCE 632**: Students are permitted to use generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) to assist with assignments. These tools can help brainstorm ideas or provide feedback but should not complete the work. Students must cite any AI-generated content, and no more than 30% of any assignment should consist of AI-generated text [Source 3].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts provided, and describe how they evaluated the output. Submitting work with a significant percentage of AI-generated content without permission can be considered academic misconduct [Source 5].
+*   **CSCE 670**: AI-generated code, or code based on or derived from AI-generated code, may be submitted as long as its use is properly documented in the comments, including the prompt and significant parts of the response. Students are responsible for identifying errors and improving generated code [Source 4].
+*   **CSCE 713**: The use of AI support is allowed for assignments if all AI interactions (prompts, responses, chatbot session links) are delivered to the instructor to allow evaluation of the student's rationale [Source 8].
+Some courses have more restrictive policies regarding AI use for assignments:
+*   **CSCE 726**: The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 7].
+*   **CSCE 748**: Large language models (e.g., ChatGPT, Copilot, Claude) are not strictly prohibited but may only be used for debugging or clarification purposes, not for generating code. Students are expected to write all code themselves, and copying or modifying AI-generated code is not permitted. Any AI tool use requires submitting a transcript of the full interaction [Source 9].</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses permit or generally accept the use of AI tools for assignments, often with specific conditions regarding documentation, attribution, and the nature of their use.
+Here's a breakdown by course:
+*   **CSCE 614 (202611)**: Generative AI tools (e.g., ChatGPT, Google Bard, Dall-E 2) are permitted on assignments. They are intended to help with ideas or provide feedback, not to do all the work. Students must cite any AI-generated material that informed their work, including in-text citations and reference list entries. No more than 30% of an assignment should come directly from AI-generated text. [Source 7]
+*   **CSCE 624 (202611)**: AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including what tool was used, how it was used, and how the student validated or modified the output. Students remain fully responsible for the correctness, originality, and understanding of all submitted work. [Source 1, Source 4]
+*   **CSCE 632 (202611)**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments. These tools can help brainstorm ideas or provide feedback but should not complete the work. Students must cite any AI-generated content that informs their work, and failure to attribute is considered academic dishonesty. No more than 30% of any assignment should consist of AI-generated text. [Source 3]
+*   **CSCE 633 (202611)**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including prompts provided, and describe how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct. Students must cite the use of Generative AI tools and document their contribution to an assignment. [Source 8]
+*   **CSCE 641 (202611)**: Large language models (e.g., ChatGPT, Copilot, Claude) are not strictly prohibited. However, they may only be used for debugging or clarification purposes, not for generating code. Students are expected to write all code themselves, and copying or modifying AI-generated code is not permitted. If any AI tool is used, a transcript of the full interaction must be submitted with the work. [Source 9]
+*   **CSCE 713 (202611)**: The use of AI support is allowed if any assignment delivered is followed by the delivery of all AI interactions (prompts, responses, chatbot session links) to the most complete extent possible, to allow the instructor to evaluate the student's rationale. [Source 5]
+*   **CSCE 748 (202611)**: Large language models (e.g., ChatGPT, Copilot, Claude) are not strictly prohibited. However, they may only be used for debugging or clarification purposes, not for generating code. Students are expected to write all code themselves, and copying or modifying AI-generated code is not permitted. If any AI tool is used, a transcript of the full interaction must be submitted with the work. [Source 6]
+**Courses where AI tools are prohibited for assignments:**
+*   **CSCE 612 (202611)**: Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating. [Source 10]
+*   **CSCE 726 (202611)**: The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing writing or assisting in debugging code. [Source 2]</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>The use of Artificial Intelligence (AI) tools in academic settings is governed by principles of academic integrity and responsible use of emerging technologies. These principles aim to balance the potential benefits of AI for learning and productivity with the necessity of ensuring original thought, proper attribution, and the development of essential student skills. Individual course syllabi at Texas A&amp;M University define the specific boundaries and expectations for AI tool usage, often requiring documentation, citation, and adherence to limits on AI-generated content.
+Based on the provided syllabi for CSCE graduate courses, several allow or permit the use of AI tools for assignments, subject to specific conditions:
+*   **CSCE 624**: AI tools may be used for assignments or projects when explicitly permitted. Students must clearly document the tool used, how it was used, and how the output was validated or modified. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 1, 4].
+*   **CSCE 632**: Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments, but should not complete the work. Students must cite any AI-generated content that informs their work, including in-text citations and reference list entries. No more than 30% of any assignment should consist of AI-generated text [Source 3].
+*   **CSCE 713**: AI support is allowed for assignments, provided that all AI interactions (prompts, responses, chatbot session links) are delivered to the instructor. This allows the instructor to evaluate the student's rationale in solving the problem [Source 5].
+*   **CSCE 614**: Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments to help brainstorm ideas or provide feedback, but not to do all the work. Any AI-generated material must be cited, and generally, no more than 30% of an assignment should come directly from AI-generated text [Source 7].
+*   **CSCE 633**: The use of Generative AI tools is generally accepted. Students are expected to document how the tools were used, including the prompts provided, and describe how they evaluated the output. Submitting work with a significant percentage of AI-generated content, unless otherwise permitted, can be considered academic misconduct [Source 8].
+Other courses have more restrictive policies regarding AI use for assignments:
+*   **CSCE 748** and **CSCE 641**: AI tools like large language models are not strictly prohibited but may only be used for debugging or clarification purposes, not for generating code. If used, a transcript of the full interaction must be submitted with the work [Source 6, 9].
+*   **CSCE 726**: The use of AI tools for completing homework assignments, exams, or the course project is strictly prohibited, though they are acceptable for editing writing or assisting in debugging code [Source 2].
+*   **CSCE 612**: Any usage of AI, copilot, or LLMs is prohibited, with violations treated as cheating [Source 10].</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The use of AI tools in CSCE graduate courses varies significantly by course. Some courses permit their use under specific conditions, while others strictly prohibit them for assignments.
+Here's a breakdown of the policies for the courses provided:
+| Course    | AI Tool Usage for Assignments                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>The use of AI tools in CSCE graduate courses at Texas A&amp;M University varies significantly by course, reflecting different approaches to academic integrity and the integration of emerging technologies. Policies range from strict prohibition to conditional allowance for specific tasks, emphasizing responsible and documented use [Source 6, 10].
+Based on the provided syllabi, the following CSCE graduate courses allow or permit the use of AI tools for assignments, with specific conditions:
+*   **CSCE 614**
+    *   **Policy:** Generative AI tools (e.g., ChatGPT, Google Bard, Dall-E 2) are permitted on assignments to help with ideas or provide feedback.
+    *   **Conditions:** Any AI-generated material that informed your work must be cited (in-text and in a reference list). No more than 30% of an assignment should come directly from AI-generated text [Source 10].
+*   **CSCE 624**
+    *   **Policy:** AI tools may be used when explicitly permitted for assignments or projects.
+    *   **Conditions:** Any AI assistance must be clearly documented, including the tool used, how it was used, and how the output was validated or modified. Students remain fully responsible for the correctness, originality, and understanding of all submitted work [Source 1, 4, 7].
+*   **CSCE 632**
+    *   **Policy:** Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments for brainstorming ideas or providing feedback.
+    *   **Conditions:** These tools should not complete your work. Any AI-generated content that informs your work must be cited, and no more than 30% of any assignment should consist of AI-generated text [Source 6].
+*   **CSCE 670**
+    *   **Policy:** Students may submit AI-generated code, or code based on or derived from AI-generated code.
+    *   **Conditions:** This use must be properly documented in the comments, including the prompt and significant parts of the response. Students are responsible for identifying errors in program logic through comprehensive, documented testing [Source 9].
+Additionally, some courses permit AI tools for more limited, supportive tasks rather than direct content generation for assignments:
+*   **CSCE 641 &amp; CSCE 748**
+    *   **Policy:** The use of large language models (e.g., ChatGPT, Copilot, Claude) is not strictly prohibited.
+    *   **Conditions:** These tools may be used *only* for debugging or clarification purposes, not for generating code. Students are expected to write all code themselves, and copying or modifying AI-generated code is not permitted. A transcript of the full interaction must be submitted with the work if any AI tool is used [Source 5, 8].
+*   **CSCE 726**
+    *   **Policy:** The use of AI tools for completing homework assignments, exams, or the course project is strictly prohibited.
+    *   **Conditions:** It is acceptable to use them for tasks such as editing writing or assisting in debugging code [Source 2].
+In contrast, **CSCE 612** explicitly prohibits any usage of AI, copilot, or LLMs, treating violations as cheating [Source 3].</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses permit or encourage the use of AI tools for assignments, with varying conditions and requirements for documentation:
+*   **CSCE 624** (term 202611): AI tools may be used when explicitly permitted for assignments or projects. Any AI assistance must be clearly documented, including the tool used, how it was used, and how the output was validated or modified. Students are fully responsible for the correctness, originality, and understanding of all submitted work [Source 1, Source 2].
+*   **CSCE 614** (term 202611): Generative AI tools (e.g., ChatGPT, Google, Bard, Dall-E 2) are permitted on assignments. They are intended to help with ideas or provide feedback, not to do all the work. Any AI-generated material must be cited, and no more than 30% of an assignment should come directly from AI-generated text. Failure to attribute AI-generated content is considered academic dishonesty [Source 6].
+*   **CSCE 632** (term 202611): Generative AI tools (e.g., ChatGPT, Google Bard, DALL·E 2) are permitted to assist with assignments. These tools can help brainstorm ideas or provide feedback but should not complete the work. Any AI-generated content must be cited, and no more than 30% of any assignment should consist of AI-generated text. Failure to properly attribute AI-generated material is considered academic dishonesty [Source 7].
+*   **CSCE 670** (term 202611): AI-generated code, or code based on or derived from AI-generated code, may be submitted if properly documented in the comments (including the prompt and significant parts of the response). Students are responsible for identifying errors and ensuring the code meets attribution and validation standards [Source 8].
+*   **CSCE 748** (term 202611): The use of large language models (e.g., ChatGPT, Copilot, Claude) is not strictly prohibited but is limited to debugging or clarification purposes, not for generating code. All code must be written by the student, and copying or modifying AI-generated code is not permitted. Any AI tool usage, even for conceptual questions, requires submitting a transcript of the full interaction [Source 9].
+*   **CSCE 641** (term 202611): Similar to CSCE 748, large language models are not strictly prohibited but are only for debugging or clarification, not code generation. Students must write all code themselves. If any AI tool is used, a transcript of the full interaction must be submitted with the work [Source 10].
+**CSCE 612** (term 202611) explicitly prohibits any usage of AI, copilot, or LLMs, stating that violations will be treated as cheating and result in an F* [Source 4].
+**CSCE 726** (term 202611) strictly prohibits the use of AI tools for completing homework assignments, exams, or the course project, but it is acceptable for tasks such as editing writing or assisting in debugging code [Source 5].</t>
         </is>
       </c>
     </row>
@@ -6982,6 +12401,63 @@
           <t>LOGISTICAL</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following CSCE graduate courses require buying a textbook:
+*   **CSCE 608** [Source 1]
+    *   **Textbook:** *Database Systems: The Complete Book* by H. Garcia-Molina, J. Ullman, and J. Widom.
+*   **CSCE 629** [Source 6]
+    *   **Textbook:** *Introduction to Algorithms, fourth edition* by Thomas H. Cormen, Charles E. Leiserson, Ronald L. Rivest, Clifford Stein. (Note: This is also freely available as an ebook from the library).
+*   **CSCE 632** [Source 8]
+    *   **Textbook:** *Ensuring Digital Accessibility Through Process And Policy* by Jonathan Lazar, Daniel Goldstein, and Anne Taylor.
+    *   **Textbook:** *A Web For Everyone: Designing Accessible User Experiences* by Sarah Horton and Whitney Quesenbery.
+*   **CSCE 652** [Source 2, 9]
+    *   **Textbook:** *Practical Malware Analysis* by Michael Sikorski, Andrew Honig. (Note: This is also freely available as an ebook from the library).
+*   **CSCE 614** [Source 10]
+    *   **Textbook:** *Computer Architecture* by John L. Hennessy, David A. Patterson.
+Other courses either state that no textbook is required, materials are provided by the instructor, or the listed materials are optional or supplementary.</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Based on the provided syllabi, none of the CSCE graduate courses explicitly state that buying a textbook is required. Some courses list textbooks as "Recommended" or "Optional", while others do not specify the status of their resource materials [Source 1, Source 3].
+I don't have enough data to answer this accurately based on the available syllabi.</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The syllabi provided indicate that textbooks are either "Recommended" or "Optional" for CSCE 612 and CSCE 670, respectively, but none explicitly state that buying a textbook is required [Source 1, Source 3]. For other courses, textbook information is not available in the provided context [Source 4, Source 5, Source 6, Source 7, Source 8, Source 9, Source 10].</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Based on the provided syllabi, the following CSCE graduate courses require buying a textbook:
+*   **CSCE 608**: "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom [Source 3]
+*   **CSCE 652**: "Practical Malware Analysis" by Michael Sikorski and Andrew Honig [Source 5]
+*   **CSCE 629**: "Introduction to Algorithms, fourth edition" by Thomas H. Cormen, Charles E. Leiserson, Ronald L. Rivest, Clifford Stein [Source 8]</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Based on the provided syllabi, the following CSCE graduate courses require buying a textbook:
+*   **CSCE 608**: "Database Systems: The Complete Book" is a required textbook [Source 3].
+*   **CSCE 652**: "Practical Malware Analysis" is a required textbook [Source 5].
+*   **CSCE 629**: "Introduction to Algorithms, fourth edition" is a required textbook [Source 8].</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Based on the provided context, the following CSCE graduate courses require buying a textbook:
+*   **CSCE 608**: "Database Systems: The Complete Book" by H. Garcia-Molina, J. Ullman, and J. Widom [Source 3]
+*   **CSCE 652**: "Practical Malware Analysis" by Michael Sikorski and Andrew Honig [Source 5]
+*   **CSCE 629**: "Introduction to Algorithms, fourth edition" by Thomas H. Cormen, Charles E. Leiserson, Ronald L. Rivest, Clifford Stein [Source 8]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7027,6 +12503,42 @@
           <t>LOGISTICAL</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>The prerequisite for CSCE 629, Section 600 (54978), is graduate classification [Source 1].</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>The prerequisite for CSCE 629, Section 600 (54978), is graduate classification [Source 1].</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>To enroll in CSCE 629, you need to have **Graduate classification** [Source 1].</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>To enroll in CSCE 629, the primary prerequisite is **Graduate classification** [Source 1].</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>To enroll in CSCE 629, "Analysis of Algorithms," you must have graduate classification [Source 1].</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>To enroll in CSCE 629, the prerequisite is graduate classification [Source 1].
+This means you must be admitted as a graduate student at Texas A&amp;M University to take this course. Understanding this prerequisite helps in planning your academic progression, as it confirms that CSCE 629 is intended for students who have already achieved graduate standing.</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>The prerequisite for CSCE 629, Section 600, is graduate classification [Source 1].</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7062,6 +12574,121 @@
           <t>PLANNING</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Course prerequisites are foundational requirements designed to ensure students possess the necessary knowledge and skills to succeed in a particular course. They are crucial for academic planning, as they dictate the sequence in which courses can be taken and help students identify appropriate entry points into different areas of study.
+Based on the provided syllabi, the CSCE graduate courses with the lightest prerequisites, offering the most flexibility, are those that primarily require "approval of instructor" or a single undergraduate course:
+*   **CSCE 648: Computer Aided Sculpting** [Source 9]
+    *   **Prerequisites:** Approval of instructor.
+*   **CSCE 608: Database Systems** [Source 6]
+    *   **Prerequisites:** CSCE 310 or approval of Instructor.
+*   **CSCE 652: Reverse Engineering and Malware Analysis** [Source 8]
+    *   **Prerequisites:** CSCE 313 or approval of instructor.
+*   **CSCE 670: Information Storage and Retrieval** [Source 1]
+    *   **Prerequisites:** CSCE 310 or CSCE 603 or approval of instructor; graduate classification.
+*   **CSCE 611: Operating Systems** [Source 10]
+    *   **Prerequisites:** CSCE 313; graduate classification.
+*   **CSCE 614: Computer Architecture** [Source 3]
+    *   **Prerequisites:** CSCE 350/ECEN 350, ECEN 350/CSCE 350, or CSCE 312; background in undergraduate computer engineering or computer science.
+*   **CSCE 713: Software Security** [Source 5]
+    *   **Prerequisites:** CSCE 431 or CSCE 606 or approval of instructor; graduate classification.
+*   **CSCE 672: Computer Supported Collaborative Work** [Source 2]
+    *   **Prerequisites:** CSCE 671 or CSCE 610 or approval of instructor.
+For academic planning, courses that list "approval of instructor" as a prerequisite or an alternative to specific course numbers offer significant flexibility. This means that if you have equivalent knowledge or experience, you might be able to enroll even without having taken the exact prerequisite courses, provided the instructor grants approval. Courses requiring only undergraduate-level courses (e.g., CSCE 310, 312, 313, 350, 431) are also considered lighter as they do not necessitate prior graduate-level coursework in that specific area.
+CSCE 669 (Computational Optimization) has a prerequisite of CSCE 629 [Source 7], which is a graduate-level course, making its prerequisites less "light" compared to the others.</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>The principle of **Prerequisite Structure and Academic Progression** ensures that students have the necessary foundational knowledge before enrolling in a course, facilitating a smoother learning experience and successful academic progression. Prerequisites can vary in their specificity and level, influencing how accessible a course is to students at different stages of their academic journey or with diverse backgrounds.
+Based on the provided syllabi, the CSCE graduate courses with the lightest prerequisites are those that primarily require instructor approval or a single undergraduate course.
+The course with the absolute lightest prerequisite is:
+*   **CSCE 648 (Computer Aided Sculpting)**: Requires only "Approval of instructor" [Source 9]. This offers the most flexibility, as it allows the instructor to assess a student's readiness directly, potentially bypassing specific course numbers if the student demonstrates equivalent knowledge or relevant experience.
+Other courses that offer relatively light prerequisites, often including an "approval of instructor" option or a single undergraduate course, are:
+*   **CSCE 608 (Database Systems)**: Requires CSCE 310 or approval of Instructor [Source 6].
+*   **CSCE 652 (Reverse Engineering and Malware Analysis)**: Requires CSCE 313 or approval of instructor [Source 8].
+*   **CSCE 670 (Information Storage and Retrieval)**: Requires CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1]. (Note: CSCE 310 is an undergraduate course, making this an accessible option if CSCE 603 is not met).
+*   **CSCE 611 (Operating Systems)**: Requires CSCE 313; graduate classification [Source 4, 10].
+*   **CSCE 672 (Computer Supported Collaborative Work)**: Requires CSCE 671 or CSCE 610 or approval of instructor [Source 2]. (Note: While CSCE 671 and CSCE 610 are graduate courses, the "approval of instructor" option provides flexibility).
+**For Academic Planning:**
+When considering these courses, students should:
+1.  **Review their transcript:** Check if they have completed the listed undergraduate prerequisites (e.g., CSCE 310, CSCE 313).
+2.  **Assess their background:** If they do not meet the formal course prerequisites but believe they have equivalent knowledge or experience, the "approval of instructor" option is a valuable pathway to discuss with the professor.
+3.  **Consider their degree plan:** Even with light prerequisites, ensure the course aligns with their academic goals and degree requirements. These courses might be suitable for students early in their graduate studies or those transitioning from different undergraduate specializations.</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>The "lightness" of a course's prerequisites refers to the minimal specific prior coursework or conditions required for enrollment. Courses with lighter prerequisites are generally more accessible to students who may not have a specific undergraduate background in that exact field or are looking to explore new areas within their graduate studies.
+Based on the provided syllabi, the CSCE graduate courses with the lightest prerequisites are those that primarily require "approval of instructor" or "graduate classification" without mandating specific prior course numbers:
+| Course Number | Course Name                 | Prerequisites                                          | Source |
+| :------------ | :-------------------------- | :----------------------------------------------------- | :----- |
+| CSCE 648      | Computer Aided Sculpting    | Approval of instructor [Source 5]                      | [5]    |
+| CSCE 679      | Data Visualization          | Graduate classification or approval of instructor [Source 6] | [6]    |
+Other courses have prerequisites that include specific undergraduate or graduate course numbers, though some also offer "approval of instructor" as an alternative:
+*   **CSCE 670 (Information Storage and Retrieval)**: CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1]
+*   **CSCE 713 (Software Security)**: CSCE 431 or CSCE 606 or approval of instructor; graduate classification [Source 3]
+*   **CSCE 641 (Computer Graphics)**: CSCE 441 or approval of instructor [Source 8]
+*   **CSCE 652 (Software Reverse Engineering)**: CSCE 313 or approval of instructor [Source 9, 10]
+*   **CSCE 611 (Operating Systems)**: CSCE 313; graduate classification [Source 7]
+*   **CSCE 614 (Computer Architecture)**: CSCE 350/ECEN 350, ECEN 350/CSCE 350, or CSCE 312; background in undergraduate computer engineering or computer science [Source 2]
+*   **CSCE 669 (Computational Optimization)**: CSCE 629 [Source 4]
+**Academic Planning Dimension:**
+For academic planning, courses with "approval of instructor" or "graduate classification" as their primary prerequisite offer flexibility. They can be good options for students early in their graduate program, those transitioning from different undergraduate disciplines, or students wishing to explore interdisciplinary topics without needing to fulfill extensive prior coursework. If you are interested in one of these courses but lack a specific prerequisite listed for other courses, reaching out to the instructor for approval could be a viable path to enrollment.</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Course prerequisites are established to ensure students possess the foundational knowledge necessary for success in a particular subject. When planning your academic progression, understanding these requirements is key to selecting courses that align with your current academic standing and future goals. Courses with "lighter" prerequisites offer more flexibility, potentially allowing students with diverse backgrounds or those exploring new areas to enroll, provided they meet the general graduate requirements or receive instructor approval.
+Based on the provided syllabi for Spring 2026, the CSCE graduate courses with the lightest prerequisites are:
+*   **CSCE 648 (Computer Aided Sculpting)**: Requires "Approval of instructor" [Source 5].
+*   **CSCE 679 (Data Visualization)**: Requires "Graduate classification or approval of instructor" [Source 6].
+These courses primarily rely on either general graduate status or direct instructor assessment of your readiness, rather than specific prior CSCE course numbers. Other courses, while sometimes offering "approval of instructor" as an alternative, also list specific prerequisite courses:
+*   **CSCE 670 (Information Storage and Retrieval)**: CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 1].
+*   **CSCE 713 (Software Security)**: CSCE 431 or CSCE 606 or approval of instructor; graduate classification [Source 3].
+*   **CSCE 641 (Computer Graphics)**: CSCE 441 or approval of instructor [Source 8].
+*   **CSCE 652 (Software Reverse Engineering)**: CSCE 313 or approval of instructor [Source 9, 10].
+Courses with more specific course prerequisites include:
+*   **CSCE 669 (Computational Optimization)**: CSCE 629 [Source 4].
+*   **CSCE 611 (Operating Systems)**: CSCE 313; graduate classification [Source 7].
+*   **CSCE 614 (Computer Architecture)**: CSCE 350/ECEN 350, ECEN 350/CSCE 350, or CSCE 312; background in undergraduate computer engineering or computer science [Source 2].</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">To determine which CSCE graduate courses have the "lightest prerequisites," we look for courses that require the fewest prior courses, particularly those that can be satisfied by undergraduate coursework or direct instructor approval, rather than requiring other graduate-level courses. This allows students more flexibility in their academic progression, especially early in their graduate studies or when transitioning between specializations.
+Based on the provided syllabi for Spring 2026, the following CSCE graduate courses have prerequisites that include undergraduate courses or primarily rely on instructor approval:
+| Course Number | Course Name                     | Prerequisites                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Course prerequisites are established to ensure students possess the foundational knowledge necessary to succeed in a given course. Courses with "lightest prerequisites" typically require minimal specific prior coursework, often relying on general academic standing or instructor discretion to assess readiness.
+Based on the provided context, the CSCE graduate courses with the lightest prerequisites are those that primarily require "graduate classification" or "approval of instructor" rather than specific course numbers:
+*   **CSCE 648 (Computer Aided Sculpting)**: Requires "Approval of instructor" [Source 8].
+*   **CSCE 679 (Data Visualization)**: Requires "Graduate classification or approval of instructor" [Source 2].
+Other courses like CSCE 670, CSCE 608, CSCE 641, and CSCE 726 also offer "approval of instructor" as an alternative to specific course prerequisites, providing some flexibility:
+*   **CSCE 670 (Information Storage and Retrieval)**: Prerequisite/Corequisite(s): CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 3, 9].
+*   **CSCE 608 (Database Systems)**: Prerequisite/Corequisite(s): CSCE 310 or approval of Instructor [Source 6].
+*   **CSCE 641 (Computer Graphics)**: Prerequisite: CSCE 441 or approval of instructor [Source 7].
+*   **CSCE 726 (Large-Scale Optimization for Machine Learning)**: Prerequisites: CSCE 633 or CSCE 636 or approval of instructor; graduate classification [Source 4].
+**Academic Planning Dimension:**
+When planning your academic progression, courses with "approval of instructor" or "graduate classification" as their primary prerequisites can be advantageous. They offer flexibility for students who may:
+*   Have an undergraduate background different from typical CSCE prerequisites.
+*   Possess equivalent knowledge through work experience or self-study.
+*   Wish to explore interdisciplinary topics without fulfilling a long chain of specific course prerequisites.
+These courses can serve as accessible entry points into new areas of study, allowing you to broaden your academic scope or accelerate your progression if you can demonstrate readiness to the instructor.</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>The "lightness" of a prerequisite is determined by the specificity and number of prior courses required, with "approval of instructor" or "graduate classification" generally being the least restrictive.
+Based on the provided syllabi, the CSCE graduate courses with the lightest prerequisites are:
+*   **CSCE 648 (Computer Aided Sculpting)**: Requires "Approval of instructor" [Source 8].
+*   **CSCE 679 (Data Visualization)**: Requires "Graduate classification or approval of instructor" [Source 10].
+These courses primarily rely on the instructor's discretion or general graduate standing rather than specific prior course completion. Other courses, while sometimes offering "approval of instructor" as an alternative, also list specific course prerequisites.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7107,6 +12734,41 @@
           <t>POLICY</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2, Source 3].</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>I cannot find information regarding the use of ChatGPT or other AI tools for assignments in the provided context [Source 1, 2, 3].</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2].</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, Source 2].</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7124,7 +12786,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>recursive</t>
+          <t>semantic_general</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7140,6 +12802,78 @@
       <c r="K63" t="inlineStr">
         <is>
           <t>POLICY</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>I cannot find information regarding specific "AI policies" or their strictness in the provided course syllabi. Therefore, I cannot determine which CSCE graduate courses have the strictest AI policies [Source 1, 2, 3, 4, 5, 6, 7, 8, 9, 10].</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>The CSCE graduate courses with the strictest AI policies are those that broadly prohibit any use of AI tools.
+Based on the provided context, the following courses have the most restrictive AI statements:
+*   **CSCE 608**: "The use of AI is strictly prohibited in this course." [Source 1]
+*   **CSCE 669**: "The use of AI is strictly prohibited in this course." [Source 3]
+*   **CSCE 612**: "Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F*." [Source 5]
+*   **CSCE 629**: "The use of AI is strictly prohibited in this course." [Source 2]
+These courses implement a blanket ban on AI usage, with CSCE 612 explicitly stating the F* penalty for violations. Other courses have more nuanced policies, allowing AI for specific tasks like editing or debugging, or prohibiting it only for certain assignments [Source 4, Source 6, Source 7, Source 8, Source 10].</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>The strictest AI policies among the provided CSCE graduate courses generally involve a complete prohibition of AI tools for any course work, or very limited exceptions with significant transparency requirements.
+Based on the provided context, the following courses have the strictest AI policies:
+*   **CSCE 629**: "The use of AI is strictly prohibited in this course." [Source 1]
+*   **CSCE 608**: "The use of AI is strictly prohibited in this course." [Source 3]
+*   **CSCE 612**: "Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F*." [Source 5]
+*   **CSCE 669**: "The use of AI is strictly prohibited in this course." [Source 2]
+*   **CSCE 726**: "The use of AI tools such as large language models for completing homework assignments, exams, or the course project is strictly prohibited. However, it is acceptable to use them for tasks such as editing your writing or assisting in debugging your code." [Source 4] (While it has exceptions, the core prohibition for assignments/exams/projects is strict).
+*   **CSCE 665**: "No AI tools such as ChatGPT are allowed to use in the review writing." [Source 7] (Specifically prohibits for paper mini-review, which is 25% of the grade).
+Courses like CSCE 641 [Source 6], CSCE 748 [Source 8], and CSCE 713 [Source 9] allow AI tools under specific conditions (e.g., debugging, clarification, or with full interaction transcripts), making their policies less strict than those with outright prohibitions.</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>The principle underlying this question is academic integrity, specifically concerning the use of Artificial Intelligence (AI) tools in academic work. Different courses may have varying policies to uphold this principle, ranging from strict prohibitions to conditional allowances.
+Based on the provided context, the CSCE graduate courses with the strictest AI policies are those that **strictly prohibit any use of AI tools** without exceptions. These include:
+*   **CSCE 629**: "The use of AI is strictly prohibited in this course." [Source 1]
+*   **CSCE 608**: "The use of AI is strictly prohibited in this course." [Source 3]
+*   **CSCE 612**: "Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F*." [Source 5]
+*   **CSCE 669**: "The use of AI is strictly prohibited in this course." [Source 2]
+Other courses have policies that allow for limited use of AI (e.g., for editing, debugging, or clarification, often with disclosure requirements) or specific prohibitions for certain tasks, making their policies less strict than a blanket ban [Source 4, Source 6, Source 7, Source 8, Source 9].</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>The CSCE graduate courses with the strictest AI policies, prohibiting any use of AI tools, are:
+*   **CSCE 612**: "Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F*." [Source 7]
+*   **CSCE 629**: "The use of AI is strictly prohibited in this course." [Source 1]
+*   **CSCE 608**: "The use of AI is strictly prohibited in this course." [Source 3]
+*   **CSCE 669**: "The use of AI is strictly prohibited in this course." [Source 2]
+Other courses have policies that allow limited use of AI for specific tasks like debugging or editing, or require explicit permission and documentation [Source 4, Source 5, Source 6, Source 8, Source 9].</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>The principle underlying AI policies in academic settings is generally to ensure academic integrity and that submitted work reflects the student's own understanding and effort. Policies vary based on how instructors define "original work" in the context of AI tools.
+Based on the provided context, the CSCE graduate courses with the strictest AI policies are those that broadly prohibit the use of AI tools for academic work:
+*   **CSCE 612** states, "Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F\*." [Source 5]
+*   **CSCE 629** states, "The use of AI is strictly prohibited in this course." [Source 1]
+*   **CSCE 608** states, "The use of AI is strictly prohibited in this course." [Source 3]
+*   **CSCE 669** states, "The use of AI is strictly prohibited in this course." [Source 2]
+*   **CSCE 611** explicitly prohibits the use of AI-generated solutions for programming assignments and homework, stating, "Do not submit or make use of AI generated solutions." [Source 10]
+These courses implement a blanket prohibition on AI use, indicating that all submitted academic content, including assignments, projects, and exams, must be the student's original work without AI assistance. CSCE 612 further emphasizes this strictness by explicitly outlining the severe consequences of violations [Source 5].</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>The strictest AI policies among the provided CSCE graduate courses are those that strictly prohibit the use of AI tools.
+The following courses have policies stating that the use of AI is strictly prohibited:
+*   **CSCE 612**: "Any usage of AI, copilot, or LLMs is prohibited. Violations will be treated as cheating and will result in an F*." [Source 4]
+*   **CSCE 608**: "The use of AI is strictly prohibited in this course." [Source 5]
+*   **CSCE 669**: "The use of AI is strictly prohibited in this course." [Source 6]
+*   **CSCE 629**: "The use of AI is strictly prohibited in this course." [Source 2]</t>
         </is>
       </c>
     </row>
@@ -7182,6 +12916,203 @@
           <t>COMPARISON</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Here's a comparison of CSCE 629, CSCE 633, and CSCE 670 based on the provided syllabi:
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| **CSCE 629** | Exams 60%, Quizzes/Exercises 10%, Homework 30% [Source 1] | Midterm exam, final exam, quizzes/exercises, homework [Source 1] | Graduate classification [Source 6] |
+| **CSCE 633** | Homework 25%, Final Project 25%, Midterm Exams 50% [Source 4] | Five homework assignments, one final project, two midterm examinations [Source 4] | CSCE 420 or CSCE 625 [Source 5] |
+| **CSCE 670** | Homework 30%, Quizzes 20%, Final 30%, Group Project 20% [Source 2] | Five programming assignments, four quizzes, one final exam, one group project [Source 2] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 3] |
+## Detailed Comparison
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is heavily weighted towards exams, with exams accounting for **60%** of the total grade (one midterm exam and one comprehensive final exam, each worth 30%). Quizzes and exercises make up 10%, and homework contributes 30%. The lowest quiz/exercise grade will be dropped. [Source 1] The midterm exam is scheduled for February 26, and the final exam for April 30. [Source 10] The use of AI is strictly prohibited. [Source 10]
+**CSCE 633**: Exams constitute **50%** of the total grade, specifically two midterm examinations. Five homework assignments account for 25%, and one final project assignment makes up the remaining 25%. [Source 4] No late assignments will be accepted. [Source 7] Midterm 1 is on March 18, Midterm 2 on April 24, and the Final Project is due May 4. [Source 7] Programming in Python is permitted. [Source 7]
+**CSCE 670**: The grading breakdown includes Homework (30%), Quizzes (20%), a Final Exam (30%), and a Group Project (20%). [Source 2] This means exams (specifically the final exam) account for **30%** of the grade. There are five programming assignments in Python, four in-class quizzes, and a group project where students work in teams of 3 or 4 on a mini-research project. [Source 2] Students receive five late days total for homework, with each late day being an indivisible 24-hour unit. Once these are used, late assignments receive a grade of 0. [Source 8, 11] AI-generated code is permitted if properly documented with the prompt and significant parts of the response. [Source 9]
+**Conclusion on Exam-Heaviness**:
+**CSCE 629** is the most exam-heavy course, with exams contributing 60% to the final grade. CSCE 633 follows with 50% from exams, and CSCE 670 has the lowest exam weight at 30%.
+### Course Overview
+**CSCE 629**: This 3-credit hour course focuses on the analysis of algorithms, covering concrete algorithm design and analysis, abstract models for complexity, NP-Completeness, and approximation and probabilistic algorithms. [Source 6]
+**CSCE 633**: This 3-credit hour course on Machine Learning studies self-modifying computer systems that acquire new knowledge and improve performance. It surveys techniques like induction from examples, conceptual clustering, explanation-based learning, exemplar learning and analogy, discovery, and genetic algorithms. [Source 5]
+**CSCE 670**: This 3-credit hour course covers Information Storage and Retrieval, including representation, storage, and access to large multimedia document collections. It delves into fundamental data structures and algorithms for retrieval systems, and techniques for designing and evaluating systems, including indexing, compressing, and querying large collections. [Source 3]
+### Prerequisites
+**CSCE 629**: Graduate classification is required. [Source 6]
+**CSCE 633**: Prerequisites are CSCE 420 or CSCE 625. [Source 5]
+**CSCE 670**: Prerequisites include CSCE 310 or CSCE 603 or approval of the instructor, and graduate classification. [Source 3]
+### Learning Outcomes
+**CSCE 629**: Upon completion, learners will be able to explain fundamental algorithms, select appropriate algorithms, analyze correctness, runtime, and space complexity, design and modify algorithms, and recognize/prove intractable problems (undecidability or NP-hardness). [Source 1, 6]
+**CSCE 633**: Students are expected to be able to formalize the fundamental techniques and methods of machine learning. [Source 5]
+**CSCE 670**: Not found.
+### Topics
+**CSCE 629**: Topics include Lower Bounds, Divide and Conquer, Greedy Algorithms, Dynamic Programming, Amortized Analysis, Graph Algorithms, Randomized Algorithms, NP Completeness, Approximation Algorithms, and Undecidability. [Source 10]
+**CSCE 633**: The course covers Introduction and Measurements, Linear Models, Logistic Regression &amp; Regularization, Decision Tree-Based Models, Support Vector Machines, Neural Networks and Deep Learning, Dimension Reduction and Unsupervised Learning, and Special Topics. [Source 7]
+**CSCE 670**: Topics include Course Overview, Boolean Retrieval, TF-IDF, Vector Space Model, BM25, Link Analysis, Evaluation of Search Engines, Learning to Rank, Recommender Systems (Content-Based; Collaborative Filtering; Matrix Factorization; Bayesian Personalized Ranking), word2vec, Neural Ranking, Transformer, BERT-Based Ranking, Neural Collaborative Filtering, Sequential Recommendation, Large Language Models Basics, Large Language Models with Search Engines, Large Language Models for Ranking and Recommendation, and Project Presentations. [Source 11]
+### Materials
+**CSCE 629**: The required textbook is "Introduction to Algorithms, fourth edition" by Cormen, Leiserson, Rivest, and Stein (MIT Press, 2022, ISBN: 9780262367509), which is freely available as an ebook from the library. [Source 1]
+**CSCE 633**: Recommended materials include "The Elements of Statistical Learning" by Hastie, Tibshirani, Friedman (Springer Science &amp; Business Media, 2009), "Deep Learning" by Bishop, Bishop (Springer Nature, 2023), and "Machine Learning Refined" by Watt, Borhani, Katsaggelos (Cambridge University Press, 2016). "Introduction to Machine Learning, fourth edition" by Alpaydin (MIT Press, 2020) is optional. [Source 4]
+**CSCE 670**: Optional resources include "Mining of Massive Datasets" by Leskovec, Rajaraman, and Ullman (2014, available online) and "Introduction to Information Retrieval" by Manning, Raghavan, and Schutze (2009, available online). [Source 2]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 629 | Exams 60%, Quizzes/Exercises 10%, Homework 30% [Source 1] | Homeworks are essay style using LaTeX; no late submissions accepted [Source 4] | Graduate classification [Source 9] |
+| CSCE 633 | Midterm Exams 50%, Homework 25%, Final Project 25% [Source 2] | Five homework assignments, one final project, two midterm examinations; no late assignments accepted [Source 2, 6] | CSCE 420 or CSCE 625 [Source 8] |
+| CSCE 670 | Homework 30%, Quizzes 20%, Final 30%, Group Project 20% [Source 3] | Five programming assignments (Python), four in-class quizzes, one final exam, one group project (teams of 3 or 4) [Source 3] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5] |
+## Detailed Comparison
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is composed of 60% exams (one midterm exam and one comprehensive final exam, each worth 30%), 10% quizzes and exercises (lowest grade dropped), and 30% homework (essay style assignments requiring LaTeX, lowest grade dropped) [Source 1, 4]. No late submissions are accepted [Source 4].
+**CSCE 633**: The grading policy includes two midterm examinations accounting for 50% of the grade, five homework assignments for 25%, and one final project assignment for 25% [Source 2]. No late assignments will be accepted [Source 6].
+**CSCE 670**: The grading policy consists of 30% homework (five programming assignments in Python), 20% quizzes (four brief in-class quizzes), 30% for a comprehensive final exam, and 20% for a group project (teams of 3 or 4) [Source 3]. Homeworks are individual assignments [Source 3].
+**Conclusion on Exam-Heaviness**:
+*   **CSCE 629** has 60% of the grade from exams (30% midterm, 30% final) [Source 1].
+*   **CSCE 633** has 50% of the grade from exams (two midterm examinations) [Source 2].
+*   **CSCE 670** has 30% of the grade from exams (final exam) [Source 3].
+Therefore, **CSCE 629** is the most exam-heavy course among the three.
+### Course Overview
+**CSCE 629**: This course focuses on the analysis of algorithms, including concrete algorithm design and analysis, abstract models for complexity, NP-Completeness, and approximation and probabilistic algorithms [Source 9].
+**CSCE 633**: This course covers Machine Learning, which is the study of self-modifying computer systems that acquire new knowledge and improve performance. It surveys techniques like induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 8].
+**CSCE 670**: This course is on Information Storage and Retrieval, covering representation, storage, and access to very large multimedia document collections. It includes fundamental data structures and algorithms, and techniques to design and evaluate retrieval systems, including indexing, compressing, and querying large collections [Source 5].
+### Prerequisites
+**CSCE 629**: Requires graduate classification [Source 9].
+**CSCE 633**: Requires CSCE 420 or CSCE 625 [Source 8].
+**CSCE 670**: Requires CSCE 310 or CSCE 603 or approval of instructor, and graduate classification [Source 5].
+### Learning Outcomes
+**CSCE 629**: Upon completion, students will be able to explain fundamental algorithms and techniques, select appropriate algorithms, analyze correctness, runtime, and space complexity, design new algorithms, modify existing ones, and recognize/prove when a problem is intractable (undecidability or NP-hardness) [Source 1, 9].
+**CSCE 633**: Upon completion, students are expected to be able to formalize the fundamental techniques and methods of machine learning [Source 8].
+**CSCE 670**: Not found.
+### Topics
+**CSCE 629**: Tentative topics include Introduction, Review of Asymptotic Analysis, Lower Bounds, Divide and Conquer, Greedy Algorithms, Dynamic Programming, Amortized Analysis, Graph Algorithms, Randomized Algorithms, NP Completeness, Approximation Algorithms, and Undecidability [Source 4, 7].
+**CSCE 633**: Modules include Introduction and Measurements, Linear Models, Logistic Regression &amp; Regularization, Decision Tree-Based Models, Support Vector Machines, Neural Networks and Deep Learning, Dimension Reduction and Unsupervised Learning, and Special Topics [Source 6].
+**CSCE 670**: Not found.
+### Materials
+**CSCE 629**: The required textbook is "Introduction to Algorithms, fourth edition" by Cormen, Leiserson, Rivest, and Stein (ISBN: 9780262367509), freely available as an ebook from the library [Source 1].
+**CSCE 633**: Recommended materials include "The Elements of Statistical Learning" by Hastie, Tibshirani, and Friedman, "Deep Learning" by Bishop, and "Machine Learning Refined" by Watt, Borhani, and Katsaggelos. An optional material is "Introduction to Machine Learning, fourth edition" by Alpaydin [Source 2].
+**CSCE 670**: Optional materials include "Mining of Massive Datasets" by Leskovec, Rajaraman, and Ullman (available online) and "Introduction to Information Retrieval" by Manning, Raghavan, and Schutze (available online) [Source 3].</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 629 | Exams 60%, Quizzes/Exercises 10%, Homework 30% [Source 1] | Essay-style homeworks (LaTeX), no late submissions [Source 4] | Graduate classification [Source 10] |
+| CSCE 633 | Homework 25%, Final Project 25%, Midterm Exams 50% [Source 2] | 5 homeworks, 1 final project, 2 midterms, no late assignments [Source 2, 8] | CSCE 420 or CSCE 625 [Source 7] |
+| CSCE 670 | Homework 30%, Quizzes 20%, Final 30%, Group Project 20% [Source 3] | 5 programming assignments (Python), 1 group project, 5 late days [Source 3, 6] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5] |
+## Detailed Comparison
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is composed of 60% exams (one midterm and one comprehensive final, each worth 30%), 10% quizzes and exercises (lowest grade dropped), and 30% homework [Source 1]. Homework assignments are essay-style and require the use of LaTeX. No late submissions are accepted [Source 4]. With 60% of the grade from exams, **CSCE 629 is the most exam-heavy** among the three courses [Source 1].
+**CSCE 633**: The grade is determined by five homework assignments (25%), one final project (25%), and two midterm examinations (50%) [Source 2]. No late assignments will be accepted [Source 8]. Programming assignments can be implemented in Python [Source 8].
+**CSCE 670**: The grading breakdown includes 30% for five programming assignments (in Python), 20% for four brief in-class quizzes, 30% for a comprehensive final exam, and 20% for a group project [Source 3]. Students are allotted five late days total for homework submissions [Source 6].
+### Course Overview
+**CSCE 629**: This course, Analysis of Algorithms, covers concrete algorithm design and analysis, abstract models for analyzing problem complexity, NP-Completeness, and approximation and probabilistic algorithms [Source 10].
+**CSCE 633**: Machine Learning focuses on self-modifying computer systems that acquire new knowledge and improve performance, surveying techniques such as induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 7].
+**CSCE 670**: Information Storage and Retrieval deals with the representation, storage, and access of very large multimedia document collections. It covers fundamental data structures and algorithms for information storage and retrieval systems, and techniques to design and evaluate complete retrieval systems, including algorithms for indexing, compressing, and querying large collections [Source 5].
+### Prerequisites
+**CSCE 629**: Requires graduate classification [Source 10].
+**CSCE 633**: Requires CSCE 420 or CSCE 625 [Source 7].
+**CSCE 670**: Requires CSCE 310 or CSCE 603 or approval of the instructor, and graduate classification [Source 5].
+### Learning Outcomes
+**CSCE 629**: Students are expected to explain fundamental algorithms, select appropriate algorithms, analyze correctness, runtime, and space complexity, design new algorithms, and recognize when a problem is intractable (proving it by showing undecidability or NP-hardness) [Source 1, 10].
+**CSCE 633**: Students should be able to formalize the fundamental techniques and methods of machine learning [Source 7].
+**CSCE 670**: Not found.
+### Topics
+**CSCE 629**: Tentative topics include Introduction, Asymptotic Analysis, Lower Bounds, Divide and Conquer, Greedy Algorithms, Dynamic Programming, Amortized Analysis, Graph Algorithms, Randomized Algorithms, NP Completeness, Approximation Algorithms, and Undecidability [Source 9].
+**CSCE 633**: Course modules cover Introduction and Measurements, Linear Models, Logistic Regression &amp; Regularization, Decision Tree-Based Models, Support Vector Machines, Neural Networks and Deep Learning, Dimension Reduction and Unsupervised Learning, and Special Topics [Source 8].
+**CSCE 670**: The catalog description indicates topics such as representation, storage, and access to very large multimedia document collections; fundamental data structures and algorithms of information storage and retrieval systems; and techniques for designing and evaluating retrieval systems, including indexing, compressing, and querying [Source 5].
+### Materials
+**CSCE 629**: The required textbook is "Introduction to Algorithms, fourth edition" by Cormen, Leiserson, Rivest, and Stein (MIT Press, 2022), which is freely available as an ebook from the library [Source 1].
+**CSCE 633**: Recommended materials include "The Elements of Statistical Learning" by Hastie, Tibshirani, and Friedman (Springer, 2009), "Deep Learning" by Bishop (Springer Nature, 2023), and "Machine Learning Refined" by Watt, Borhani, and Katsaggelos (Cambridge University Press, 2016). "Introduction to Machine Learning, fourth edition" by Alpaydin (MIT Press, 2020) is optional [Source 2].
+**CSCE 670**: Optional materials include "Mining of Massive Datasets" by Leskovec, Rajaraman, and Ullman (2014), and "Introduction to Information Retrieval" by Manning, Raghavan, and Schutze (2009), both available online [Source 3].</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 629 | Exams 60%, Homework 30%, Quizzes/Exercises 10% | Essay-style homeworks requiring LaTeX; lowest quiz/exercise and homework grade dropped; no late submissions accepted. | Graduate classification [Source 10] |
+| CSCE 633 | Midterm Examinations 50%, Homework 25%, Final Project 25% | Five homework assignments, one final project; no late assignments accepted. | CSCE 420 or CSCE 625 [Source 7] |
+| CSCE 670 | Homework 30%, Final 30%, Quizzes 20%, Group Project 20% | Five programming assignments (Python); four in-class quizzes; one group project; five late days for homeworks. | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5] |
+## Detailed Comparison
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is composed of 60% exams (one midterm and one comprehensive final, each 30%), 10% quizzes and exercises (lowest grade dropped), and 30% homework (essay-style assignments requiring LaTeX, lowest grade dropped) [Source 1, 4]. No late submissions are accepted [Source 4].
+**CSCE 633**: Grades are based on two midterm examinations (50%), five homework assignments (25%), and one final project assignment (25%) [Source 2]. No late assignments will be accepted [Source 8].
+**CSCE 670**: The grading breakdown includes 30% for five programming assignments (in Python), 20% for four brief in-class quizzes, 30% for a comprehensive final exam, and 20% for a group project [Source 3]. Students receive five late days total for homeworks [Source 6].
+Comparing the exam weights:
+*   **CSCE 629**: Exams constitute 60% of the final grade (30% midterm + 30% final) [Source 1].
+*   **CSCE 633**: Exams constitute 50% of the final grade (two midterm examinations) [Source 2].
+*   **CSCE 670**: Exams constitute 30% of the final grade (final exam) [Source 3].
+Based on these percentages, **CSCE 629 is the most exam-heavy** course.
+### Prerequisites
+**CSCE 629**: Requires graduate classification [Source 10].
+**CSCE 633**: Requires CSCE 420 or CSCE 625 [Source 7].
+**CSCE 670**: Requires CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 5].</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 629 | Exams 60%, Homework 30%, Quizzes and exercises 10% | Homework: essay style, LaTeX required. Lowest homework and quiz grade dropped. | Graduate classification [Source 7] |
+| CSCE 633 | Two Midterm Examinations 50%, Five homework assignments 25%, One Final Project Assignment 25% | Not found | CSCE 420 or CSCE 625 [Source 5] |
+| CSCE 670 | Homework 30%, Final 30%, Quizzes 20%, Group Project 20% | Homework: five programming assignments in Python. Group Project: teams of 3 or 4 for a mini-research project. | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 6] |
+## Detailed Comparison
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is composed of exams (60%), homework (30%), and quizzes and exercises (10%). There will be one midterm exam and one comprehensive final exam, each worth 30% of the final grade. The homework assignments are essay style and require the use of LaTeX. The lowest grade in quizzes/exercises and homework will be dropped. No late submissions are accepted [Source 1, Source 8].
+**CSCE 633**: The grading policy consists of two midterm examinations (50%), five homework assignments (25%), and one final project assignment (25%) [Source 3].
+**CSCE 670**: The grading policy includes homework (30%), a comprehensive final exam (30%), quizzes (20%), and a group project (20%). Homework consists of five programming assignments in Python. Students will work in teams of 3 or 4 for a mini-research project. Each student receives five late days for homework [Source 2, Source 4].
+**Most Exam-Heavy:** CSCE 629 is the most exam-heavy, with exams accounting for 60% of the final grade [Source 1]. CSCE 633 has exams accounting for 50% [Source 3], and CSCE 670 has exams accounting for 30% [Source 2].</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 629 | Exams 60%, Homework 30%, Quizzes &amp; Exercises 10% | Not found | Graduate classification [Source 9] |
+| CSCE 633 | Midterm Examinations 50%, Homework 25%, Final Project 25% | Five homework assignments, One Final Project Assignment, Two Midterm Examinations [Source 3] | CSCE 420 or CSCE 625 [Source 8] |
+| CSCE 670 | Homework 30%, Quizzes 20%, Final 30%, Group Project 20% | Five programming assignments, Four brief in-class quizzes, One comprehensive final exam, One mini-research project [Source 2] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 6] |
+## Detailed Comparison
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is based on exams (60%), homework (30%), and quizzes and exercises (10%). There will be one midterm exam and one comprehensive final exam, each worth 30% of the grade. The lowest grade in the quizzes and exercises component will be dropped, as will the lowest homework grade. Homework assignments are essay style and require the use of LaTeX [Source 1, 4]. The use of AI is strictly prohibited [Source 5].
+**CSCE 633**: The grading policy consists of two midterm examinations (50%), five homework assignments (25%), and one final project assignment (25%) [Source 3]. The cutoff for an 'A' is at most 90%, 'B' at 80%, 'C' at 70%, and 'D' at 60% [Source 3]. Programming languages permitted are Python, executable on CS unix hosts [Source 10].
+**CSCE 670**: The grading policy includes homework (30%), quizzes (20%), a final exam (30%), and a group project (20%). Homework consists of five programming assignments, all in Python. Quizzes are four brief in-class quizzes. The group project involves working in teams of 3 or 4 on a mini-research project [Source 2]. Homeworks are individual assignments, but discussion about approaches is encouraged, though sharing code or pair programming is inappropriate [Source 7].
+**Conclusion on Exam-Heaviness**:
+**CSCE 629** is the most exam-heavy, with exams accounting for 60% of the final grade [Source 1].
+**CSCE 633** has exams accounting for 50% of the final grade [Source 3].
+**CSCE 670** has exams accounting for 30% of the final grade [Source 2].</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>**Summary Table**
+| Course | Grading | Workload | Prerequisites |
+|---|---|---|---|
+| CSCE 629 | Exams 60%, Quizzes/Exercises 10%, Homework 30% [Source 1] | Midterm exam, final exam, online/in-class quizzes/exercises, essay-style homework (LaTeX required) [Source 1, 5] | Graduate classification [Source 8] |
+| CSCE 633 | Homework 25%, Final Project 25%, Midterm Exams 50% [Source 3] | Five homework assignments, one final project, two midterm examinations [Source 3] | CSCE 420 or CSCE 625 [Source 7] |
+| CSCE 670 | Homework 30%, Quizzes 20%, Final 30%, Group Project 20% [Source 2] | Five programming assignments, four in-class quizzes, comprehensive final exam, group research project [Source 2] | CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 4, 12] |
+CSCE 629 is the most exam-heavy course, with exams accounting for 60% of the final grade [Source 1].
+## Detailed Comparison
+### Course Overview
+**CSCE 629**: This course focuses on the Analysis of Algorithms, covering concrete algorithm design and analysis, abstract models for complexity, NP-Completeness, approximation, and probabilistic algorithms [Source 8].
+**CSCE 633**: This course is on Machine Learning, studying self-modifying computer systems that acquire new knowledge and improve their performance. It surveys various machine learning techniques, including induction from examples, conceptual clustering, explanation-based learning, exemplar learning, analogy, discovery, and genetic algorithms [Source 7].
+**CSCE 670**: This course covers Information Storage and Retrieval, including the representation, storage, and access to very large multimedia document collections. It delves into fundamental data structures and algorithms, and techniques for designing and evaluating complete retrieval systems, such as indexing, compressing, and querying large collections [Source 4].
+### Grading &amp; Workload
+**CSCE 629**: The grading policy is composed of exams (60%), quizzes and exercises (10%), and homework (30%) [Source 1]. There will be one midterm exam and one comprehensive final exam, each worth 30% [Source 1]. Quizzes and exercises are online or in-class, with the lowest grade dropped. Homework assignments are essay-style and require the use of LaTeX [Source 1, 5]. The lowest homework grade will also be dropped [Source 5]. Final grades are assigned on a standard scale (A: &gt;=90, B: [80,90), etc.), with a potential curve if the course average is low [Source 5]. No late submissions are accepted [Source 5]. The use of AI is strictly prohibited [Source 6].
+**CSCE 633**: The grade is based on five homework assignments (25%), one final project assignment (25%), and two midterm examinations (50%) [Source 3]. The cutoff for an 'A' is at most 90%, 'B' at 80%, 'C' at 70%, and 'D' at 60% [Source 3]. No late assignments will be accepted [Source 10]. Programming assignments are permitted in Python and must be executable on CS unix hosts [Source 10].
+**CSCE 670**: The grading breakdown is Homework (30%), Quizzes (20%), Final (30%), and Group Project (20%) [Source 2]. There will be five programming assignments in Python, with the first being an introductory one [Source 2]. Four brief in-class quizzes will be given [Source 2]. A comprehensive final exam accounts for 30% [Source 2]. Students will work in teams of 3 or 4 on a mini-research project [Source 2]. The course uses a standard grading scale (A: &gt;=90%, B: &gt;=80% and &lt;90%, etc.) [Source 2]. Students receive five late days total for homework, with a late day being an indivisible 24-hour unit. After using the five late days, late assignments receive a grade of 0 [Source 9, 13]. Homeworks are individual assignments, but discussion of approaches is encouraged, with acknowledgment of all help required [Source 9]. AI-generated code is permitted if properly documented (prompt and significant parts of response) and tested, with the student responsible for correctness [Source 11].
+### Prerequisites
+**CSCE 629**: Graduate classification [Source 8].
+**CSCE 633**: CSCE 420 or CSCE 625 [Source 7].
+**CSCE 670**: CSCE 310 or CSCE 603 or approval of instructor; graduate classification [Source 4, 12].
+### Learning Outcomes
+**CSCE 629**: Upon completion, learners will be able to explain fundamental algorithms, select appropriate algorithms, analyze correctness/runtime/space complexity, design new algorithms, and recognize/prove intractability (undecidability or NP-hardness) [Source 1, 8].
+**CSCE 633**: Upon completion, students are expected to be able to formalize the fundamental techniques and methods of machine learning [Source 7].
+**CSCE 670**: Upon completion, learners will be able to define and explain key concepts and models relevant to web search (e.g., text indexing, retrieval models, PageRank) and recommender systems (e.g., collaborative filtering, matrix factorization). They will also be able to design, implement, and evaluate core algorithms for these systems, and identify/apply recent research results in these areas [Source 12].
+### Materials
+**CSCE 629**: The required textbook is "Introduction to Algorithms, fourth edition" by Cormen, Leiserson, Rivest, and Stein (MIT Press, 2022), which is freely available as an ebook from the library [Source 1].
+**CSCE 633**: Recommended textbooks include "The Elements of Statistical Learning" by Hastie, Tibshirani, and Friedman (Springer, 2009), "Deep</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7197,6 +13128,41 @@
           <t>out_of_scope</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, 2, 3, 4, 5, 6, 7, 8, 9, 10]. The provided documents are course syllabi and do not contain details about the CSCE department's office hours.</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The syllabi only list individual instructor office hours and locations, not the general opening hours for the CSCE department office.</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context. The syllabi only list individual instructor office hours, not the general CSCE department office opening times.</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>I cannot find that information in the provided context [Source 1, 2, 3, 4, 5, 6, 7, 8, 9, 10].</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Howdy! I'm TamuBot, your Texas A&amp;M academic assistant. I can help you with questions about courses, syllabi, grading policies, schedules, and university policies. What would you like to know?</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7232,6 +13198,77 @@
           <t>LOGISTICAL</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Yes, several CSCE graduate courses have in-person attendance requirements.
+For example:
+*   **CSCE 611** explicitly states, "In-person sections will meet during scheduled class times in the assigned room" [Source 2].
+*   **CSCE 632** includes "Group Class Activities (10%)" where students "will work with people at your table or move to a table so that there are at least 3 people per group" and receive credit for attending class and providing what is required for the activity [Source 7].
+*   **CSCE 652** requires students to "bring a laptop to class" [Source 8].
+*   Other courses like **CSCE 648**, **CSCE 612**, **CSCE 670**, **CSCE 752**, **CSCE 672**, **CSCE 681**, and **CSCE 665** list specific meeting days, times, and physical locations (e.g., ARCC 414, HRBB 113, EABB 106, ZACH 598) for their lectures, labs, or seminars, indicating an in-person format [Source 1, 3, 4, 5, 6, 9, 10].</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Yes, several CSCE graduate courses have in-person attendance requirements or strong recommendations:
+*   **CSCE 611**: In-person sections will meet during scheduled class times in the assigned room [Source 1].
+*   **CSCE 681**:
+    *   For Section 600, students are required to reserve the entire scheduled time slot and arrive at least 10 minutes before the start of the talk, as attendance will be taken. An Aggie ID card is required for attendance [Source 3].
+    *   Students are expected to attend all scheduled lectures and bring their TAMU ID to the seminar for verification of attendance [Source 5].
+*   **CSCE 629**: Class attendance is strongly recommended. The student is responsible for any material missed [Source 4].
+*   **CSCE 608**: Class attendance is strongly recommended. The student is responsible for any material missed [Source 6].
+*   **CSCE 752**: Students are expected to attend and participate in each lecture [Source 7].
+*   **CSCE 669**: Class attendance is strongly recommended. The student is responsible for any material missed [Source 8].
+*   **CSCE 624**: This course relies heavily on in-class discussion and activities. Students are expected to attend class regularly and participate actively. If attendance or participation is graded, expectations and evaluation criteria will be clearly communicated [Source 10].</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Yes, some CSCE graduate courses have in-person attendance requirements or expectations based on the provided syllabi:
+*   **CSCE 611** explicitly states, "Classroom: In-person sections will meet during scheduled class times in the assigned room" [Source 2].
+*   **CSCE 632** requires attendance for "Group Class Activities" to receive credit, stating, "You will get credit if you attend class and you provide what is required for the activity" [Source 7].
+*   **CSCE 652** notes that "Students will need to bring a laptop to class," indicating an expectation of in-person presence for class activities [Source 8].</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Yes, some CSCE graduate courses have in-person attendance requirements or expectations based on the provided syllabi:
+*   **CSCE 611** states that "In-person sections will meet during scheduled class times in the assigned room" [Source 2].
+*   **CSCE 632** includes "Group Class Activities" where students "will get credit if you attend class and you provide what is required for the activity" [Source 7].
+*   **CSCE 652** requires students to "bring a laptop to class" [Source 8].</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Yes, some CSCE graduate courses have in-person attendance requirements:
+*   **CSCE 611**: In-person sections of this course will meet during scheduled class times in the assigned room [Source 1].
+*   **CSCE 681 (Section 600)**: Students are required to attend all scheduled lectures and bring their Aggie ID card for attendance verification. Attendance is taken, and students are expected to reserve the entire time slot and arrive early. Not receiving credit for attending a seminar can occur if students are noticed exhibiting behaviors like doing other work or sleeping [Source 3, Source 5].
+*   **CSCE 632**: Students receive credit for Group Class Activities if they attend class and provide what is required for the activity [Source 2].
+Other courses, such as CSCE 629, CSCE 608, CSCE 752, CSCE 669, and CSCE 624, strongly recommend or expect attendance, but do not explicitly state it as a strict requirement for all components in the provided context [Source 4, Source 6, Source 7, Source 8, Source 10].</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Several CSCE graduate courses have specific in-person attendance requirements or strong expectations for attendance. The principle underlying these requirements is the "Course Specific Attendance Policy" outlined in each syllabus, which dictates the expectations for student presence and participation in the learning environment.
+Based on the provided context, the following courses have in-person attendance requirements:
+*   **CSCE 632:** "You are required to attend every class, arrive on time, and stay the whole time." [Source 2]
+*   **CSCE 681:** Students are "expected to attend all the lectures scheduled during the semester" and attendance is taken, requiring students to "have your Aggie ID card with you." [Source 4, 6]
+*   **CSCE 752:** Students are "expected to attend and participate in each lecture." [Source 7]
+*   **CSCE 624:** Students are "expected to attend class regularly and participate actively." [Source 10]
+Other courses, such as CSCE 629, CSCE 608, and CSCE 669, state that "Class attendance is strongly recommended" but do not explicitly mandate it as a requirement [Source 5, 8, 9]. CSCE 611 notes that "In-person sections will meet during scheduled class times" and discusses make-up exams for extraordinary circumstances, implying exam attendance is required, but does not explicitly state a general class attendance requirement [Source 3].</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Yes, several CSCE graduate courses have in-person attendance requirements or strong expectations:
+*   **CSCE 611**: In-person sections are required to meet during scheduled class times in the assigned room [Source 1].
+*   **CSCE 681 (Section 600)**: Students are required to attend all scheduled lectures, arrive at least 10 minutes before the start of the talk, and have their Aggie ID card for attendance verification. Not receiving credit for attending a seminar can occur if students are noticed exhibiting inappropriate behavior [Source 3, Source 5].
+*   **CSCE 632**: Students receive credit for Group Class Activities if they attend class and provide what is required for the activity [Source 2].
+*   **CSCE 752**: Students are expected to attend and participate in each lecture [Source 7].
+*   **CSCE 624**: Students are expected to attend class regularly and participate actively. If attendance or participation is graded, expectations will be communicated [Source 10].
+Other courses, such as CSCE 629, CSCE 608, and CSCE 669, state that class attendance is "strongly recommended" [Source 4, Source 6, Source 8].</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7275,6 +13312,41 @@
       <c r="K67" t="inlineStr">
         <is>
           <t>LOGISTICAL</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600 (54978) is scheduled for Thursday, February 26th, in class [Source 1].</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600 (54978) is scheduled for Thursday, February 26th, in class [Source 1].</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26th, in class [Source 2, Source 4].</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600, is scheduled for Thursday, February 26th, in class [Source 2, Source 4].</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600 (54978), is scheduled for Thursday, February 26, in class [1, 3, 4].</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, section 600, is scheduled for Thursday, February 26th, in class [1, 4].</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>The midterm exam for CSCE 629, Section 600 (54978), is scheduled for Thursday, February 26, in class [1, 3, 4].</t>
         </is>
       </c>
     </row>
